--- a/workbooks/scenarios/HVACRagScenarios.xlsx
+++ b/workbooks/scenarios/HVACRagScenarios.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -520,242 +520,236 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The house will be empty for 8 hours today. What AC temperature should I set?</t>
+          <t>I'm heading out for a quick errand — what AC temperature should I set for the townhouse?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chester Springs, PA</t>
+          <t>King of Prussia, PA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1800</v>
+        <v>2200</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>$200</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>285</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Condo</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="J2" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>75</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>5.05</v>
+        <v>3.99</v>
       </c>
       <c r="M2" t="n">
-        <v>5.21</v>
+        <v>3.95</v>
       </c>
       <c r="N2" t="n">
-        <v>8.6</v>
+        <v>9.18</v>
       </c>
       <c r="O2" t="n">
         <v>9.630000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>6.503</v>
+        <v>5.860000000000001</v>
       </c>
       <c r="Q2" t="n">
         <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>9.550000000000001</v>
+        <v>11.46</v>
       </c>
       <c r="S2" t="n">
-        <v>1.81</v>
+        <v>2.18</v>
       </c>
       <c r="T2" t="n">
-        <v>9.94</v>
+        <v>11.93</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The house will be empty for 8 hours today. What AC temperature should I set?</t>
+          <t>I'm heading out for a quick errand — what AC temperature should I set for the townhouse?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chester Springs, PA</t>
+          <t>King of Prussia, PA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1800</v>
+        <v>2200</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>$200</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>285</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Condo</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="J3" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>78</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>5.63</v>
+        <v>4.4</v>
       </c>
       <c r="M3" t="n">
-        <v>5.58</v>
+        <v>4.36</v>
       </c>
       <c r="N3" t="n">
-        <v>7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>10</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>6.542</v>
+        <v>5.9505</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>9</v>
+        <v>10.85</v>
       </c>
       <c r="S3" t="n">
-        <v>1.71</v>
+        <v>2.06</v>
       </c>
       <c r="T3" t="n">
-        <v>9.369999999999999</v>
+        <v>11.29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The house will be empty for 8 hours today. What AC temperature should I set?</t>
+          <t>I'm heading out for a quick errand — what AC temperature should I set for the townhouse?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chester Springs, PA</t>
+          <t>King of Prussia, PA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1800</v>
+        <v>2200</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>$200</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>285</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Condo</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="J4" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>81</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>6.18</v>
+        <v>4.81</v>
       </c>
       <c r="M4" t="n">
-        <v>6.12</v>
+        <v>4.76</v>
       </c>
       <c r="N4" t="n">
-        <v>4.06</v>
+        <v>5.13</v>
       </c>
       <c r="O4" t="n">
-        <v>8.859999999999999</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>6.137</v>
+        <v>5.579499999999999</v>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>8.18</v>
+        <v>10.23</v>
       </c>
       <c r="S4" t="n">
-        <v>1.55</v>
+        <v>1.94</v>
       </c>
       <c r="T4" t="n">
-        <v>8.52</v>
+        <v>10.65</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The house will be empty for 8 hours today. What heat setting should I use?</t>
+          <t>With 2 people home, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chester Springs, PA</t>
+          <t>Carlisle, PA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1800</v>
+        <v>1650</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -763,23 +757,21 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>$200</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>255</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Condo</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -787,10 +779,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>6.22</v>
+        <v>4.39</v>
       </c>
       <c r="M5" t="n">
-        <v>6.16</v>
+        <v>4.5</v>
       </c>
       <c r="N5" t="n">
         <v>6.11</v>
@@ -799,37 +791,37 @@
         <v>7.6</v>
       </c>
       <c r="P5" t="n">
-        <v>6.384</v>
+        <v>5.254</v>
       </c>
       <c r="Q5" t="n">
         <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>8.119999999999999</v>
+        <v>10.86</v>
       </c>
       <c r="S5" t="n">
-        <v>1.54</v>
+        <v>2.06</v>
       </c>
       <c r="T5" t="n">
-        <v>8.449999999999999</v>
+        <v>11.07</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The house will be empty for 8 hours today. What heat setting should I use?</t>
+          <t>With 2 people home, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chester Springs, PA</t>
+          <t>Carlisle, PA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1800</v>
+        <v>1650</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -837,23 +829,21 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>$200</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>255</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Condo</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -861,10 +851,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5.67</v>
+        <v>3.73</v>
       </c>
       <c r="M6" t="n">
-        <v>5.62</v>
+        <v>3.86</v>
       </c>
       <c r="N6" t="n">
         <v>8.6</v>
@@ -873,37 +863,37 @@
         <v>7.6</v>
       </c>
       <c r="P6" t="n">
-        <v>6.528</v>
+        <v>5.329999999999999</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>8.94</v>
+        <v>11.85</v>
       </c>
       <c r="S6" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="T6" t="n">
-        <v>9.31</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The house will be empty for 8 hours today. What heat setting should I use?</t>
+          <t>With 2 people home, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chester Springs, PA</t>
+          <t>Carlisle, PA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1800</v>
+        <v>1650</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -911,23 +901,21 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>$200</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>255</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Condo</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -935,10 +923,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.69</v>
+        <v>2.6</v>
       </c>
       <c r="M7" t="n">
-        <v>5.08</v>
+        <v>3.21</v>
       </c>
       <c r="N7" t="n">
         <v>9.32</v>
@@ -947,37 +935,37 @@
         <v>7.6</v>
       </c>
       <c r="P7" t="n">
-        <v>6.188999999999999</v>
+        <v>4.9075</v>
       </c>
       <c r="Q7" t="n">
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>9.76</v>
+        <v>12.84</v>
       </c>
       <c r="S7" t="n">
-        <v>1.85</v>
+        <v>2.44</v>
       </c>
       <c r="T7" t="n">
-        <v>10.16</v>
+        <v>13.09</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The house will be empty for 4 hours today. What AC temperature should I set?</t>
+          <t>With 3 people home, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA</t>
+          <t>Lebanon, PA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2000</v>
+        <v>2350</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -985,12 +973,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>$250</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="G8" t="n">
+        <v>335</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -998,60 +984,60 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="J8" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.19</v>
+        <v>3.09</v>
       </c>
       <c r="M8" t="n">
-        <v>4.15</v>
+        <v>3.24</v>
       </c>
       <c r="N8" t="n">
-        <v>9.32</v>
+        <v>7</v>
       </c>
       <c r="O8" t="n">
-        <v>9.630000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="P8" t="n">
-        <v>6.018000000000001</v>
+        <v>4.601</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>11.16</v>
+        <v>12.8</v>
       </c>
       <c r="S8" t="n">
-        <v>2.12</v>
+        <v>2.43</v>
       </c>
       <c r="T8" t="n">
-        <v>11.62</v>
+        <v>13.04</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The house will be empty for 4 hours today. What AC temperature should I set?</t>
+          <t>With 3 people home, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA</t>
+          <t>Lebanon, PA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2000</v>
+        <v>2350</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1059,73 +1045,71 @@
         </is>
       </c>
       <c r="F9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>335</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Single-family</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>21</v>
+      </c>
+      <c r="J9" t="n">
+        <v>25</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="N9" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="O9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4.588</v>
+      </c>
+      <c r="Q9" t="n">
         <v>2</v>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>$250</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Single-family</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>85</v>
-      </c>
-      <c r="J9" t="n">
-        <v>32</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="M9" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="N9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="O9" t="n">
-        <v>10</v>
-      </c>
-      <c r="P9" t="n">
-        <v>6.3225</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
       <c r="R9" t="n">
-        <v>10.25</v>
+        <v>13.92</v>
       </c>
       <c r="S9" t="n">
-        <v>1.95</v>
+        <v>2.64</v>
       </c>
       <c r="T9" t="n">
-        <v>10.67</v>
+        <v>14.19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The house will be empty for 4 hours today. What AC temperature should I set?</t>
+          <t>With 3 people home, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA</t>
+          <t>Lebanon, PA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2000</v>
+        <v>2350</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1133,12 +1117,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>$250</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="G10" t="n">
+        <v>335</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1146,73 +1128,71 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="J10" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.41</v>
+        <v>1.59</v>
       </c>
       <c r="M10" t="n">
-        <v>5.36</v>
+        <v>1.79</v>
       </c>
       <c r="N10" t="n">
-        <v>6.11</v>
+        <v>8.6</v>
       </c>
       <c r="O10" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="P10" t="n">
-        <v>6.221</v>
+        <v>3.9635</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>9.33</v>
+        <v>15.04</v>
       </c>
       <c r="S10" t="n">
-        <v>1.77</v>
+        <v>2.86</v>
       </c>
       <c r="T10" t="n">
-        <v>9.710000000000001</v>
+        <v>15.33</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
+        <v>28</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>With 5 people home, what AC temperature should I set?</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Gettysburg, PA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>5</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>The house will be empty for 4 hours today. What heat setting should I use?</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>2</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>$250</t>
-        </is>
+      <c r="G11" t="n">
+        <v>360</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1220,73 +1200,71 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="J11" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>74</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5.91</v>
+        <v>2.77</v>
       </c>
       <c r="M11" t="n">
-        <v>5.85</v>
+        <v>2.93</v>
       </c>
       <c r="N11" t="n">
-        <v>7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>7.6</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>6.3605</v>
+        <v>4.961</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>8.59</v>
+        <v>13.27</v>
       </c>
       <c r="S11" t="n">
-        <v>1.63</v>
+        <v>2.52</v>
       </c>
       <c r="T11" t="n">
-        <v>8.94</v>
+        <v>13.53</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
+        <v>28</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>With 5 people home, what AC temperature should I set?</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Gettysburg, PA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>5</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>The house will be empty for 4 hours today. What heat setting should I use?</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>$250</t>
-        </is>
+      <c r="G12" t="n">
+        <v>360</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1294,134 +1272,132 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="J12" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>77</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>5.3</v>
+        <v>3.24</v>
       </c>
       <c r="M12" t="n">
-        <v>5.25</v>
+        <v>3.38</v>
       </c>
       <c r="N12" t="n">
-        <v>9.32</v>
+        <v>9.18</v>
       </c>
       <c r="O12" t="n">
-        <v>7.6</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>6.4315</v>
+        <v>5.435499999999999</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>9.5</v>
+        <v>12.58</v>
       </c>
       <c r="S12" t="n">
-        <v>1.81</v>
+        <v>2.39</v>
       </c>
       <c r="T12" t="n">
-        <v>9.890000000000001</v>
+        <v>12.83</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
+        <v>28</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>With 5 people home, what AC temperature should I set?</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Gettysburg, PA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>5</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>The house will be empty for 4 hours today. What heat setting should I use?</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
+        <v>360</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Single-family</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>88</v>
+      </c>
+      <c r="J13" t="n">
+        <v>26</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="N13" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="O13" t="n">
+        <v>10</v>
+      </c>
+      <c r="P13" t="n">
+        <v>5.2085</v>
+      </c>
+      <c r="Q13" t="n">
         <v>2</v>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>$250</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Single-family</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>28</v>
-      </c>
-      <c r="J13" t="n">
-        <v>32</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="M13" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="N13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="O13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="P13" t="n">
-        <v>5.887999999999999</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3</v>
-      </c>
       <c r="R13" t="n">
-        <v>10.42</v>
+        <v>11.89</v>
       </c>
       <c r="S13" t="n">
-        <v>1.98</v>
+        <v>2.26</v>
       </c>
       <c r="T13" t="n">
-        <v>10.85</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Someone's home all day and it's hot outside. What should I set the AC to?</t>
+          <t>With 3 people home, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>West Chester, PA</t>
+          <t>Monroeville, PA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1429,73 +1405,71 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>$220</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="G14" t="n">
+        <v>270</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Condo</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J14" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>76</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.48</v>
+        <v>3.24</v>
       </c>
       <c r="M14" t="n">
-        <v>3.79</v>
+        <v>3.38</v>
       </c>
       <c r="N14" t="n">
-        <v>9.32</v>
+        <v>10</v>
       </c>
       <c r="O14" t="n">
         <v>9.630000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>5.379</v>
+        <v>5.599499999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>11.95</v>
+        <v>12.58</v>
       </c>
       <c r="S14" t="n">
-        <v>2.27</v>
+        <v>2.39</v>
       </c>
       <c r="T14" t="n">
-        <v>12.18</v>
+        <v>12.83</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Someone's home all day and it's hot outside. What should I set the AC to?</t>
+          <t>With 3 people home, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>West Chester, PA</t>
+          <t>Monroeville, PA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1503,73 +1477,71 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>$220</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="G15" t="n">
+        <v>270</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Condo</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J15" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>78</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.61</v>
+        <v>3.54</v>
       </c>
       <c r="M15" t="n">
-        <v>4.36</v>
+        <v>3.67</v>
       </c>
       <c r="N15" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="O15" t="n">
         <v>9.630000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>5.4535</v>
+        <v>5.510999999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>11.07</v>
+        <v>12.13</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1</v>
+        <v>2.31</v>
       </c>
       <c r="T15" t="n">
-        <v>11.28</v>
+        <v>12.37</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Someone's home all day and it's hot outside. What should I set the AC to?</t>
+          <t>With 3 people home, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>West Chester, PA</t>
+          <t>Monroeville, PA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1577,73 +1549,71 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>$220</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="G16" t="n">
+        <v>270</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Condo</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J16" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>80</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.84</v>
+        <v>3.84</v>
       </c>
       <c r="M16" t="n">
-        <v>4.94</v>
+        <v>3.96</v>
       </c>
       <c r="N16" t="n">
-        <v>4.06</v>
+        <v>7</v>
       </c>
       <c r="O16" t="n">
-        <v>8.859999999999999</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>5.322</v>
+        <v>5.3825</v>
       </c>
       <c r="Q16" t="n">
         <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>10.18</v>
+        <v>11.68</v>
       </c>
       <c r="S16" t="n">
-        <v>1.93</v>
+        <v>2.22</v>
       </c>
       <c r="T16" t="n">
-        <v>10.38</v>
+        <v>11.91</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Someone's home all day and it's cold. What heating temperature should I use?</t>
+          <t>With 3 people home, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>West Chester, PA</t>
+          <t>Indiana, PA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1600</v>
+        <v>1900</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1651,23 +1621,21 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>$220</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="G17" t="n">
+        <v>235</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J17" t="n">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1675,10 +1643,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>5.36</v>
+        <v>5.49</v>
       </c>
       <c r="M17" t="n">
-        <v>5.44</v>
+        <v>5.57</v>
       </c>
       <c r="N17" t="n">
         <v>6.11</v>
@@ -1687,37 +1655,37 @@
         <v>7.6</v>
       </c>
       <c r="P17" t="n">
-        <v>5.874</v>
+        <v>5.9585</v>
       </c>
       <c r="Q17" t="n">
         <v>2</v>
       </c>
       <c r="R17" t="n">
-        <v>9.41</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="T17" t="n">
-        <v>9.59</v>
+        <v>9.390000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Someone's home all day and it's cold. What heating temperature should I use?</t>
+          <t>With 3 people home, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>West Chester, PA</t>
+          <t>Indiana, PA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1600</v>
+        <v>1900</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1725,23 +1693,21 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>$220</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="G18" t="n">
+        <v>235</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J18" t="n">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1749,10 +1715,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4.77</v>
+        <v>4.89</v>
       </c>
       <c r="M18" t="n">
-        <v>4.87</v>
+        <v>4.98</v>
       </c>
       <c r="N18" t="n">
         <v>8.6</v>
@@ -1761,37 +1727,37 @@
         <v>7.6</v>
       </c>
       <c r="P18" t="n">
-        <v>5.995499999999999</v>
+        <v>6.069999999999999</v>
       </c>
       <c r="Q18" t="n">
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>10.29</v>
+        <v>10.11</v>
       </c>
       <c r="S18" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="T18" t="n">
-        <v>10.49</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Someone's home all day and it's cold. What heating temperature should I use?</t>
+          <t>With 3 people home, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>West Chester, PA</t>
+          <t>Indiana, PA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1600</v>
+        <v>1900</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1799,23 +1765,21 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>$220</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="G19" t="n">
+        <v>235</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J19" t="n">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1823,10 +1787,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.46</v>
+        <v>4.27</v>
       </c>
       <c r="M19" t="n">
-        <v>4.29</v>
+        <v>4.4</v>
       </c>
       <c r="N19" t="n">
         <v>9.32</v>
@@ -1835,50 +1799,48 @@
         <v>7.6</v>
       </c>
       <c r="P19" t="n">
-        <v>5.5435</v>
+        <v>5.824999999999999</v>
       </c>
       <c r="Q19" t="n">
         <v>3</v>
       </c>
       <c r="R19" t="n">
-        <v>11.17</v>
+        <v>11.01</v>
       </c>
       <c r="S19" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="T19" t="n">
-        <v>11.39</v>
+        <v>11.23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The house is unoccupied for 8 hours today. What's the best AC temperature?</t>
+          <t>With 3 people home, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>State College, PA</t>
+          <t>DuBois, PA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2100</v>
+        <v>1950</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>3</v>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>$300</t>
-        </is>
+      <c r="G20" t="n">
+        <v>305</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1886,73 +1848,71 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J20" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>76</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.87</v>
+        <v>4.56</v>
       </c>
       <c r="M20" t="n">
-        <v>2.84</v>
+        <v>4.66</v>
       </c>
       <c r="N20" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="O20" t="n">
         <v>9.630000000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>5.019500000000001</v>
+        <v>6.4435</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>13.13</v>
+        <v>10.61</v>
       </c>
       <c r="S20" t="n">
-        <v>2.5</v>
+        <v>2.02</v>
       </c>
       <c r="T20" t="n">
-        <v>13.67</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The house is unoccupied for 8 hours today. What's the best AC temperature?</t>
+          <t>With 3 people home, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>State College, PA</t>
+          <t>DuBois, PA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2100</v>
+        <v>1950</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>3</v>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>$300</t>
-        </is>
+      <c r="G21" t="n">
+        <v>305</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1960,10 +1920,10 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J21" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1971,62 +1931,60 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.42</v>
+        <v>4.71</v>
       </c>
       <c r="M21" t="n">
-        <v>3.39</v>
+        <v>4.81</v>
       </c>
       <c r="N21" t="n">
         <v>9.32</v>
       </c>
       <c r="O21" t="n">
-        <v>10</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>5.5765</v>
+        <v>6.404999999999999</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R21" t="n">
-        <v>12.3</v>
+        <v>10.38</v>
       </c>
       <c r="S21" t="n">
-        <v>2.34</v>
+        <v>1.97</v>
       </c>
       <c r="T21" t="n">
-        <v>12.81</v>
+        <v>10.58</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The house is unoccupied for 8 hours today. What's the best AC temperature?</t>
+          <t>With 3 people home, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>State College, PA</t>
+          <t>DuBois, PA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2100</v>
+        <v>1950</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>3</v>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>$300</t>
-        </is>
+      <c r="G22" t="n">
+        <v>305</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -2034,73 +1992,71 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J22" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>78</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.98</v>
+        <v>4.87</v>
       </c>
       <c r="M22" t="n">
-        <v>3.94</v>
+        <v>4.96</v>
       </c>
       <c r="N22" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="O22" t="n">
-        <v>10</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>5.473</v>
+        <v>6.361499999999999</v>
       </c>
       <c r="Q22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>11.47</v>
+        <v>10.15</v>
       </c>
       <c r="S22" t="n">
-        <v>2.18</v>
+        <v>1.93</v>
       </c>
       <c r="T22" t="n">
-        <v>11.94</v>
+        <v>10.35</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The house is unoccupied for 8 hours. What should I set the thermostat to?</t>
+          <t>With 3 people home, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>State College, PA</t>
+          <t>Reading, PA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>3</v>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>$300</t>
-        </is>
+      <c r="G23" t="n">
+        <v>340</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -2108,73 +2064,71 @@
         </is>
       </c>
       <c r="I23" t="n">
+        <v>20</v>
+      </c>
+      <c r="J23" t="n">
         <v>18</v>
       </c>
-      <c r="J23" t="n">
-        <v>42</v>
-      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>65</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>5.35</v>
+        <v>6.06</v>
       </c>
       <c r="M23" t="n">
-        <v>5.29</v>
+        <v>6.12</v>
       </c>
       <c r="N23" t="n">
-        <v>7</v>
+        <v>6.11</v>
       </c>
       <c r="O23" t="n">
         <v>7.6</v>
       </c>
       <c r="P23" t="n">
-        <v>5.996499999999999</v>
+        <v>6.322</v>
       </c>
       <c r="Q23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>9.43</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>1.79</v>
+        <v>1.59</v>
       </c>
       <c r="T23" t="n">
-        <v>9.82</v>
+        <v>8.52</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The house is unoccupied for 8 hours. What should I set the thermostat to?</t>
+          <t>With 3 people home, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>State College, PA</t>
+          <t>Reading, PA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>3</v>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>$300</t>
-        </is>
+      <c r="G24" t="n">
+        <v>340</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -2182,73 +2136,71 @@
         </is>
       </c>
       <c r="I24" t="n">
+        <v>20</v>
+      </c>
+      <c r="J24" t="n">
         <v>18</v>
       </c>
-      <c r="J24" t="n">
-        <v>42</v>
-      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.79</v>
+        <v>4.85</v>
       </c>
       <c r="M24" t="n">
-        <v>4.74</v>
+        <v>4.94</v>
       </c>
       <c r="N24" t="n">
-        <v>9.32</v>
+        <v>8.6</v>
       </c>
       <c r="O24" t="n">
         <v>7.6</v>
       </c>
       <c r="P24" t="n">
-        <v>6.1</v>
+        <v>6.044</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R24" t="n">
-        <v>10.26</v>
+        <v>10.17</v>
       </c>
       <c r="S24" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="T24" t="n">
-        <v>10.68</v>
+        <v>10.37</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The house is unoccupied for 8 hours. What should I set the thermostat to?</t>
+          <t>With 3 people home, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>State College, PA</t>
+          <t>Reading, PA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>3</v>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>$300</t>
-        </is>
+      <c r="G25" t="n">
+        <v>340</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -2256,454 +2208,442 @@
         </is>
       </c>
       <c r="I25" t="n">
+        <v>20</v>
+      </c>
+      <c r="J25" t="n">
         <v>18</v>
       </c>
-      <c r="J25" t="n">
-        <v>42</v>
-      </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>79</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.23</v>
+        <v>3.64</v>
       </c>
       <c r="M25" t="n">
-        <v>4.19</v>
+        <v>3.77</v>
       </c>
       <c r="N25" t="n">
-        <v>8.6</v>
+        <v>1.53</v>
       </c>
       <c r="O25" t="n">
-        <v>7.6</v>
+        <v>6.03</v>
       </c>
       <c r="P25" t="n">
-        <v>5.5955</v>
+        <v>3.622</v>
       </c>
       <c r="Q25" t="n">
         <v>3</v>
       </c>
       <c r="R25" t="n">
-        <v>11.09</v>
+        <v>11.99</v>
       </c>
       <c r="S25" t="n">
-        <v>2.11</v>
+        <v>2.28</v>
       </c>
       <c r="T25" t="n">
-        <v>11.55</v>
+        <v>12.22</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
+        <v>40</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>We're just getting in for the night — what heat temperature should I set overnight?</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Quakertown, PA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1900</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" t="n">
+        <v>280</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Single-family</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>22</v>
+      </c>
+      <c r="J26" t="n">
+        <v>11</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="M26" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="N26" t="n">
         <v>10</v>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>With 1 people home on a hot day, what's the best AC setting?</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>900</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>$150</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Apartment</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>93</v>
-      </c>
-      <c r="J26" t="n">
-        <v>47</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="M26" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="N26" t="n">
-        <v>8.6</v>
-      </c>
       <c r="O26" t="n">
-        <v>9.630000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="P26" t="n">
-        <v>5.581999999999999</v>
+        <v>9.0665</v>
       </c>
       <c r="Q26" t="n">
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>9.67</v>
+        <v>3.85</v>
       </c>
       <c r="S26" t="n">
-        <v>1.84</v>
+        <v>0.73</v>
       </c>
       <c r="T26" t="n">
-        <v>9.85</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>With 1 people home on a hot day, what's the best AC setting?</t>
+          <t>We're just getting in for the night — what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>Quakertown, PA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>900</v>
+        <v>1900</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>$150</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="G27" t="n">
+        <v>280</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Single-family</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>93</v>
+        <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>65</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.65</v>
+        <v>9.5</v>
       </c>
       <c r="M27" t="n">
-        <v>5.73</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="N27" t="n">
         <v>6.11</v>
       </c>
       <c r="O27" t="n">
-        <v>9.630000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="P27" t="n">
-        <v>5.467000000000001</v>
+        <v>8.551</v>
       </c>
       <c r="Q27" t="n">
         <v>2</v>
       </c>
       <c r="R27" t="n">
-        <v>8.960000000000001</v>
+        <v>3.23</v>
       </c>
       <c r="S27" t="n">
-        <v>1.7</v>
+        <v>0.61</v>
       </c>
       <c r="T27" t="n">
-        <v>9.130000000000001</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>With 1 people home on a hot day, what's the best AC setting?</t>
+          <t>We're just getting in for the night — what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>Quakertown, PA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>900</v>
+        <v>1900</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>$150</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="G28" t="n">
+        <v>280</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Single-family</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>93</v>
+        <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.97</v>
+        <v>9.91</v>
       </c>
       <c r="M28" t="n">
-        <v>6.19</v>
+        <v>9.92</v>
       </c>
       <c r="N28" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>7.6</v>
+        <v>3.75</v>
       </c>
       <c r="P28" t="n">
-        <v>5.0695</v>
+        <v>7.0075</v>
       </c>
       <c r="Q28" t="n">
         <v>3</v>
       </c>
       <c r="R28" t="n">
-        <v>8.25</v>
+        <v>2.61</v>
       </c>
       <c r="S28" t="n">
-        <v>1.57</v>
+        <v>0.5</v>
       </c>
       <c r="T28" t="n">
-        <v>8.41</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cold day today with 1 people home. What's a good heating temperature?</t>
+          <t>We're done for the day — what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>Wilkes-Barre, PA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>900</v>
+        <v>1900</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>$150</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G29" t="n">
+        <v>290</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Single-family</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J29" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>65</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>7.14</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>7.17</v>
+        <v>9.18</v>
       </c>
       <c r="N29" t="n">
-        <v>5.13</v>
+        <v>6.11</v>
       </c>
       <c r="O29" t="n">
         <v>7.6</v>
       </c>
       <c r="P29" t="n">
-        <v>6.817499999999999</v>
+        <v>8.308</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R29" t="n">
-        <v>6.74</v>
+        <v>3.8</v>
       </c>
       <c r="S29" t="n">
-        <v>1.28</v>
+        <v>0.72</v>
       </c>
       <c r="T29" t="n">
-        <v>6.87</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cold day today with 1 people home. What's a good heating temperature?</t>
+          <t>We're done for the day — what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>Wilkes-Barre, PA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>900</v>
+        <v>1900</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>$150</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G30" t="n">
+        <v>290</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Single-family</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>5.85</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="M30" t="n">
-        <v>6.71</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>7.83</v>
+        <v>8.6</v>
       </c>
       <c r="O30" t="n">
         <v>7.6</v>
       </c>
       <c r="P30" t="n">
-        <v>6.8095</v>
+        <v>8.663499999999999</v>
       </c>
       <c r="Q30" t="n">
         <v>2</v>
       </c>
       <c r="R30" t="n">
-        <v>7.45</v>
+        <v>4.15</v>
       </c>
       <c r="S30" t="n">
-        <v>1.42</v>
+        <v>0.79</v>
       </c>
       <c r="T30" t="n">
-        <v>7.59</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cold day today with 1 people home. What's a good heating temperature?</t>
+          <t>We're done for the day — what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>Wilkes-Barre, PA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>900</v>
+        <v>1900</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>$150</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G31" t="n">
+        <v>290</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Single-family</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J31" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2711,10 +2651,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>4.19</v>
+        <v>8.73</v>
       </c>
       <c r="M31" t="n">
-        <v>6.25</v>
+        <v>8.82</v>
       </c>
       <c r="N31" t="n">
         <v>10</v>
@@ -2723,135 +2663,131 @@
         <v>7.6</v>
       </c>
       <c r="P31" t="n">
-        <v>6.584499999999999</v>
+        <v>8.846</v>
       </c>
       <c r="Q31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>8.16</v>
+        <v>4.38</v>
       </c>
       <c r="S31" t="n">
-        <v>1.55</v>
+        <v>0.83</v>
       </c>
       <c r="T31" t="n">
-        <v>8.31</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>The house is unoccupied for 4 hours today. What's the best AC temperature?</t>
+          <t>I'm sticking around the house with 2 people — what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Erie, PA</t>
+          <t>West Chester, PA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1800</v>
+        <v>1400</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>4</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>$260</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G32" t="n">
+        <v>220</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Condo</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="J32" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>73</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>5.28</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>5.23</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="N32" t="n">
-        <v>8.460000000000001</v>
+        <v>7.83</v>
       </c>
       <c r="O32" t="n">
         <v>10</v>
       </c>
       <c r="P32" t="n">
-        <v>6.6065</v>
+        <v>8.340499999999999</v>
       </c>
       <c r="Q32" t="n">
         <v>3</v>
       </c>
       <c r="R32" t="n">
-        <v>9.529999999999999</v>
+        <v>5.29</v>
       </c>
       <c r="S32" t="n">
-        <v>1.81</v>
+        <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>9.92</v>
+        <v>5.39</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The house is unoccupied for 4 hours today. What's the best AC temperature?</t>
+          <t>I'm sticking around the house with 2 people — what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Erie, PA</t>
+          <t>West Chester, PA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1800</v>
+        <v>1400</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>4</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>$260</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G33" t="n">
+        <v>220</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Condo</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="J33" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2859,73 +2795,71 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>5.79</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="M33" t="n">
-        <v>5.73</v>
+        <v>8.35</v>
       </c>
       <c r="N33" t="n">
-        <v>9.25</v>
+        <v>9.32</v>
       </c>
       <c r="O33" t="n">
         <v>10</v>
       </c>
       <c r="P33" t="n">
-        <v>7.092499999999999</v>
+        <v>8.797499999999999</v>
       </c>
       <c r="Q33" t="n">
         <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>8.77</v>
+        <v>4.91</v>
       </c>
       <c r="S33" t="n">
-        <v>1.67</v>
+        <v>0.93</v>
       </c>
       <c r="T33" t="n">
-        <v>9.130000000000001</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The house is unoccupied for 4 hours today. What's the best AC temperature?</t>
+          <t>I'm sticking around the house with 2 people — what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Erie, PA</t>
+          <t>West Chester, PA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1800</v>
+        <v>1400</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>4</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>$260</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G34" t="n">
+        <v>220</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Condo</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="J34" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2933,62 +2867,60 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>6.3</v>
+        <v>8.56</v>
       </c>
       <c r="M34" t="n">
-        <v>6.24</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="N34" t="n">
-        <v>6.65</v>
+        <v>7</v>
       </c>
       <c r="O34" t="n">
         <v>10</v>
       </c>
       <c r="P34" t="n">
-        <v>6.904</v>
+        <v>8.457000000000001</v>
       </c>
       <c r="Q34" t="n">
         <v>2</v>
       </c>
       <c r="R34" t="n">
-        <v>8</v>
+        <v>4.63</v>
       </c>
       <c r="S34" t="n">
-        <v>1.52</v>
+        <v>0.88</v>
       </c>
       <c r="T34" t="n">
-        <v>8.33</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The house is unoccupied for 4 hours. What should I set the thermostat to?</t>
+          <t>With 4 people home, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Erie, PA</t>
+          <t>Reading, PA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1800</v>
+        <v>2400</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="F35" t="n">
         <v>4</v>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>$260</t>
-        </is>
+      <c r="G35" t="n">
+        <v>380</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -2996,73 +2928,71 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="J35" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>70</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>5.11</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>6.65</v>
+        <v>4.5</v>
       </c>
       <c r="O35" t="n">
-        <v>7.6</v>
+        <v>8.16</v>
       </c>
       <c r="P35" t="n">
-        <v>5.8065</v>
+        <v>2.124</v>
       </c>
       <c r="Q35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R35" t="n">
-        <v>9.710000000000001</v>
+        <v>21.3</v>
       </c>
       <c r="S35" t="n">
-        <v>1.84</v>
+        <v>4.05</v>
       </c>
       <c r="T35" t="n">
-        <v>10.1</v>
+        <v>21.71</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>The house is unoccupied for 4 hours. What should I set the thermostat to?</t>
+          <t>With 4 people home, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Erie, PA</t>
+          <t>Reading, PA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1800</v>
+        <v>2400</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="F36" t="n">
         <v>4</v>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>$260</t>
-        </is>
+      <c r="G36" t="n">
+        <v>380</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -3070,73 +3000,71 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="J36" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>76</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>9.25</v>
+        <v>10</v>
       </c>
       <c r="O36" t="n">
-        <v>7.6</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="P36" t="n">
-        <v>5.998499999999999</v>
+        <v>3.4445</v>
       </c>
       <c r="Q36" t="n">
         <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>10.47</v>
+        <v>18.18</v>
       </c>
       <c r="S36" t="n">
-        <v>1.99</v>
+        <v>3.45</v>
       </c>
       <c r="T36" t="n">
-        <v>10.9</v>
+        <v>18.53</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The house is unoccupied for 4 hours. What should I set the thermostat to?</t>
+          <t>With 4 people home, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Erie, PA</t>
+          <t>Reading, PA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1800</v>
+        <v>2400</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>4</v>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>$260</t>
-        </is>
+      <c r="G37" t="n">
+        <v>380</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -3144,60 +3072,60 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="J37" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>79</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>4.14</v>
+        <v>0.54</v>
       </c>
       <c r="M37" t="n">
-        <v>4.1</v>
+        <v>0.77</v>
       </c>
       <c r="N37" t="n">
-        <v>8.460000000000001</v>
+        <v>7.59</v>
       </c>
       <c r="O37" t="n">
-        <v>7.6</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="P37" t="n">
-        <v>5.509</v>
+        <v>3.394</v>
       </c>
       <c r="Q37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R37" t="n">
-        <v>11.23</v>
+        <v>16.61</v>
       </c>
       <c r="S37" t="n">
-        <v>2.13</v>
+        <v>3.16</v>
       </c>
       <c r="T37" t="n">
-        <v>11.69</v>
+        <v>16.94</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>With 2 people home on a hot day, what's the best AC setting?</t>
+          <t>I'm heading out and won't be back for hours — what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bethlehem, PA</t>
+          <t>King of Prussia, PA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1400</v>
+        <v>1800</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -3207,71 +3135,69 @@
       <c r="F38" t="n">
         <v>2</v>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>$200</t>
-        </is>
+      <c r="G38" t="n">
+        <v>270</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Rowhouse</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="J38" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>6.07</v>
+        <v>6.76</v>
       </c>
       <c r="M38" t="n">
-        <v>6.13</v>
+        <v>6.69</v>
       </c>
       <c r="N38" t="n">
-        <v>10</v>
+        <v>7.83</v>
       </c>
       <c r="O38" t="n">
         <v>9.630000000000001</v>
       </c>
       <c r="P38" t="n">
-        <v>7.411</v>
+        <v>7.380000000000001</v>
       </c>
       <c r="Q38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R38" t="n">
-        <v>8.34</v>
+        <v>7.32</v>
       </c>
       <c r="S38" t="n">
-        <v>1.58</v>
+        <v>1.39</v>
       </c>
       <c r="T38" t="n">
-        <v>8.5</v>
+        <v>7.62</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>With 2 people home on a hot day, what's the best AC setting?</t>
+          <t>I'm heading out and won't be back for hours — what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bethlehem, PA</t>
+          <t>King of Prussia, PA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1400</v>
+        <v>1800</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -3281,71 +3207,69 @@
       <c r="F39" t="n">
         <v>2</v>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>$200</t>
-        </is>
+      <c r="G39" t="n">
+        <v>270</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Rowhouse</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="J39" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>77</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>6.41</v>
+        <v>7.07</v>
       </c>
       <c r="M39" t="n">
-        <v>6.46</v>
+        <v>7</v>
       </c>
       <c r="N39" t="n">
-        <v>7.83</v>
+        <v>9.32</v>
       </c>
       <c r="O39" t="n">
         <v>9.630000000000001</v>
       </c>
       <c r="P39" t="n">
-        <v>7.1945</v>
+        <v>7.8795</v>
       </c>
       <c r="Q39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>7.84</v>
+        <v>6.85</v>
       </c>
       <c r="S39" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="T39" t="n">
-        <v>7.99</v>
+        <v>7.13</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>With 2 people home on a hot day, what's the best AC setting?</t>
+          <t>I'm heading out and won't be back for hours — what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bethlehem, PA</t>
+          <t>King of Prussia, PA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1400</v>
+        <v>1800</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -3355,21 +3279,19 @@
       <c r="F40" t="n">
         <v>2</v>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>$200</t>
-        </is>
+      <c r="G40" t="n">
+        <v>270</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Rowhouse</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="J40" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3377,45 +3299,45 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>6.75</v>
+        <v>7.47</v>
       </c>
       <c r="M40" t="n">
-        <v>6.78</v>
+        <v>7.39</v>
       </c>
       <c r="N40" t="n">
         <v>5.13</v>
       </c>
       <c r="O40" t="n">
-        <v>10</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="P40" t="n">
-        <v>6.924</v>
+        <v>7.297999999999998</v>
       </c>
       <c r="Q40" t="n">
         <v>3</v>
       </c>
       <c r="R40" t="n">
-        <v>7.34</v>
+        <v>6.26</v>
       </c>
       <c r="S40" t="n">
-        <v>1.39</v>
+        <v>1.19</v>
       </c>
       <c r="T40" t="n">
-        <v>7.48</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>We're all out for 8 hours in the heat. What AC setting makes sense?</t>
+          <t>With 3 people home, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pottstown, PA</t>
+          <t>Williamsport, PA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -3429,10 +3351,8 @@
       <c r="F41" t="n">
         <v>3</v>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>$270</t>
-        </is>
+      <c r="G41" t="n">
+        <v>280</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -3440,56 +3360,56 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="J41" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>64</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.87</v>
+        <v>5.43</v>
       </c>
       <c r="M41" t="n">
-        <v>2.98</v>
+        <v>5.51</v>
       </c>
       <c r="N41" t="n">
-        <v>9.32</v>
+        <v>5.13</v>
       </c>
       <c r="O41" t="n">
-        <v>8.859999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="P41" t="n">
-        <v>5.097</v>
+        <v>5.7235</v>
       </c>
       <c r="Q41" t="n">
         <v>2</v>
       </c>
       <c r="R41" t="n">
-        <v>12.93</v>
+        <v>9.31</v>
       </c>
       <c r="S41" t="n">
-        <v>2.46</v>
+        <v>1.77</v>
       </c>
       <c r="T41" t="n">
-        <v>13.46</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>We're all out for 8 hours in the heat. What AC setting makes sense?</t>
+          <t>With 3 people home, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pottstown, PA</t>
+          <t>Williamsport, PA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -3503,10 +3423,8 @@
       <c r="F42" t="n">
         <v>3</v>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>$270</t>
-        </is>
+      <c r="G42" t="n">
+        <v>280</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -3514,56 +3432,56 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="J42" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.54</v>
+        <v>4.69</v>
       </c>
       <c r="M42" t="n">
-        <v>3.51</v>
+        <v>4.79</v>
       </c>
       <c r="N42" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="O42" t="n">
-        <v>9.630000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="P42" t="n">
-        <v>5.135</v>
+        <v>5.943499999999999</v>
       </c>
       <c r="Q42" t="n">
         <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>12.12</v>
+        <v>10.42</v>
       </c>
       <c r="S42" t="n">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="T42" t="n">
-        <v>12.62</v>
+        <v>10.62</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>We're all out for 8 hours in the heat. What AC setting makes sense?</t>
+          <t>With 3 people home, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pottstown, PA</t>
+          <t>Williamsport, PA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -3577,10 +3495,8 @@
       <c r="F43" t="n">
         <v>3</v>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>$270</t>
-        </is>
+      <c r="G43" t="n">
+        <v>280</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -3588,60 +3504,60 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="J43" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>74</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>4.08</v>
+        <v>3.57</v>
       </c>
       <c r="M43" t="n">
-        <v>4.04</v>
+        <v>3.71</v>
       </c>
       <c r="N43" t="n">
-        <v>4.06</v>
+        <v>7</v>
       </c>
       <c r="O43" t="n">
-        <v>8.51</v>
+        <v>7.6</v>
       </c>
       <c r="P43" t="n">
-        <v>4.7265</v>
+        <v>4.9095</v>
       </c>
       <c r="Q43" t="n">
         <v>3</v>
       </c>
       <c r="R43" t="n">
-        <v>11.32</v>
+        <v>12.08</v>
       </c>
       <c r="S43" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="T43" t="n">
-        <v>11.79</v>
+        <v>12.31</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>I'm setting the thermostat for bedtime. What heating temperature is best for sleeping?</t>
+          <t>I'm spending the day at home with 3 people — what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Quakertown, PA</t>
+          <t>Stroudsburg, PA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1900</v>
+        <v>2300</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -3651,10 +3567,8 @@
       <c r="F44" t="n">
         <v>3</v>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>$240</t>
-        </is>
+      <c r="G44" t="n">
+        <v>340</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -3662,60 +3576,60 @@
         </is>
       </c>
       <c r="I44" t="n">
+        <v>77</v>
+      </c>
+      <c r="J44" t="n">
         <v>22</v>
       </c>
-      <c r="J44" t="n">
-        <v>11</v>
-      </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>73</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>8.470000000000001</v>
+        <v>5.38</v>
       </c>
       <c r="M44" t="n">
-        <v>8.58</v>
+        <v>5.45</v>
       </c>
       <c r="N44" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="O44" t="n">
         <v>10</v>
       </c>
-      <c r="O44" t="n">
-        <v>7.6</v>
-      </c>
       <c r="P44" t="n">
-        <v>8.683999999999999</v>
+        <v>6.587499999999999</v>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R44" t="n">
-        <v>4.76</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="S44" t="n">
-        <v>0.9</v>
+        <v>1.78</v>
       </c>
       <c r="T44" t="n">
-        <v>4.65</v>
+        <v>9.57</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>I'm setting the thermostat for bedtime. What heating temperature is best for sleeping?</t>
+          <t>I'm spending the day at home with 3 people — what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Quakertown, PA</t>
+          <t>Stroudsburg, PA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1900</v>
+        <v>2300</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -3725,10 +3639,8 @@
       <c r="F45" t="n">
         <v>3</v>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>$240</t>
-        </is>
+      <c r="G45" t="n">
+        <v>340</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -3736,60 +3648,60 @@
         </is>
       </c>
       <c r="I45" t="n">
+        <v>77</v>
+      </c>
+      <c r="J45" t="n">
         <v>22</v>
       </c>
-      <c r="J45" t="n">
-        <v>11</v>
-      </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>77</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>8.949999999999999</v>
+        <v>6</v>
       </c>
       <c r="M45" t="n">
-        <v>9.029999999999999</v>
+        <v>6.06</v>
       </c>
       <c r="N45" t="n">
-        <v>6.11</v>
+        <v>9.32</v>
       </c>
       <c r="O45" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="P45" t="n">
-        <v>8.2075</v>
+        <v>7.284999999999999</v>
       </c>
       <c r="Q45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>4.05</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="S45" t="n">
-        <v>0.77</v>
+        <v>1.6</v>
       </c>
       <c r="T45" t="n">
-        <v>3.95</v>
+        <v>8.609999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>I'm setting the thermostat for bedtime. What heating temperature is best for sleeping?</t>
+          <t>I'm spending the day at home with 3 people — what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Quakertown, PA</t>
+          <t>Stroudsburg, PA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1900</v>
+        <v>2300</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -3799,10 +3711,8 @@
       <c r="F46" t="n">
         <v>3</v>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>$240</t>
-        </is>
+      <c r="G46" t="n">
+        <v>340</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -3810,295 +3720,287 @@
         </is>
       </c>
       <c r="I46" t="n">
+        <v>77</v>
+      </c>
+      <c r="J46" t="n">
         <v>22</v>
       </c>
-      <c r="J46" t="n">
-        <v>11</v>
-      </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>80</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>9.43</v>
+        <v>6.48</v>
       </c>
       <c r="M46" t="n">
-        <v>9.470000000000001</v>
+        <v>6.52</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O46" t="n">
-        <v>3.75</v>
+        <v>10</v>
       </c>
       <c r="P46" t="n">
-        <v>6.706</v>
+        <v>7.125999999999999</v>
       </c>
       <c r="Q46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R46" t="n">
-        <v>3.33</v>
+        <v>7.74</v>
       </c>
       <c r="S46" t="n">
-        <v>0.63</v>
+        <v>1.47</v>
       </c>
       <c r="T46" t="n">
-        <v>3.25</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>I'm setting the thermostat for bedtime. What AC temperature is best for sleeping?</t>
+          <t>I'm heading out for the day — what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Phoenixville, PA</t>
+          <t>Lebanon, PA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1750</v>
+        <v>2000</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>2</v>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>$250</t>
-        </is>
+      <c r="G47" t="n">
+        <v>230</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="J47" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>65</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>6.62</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="M47" t="n">
-        <v>6.87</v>
+        <v>9.44</v>
       </c>
       <c r="N47" t="n">
-        <v>8.6</v>
+        <v>6.11</v>
       </c>
       <c r="O47" t="n">
-        <v>9.630000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="P47" t="n">
-        <v>7.555</v>
+        <v>8.714</v>
       </c>
       <c r="Q47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R47" t="n">
-        <v>7.52</v>
+        <v>3.18</v>
       </c>
       <c r="S47" t="n">
-        <v>1.43</v>
+        <v>0.6</v>
       </c>
       <c r="T47" t="n">
-        <v>7.34</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>I'm setting the thermostat for bedtime. What AC temperature is best for sleeping?</t>
+          <t>I'm heading out for the day — what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Phoenixville, PA</t>
+          <t>Lebanon, PA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1750</v>
+        <v>2000</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="F48" t="n">
         <v>2</v>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>$250</t>
-        </is>
+      <c r="G48" t="n">
+        <v>230</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="J48" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>6.99</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="M48" t="n">
-        <v>7.21</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="N48" t="n">
-        <v>6.11</v>
+        <v>8.6</v>
       </c>
       <c r="O48" t="n">
-        <v>9.630000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="P48" t="n">
-        <v>7.287000000000001</v>
+        <v>8.8415</v>
       </c>
       <c r="Q48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R48" t="n">
-        <v>6.97</v>
+        <v>4.03</v>
       </c>
       <c r="S48" t="n">
-        <v>1.32</v>
+        <v>0.77</v>
       </c>
       <c r="T48" t="n">
-        <v>6.8</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>I'm setting the thermostat for bedtime. What AC temperature is best for sleeping?</t>
+          <t>I'm heading out for the day — what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Phoenixville, PA</t>
+          <t>Lebanon, PA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1750</v>
+        <v>2000</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="F49" t="n">
         <v>2</v>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>$250</t>
-        </is>
+      <c r="G49" t="n">
+        <v>230</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="J49" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>71</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>7.36</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="M49" t="n">
-        <v>7.55</v>
+        <v>8.31</v>
       </c>
       <c r="N49" t="n">
-        <v>2.86</v>
+        <v>9.32</v>
       </c>
       <c r="O49" t="n">
-        <v>7.6</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="P49" t="n">
-        <v>6.5625</v>
+        <v>8.618499999999999</v>
       </c>
       <c r="Q49" t="n">
         <v>3</v>
       </c>
       <c r="R49" t="n">
-        <v>6.42</v>
+        <v>4.88</v>
       </c>
       <c r="S49" t="n">
-        <v>1.22</v>
+        <v>0.93</v>
       </c>
       <c r="T49" t="n">
-        <v>6.27</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>We're all out for 12 hours in the heat. What AC setting makes sense?</t>
+          <t>With 2 people home, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>West Mifflin, PA</t>
+          <t>DuBois, PA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2300</v>
+        <v>1850</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>4</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>$165</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G50" t="n">
+        <v>275</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -4106,73 +4008,71 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="J50" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>63</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0.28</v>
+        <v>5.88</v>
       </c>
       <c r="M50" t="n">
-        <v>2.23</v>
+        <v>5.95</v>
       </c>
       <c r="N50" t="n">
-        <v>7.59</v>
+        <v>4.06</v>
       </c>
       <c r="O50" t="n">
-        <v>9.630000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="P50" t="n">
-        <v>3.827</v>
+        <v>5.7985</v>
       </c>
       <c r="Q50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R50" t="n">
-        <v>14.06</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="S50" t="n">
-        <v>2.67</v>
+        <v>1.64</v>
       </c>
       <c r="T50" t="n">
-        <v>14.64</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>We're all out for 12 hours in the heat. What AC setting makes sense?</t>
+          <t>With 2 people home, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>West Mifflin, PA</t>
+          <t>DuBois, PA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2300</v>
+        <v>1850</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>4</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>$165</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G51" t="n">
+        <v>275</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -4180,73 +4080,71 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="J51" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0.43</v>
+        <v>5.15</v>
       </c>
       <c r="M51" t="n">
-        <v>2.7</v>
+        <v>5.23</v>
       </c>
       <c r="N51" t="n">
-        <v>5.63</v>
+        <v>8.6</v>
       </c>
       <c r="O51" t="n">
-        <v>9.630000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="P51" t="n">
-        <v>3.6445</v>
+        <v>6.2355</v>
       </c>
       <c r="Q51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R51" t="n">
-        <v>13.35</v>
+        <v>9.73</v>
       </c>
       <c r="S51" t="n">
-        <v>2.54</v>
+        <v>1.85</v>
       </c>
       <c r="T51" t="n">
-        <v>13.9</v>
+        <v>9.91</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>We're all out for 12 hours in the heat. What AC setting makes sense?</t>
+          <t>With 2 people home, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>West Mifflin, PA</t>
+          <t>DuBois, PA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2300</v>
+        <v>1850</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>4</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>$165</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G52" t="n">
+        <v>275</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -4254,60 +4152,60 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="J52" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>75</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0.63</v>
+        <v>4.12</v>
       </c>
       <c r="M52" t="n">
-        <v>3.17</v>
+        <v>4.24</v>
       </c>
       <c r="N52" t="n">
-        <v>3.23</v>
+        <v>6.11</v>
       </c>
       <c r="O52" t="n">
-        <v>8.51</v>
+        <v>7.6</v>
       </c>
       <c r="P52" t="n">
-        <v>3.221</v>
+        <v>5.082</v>
       </c>
       <c r="Q52" t="n">
         <v>3</v>
       </c>
       <c r="R52" t="n">
-        <v>12.64</v>
+        <v>11.26</v>
       </c>
       <c r="S52" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="T52" t="n">
-        <v>13.16</v>
+        <v>11.48</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>I'm working from home today and it's hot. What AC temperature should I use?</t>
+          <t>We're just getting in for the night — what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cheltenham, PA</t>
+          <t>Erie, PA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2000</v>
+        <v>2750</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -4315,12 +4213,10 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>3</v>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>$450</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="G53" t="n">
+        <v>285</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -4328,60 +4224,60 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>88</v>
+        <v>5</v>
       </c>
       <c r="J53" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>63</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>5.96</v>
+        <v>7.59</v>
       </c>
       <c r="M53" t="n">
-        <v>6.02</v>
+        <v>7.77</v>
       </c>
       <c r="N53" t="n">
-        <v>7.83</v>
+        <v>1.38</v>
       </c>
       <c r="O53" t="n">
-        <v>9.630000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="P53" t="n">
-        <v>6.9055</v>
+        <v>6.412499999999999</v>
       </c>
       <c r="Q53" t="n">
         <v>3</v>
       </c>
       <c r="R53" t="n">
-        <v>8.51</v>
+        <v>6.07</v>
       </c>
       <c r="S53" t="n">
-        <v>1.62</v>
+        <v>1.15</v>
       </c>
       <c r="T53" t="n">
-        <v>8.68</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>I'm working from home today and it's hot. What AC temperature should I use?</t>
+          <t>We're just getting in for the night — what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cheltenham, PA</t>
+          <t>Erie, PA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2000</v>
+        <v>2750</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -4389,12 +4285,10 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>$450</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="G54" t="n">
+        <v>285</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -4402,60 +4296,60 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>88</v>
+        <v>5</v>
       </c>
       <c r="J54" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>6.18</v>
+        <v>7.29</v>
       </c>
       <c r="M54" t="n">
-        <v>6.24</v>
+        <v>7.49</v>
       </c>
       <c r="N54" t="n">
-        <v>9.32</v>
+        <v>5.92</v>
       </c>
       <c r="O54" t="n">
-        <v>9.630000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="P54" t="n">
-        <v>7.346499999999999</v>
+        <v>7.132499999999999</v>
       </c>
       <c r="Q54" t="n">
         <v>2</v>
       </c>
       <c r="R54" t="n">
-        <v>8.18</v>
+        <v>6.53</v>
       </c>
       <c r="S54" t="n">
-        <v>1.55</v>
+        <v>1.24</v>
       </c>
       <c r="T54" t="n">
-        <v>8.33</v>
+        <v>6.37</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>I'm working from home today and it's hot. What AC temperature should I use?</t>
+          <t>We're just getting in for the night — what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cheltenham, PA</t>
+          <t>Erie, PA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2000</v>
+        <v>2750</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -4463,12 +4357,10 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>3</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>$450</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="G55" t="n">
+        <v>285</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -4476,88 +4368,86 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>88</v>
+        <v>5</v>
       </c>
       <c r="J55" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>69</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>6.41</v>
+        <v>6.98</v>
       </c>
       <c r="M55" t="n">
-        <v>6.46</v>
+        <v>7.21</v>
       </c>
       <c r="N55" t="n">
-        <v>9.32</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="O55" t="n">
-        <v>9.630000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="P55" t="n">
-        <v>7.4925</v>
+        <v>7.579499999999999</v>
       </c>
       <c r="Q55" t="n">
         <v>1</v>
       </c>
       <c r="R55" t="n">
-        <v>7.84</v>
+        <v>6.98</v>
       </c>
       <c r="S55" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="T55" t="n">
-        <v>7.99</v>
+        <v>6.81</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>It's a mild spring day but the house feels chilly. What should I set the heat to?</t>
+          <t>I'm stepping out for a few hours — what heat temperature should I set for the condo?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Norristown, PA</t>
+          <t>King of Prussia, PA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1600</v>
+        <v>1120</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>$260</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="G56" t="n">
+        <v>155</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Condo</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J56" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>62</t>
         </is>
       </c>
       <c r="L56" t="n">
@@ -4567,16 +4457,16 @@
         <v>10</v>
       </c>
       <c r="N56" t="n">
-        <v>8.6</v>
+        <v>2.86</v>
       </c>
       <c r="O56" t="n">
-        <v>10</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="P56" t="n">
-        <v>9.720000000000001</v>
+        <v>8.314</v>
       </c>
       <c r="Q56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
@@ -4590,48 +4480,46 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>It's a mild spring day but the house feels chilly. What should I set the heat to?</t>
+          <t>I'm stepping out for a few hours — what heat temperature should I set for the condo?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Norristown, PA</t>
+          <t>King of Prussia, PA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1600</v>
+        <v>1120</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>3</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>$260</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="G57" t="n">
+        <v>155</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Condo</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J57" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L57" t="n">
@@ -4641,16 +4529,16 @@
         <v>10</v>
       </c>
       <c r="N57" t="n">
-        <v>9.32</v>
+        <v>7</v>
       </c>
       <c r="O57" t="n">
         <v>9.630000000000001</v>
       </c>
       <c r="P57" t="n">
-        <v>9.8085</v>
+        <v>9.3445</v>
       </c>
       <c r="Q57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
@@ -4664,48 +4552,46 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>It's a mild spring day but the house feels chilly. What should I set the heat to?</t>
+          <t>I'm stepping out for a few hours — what heat temperature should I set for the condo?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Norristown, PA</t>
+          <t>King of Prussia, PA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1600</v>
+        <v>1120</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3</v>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>$260</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="G58" t="n">
+        <v>155</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Condo</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J58" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>69</t>
         </is>
       </c>
       <c r="L58" t="n">
@@ -4715,56 +4601,54 @@
         <v>10</v>
       </c>
       <c r="N58" t="n">
-        <v>7</v>
+        <v>9.32</v>
       </c>
       <c r="O58" t="n">
         <v>9.630000000000001</v>
       </c>
       <c r="P58" t="n">
-        <v>9.3445</v>
+        <v>9.8085</v>
       </c>
       <c r="Q58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R58" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>I'm setting the thermostat for bedtime on a cold night. What heating temperature is best?</t>
+          <t>With 3 people home, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Wilkes-Barre, PA</t>
+          <t>Reading, PA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1900</v>
+        <v>2250</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>2</v>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>$230</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="G59" t="n">
+        <v>245</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -4772,10 +4656,10 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="J59" t="n">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -4783,62 +4667,60 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>8.539999999999999</v>
+        <v>10</v>
       </c>
       <c r="M59" t="n">
-        <v>8.65</v>
+        <v>10</v>
       </c>
       <c r="N59" t="n">
         <v>6.11</v>
       </c>
       <c r="O59" t="n">
-        <v>7.6</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="P59" t="n">
-        <v>7.951499999999999</v>
+        <v>9.166500000000001</v>
       </c>
       <c r="Q59" t="n">
         <v>3</v>
       </c>
       <c r="R59" t="n">
-        <v>4.65</v>
+        <v>0.73</v>
       </c>
       <c r="S59" t="n">
-        <v>0.88</v>
+        <v>0.14</v>
       </c>
       <c r="T59" t="n">
-        <v>4.54</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>I'm setting the thermostat for bedtime on a cold night. What heating temperature is best?</t>
+          <t>With 3 people home, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Wilkes-Barre, PA</t>
+          <t>Reading, PA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1900</v>
+        <v>2250</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2</v>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>$230</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="G60" t="n">
+        <v>245</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -4846,10 +4728,10 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="J60" t="n">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -4857,62 +4739,60 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>8.27</v>
+        <v>10</v>
       </c>
       <c r="M60" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="N60" t="n">
         <v>8.6</v>
       </c>
       <c r="O60" t="n">
-        <v>7.6</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="P60" t="n">
-        <v>8.280999999999999</v>
+        <v>9.6645</v>
       </c>
       <c r="Q60" t="n">
         <v>2</v>
       </c>
       <c r="R60" t="n">
-        <v>5.05</v>
+        <v>1.97</v>
       </c>
       <c r="S60" t="n">
-        <v>0.96</v>
+        <v>0.37</v>
       </c>
       <c r="T60" t="n">
-        <v>4.93</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>I'm setting the thermostat for bedtime on a cold night. What heating temperature is best?</t>
+          <t>With 3 people home, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Wilkes-Barre, PA</t>
+          <t>Reading, PA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1900</v>
+        <v>2250</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2</v>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>$230</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="G61" t="n">
+        <v>245</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -4920,10 +4800,10 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="J61" t="n">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -4931,506 +4811,492 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>8.1</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="M61" t="n">
-        <v>8.24</v>
+        <v>9.73</v>
       </c>
       <c r="N61" t="n">
         <v>10</v>
       </c>
       <c r="O61" t="n">
-        <v>7.6</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="P61" t="n">
-        <v>8.454000000000001</v>
+        <v>9.783999999999999</v>
       </c>
       <c r="Q61" t="n">
         <v>1</v>
       </c>
       <c r="R61" t="n">
-        <v>5.32</v>
+        <v>2.8</v>
       </c>
       <c r="S61" t="n">
-        <v>1.01</v>
+        <v>0.53</v>
       </c>
       <c r="T61" t="n">
-        <v>5.19</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>It's a scorching day and we're all home. What AC setting balances comfort and cost with our older system?</t>
+          <t>I'm staying put today with 1 person — what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Easton, PA</t>
+          <t>State College, PA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>2200</v>
+        <v>760</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>4</v>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>$165</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="G62" t="n">
+        <v>135</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="J62" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N62" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="O62" t="n">
         <v>10</v>
       </c>
-      <c r="O62" t="n">
-        <v>8.859999999999999</v>
-      </c>
       <c r="P62" t="n">
-        <v>3.329</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="Q62" t="n">
         <v>1</v>
       </c>
       <c r="R62" t="n">
-        <v>24.87</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>25.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>It's a scorching day and we're all home. What AC setting balances comfort and cost with our older system?</t>
+          <t>I'm staying put today with 1 person — what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Easton, PA</t>
+          <t>State College, PA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>2200</v>
+        <v>760</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>4</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>$165</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="G63" t="n">
+        <v>135</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="J63" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N63" t="n">
-        <v>8.460000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="O63" t="n">
         <v>9.630000000000001</v>
       </c>
       <c r="P63" t="n">
-        <v>3.1365</v>
+        <v>9.6645</v>
       </c>
       <c r="Q63" t="n">
         <v>2</v>
       </c>
       <c r="R63" t="n">
-        <v>23.78</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>24.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>It's a scorching day and we're all home. What AC setting balances comfort and cost with our older system?</t>
+          <t>I'm staying put today with 1 person — what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Easton, PA</t>
+          <t>State College, PA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>2200</v>
+        <v>760</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>4</v>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>$165</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="G64" t="n">
+        <v>135</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="J64" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>76</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N64" t="n">
-        <v>6.65</v>
+        <v>5.13</v>
       </c>
       <c r="O64" t="n">
         <v>9.630000000000001</v>
       </c>
       <c r="P64" t="n">
-        <v>2.7745</v>
+        <v>8.970499999999999</v>
       </c>
       <c r="Q64" t="n">
         <v>3</v>
       </c>
       <c r="R64" t="n">
-        <v>22.7</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>23.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>We're leaving for 12 hours on a very cold day. How far should I set back the heat?</t>
+          <t>We're done for the day — what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Stroudsburg, PA</t>
+          <t>York, PA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>3000</v>
+        <v>1480</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>5</v>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>$350</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="G65" t="n">
+        <v>180</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="J65" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>64</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0.8100000000000001</v>
+        <v>10</v>
       </c>
       <c r="M65" t="n">
-        <v>0.8100000000000001</v>
+        <v>10</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="O65" t="n">
-        <v>3.75</v>
+        <v>10</v>
       </c>
       <c r="P65" t="n">
-        <v>1.089</v>
+        <v>9.026</v>
       </c>
       <c r="Q65" t="n">
         <v>3</v>
       </c>
       <c r="R65" t="n">
-        <v>16.21</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>16.87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>We're leaving for 12 hours on a very cold day. How far should I set back the heat?</t>
+          <t>We're done for the day — what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Stroudsburg, PA</t>
+          <t>York, PA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>3000</v>
+        <v>1480</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>5</v>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>$350</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="G66" t="n">
+        <v>180</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="J66" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L66" t="n">
+        <v>10</v>
+      </c>
+      <c r="M66" t="n">
+        <v>10</v>
+      </c>
+      <c r="N66" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="O66" t="n">
+        <v>10</v>
+      </c>
+      <c r="P66" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>1</v>
+      </c>
+      <c r="R66" t="n">
         <v>0</v>
       </c>
-      <c r="M66" t="n">
+      <c r="S66" t="n">
         <v>0</v>
       </c>
-      <c r="N66" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="O66" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="P66" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>2</v>
-      </c>
-      <c r="R66" t="n">
-        <v>17.58</v>
-      </c>
-      <c r="S66" t="n">
-        <v>3.34</v>
-      </c>
       <c r="T66" t="n">
-        <v>18.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>We're leaving for 12 hours on a very cold day. How far should I set back the heat?</t>
+          <t>We're done for the day — what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Stroudsburg, PA</t>
+          <t>York, PA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>3000</v>
+        <v>1480</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>5</v>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>$350</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="G67" t="n">
+        <v>180</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="J67" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L67" t="n">
+        <v>10</v>
+      </c>
+      <c r="M67" t="n">
+        <v>10</v>
+      </c>
+      <c r="N67" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="O67" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="P67" t="n">
+        <v>9.6645</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>2</v>
+      </c>
+      <c r="R67" t="n">
         <v>0</v>
       </c>
-      <c r="M67" t="n">
+      <c r="S67" t="n">
         <v>0</v>
       </c>
-      <c r="N67" t="n">
-        <v>7.34</v>
-      </c>
-      <c r="O67" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="P67" t="n">
-        <v>2.608</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>1</v>
-      </c>
-      <c r="R67" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="S67" t="n">
-        <v>3.69</v>
-      </c>
       <c r="T67" t="n">
-        <v>20.19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>It's a warm day but nothing too bad. What should I set the AC to?</t>
+          <t>With 4 people home, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chambersburg, PA</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1750</v>
+        <v>1320</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>2</v>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>$210</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="G68" t="n">
+        <v>215</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -5438,73 +5304,71 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="J68" t="n">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>6.07</v>
+        <v>10</v>
       </c>
       <c r="M68" t="n">
-        <v>6.12</v>
+        <v>10</v>
       </c>
       <c r="N68" t="n">
-        <v>8.6</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="O68" t="n">
         <v>10</v>
       </c>
       <c r="P68" t="n">
-        <v>7.183</v>
+        <v>9.692</v>
       </c>
       <c r="Q68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R68" t="n">
-        <v>8.35</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>8.52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>It's a warm day but nothing too bad. What should I set the AC to?</t>
+          <t>With 4 people home, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chambersburg, PA</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1750</v>
+        <v>1320</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>2</v>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>$210</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="G69" t="n">
+        <v>215</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -5512,73 +5376,71 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="J69" t="n">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>6.56</v>
+        <v>10</v>
       </c>
       <c r="M69" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="N69" t="n">
-        <v>9.32</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="O69" t="n">
         <v>10</v>
       </c>
       <c r="P69" t="n">
-        <v>7.641999999999999</v>
+        <v>9.692</v>
       </c>
       <c r="Q69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R69" t="n">
-        <v>7.62</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>7.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>It's a warm day but nothing too bad. What should I set the AC to?</t>
+          <t>With 4 people home, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chambersburg, PA</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1750</v>
+        <v>1320</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2</v>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>$210</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="G70" t="n">
+        <v>215</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -5586,717 +5448,699 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="J70" t="n">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>76</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>7.05</v>
+        <v>10</v>
       </c>
       <c r="M70" t="n">
-        <v>7.07</v>
+        <v>10</v>
       </c>
       <c r="N70" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="O70" t="n">
         <v>10</v>
       </c>
       <c r="P70" t="n">
-        <v>7.4895</v>
+        <v>8.9</v>
       </c>
       <c r="Q70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R70" t="n">
-        <v>6.89</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>7.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>It's just slightly warm today and we're home. What AC temperature makes sense?</t>
+          <t>I'm away most of today — what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Stroudsburg, PA</t>
+          <t>Lancaster, PA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>2300</v>
+        <v>1550</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F71" t="n">
         <v>3</v>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>$310</t>
-        </is>
+      <c r="G71" t="n">
+        <v>195</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="J71" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>76</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>5.35</v>
+        <v>7.8</v>
       </c>
       <c r="M71" t="n">
-        <v>5.43</v>
+        <v>7.72</v>
       </c>
       <c r="N71" t="n">
-        <v>7.83</v>
+        <v>10</v>
       </c>
       <c r="O71" t="n">
         <v>10</v>
       </c>
       <c r="P71" t="n">
-        <v>6.5715</v>
+        <v>8.542</v>
       </c>
       <c r="Q71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R71" t="n">
-        <v>9.42</v>
+        <v>5.77</v>
       </c>
       <c r="S71" t="n">
-        <v>1.79</v>
+        <v>1.1</v>
       </c>
       <c r="T71" t="n">
-        <v>9.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>It's just slightly warm today and we're home. What AC temperature makes sense?</t>
+          <t>I'm away most of today — what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Stroudsburg, PA</t>
+          <t>Lancaster, PA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>2300</v>
+        <v>1550</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F72" t="n">
         <v>3</v>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>$310</t>
-        </is>
+      <c r="G72" t="n">
+        <v>195</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="J72" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>80</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>6</v>
+        <v>8.16</v>
       </c>
       <c r="M72" t="n">
-        <v>6.06</v>
+        <v>8.08</v>
       </c>
       <c r="N72" t="n">
-        <v>9.32</v>
+        <v>7</v>
       </c>
       <c r="O72" t="n">
         <v>10</v>
       </c>
       <c r="P72" t="n">
-        <v>7.284999999999999</v>
+        <v>8.176</v>
       </c>
       <c r="Q72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R72" t="n">
-        <v>8.449999999999999</v>
+        <v>5.23</v>
       </c>
       <c r="S72" t="n">
-        <v>1.6</v>
+        <v>0.99</v>
       </c>
       <c r="T72" t="n">
-        <v>8.609999999999999</v>
+        <v>5.44</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>It's just slightly warm today and we're home. What AC temperature makes sense?</t>
+          <t>I'm away most of today — what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Stroudsburg, PA</t>
+          <t>Lancaster, PA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>2300</v>
+        <v>1550</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F73" t="n">
         <v>3</v>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>$310</t>
-        </is>
+      <c r="G73" t="n">
+        <v>195</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="J73" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>83</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>6.49</v>
+        <v>8.43</v>
       </c>
       <c r="M73" t="n">
-        <v>6.53</v>
+        <v>8.35</v>
       </c>
       <c r="N73" t="n">
-        <v>7</v>
+        <v>4.06</v>
       </c>
       <c r="O73" t="n">
-        <v>10</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="P73" t="n">
-        <v>7.1325</v>
+        <v>7.592499999999999</v>
       </c>
       <c r="Q73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R73" t="n">
-        <v>7.72</v>
+        <v>4.82</v>
       </c>
       <c r="S73" t="n">
-        <v>1.47</v>
+        <v>0.92</v>
       </c>
       <c r="T73" t="n">
-        <v>7.87</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>It's a mild autumn evening and the house feels cool. What should I set the heat to?</t>
+          <t>With 1 person home, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Carlisle, PA</t>
+          <t>Wilkes-Barre, PA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1950</v>
+        <v>880</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>3</v>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>$245</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="G74" t="n">
+        <v>145</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="J74" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>74</t>
         </is>
       </c>
       <c r="L74" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="M74" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="N74" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="O74" t="n">
         <v>10</v>
       </c>
-      <c r="M74" t="n">
-        <v>10</v>
-      </c>
-      <c r="N74" t="n">
-        <v>7</v>
-      </c>
-      <c r="O74" t="n">
-        <v>9.630000000000001</v>
-      </c>
       <c r="P74" t="n">
-        <v>9.3445</v>
+        <v>8.763999999999999</v>
       </c>
       <c r="Q74" t="n">
         <v>2</v>
       </c>
       <c r="R74" t="n">
-        <v>1.45</v>
+        <v>4.65</v>
       </c>
       <c r="S74" t="n">
-        <v>0.28</v>
+        <v>0.88</v>
       </c>
       <c r="T74" t="n">
-        <v>1.48</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>It's a mild autumn evening and the house feels cool. What should I set the heat to?</t>
+          <t>With 1 person home, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Carlisle, PA</t>
+          <t>Wilkes-Barre, PA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1950</v>
+        <v>880</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>3</v>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>$245</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="G75" t="n">
+        <v>145</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="J75" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>77</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>10</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="M75" t="n">
-        <v>10</v>
+        <v>8.77</v>
       </c>
       <c r="N75" t="n">
         <v>9.32</v>
       </c>
       <c r="O75" t="n">
-        <v>9.630000000000001</v>
+        <v>10</v>
       </c>
       <c r="P75" t="n">
-        <v>9.8085</v>
+        <v>9.070499999999999</v>
       </c>
       <c r="Q75" t="n">
         <v>1</v>
       </c>
       <c r="R75" t="n">
-        <v>2.35</v>
+        <v>4.28</v>
       </c>
       <c r="S75" t="n">
-        <v>0.45</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="T75" t="n">
-        <v>2.4</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>It's a mild autumn evening and the house feels cool. What should I set the heat to?</t>
+          <t>With 1 person home, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Carlisle, PA</t>
+          <t>Wilkes-Barre, PA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1950</v>
+        <v>880</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>$245</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="G76" t="n">
+        <v>145</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="J76" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>81</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>9.279999999999999</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="M76" t="n">
-        <v>9.23</v>
+        <v>9.09</v>
       </c>
       <c r="N76" t="n">
-        <v>7.83</v>
+        <v>6.11</v>
       </c>
       <c r="O76" t="n">
-        <v>8.859999999999999</v>
+        <v>10</v>
       </c>
       <c r="P76" t="n">
-        <v>8.9095</v>
+        <v>8.6395</v>
       </c>
       <c r="Q76" t="n">
         <v>3</v>
       </c>
       <c r="R76" t="n">
-        <v>3.56</v>
+        <v>3.78</v>
       </c>
       <c r="S76" t="n">
-        <v>0.68</v>
+        <v>0.72</v>
       </c>
       <c r="T76" t="n">
-        <v>3.62</v>
+        <v>3.86</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>The house will be empty for 8 hours on a cool spring day. What heat setting should I use?</t>
+          <t>I'm out running errands all day — what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Lebanon, PA</t>
+          <t>West Chester, PA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>2000</v>
+        <v>2950</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>2</v>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>$195</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="G77" t="n">
+        <v>300</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Single-family</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="J77" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>77</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>9.07</v>
+        <v>5.75</v>
       </c>
       <c r="M77" t="n">
-        <v>8.98</v>
+        <v>5.7</v>
       </c>
       <c r="N77" t="n">
-        <v>6.11</v>
+        <v>9.18</v>
       </c>
       <c r="O77" t="n">
-        <v>8.859999999999999</v>
+        <v>10</v>
       </c>
       <c r="P77" t="n">
-        <v>8.415000000000001</v>
+        <v>7.056</v>
       </c>
       <c r="Q77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R77" t="n">
-        <v>3.86</v>
+        <v>8.82</v>
       </c>
       <c r="S77" t="n">
-        <v>0.73</v>
+        <v>1.68</v>
       </c>
       <c r="T77" t="n">
-        <v>4.02</v>
+        <v>9.19</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>The house will be empty for 8 hours on a cool spring day. What heat setting should I use?</t>
+          <t>I'm out running errands all day — what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Lebanon, PA</t>
+          <t>West Chester, PA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>2000</v>
+        <v>2950</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F78" t="n">
+        <v>5</v>
+      </c>
+      <c r="G78" t="n">
+        <v>300</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Single-family</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>83</v>
+      </c>
+      <c r="J78" t="n">
+        <v>22</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="M78" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="N78" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="O78" t="n">
+        <v>10</v>
+      </c>
+      <c r="P78" t="n">
+        <v>6.625999999999999</v>
+      </c>
+      <c r="Q78" t="n">
         <v>2</v>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>$195</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Apartment</t>
-        </is>
-      </c>
-      <c r="I78" t="n">
-        <v>44</v>
-      </c>
-      <c r="J78" t="n">
-        <v>32</v>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="L78" t="n">
-        <v>8.44</v>
-      </c>
-      <c r="M78" t="n">
-        <v>8.35</v>
-      </c>
-      <c r="N78" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="O78" t="n">
-        <v>8.859999999999999</v>
-      </c>
-      <c r="P78" t="n">
-        <v>8.503499999999999</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>1</v>
-      </c>
       <c r="R78" t="n">
-        <v>4.81</v>
+        <v>7.95</v>
       </c>
       <c r="S78" t="n">
-        <v>0.91</v>
+        <v>1.51</v>
       </c>
       <c r="T78" t="n">
-        <v>5.01</v>
+        <v>8.27</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>The house will be empty for 8 hours on a cool spring day. What heat setting should I use?</t>
+          <t>I'm out running errands all day — what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Lebanon, PA</t>
+          <t>West Chester, PA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>2000</v>
+        <v>2950</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>2</v>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>$195</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="G79" t="n">
+        <v>300</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Single-family</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="J79" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>84</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>7.8</v>
+        <v>6.78</v>
       </c>
       <c r="M79" t="n">
-        <v>7.72</v>
+        <v>6.71</v>
       </c>
       <c r="N79" t="n">
-        <v>9.32</v>
+        <v>0.64</v>
       </c>
       <c r="O79" t="n">
-        <v>8.859999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="P79" t="n">
-        <v>8.234999999999999</v>
+        <v>5.6505</v>
       </c>
       <c r="Q79" t="n">
         <v>3</v>
       </c>
       <c r="R79" t="n">
-        <v>5.76</v>
+        <v>7.29</v>
       </c>
       <c r="S79" t="n">
-        <v>1.09</v>
+        <v>1.38</v>
       </c>
       <c r="T79" t="n">
-        <v>6</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>We're all home on a hot day and debating how cold to keep it. What AC temperature should I set?</t>
+          <t>I'm leaving for work shortly — what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -6305,72 +6149,70 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>2050</v>
+        <v>1180</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>4</v>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>$215</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G80" t="n">
+        <v>175</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Condo</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J80" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>78</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>7.63</v>
       </c>
       <c r="M80" t="n">
-        <v>0.23</v>
+        <v>7.55</v>
       </c>
       <c r="N80" t="n">
-        <v>4.5</v>
+        <v>8.6</v>
       </c>
       <c r="O80" t="n">
-        <v>8.16</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="P80" t="n">
-        <v>2.2045</v>
+        <v>7.980499999999999</v>
       </c>
       <c r="Q80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R80" t="n">
-        <v>17.45</v>
+        <v>6.02</v>
       </c>
       <c r="S80" t="n">
-        <v>3.31</v>
+        <v>1.14</v>
       </c>
       <c r="T80" t="n">
-        <v>17.78</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>We're all home on a hot day and debating how cold to keep it. What AC temperature should I set?</t>
+          <t>I'm leaving for work shortly — what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6379,72 +6221,70 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>2050</v>
+        <v>1180</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>4</v>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>$215</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G81" t="n">
+        <v>175</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Condo</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J81" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>81</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0.28</v>
+        <v>7.82</v>
       </c>
       <c r="M81" t="n">
-        <v>1.38</v>
+        <v>7.75</v>
       </c>
       <c r="N81" t="n">
-        <v>9.25</v>
+        <v>6.11</v>
       </c>
       <c r="O81" t="n">
         <v>9.630000000000001</v>
       </c>
       <c r="P81" t="n">
-        <v>3.8615</v>
+        <v>7.725000000000001</v>
       </c>
       <c r="Q81" t="n">
         <v>2</v>
       </c>
       <c r="R81" t="n">
-        <v>15.67</v>
+        <v>5.73</v>
       </c>
       <c r="S81" t="n">
-        <v>2.98</v>
+        <v>1.09</v>
       </c>
       <c r="T81" t="n">
-        <v>15.98</v>
+        <v>5.96</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>We're all home on a hot day and debating how cold to keep it. What AC temperature should I set?</t>
+          <t>I'm leaving for work shortly — what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6453,94 +6293,90 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>2050</v>
+        <v>1180</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>4</v>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>$215</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G82" t="n">
+        <v>175</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Condo</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J82" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>84</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0.86</v>
+        <v>8.02</v>
       </c>
       <c r="M82" t="n">
-        <v>2.53</v>
+        <v>7.94</v>
       </c>
       <c r="N82" t="n">
-        <v>6.65</v>
+        <v>2.86</v>
       </c>
       <c r="O82" t="n">
-        <v>9.630000000000001</v>
+        <v>7.29</v>
       </c>
       <c r="P82" t="n">
-        <v>3.918</v>
+        <v>6.850499999999999</v>
       </c>
       <c r="Q82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R82" t="n">
-        <v>13.9</v>
+        <v>5.43</v>
       </c>
       <c r="S82" t="n">
-        <v>2.64</v>
+        <v>1.03</v>
       </c>
       <c r="T82" t="n">
-        <v>14.17</v>
+        <v>5.65</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>It's a very cold day and I want to find the best heating setting. What temperature should I use?</t>
+          <t>I'm gone for the entire workday — what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>DuBois, PA</t>
+          <t>Erie, PA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1850</v>
+        <v>1700</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F83" t="n">
         <v>2</v>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>$230</t>
-        </is>
+      <c r="G83" t="n">
+        <v>220</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -6548,73 +6384,71 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J83" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>5.63</v>
+        <v>7.82</v>
       </c>
       <c r="M83" t="n">
-        <v>5.7</v>
+        <v>7.75</v>
       </c>
       <c r="N83" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>7.6</v>
+        <v>3.75</v>
       </c>
       <c r="P83" t="n">
-        <v>5.635999999999999</v>
+        <v>5.621</v>
       </c>
       <c r="Q83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R83" t="n">
-        <v>9.01</v>
+        <v>5.73</v>
       </c>
       <c r="S83" t="n">
-        <v>1.71</v>
+        <v>1.09</v>
       </c>
       <c r="T83" t="n">
-        <v>9.18</v>
+        <v>5.96</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>It's a very cold day and I want to find the best heating setting. What temperature should I use?</t>
+          <t>I'm gone for the entire workday — what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>DuBois, PA</t>
+          <t>Erie, PA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1850</v>
+        <v>1700</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F84" t="n">
         <v>2</v>
       </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>$230</t>
-        </is>
+      <c r="G84" t="n">
+        <v>220</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -6622,73 +6456,71 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>63</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>4.87</v>
+        <v>7.45</v>
       </c>
       <c r="M84" t="n">
-        <v>4.96</v>
+        <v>7.37</v>
       </c>
       <c r="N84" t="n">
-        <v>8.6</v>
+        <v>4.06</v>
       </c>
       <c r="O84" t="n">
         <v>7.6</v>
       </c>
       <c r="P84" t="n">
-        <v>6.057</v>
+        <v>6.7665</v>
       </c>
       <c r="Q84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R84" t="n">
-        <v>10.15</v>
+        <v>6.29</v>
       </c>
       <c r="S84" t="n">
-        <v>1.93</v>
+        <v>1.19</v>
       </c>
       <c r="T84" t="n">
-        <v>10.34</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>It's a very cold day and I want to find the best heating setting. What temperature should I use?</t>
+          <t>I'm gone for the entire workday — what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>DuBois, PA</t>
+          <t>Erie, PA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1850</v>
+        <v>1700</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F85" t="n">
         <v>2</v>
       </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>$230</t>
-        </is>
+      <c r="G85" t="n">
+        <v>220</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -6696,73 +6528,71 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J85" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>3.11</v>
+        <v>7.07</v>
       </c>
       <c r="M85" t="n">
-        <v>3.93</v>
+        <v>7</v>
       </c>
       <c r="N85" t="n">
-        <v>6.11</v>
+        <v>7</v>
       </c>
       <c r="O85" t="n">
         <v>7.6</v>
       </c>
       <c r="P85" t="n">
-        <v>4.6705</v>
+        <v>7.111</v>
       </c>
       <c r="Q85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R85" t="n">
-        <v>11.74</v>
+        <v>6.85</v>
       </c>
       <c r="S85" t="n">
-        <v>2.23</v>
+        <v>1.3</v>
       </c>
       <c r="T85" t="n">
-        <v>11.96</v>
+        <v>7.13</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>We're all out for 8 hours in extreme heat. Should I leave the AC running or just turn it off?</t>
+          <t>I'm working from home today with 3 people — what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Coatesville, PA</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1650</v>
+        <v>1750</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>2</v>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>$200</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="G86" t="n">
+        <v>250</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -6770,73 +6600,71 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="J86" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>73</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>3.86</v>
+        <v>5.53</v>
       </c>
       <c r="M86" t="n">
-        <v>4.74</v>
+        <v>5.6</v>
       </c>
       <c r="N86" t="n">
-        <v>7</v>
+        <v>7.83</v>
       </c>
       <c r="O86" t="n">
         <v>9.630000000000001</v>
       </c>
       <c r="P86" t="n">
-        <v>5.6615</v>
+        <v>6.6295</v>
       </c>
       <c r="Q86" t="n">
         <v>3</v>
       </c>
       <c r="R86" t="n">
-        <v>10.26</v>
+        <v>9.15</v>
       </c>
       <c r="S86" t="n">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="T86" t="n">
-        <v>10.69</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>We're all out for 8 hours in extreme heat. Should I leave the AC running or just turn it off?</t>
+          <t>I'm working from home today with 3 people — what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Coatesville, PA</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1650</v>
+        <v>1750</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>2</v>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>$200</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="G87" t="n">
+        <v>250</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -6844,73 +6672,71 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="J87" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Off (85)</t>
+          <t>76</t>
         </is>
       </c>
       <c r="L87" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="M87" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="N87" t="n">
         <v>10</v>
       </c>
-      <c r="M87" t="n">
-        <v>10</v>
-      </c>
-      <c r="N87" t="n">
-        <v>1.53</v>
-      </c>
       <c r="O87" t="n">
-        <v>5.94</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="P87" t="n">
-        <v>7.697</v>
+        <v>7.267999999999999</v>
       </c>
       <c r="Q87" t="n">
         <v>1</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>8.67</v>
       </c>
       <c r="S87" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="T87" t="n">
-        <v>0</v>
+        <v>8.84</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>We're all out for 8 hours in extreme heat. Should I leave the AC running or just turn it off?</t>
+          <t>I'm working from home today with 3 people — what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Coatesville, PA</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1650</v>
+        <v>1750</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>2</v>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>$200</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="G88" t="n">
+        <v>250</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -6918,73 +6744,71 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="J88" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>79</t>
         </is>
       </c>
       <c r="L88" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="M88" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="N88" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="O88" t="n">
         <v>10</v>
       </c>
-      <c r="M88" t="n">
-        <v>10</v>
-      </c>
-      <c r="N88" t="n">
-        <v>0</v>
-      </c>
-      <c r="O88" t="n">
-        <v>1.51</v>
-      </c>
       <c r="P88" t="n">
-        <v>6.7265</v>
+        <v>7.093999999999999</v>
       </c>
       <c r="Q88" t="n">
         <v>2</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S88" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="T88" t="n">
-        <v>0</v>
+        <v>8.35</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>123</v>
+        <v>89</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>We're leaving for 12 hours on a freezing day. What should I do with the heat?</t>
+          <t>I'm heading out for the day — what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Williamsport, PA</t>
+          <t>West Mifflin, PA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>2300</v>
+        <v>1500</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>3</v>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>$260</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G89" t="n">
+        <v>200</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -6992,73 +6816,71 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="J89" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0.91</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="M89" t="n">
-        <v>1.66</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="N89" t="n">
         <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>1.51</v>
+        <v>3.75</v>
       </c>
       <c r="P89" t="n">
-        <v>1.0805</v>
+        <v>5.8775</v>
       </c>
       <c r="Q89" t="n">
         <v>3</v>
       </c>
       <c r="R89" t="n">
-        <v>14.92</v>
+        <v>5.14</v>
       </c>
       <c r="S89" t="n">
-        <v>2.84</v>
+        <v>0.98</v>
       </c>
       <c r="T89" t="n">
-        <v>15.53</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>123</v>
+        <v>89</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>We're leaving for 12 hours on a freezing day. What should I do with the heat?</t>
+          <t>I'm heading out for the day — what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Williamsport, PA</t>
+          <t>West Mifflin, PA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>2300</v>
+        <v>1500</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>3</v>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>$260</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G90" t="n">
+        <v>200</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -7066,10 +6888,10 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="J90" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -7077,10 +6899,10 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0.17</v>
+        <v>7.82</v>
       </c>
       <c r="M90" t="n">
-        <v>0.45</v>
+        <v>7.74</v>
       </c>
       <c r="N90" t="n">
         <v>4.06</v>
@@ -7089,50 +6911,48 @@
         <v>7.6</v>
       </c>
       <c r="P90" t="n">
-        <v>2.1605</v>
+        <v>7.007</v>
       </c>
       <c r="Q90" t="n">
         <v>2</v>
       </c>
       <c r="R90" t="n">
-        <v>16.75</v>
+        <v>5.73</v>
       </c>
       <c r="S90" t="n">
-        <v>3.18</v>
+        <v>1.09</v>
       </c>
       <c r="T90" t="n">
-        <v>17.43</v>
+        <v>5.97</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123</v>
+        <v>89</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>We're leaving for 12 hours on a freezing day. What should I do with the heat?</t>
+          <t>I'm heading out for the day — what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Williamsport, PA</t>
+          <t>West Mifflin, PA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>2300</v>
+        <v>1500</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>3</v>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>$260</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G91" t="n">
+        <v>200</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -7140,517 +6960,503 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="J91" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Off (50)</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>10</v>
+        <v>7.42</v>
       </c>
       <c r="M91" t="n">
-        <v>10</v>
+        <v>7.35</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O91" t="n">
-        <v>1.51</v>
+        <v>7.6</v>
       </c>
       <c r="P91" t="n">
-        <v>6.7265</v>
+        <v>7.3385</v>
       </c>
       <c r="Q91" t="n">
         <v>1</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>6.32</v>
       </c>
       <c r="S91" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T91" t="n">
-        <v>0</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>I'm heading to bed on a hot summer night. What's the best AC temperature for sleeping?</t>
+          <t>With 4 people home, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Pottstown, PA</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1600</v>
+        <v>2200</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>3</v>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>$185</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="G92" t="n">
+        <v>320</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Rowhouse</t>
+          <t>Single-family</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="J92" t="n">
         <v>28</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>76</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>5.41</v>
+        <v>1.83</v>
       </c>
       <c r="M92" t="n">
-        <v>6.02</v>
+        <v>2.01</v>
       </c>
       <c r="N92" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O92" t="n">
         <v>9.630000000000001</v>
       </c>
       <c r="P92" t="n">
-        <v>6.5745</v>
+        <v>4.697</v>
       </c>
       <c r="Q92" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R92" t="n">
-        <v>8.880000000000001</v>
+        <v>14.69</v>
       </c>
       <c r="S92" t="n">
-        <v>1.69</v>
+        <v>2.79</v>
       </c>
       <c r="T92" t="n">
-        <v>8.67</v>
+        <v>14.97</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>I'm heading to bed on a hot summer night. What's the best AC temperature for sleeping?</t>
+          <t>With 4 people home, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Pottstown, PA</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1600</v>
+        <v>2200</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>3</v>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>$185</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="G93" t="n">
+        <v>320</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Rowhouse</t>
+          <t>Single-family</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="J93" t="n">
         <v>28</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>79</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>6.16</v>
+        <v>2.47</v>
       </c>
       <c r="M93" t="n">
-        <v>6.44</v>
+        <v>2.64</v>
       </c>
       <c r="N93" t="n">
-        <v>9.32</v>
+        <v>7.59</v>
       </c>
       <c r="O93" t="n">
         <v>9.630000000000001</v>
       </c>
       <c r="P93" t="n">
-        <v>7.410500000000001</v>
+        <v>4.6275</v>
       </c>
       <c r="Q93" t="n">
         <v>2</v>
       </c>
       <c r="R93" t="n">
-        <v>8.210000000000001</v>
+        <v>13.72</v>
       </c>
       <c r="S93" t="n">
-        <v>1.56</v>
+        <v>2.61</v>
       </c>
       <c r="T93" t="n">
-        <v>8.01</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>I'm heading to bed on a hot summer night. What's the best AC temperature for sleeping?</t>
+          <t>With 4 people home, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Pottstown, PA</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1600</v>
+        <v>2200</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>3</v>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>$185</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="G94" t="n">
+        <v>320</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Rowhouse</t>
+          <t>Single-family</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="J94" t="n">
         <v>28</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>82</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>6.61</v>
+        <v>3.12</v>
       </c>
       <c r="M94" t="n">
-        <v>6.86</v>
+        <v>3.27</v>
       </c>
       <c r="N94" t="n">
-        <v>8.6</v>
+        <v>4.5</v>
       </c>
       <c r="O94" t="n">
-        <v>10</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="P94" t="n">
-        <v>7.604</v>
+        <v>4.425</v>
       </c>
       <c r="Q94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R94" t="n">
-        <v>7.54</v>
+        <v>12.76</v>
       </c>
       <c r="S94" t="n">
-        <v>1.43</v>
+        <v>2.42</v>
       </c>
       <c r="T94" t="n">
-        <v>7.36</v>
+        <v>13.01</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>It's a cold night and I'm setting the heat before bed. What temperature is best for sleeping?</t>
+          <t>I'm gone most of the day — what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Oil City, PA</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>2050</v>
+        <v>1350</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>2</v>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>$240</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="G95" t="n">
+        <v>210</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Rowhouse</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J95" t="n">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>5.66</v>
+        <v>4.37</v>
       </c>
       <c r="M95" t="n">
-        <v>5.98</v>
+        <v>4.75</v>
       </c>
       <c r="N95" t="n">
-        <v>6.11</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>7.6</v>
+        <v>3.75</v>
       </c>
       <c r="P95" t="n">
-        <v>6.153</v>
+        <v>3.536</v>
       </c>
       <c r="Q95" t="n">
         <v>3</v>
       </c>
       <c r="R95" t="n">
-        <v>8.949999999999999</v>
+        <v>10.26</v>
       </c>
       <c r="S95" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="T95" t="n">
-        <v>8.74</v>
+        <v>10.68</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>It's a cold night and I'm setting the heat before bed. What temperature is best for sleeping?</t>
+          <t>I'm gone most of the day — what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Oil City, PA</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>2050</v>
+        <v>1350</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>2</v>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>$240</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="G96" t="n">
+        <v>210</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Rowhouse</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J96" t="n">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>64</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>5.21</v>
+        <v>2.72</v>
       </c>
       <c r="M96" t="n">
-        <v>5.55</v>
+        <v>3.98</v>
       </c>
       <c r="N96" t="n">
-        <v>8.6</v>
+        <v>5.13</v>
       </c>
       <c r="O96" t="n">
         <v>7.6</v>
       </c>
       <c r="P96" t="n">
-        <v>6.365499999999999</v>
+        <v>4.375</v>
       </c>
       <c r="Q96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R96" t="n">
-        <v>9.640000000000001</v>
+        <v>11.41</v>
       </c>
       <c r="S96" t="n">
-        <v>1.83</v>
+        <v>2.17</v>
       </c>
       <c r="T96" t="n">
-        <v>9.41</v>
+        <v>11.88</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>It's a cold night and I'm setting the heat before bed. What temperature is best for sleeping?</t>
+          <t>I'm gone most of the day — what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Oil City, PA</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>2050</v>
+        <v>1350</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>2</v>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>$240</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="G97" t="n">
+        <v>210</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Rowhouse</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J97" t="n">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>4.75</v>
+        <v>1.52</v>
       </c>
       <c r="M97" t="n">
-        <v>5.13</v>
+        <v>3.22</v>
       </c>
       <c r="N97" t="n">
-        <v>9.32</v>
+        <v>8.6</v>
       </c>
       <c r="O97" t="n">
         <v>7.6</v>
       </c>
       <c r="P97" t="n">
-        <v>6.2245</v>
+        <v>4.443</v>
       </c>
       <c r="Q97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R97" t="n">
-        <v>10.32</v>
+        <v>12.56</v>
       </c>
       <c r="S97" t="n">
-        <v>1.96</v>
+        <v>2.39</v>
       </c>
       <c r="T97" t="n">
-        <v>10.08</v>
+        <v>13.08</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>We just installed a new high-efficiency AC and it's a warm day. What temperature is ideal?</t>
+          <t>We're winding down for the night — what AC temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Phoenixville, PA</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>2350</v>
+        <v>2050</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>4</v>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>$420</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="G98" t="n">
+        <v>220</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -7658,10 +7464,10 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J98" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -7669,62 +7475,60 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>5.52</v>
+        <v>4.16</v>
       </c>
       <c r="M98" t="n">
-        <v>5.59</v>
+        <v>4.9</v>
       </c>
       <c r="N98" t="n">
-        <v>6.65</v>
+        <v>7</v>
       </c>
       <c r="O98" t="n">
         <v>9.630000000000001</v>
       </c>
       <c r="P98" t="n">
-        <v>6.387</v>
+        <v>5.807500000000001</v>
       </c>
       <c r="Q98" t="n">
         <v>3</v>
       </c>
       <c r="R98" t="n">
-        <v>9.17</v>
+        <v>10.69</v>
       </c>
       <c r="S98" t="n">
-        <v>1.74</v>
+        <v>2.03</v>
       </c>
       <c r="T98" t="n">
-        <v>9.35</v>
+        <v>10.43</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>We just installed a new high-efficiency AC and it's a warm day. What temperature is ideal?</t>
+          <t>We're winding down for the night — what AC temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Phoenixville, PA</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>2350</v>
+        <v>2050</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>4</v>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>$420</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="G99" t="n">
+        <v>220</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -7732,73 +7536,71 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J99" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>75</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>5.99</v>
+        <v>4.98</v>
       </c>
       <c r="M99" t="n">
-        <v>6.05</v>
+        <v>5.34</v>
       </c>
       <c r="N99" t="n">
-        <v>10</v>
+        <v>9.32</v>
       </c>
       <c r="O99" t="n">
         <v>9.630000000000001</v>
       </c>
       <c r="P99" t="n">
-        <v>7.359</v>
+        <v>6.6715</v>
       </c>
       <c r="Q99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R99" t="n">
-        <v>8.470000000000001</v>
+        <v>9.98</v>
       </c>
       <c r="S99" t="n">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="T99" t="n">
-        <v>8.630000000000001</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>We just installed a new high-efficiency AC and it's a warm day. What temperature is ideal?</t>
+          <t>We're winding down for the night — what AC temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Phoenixville, PA</t>
+          <t>Pittsburgh, PA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>2350</v>
+        <v>2050</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>4</v>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>$420</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="G100" t="n">
+        <v>220</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -7806,56 +7608,56 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J100" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>78</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>6.35</v>
+        <v>5.45</v>
       </c>
       <c r="M100" t="n">
-        <v>6.39</v>
+        <v>5.78</v>
       </c>
       <c r="N100" t="n">
-        <v>7.59</v>
+        <v>8.6</v>
       </c>
       <c r="O100" t="n">
         <v>10</v>
       </c>
       <c r="P100" t="n">
-        <v>7.1595</v>
+        <v>6.878</v>
       </c>
       <c r="Q100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R100" t="n">
-        <v>7.94</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="S100" t="n">
-        <v>1.51</v>
+        <v>1.76</v>
       </c>
       <c r="T100" t="n">
-        <v>8.09</v>
+        <v>9.050000000000001</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>On a mild spring day, what thermostat setting keeps the house comfortable without wasting energy?</t>
+          <t>I'm setting the thermostat for bedtime during a spring cold snap. What heat temperature is best for sleeping?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Blue Bell, PA</t>
+          <t>Harrisburg, PA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -7867,69 +7669,67 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>3</v>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>$240</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G101" t="n">
+        <v>230</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Condo</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="J101" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>64</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>10</v>
+        <v>9.83</v>
       </c>
       <c r="M101" t="n">
-        <v>10</v>
+        <v>9.84</v>
       </c>
       <c r="N101" t="n">
-        <v>8.6</v>
+        <v>5.13</v>
       </c>
       <c r="O101" t="n">
-        <v>10</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="P101" t="n">
-        <v>9.720000000000001</v>
+        <v>8.747999999999999</v>
       </c>
       <c r="Q101" t="n">
         <v>3</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S101" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="T101" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>On a mild spring day, what thermostat setting keeps the house comfortable without wasting energy?</t>
+          <t>I'm setting the thermostat for bedtime during a spring cold snap. What heat temperature is best for sleeping?</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Blue Bell, PA</t>
+          <t>Harrisburg, PA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -7941,69 +7741,67 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>3</v>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>$240</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G102" t="n">
+        <v>230</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Condo</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="J102" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>67</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="M102" t="n">
-        <v>10</v>
+        <v>9.56</v>
       </c>
       <c r="N102" t="n">
-        <v>10</v>
+        <v>7.83</v>
       </c>
       <c r="O102" t="n">
-        <v>10</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="P102" t="n">
-        <v>10</v>
+        <v>9.097</v>
       </c>
       <c r="Q102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="S102" t="n">
-        <v>0</v>
+        <v>0.61</v>
       </c>
       <c r="T102" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>On a mild spring day, what thermostat setting keeps the house comfortable without wasting energy?</t>
+          <t>I'm setting the thermostat for bedtime during a spring cold snap. What heat temperature is best for sleeping?</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Blue Bell, PA</t>
+          <t>Harrisburg, PA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -8015,73 +7813,71 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>3</v>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>$240</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G103" t="n">
+        <v>230</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Condo</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="J103" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>70</t>
         </is>
       </c>
       <c r="L103" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="M103" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="N103" t="n">
         <v>10</v>
       </c>
-      <c r="M103" t="n">
-        <v>10</v>
-      </c>
-      <c r="N103" t="n">
-        <v>8.6</v>
-      </c>
       <c r="O103" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="P103" t="n">
-        <v>9.720000000000001</v>
+        <v>9.154</v>
       </c>
       <c r="Q103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S103" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="T103" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>It's a mild early evening. What indoor temperature should I use to stay comfortable?</t>
+          <t>It's a very humid summer night and we're going to sleep. What AC temperature should I use?</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>West Chester, PA</t>
+          <t>York, PA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>2100</v>
+        <v>1450</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -8089,73 +7885,71 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>4</v>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>$300</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="G104" t="n">
+        <v>240</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Condo</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="J104" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>74</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>10</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="M104" t="n">
-        <v>10</v>
+        <v>8.49</v>
       </c>
       <c r="N104" t="n">
-        <v>8.460000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="O104" t="n">
-        <v>10</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="P104" t="n">
-        <v>9.692</v>
+        <v>8.647</v>
       </c>
       <c r="Q104" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="S104" t="n">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="T104" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>It's a mild early evening. What indoor temperature should I use to stay comfortable?</t>
+          <t>It's a very humid summer night and we're going to sleep. What AC temperature should I use?</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>West Chester, PA</t>
+          <t>York, PA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>2100</v>
+        <v>1450</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -8163,73 +7957,71 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>4</v>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>$300</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="G105" t="n">
+        <v>240</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Condo</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="J105" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>76</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>10</v>
+        <v>8.48</v>
       </c>
       <c r="M105" t="n">
-        <v>10</v>
+        <v>8.59</v>
       </c>
       <c r="N105" t="n">
         <v>10</v>
       </c>
       <c r="O105" t="n">
-        <v>10</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="P105" t="n">
-        <v>10</v>
+        <v>8.994999999999999</v>
       </c>
       <c r="Q105" t="n">
         <v>1</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="S105" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="T105" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>It's a mild early evening. What indoor temperature should I use to stay comfortable?</t>
+          <t>It's a very humid summer night and we're going to sleep. What AC temperature should I use?</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>West Chester, PA</t>
+          <t>York, PA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>2100</v>
+        <v>1450</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -8237,55 +8029,53 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>4</v>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>$300</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="G106" t="n">
+        <v>240</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Single-family</t>
+          <t>Condo</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="J106" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>79</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>10</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="M106" t="n">
-        <v>10</v>
+        <v>8.75</v>
       </c>
       <c r="N106" t="n">
-        <v>7.59</v>
+        <v>7.83</v>
       </c>
       <c r="O106" t="n">
         <v>10</v>
       </c>
       <c r="P106" t="n">
-        <v>9.518000000000001</v>
+        <v>8.720500000000001</v>
       </c>
       <c r="Q106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="S106" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="T106" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
     </row>
   </sheetData>

--- a/workbooks/scenarios/HVACRagScenarios.xlsx
+++ b/workbooks/scenarios/HVACRagScenarios.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/workbooks/scenarios/HVACRagScenarios.xlsx
+++ b/workbooks/scenarios/HVACRagScenarios.xlsx
@@ -554,8 +554,10 @@
       <c r="I2" t="n">
         <v>93</v>
       </c>
-      <c r="J2" t="n">
-        <v>12</v>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -626,8 +628,10 @@
       <c r="I3" t="n">
         <v>93</v>
       </c>
-      <c r="J3" t="n">
-        <v>12</v>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -698,8 +702,10 @@
       <c r="I4" t="n">
         <v>93</v>
       </c>
-      <c r="J4" t="n">
-        <v>12</v>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -770,8 +776,10 @@
       <c r="I5" t="n">
         <v>23</v>
       </c>
-      <c r="J5" t="n">
-        <v>21</v>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -842,8 +850,10 @@
       <c r="I6" t="n">
         <v>23</v>
       </c>
-      <c r="J6" t="n">
-        <v>21</v>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -914,8 +924,10 @@
       <c r="I7" t="n">
         <v>23</v>
       </c>
-      <c r="J7" t="n">
-        <v>21</v>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -986,8 +998,10 @@
       <c r="I8" t="n">
         <v>21</v>
       </c>
-      <c r="J8" t="n">
-        <v>25</v>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1058,8 +1072,10 @@
       <c r="I9" t="n">
         <v>21</v>
       </c>
-      <c r="J9" t="n">
-        <v>25</v>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1130,8 +1146,10 @@
       <c r="I10" t="n">
         <v>21</v>
       </c>
-      <c r="J10" t="n">
-        <v>25</v>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1202,8 +1220,10 @@
       <c r="I11" t="n">
         <v>88</v>
       </c>
-      <c r="J11" t="n">
-        <v>26</v>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1274,8 +1294,10 @@
       <c r="I12" t="n">
         <v>88</v>
       </c>
-      <c r="J12" t="n">
-        <v>26</v>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1346,8 +1368,10 @@
       <c r="I13" t="n">
         <v>88</v>
       </c>
-      <c r="J13" t="n">
-        <v>26</v>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1418,8 +1442,10 @@
       <c r="I14" t="n">
         <v>92</v>
       </c>
-      <c r="J14" t="n">
-        <v>25</v>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1490,8 +1516,10 @@
       <c r="I15" t="n">
         <v>92</v>
       </c>
-      <c r="J15" t="n">
-        <v>25</v>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1562,8 +1590,10 @@
       <c r="I16" t="n">
         <v>92</v>
       </c>
-      <c r="J16" t="n">
-        <v>25</v>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1634,8 +1664,10 @@
       <c r="I17" t="n">
         <v>18</v>
       </c>
-      <c r="J17" t="n">
-        <v>60</v>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1706,8 +1738,10 @@
       <c r="I18" t="n">
         <v>18</v>
       </c>
-      <c r="J18" t="n">
-        <v>60</v>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1778,8 +1812,10 @@
       <c r="I19" t="n">
         <v>18</v>
       </c>
-      <c r="J19" t="n">
-        <v>60</v>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1850,8 +1886,10 @@
       <c r="I20" t="n">
         <v>89</v>
       </c>
-      <c r="J20" t="n">
-        <v>18</v>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1922,8 +1960,10 @@
       <c r="I21" t="n">
         <v>89</v>
       </c>
-      <c r="J21" t="n">
-        <v>18</v>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1994,8 +2034,10 @@
       <c r="I22" t="n">
         <v>89</v>
       </c>
-      <c r="J22" t="n">
-        <v>18</v>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -2066,8 +2108,10 @@
       <c r="I23" t="n">
         <v>20</v>
       </c>
-      <c r="J23" t="n">
-        <v>18</v>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -2138,8 +2182,10 @@
       <c r="I24" t="n">
         <v>20</v>
       </c>
-      <c r="J24" t="n">
-        <v>18</v>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -2210,8 +2256,10 @@
       <c r="I25" t="n">
         <v>20</v>
       </c>
-      <c r="J25" t="n">
-        <v>18</v>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -2282,8 +2330,10 @@
       <c r="I26" t="n">
         <v>22</v>
       </c>
-      <c r="J26" t="n">
-        <v>11</v>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -2354,8 +2404,10 @@
       <c r="I27" t="n">
         <v>22</v>
       </c>
-      <c r="J27" t="n">
-        <v>11</v>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2426,8 +2478,10 @@
       <c r="I28" t="n">
         <v>22</v>
       </c>
-      <c r="J28" t="n">
-        <v>11</v>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2498,8 +2552,10 @@
       <c r="I29" t="n">
         <v>17</v>
       </c>
-      <c r="J29" t="n">
-        <v>9</v>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -2570,8 +2626,10 @@
       <c r="I30" t="n">
         <v>17</v>
       </c>
-      <c r="J30" t="n">
-        <v>9</v>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2642,8 +2700,10 @@
       <c r="I31" t="n">
         <v>17</v>
       </c>
-      <c r="J31" t="n">
-        <v>9</v>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2714,8 +2774,10 @@
       <c r="I32" t="n">
         <v>79</v>
       </c>
-      <c r="J32" t="n">
-        <v>8</v>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2786,8 +2848,10 @@
       <c r="I33" t="n">
         <v>79</v>
       </c>
-      <c r="J33" t="n">
-        <v>8</v>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2858,8 +2922,10 @@
       <c r="I34" t="n">
         <v>79</v>
       </c>
-      <c r="J34" t="n">
-        <v>8</v>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2930,8 +2996,10 @@
       <c r="I35" t="n">
         <v>90</v>
       </c>
-      <c r="J35" t="n">
-        <v>28</v>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -3002,8 +3070,10 @@
       <c r="I36" t="n">
         <v>90</v>
       </c>
-      <c r="J36" t="n">
-        <v>28</v>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -3074,8 +3144,10 @@
       <c r="I37" t="n">
         <v>90</v>
       </c>
-      <c r="J37" t="n">
-        <v>28</v>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -3146,8 +3218,10 @@
       <c r="I38" t="n">
         <v>92</v>
       </c>
-      <c r="J38" t="n">
-        <v>14</v>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -3218,8 +3292,10 @@
       <c r="I39" t="n">
         <v>92</v>
       </c>
-      <c r="J39" t="n">
-        <v>14</v>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -3290,8 +3366,10 @@
       <c r="I40" t="n">
         <v>92</v>
       </c>
-      <c r="J40" t="n">
-        <v>14</v>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3362,8 +3440,10 @@
       <c r="I41" t="n">
         <v>18</v>
       </c>
-      <c r="J41" t="n">
-        <v>25</v>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -3434,8 +3514,10 @@
       <c r="I42" t="n">
         <v>18</v>
       </c>
-      <c r="J42" t="n">
-        <v>25</v>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -3506,8 +3588,10 @@
       <c r="I43" t="n">
         <v>18</v>
       </c>
-      <c r="J43" t="n">
-        <v>25</v>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -3578,8 +3662,10 @@
       <c r="I44" t="n">
         <v>77</v>
       </c>
-      <c r="J44" t="n">
-        <v>22</v>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -3650,8 +3736,10 @@
       <c r="I45" t="n">
         <v>77</v>
       </c>
-      <c r="J45" t="n">
-        <v>22</v>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -3722,8 +3810,10 @@
       <c r="I46" t="n">
         <v>77</v>
       </c>
-      <c r="J46" t="n">
-        <v>22</v>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -3794,8 +3884,10 @@
       <c r="I47" t="n">
         <v>44</v>
       </c>
-      <c r="J47" t="n">
-        <v>32</v>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -3866,8 +3958,10 @@
       <c r="I48" t="n">
         <v>44</v>
       </c>
-      <c r="J48" t="n">
-        <v>32</v>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -3938,8 +4032,10 @@
       <c r="I49" t="n">
         <v>44</v>
       </c>
-      <c r="J49" t="n">
-        <v>32</v>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -4010,8 +4106,10 @@
       <c r="I50" t="n">
         <v>10</v>
       </c>
-      <c r="J50" t="n">
-        <v>33</v>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -4082,8 +4180,10 @@
       <c r="I51" t="n">
         <v>10</v>
       </c>
-      <c r="J51" t="n">
-        <v>33</v>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -4154,8 +4254,10 @@
       <c r="I52" t="n">
         <v>10</v>
       </c>
-      <c r="J52" t="n">
-        <v>33</v>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -4226,8 +4328,10 @@
       <c r="I53" t="n">
         <v>5</v>
       </c>
-      <c r="J53" t="n">
-        <v>11</v>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -4298,8 +4402,10 @@
       <c r="I54" t="n">
         <v>5</v>
       </c>
-      <c r="J54" t="n">
-        <v>11</v>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -4370,8 +4476,10 @@
       <c r="I55" t="n">
         <v>5</v>
       </c>
-      <c r="J55" t="n">
-        <v>11</v>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -4442,8 +4550,10 @@
       <c r="I56" t="n">
         <v>50</v>
       </c>
-      <c r="J56" t="n">
-        <v>9</v>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -4514,8 +4624,10 @@
       <c r="I57" t="n">
         <v>50</v>
       </c>
-      <c r="J57" t="n">
-        <v>9</v>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -4586,8 +4698,10 @@
       <c r="I58" t="n">
         <v>50</v>
       </c>
-      <c r="J58" t="n">
-        <v>9</v>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -4658,8 +4772,10 @@
       <c r="I59" t="n">
         <v>54</v>
       </c>
-      <c r="J59" t="n">
-        <v>52</v>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -4730,8 +4846,10 @@
       <c r="I60" t="n">
         <v>54</v>
       </c>
-      <c r="J60" t="n">
-        <v>52</v>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -4802,8 +4920,10 @@
       <c r="I61" t="n">
         <v>54</v>
       </c>
-      <c r="J61" t="n">
-        <v>52</v>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -4874,8 +4994,10 @@
       <c r="I62" t="n">
         <v>62</v>
       </c>
-      <c r="J62" t="n">
-        <v>24</v>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -4946,8 +5068,10 @@
       <c r="I63" t="n">
         <v>62</v>
       </c>
-      <c r="J63" t="n">
-        <v>24</v>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -5018,8 +5142,10 @@
       <c r="I64" t="n">
         <v>62</v>
       </c>
-      <c r="J64" t="n">
-        <v>24</v>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -5090,8 +5216,10 @@
       <c r="I65" t="n">
         <v>59</v>
       </c>
-      <c r="J65" t="n">
-        <v>35</v>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -5162,8 +5290,10 @@
       <c r="I66" t="n">
         <v>59</v>
       </c>
-      <c r="J66" t="n">
-        <v>35</v>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -5234,8 +5364,10 @@
       <c r="I67" t="n">
         <v>59</v>
       </c>
-      <c r="J67" t="n">
-        <v>35</v>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -5306,8 +5438,10 @@
       <c r="I68" t="n">
         <v>72</v>
       </c>
-      <c r="J68" t="n">
-        <v>74</v>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -5378,8 +5512,10 @@
       <c r="I69" t="n">
         <v>72</v>
       </c>
-      <c r="J69" t="n">
-        <v>74</v>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -5450,8 +5586,10 @@
       <c r="I70" t="n">
         <v>72</v>
       </c>
-      <c r="J70" t="n">
-        <v>74</v>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -5522,8 +5660,10 @@
       <c r="I71" t="n">
         <v>82</v>
       </c>
-      <c r="J71" t="n">
-        <v>31</v>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -5594,8 +5734,10 @@
       <c r="I72" t="n">
         <v>82</v>
       </c>
-      <c r="J72" t="n">
-        <v>31</v>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -5666,8 +5808,10 @@
       <c r="I73" t="n">
         <v>82</v>
       </c>
-      <c r="J73" t="n">
-        <v>31</v>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -5738,8 +5882,10 @@
       <c r="I74" t="n">
         <v>80</v>
       </c>
-      <c r="J74" t="n">
-        <v>44</v>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -5810,8 +5956,10 @@
       <c r="I75" t="n">
         <v>80</v>
       </c>
-      <c r="J75" t="n">
-        <v>44</v>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -5882,8 +6030,10 @@
       <c r="I76" t="n">
         <v>80</v>
       </c>
-      <c r="J76" t="n">
-        <v>44</v>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -5954,8 +6104,10 @@
       <c r="I77" t="n">
         <v>83</v>
       </c>
-      <c r="J77" t="n">
-        <v>22</v>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -6026,8 +6178,10 @@
       <c r="I78" t="n">
         <v>83</v>
       </c>
-      <c r="J78" t="n">
-        <v>22</v>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -6098,8 +6252,10 @@
       <c r="I79" t="n">
         <v>83</v>
       </c>
-      <c r="J79" t="n">
-        <v>22</v>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -6170,8 +6326,10 @@
       <c r="I80" t="n">
         <v>98</v>
       </c>
-      <c r="J80" t="n">
-        <v>26</v>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -6242,8 +6400,10 @@
       <c r="I81" t="n">
         <v>98</v>
       </c>
-      <c r="J81" t="n">
-        <v>26</v>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -6314,8 +6474,10 @@
       <c r="I82" t="n">
         <v>98</v>
       </c>
-      <c r="J82" t="n">
-        <v>26</v>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -6386,8 +6548,10 @@
       <c r="I83" t="n">
         <v>18</v>
       </c>
-      <c r="J83" t="n">
-        <v>25</v>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -6458,8 +6622,10 @@
       <c r="I84" t="n">
         <v>18</v>
       </c>
-      <c r="J84" t="n">
-        <v>25</v>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -6530,8 +6696,10 @@
       <c r="I85" t="n">
         <v>18</v>
       </c>
-      <c r="J85" t="n">
-        <v>25</v>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -6602,8 +6770,10 @@
       <c r="I86" t="n">
         <v>87</v>
       </c>
-      <c r="J86" t="n">
-        <v>15</v>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -6674,8 +6844,10 @@
       <c r="I87" t="n">
         <v>87</v>
       </c>
-      <c r="J87" t="n">
-        <v>15</v>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -6746,8 +6918,10 @@
       <c r="I88" t="n">
         <v>87</v>
       </c>
-      <c r="J88" t="n">
-        <v>15</v>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -6818,8 +6992,10 @@
       <c r="I89" t="n">
         <v>22</v>
       </c>
-      <c r="J89" t="n">
-        <v>30</v>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -6890,8 +7066,10 @@
       <c r="I90" t="n">
         <v>22</v>
       </c>
-      <c r="J90" t="n">
-        <v>30</v>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -6962,8 +7140,10 @@
       <c r="I91" t="n">
         <v>22</v>
       </c>
-      <c r="J91" t="n">
-        <v>30</v>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -7034,8 +7214,10 @@
       <c r="I92" t="n">
         <v>92</v>
       </c>
-      <c r="J92" t="n">
-        <v>28</v>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -7106,8 +7288,10 @@
       <c r="I93" t="n">
         <v>92</v>
       </c>
-      <c r="J93" t="n">
-        <v>28</v>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -7178,8 +7362,10 @@
       <c r="I94" t="n">
         <v>92</v>
       </c>
-      <c r="J94" t="n">
-        <v>28</v>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -7250,8 +7436,10 @@
       <c r="I95" t="n">
         <v>12</v>
       </c>
-      <c r="J95" t="n">
-        <v>68</v>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -7322,8 +7510,10 @@
       <c r="I96" t="n">
         <v>12</v>
       </c>
-      <c r="J96" t="n">
-        <v>68</v>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -7394,8 +7584,10 @@
       <c r="I97" t="n">
         <v>12</v>
       </c>
-      <c r="J97" t="n">
-        <v>68</v>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -7466,8 +7658,10 @@
       <c r="I98" t="n">
         <v>87</v>
       </c>
-      <c r="J98" t="n">
-        <v>33</v>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -7538,8 +7732,10 @@
       <c r="I99" t="n">
         <v>87</v>
       </c>
-      <c r="J99" t="n">
-        <v>33</v>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -7610,8 +7806,10 @@
       <c r="I100" t="n">
         <v>87</v>
       </c>
-      <c r="J100" t="n">
-        <v>33</v>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
@@ -7682,8 +7880,10 @@
       <c r="I101" t="n">
         <v>34</v>
       </c>
-      <c r="J101" t="n">
-        <v>30</v>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
@@ -7754,8 +7954,10 @@
       <c r="I102" t="n">
         <v>34</v>
       </c>
-      <c r="J102" t="n">
-        <v>30</v>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -7826,8 +8028,10 @@
       <c r="I103" t="n">
         <v>34</v>
       </c>
-      <c r="J103" t="n">
-        <v>30</v>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -7898,8 +8102,10 @@
       <c r="I104" t="n">
         <v>86</v>
       </c>
-      <c r="J104" t="n">
-        <v>18</v>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -7970,8 +8176,10 @@
       <c r="I105" t="n">
         <v>86</v>
       </c>
-      <c r="J105" t="n">
-        <v>18</v>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -8042,8 +8250,10 @@
       <c r="I106" t="n">
         <v>86</v>
       </c>
-      <c r="J106" t="n">
-        <v>18</v>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>

--- a/workbooks/scenarios/HVACRagScenarios.xlsx
+++ b/workbooks/scenarios/HVACRagScenarios.xlsx
@@ -524,7 +524,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>I'm heading out for a quick errand — what AC temperature should I set for the townhouse?</t>
+          <t>I'm heading out for a quick errand, what AC temperature should I set for the townhouse?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>I'm heading out for a quick errand — what AC temperature should I set for the townhouse?</t>
+          <t>I'm heading out for a quick errand, what AC temperature should I set for the townhouse?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>I'm heading out for a quick errand — what AC temperature should I set for the townhouse?</t>
+          <t>I'm heading out for a quick errand, what AC temperature should I set for the townhouse?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>We're just getting in for the night — what heat temperature should I set overnight?</t>
+          <t>We're just getting in for the night, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>We're just getting in for the night — what heat temperature should I set overnight?</t>
+          <t>We're just getting in for the night, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>We're just getting in for the night — what heat temperature should I set overnight?</t>
+          <t>We're just getting in for the night, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>We're done for the day — what heat temperature should I set overnight?</t>
+          <t>We're done for the day, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>We're done for the day — what heat temperature should I set overnight?</t>
+          <t>We're done for the day, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>We're done for the day — what heat temperature should I set overnight?</t>
+          <t>We're done for the day, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>I'm sticking around the house with 2 people — what AC temperature should I set?</t>
+          <t>I'm sticking around the house with 2 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>I'm sticking around the house with 2 people — what AC temperature should I set?</t>
+          <t>I'm sticking around the house with 2 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>I'm sticking around the house with 2 people — what AC temperature should I set?</t>
+          <t>I'm sticking around the house with 2 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>I'm heading out and won't be back for hours — what AC temperature should I set?</t>
+          <t>I'm heading out and won't be back for hours, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>I'm heading out and won't be back for hours — what AC temperature should I set?</t>
+          <t>I'm heading out and won't be back for hours, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>I'm heading out and won't be back for hours — what AC temperature should I set?</t>
+          <t>I'm heading out and won't be back for hours, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>I'm spending the day at home with 3 people — what AC temperature should I set?</t>
+          <t>I'm spending the day at home with 3 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>I'm spending the day at home with 3 people — what AC temperature should I set?</t>
+          <t>I'm spending the day at home with 3 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>I'm spending the day at home with 3 people — what AC temperature should I set?</t>
+          <t>I'm spending the day at home with 3 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>I'm heading out for the day — what heat temperature should I set?</t>
+          <t>I'm heading out for the day, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>I'm heading out for the day — what heat temperature should I set?</t>
+          <t>I'm heading out for the day, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>I'm heading out for the day — what heat temperature should I set?</t>
+          <t>I'm heading out for the day, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>We're just getting in for the night — what heat temperature should I set overnight?</t>
+          <t>We're just getting in for the night, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>We're just getting in for the night — what heat temperature should I set overnight?</t>
+          <t>We're just getting in for the night, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>We're just getting in for the night — what heat temperature should I set overnight?</t>
+          <t>We're just getting in for the night, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>I'm stepping out for a few hours — what heat temperature should I set for the condo?</t>
+          <t>I'm stepping out for a few hours, what heat temperature should I set for the condo?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>I'm stepping out for a few hours — what heat temperature should I set for the condo?</t>
+          <t>I'm stepping out for a few hours, what heat temperature should I set for the condo?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>I'm stepping out for a few hours — what heat temperature should I set for the condo?</t>
+          <t>I'm stepping out for a few hours, what heat temperature should I set for the condo?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>I'm staying put today with 1 person — what heat temperature should I set?</t>
+          <t>I'm staying put today with 1 person, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>I'm staying put today with 1 person — what heat temperature should I set?</t>
+          <t>I'm staying put today with 1 person, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>I'm staying put today with 1 person — what heat temperature should I set?</t>
+          <t>I'm staying put today with 1 person, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>We're done for the day — what heat temperature should I set overnight?</t>
+          <t>We're done for the day, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>We're done for the day — what heat temperature should I set overnight?</t>
+          <t>We're done for the day, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>We're done for the day — what heat temperature should I set overnight?</t>
+          <t>We're done for the day, what heat temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>I'm away most of today — what AC temperature should I set?</t>
+          <t>I'm away most of today, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>I'm away most of today — what AC temperature should I set?</t>
+          <t>I'm away most of today, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>I'm away most of today — what AC temperature should I set?</t>
+          <t>I'm away most of today, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>I'm out running errands all day — what AC temperature should I set?</t>
+          <t>I'm out running errands all day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>I'm out running errands all day — what AC temperature should I set?</t>
+          <t>I'm out running errands all day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>I'm out running errands all day — what AC temperature should I set?</t>
+          <t>I'm out running errands all day, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>I'm leaving for work shortly — what AC temperature should I set?</t>
+          <t>I'm leaving for work shortly, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>I'm leaving for work shortly — what AC temperature should I set?</t>
+          <t>I'm leaving for work shortly, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>I'm leaving for work shortly — what AC temperature should I set?</t>
+          <t>I'm leaving for work shortly, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>I'm gone for the entire workday — what heat temperature should I set?</t>
+          <t>I'm gone for the entire workday, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -6592,7 +6592,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>I'm gone for the entire workday — what heat temperature should I set?</t>
+          <t>I'm gone for the entire workday, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -6666,7 +6666,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>I'm gone for the entire workday — what heat temperature should I set?</t>
+          <t>I'm gone for the entire workday, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6740,7 +6740,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>I'm working from home today with 3 people — what AC temperature should I set?</t>
+          <t>I'm working from home today with 3 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>I'm working from home today with 3 people — what AC temperature should I set?</t>
+          <t>I'm working from home today with 3 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>I'm working from home today with 3 people — what AC temperature should I set?</t>
+          <t>I'm working from home today with 3 people, what AC temperature should I set?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>I'm heading out for the day — what heat temperature should I set?</t>
+          <t>I'm heading out for the day, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>I'm heading out for the day — what heat temperature should I set?</t>
+          <t>I'm heading out for the day, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>I'm heading out for the day — what heat temperature should I set?</t>
+          <t>I'm heading out for the day, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>I'm gone most of the day — what heat temperature should I set?</t>
+          <t>I'm gone most of the day, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>I'm gone most of the day — what heat temperature should I set?</t>
+          <t>I'm gone most of the day, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>I'm gone most of the day — what heat temperature should I set?</t>
+          <t>I'm gone most of the day, what heat temperature should I set?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>We're winding down for the night — what AC temperature should I set overnight?</t>
+          <t>We're winding down for the night, what AC temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>We're winding down for the night — what AC temperature should I set overnight?</t>
+          <t>We're winding down for the night, what AC temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>We're winding down for the night — what AC temperature should I set overnight?</t>
+          <t>We're winding down for the night, what AC temperature should I set overnight?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">

--- a/workbooks/scenarios/HVACRagScenarios.xlsx
+++ b/workbooks/scenarios/HVACRagScenarios.xlsx
@@ -587,31 +587,31 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>3.99</v>
+        <v>4.84</v>
       </c>
       <c r="P2" t="n">
-        <v>3.95</v>
+        <v>4.79</v>
       </c>
       <c r="Q2" t="n">
         <v>9.18</v>
       </c>
       <c r="R2" t="n">
-        <v>9.630000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="S2" t="n">
-        <v>5.860000000000001</v>
+        <v>6.2305</v>
       </c>
       <c r="T2" t="n">
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>11.46</v>
+        <v>10.19</v>
       </c>
       <c r="V2" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="W2" t="n">
-        <v>11.93</v>
+        <v>10.61</v>
       </c>
     </row>
     <row r="3">
@@ -668,31 +668,31 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="P3" t="n">
-        <v>4.36</v>
+        <v>5.15</v>
       </c>
       <c r="Q3" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="R3" t="n">
-        <v>9.630000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="S3" t="n">
-        <v>5.9505</v>
+        <v>6.2885</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>10.85</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="W3" t="n">
-        <v>11.29</v>
+        <v>10.04</v>
       </c>
     </row>
     <row r="4">
@@ -749,31 +749,31 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>4.81</v>
+        <v>5.57</v>
       </c>
       <c r="P4" t="n">
-        <v>4.76</v>
+        <v>5.51</v>
       </c>
       <c r="Q4" t="n">
         <v>5.13</v>
       </c>
       <c r="R4" t="n">
-        <v>9.630000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="S4" t="n">
-        <v>5.579499999999999</v>
+        <v>5.8915</v>
       </c>
       <c r="T4" t="n">
         <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>10.23</v>
+        <v>9.1</v>
       </c>
       <c r="V4" t="n">
-        <v>1.94</v>
+        <v>1.73</v>
       </c>
       <c r="W4" t="n">
-        <v>10.65</v>
+        <v>9.470000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -830,31 +830,31 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>4.39</v>
+        <v>5.68</v>
       </c>
       <c r="P5" t="n">
-        <v>4.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q5" t="n">
         <v>6.11</v>
       </c>
       <c r="R5" t="n">
-        <v>7.6</v>
+        <v>6.14</v>
       </c>
       <c r="S5" t="n">
-        <v>5.254</v>
+        <v>5.859500000000001</v>
       </c>
       <c r="T5" t="n">
         <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>10.86</v>
+        <v>8.93</v>
       </c>
       <c r="V5" t="n">
-        <v>2.06</v>
+        <v>1.7</v>
       </c>
       <c r="W5" t="n">
-        <v>11.07</v>
+        <v>9.109999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -911,31 +911,31 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>3.73</v>
+        <v>5.13</v>
       </c>
       <c r="P6" t="n">
-        <v>3.86</v>
+        <v>5.22</v>
       </c>
       <c r="Q6" t="n">
         <v>8.6</v>
       </c>
       <c r="R6" t="n">
-        <v>7.6</v>
+        <v>6.14</v>
       </c>
       <c r="S6" t="n">
-        <v>5.329999999999999</v>
+        <v>6.007</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>11.85</v>
+        <v>9.75</v>
       </c>
       <c r="V6" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="W6" t="n">
-        <v>12.08</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="7">
@@ -992,31 +992,31 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>2.6</v>
+        <v>4.59</v>
       </c>
       <c r="P7" t="n">
-        <v>3.21</v>
+        <v>4.69</v>
       </c>
       <c r="Q7" t="n">
         <v>9.32</v>
       </c>
       <c r="R7" t="n">
-        <v>7.6</v>
+        <v>6.14</v>
       </c>
       <c r="S7" t="n">
-        <v>4.9075</v>
+        <v>5.803500000000001</v>
       </c>
       <c r="T7" t="n">
         <v>3</v>
       </c>
       <c r="U7" t="n">
-        <v>12.84</v>
+        <v>10.56</v>
       </c>
       <c r="V7" t="n">
-        <v>2.44</v>
+        <v>2.01</v>
       </c>
       <c r="W7" t="n">
-        <v>13.09</v>
+        <v>10.77</v>
       </c>
     </row>
     <row r="8">
@@ -1073,31 +1073,31 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>3.09</v>
+        <v>4.65</v>
       </c>
       <c r="P8" t="n">
-        <v>3.24</v>
+        <v>4.75</v>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>7.6</v>
+        <v>6.1</v>
       </c>
       <c r="S8" t="n">
-        <v>4.601</v>
+        <v>5.3725</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>12.8</v>
+        <v>10.47</v>
       </c>
       <c r="V8" t="n">
-        <v>2.43</v>
+        <v>1.99</v>
       </c>
       <c r="W8" t="n">
-        <v>13.04</v>
+        <v>10.67</v>
       </c>
     </row>
     <row r="9">
@@ -1154,31 +1154,31 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>2.34</v>
+        <v>4.04</v>
       </c>
       <c r="P9" t="n">
-        <v>2.52</v>
+        <v>4.16</v>
       </c>
       <c r="Q9" t="n">
         <v>9.32</v>
       </c>
       <c r="R9" t="n">
-        <v>7.6</v>
+        <v>6.1</v>
       </c>
       <c r="S9" t="n">
-        <v>4.588</v>
+        <v>5.447</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>13.92</v>
+        <v>11.39</v>
       </c>
       <c r="V9" t="n">
-        <v>2.64</v>
+        <v>2.16</v>
       </c>
       <c r="W9" t="n">
-        <v>14.19</v>
+        <v>11.61</v>
       </c>
     </row>
     <row r="10">
@@ -1235,31 +1235,31 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>1.59</v>
+        <v>3.42</v>
       </c>
       <c r="P10" t="n">
-        <v>1.79</v>
+        <v>3.56</v>
       </c>
       <c r="Q10" t="n">
         <v>8.6</v>
       </c>
       <c r="R10" t="n">
-        <v>7.6</v>
+        <v>6.1</v>
       </c>
       <c r="S10" t="n">
-        <v>3.9635</v>
+        <v>4.907</v>
       </c>
       <c r="T10" t="n">
         <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>15.04</v>
+        <v>12.31</v>
       </c>
       <c r="V10" t="n">
-        <v>2.86</v>
+        <v>2.34</v>
       </c>
       <c r="W10" t="n">
-        <v>15.33</v>
+        <v>12.54</v>
       </c>
     </row>
     <row r="11">
@@ -1316,31 +1316,31 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>2.77</v>
+        <v>4.51</v>
       </c>
       <c r="P11" t="n">
-        <v>2.93</v>
+        <v>4.61</v>
       </c>
       <c r="Q11" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>9.630000000000001</v>
+        <v>7.79</v>
       </c>
       <c r="S11" t="n">
-        <v>4.961</v>
+        <v>5.795</v>
       </c>
       <c r="T11" t="n">
         <v>3</v>
       </c>
       <c r="U11" t="n">
-        <v>13.27</v>
+        <v>10.68</v>
       </c>
       <c r="V11" t="n">
-        <v>2.52</v>
+        <v>2.03</v>
       </c>
       <c r="W11" t="n">
-        <v>13.53</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="12">
@@ -1397,31 +1397,31 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>3.24</v>
+        <v>4.88</v>
       </c>
       <c r="P12" t="n">
-        <v>3.38</v>
+        <v>4.98</v>
       </c>
       <c r="Q12" t="n">
         <v>9.18</v>
       </c>
       <c r="R12" t="n">
-        <v>9.630000000000001</v>
+        <v>7.79</v>
       </c>
       <c r="S12" t="n">
-        <v>5.435499999999999</v>
+        <v>6.2115</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>12.58</v>
+        <v>10.12</v>
       </c>
       <c r="V12" t="n">
-        <v>2.39</v>
+        <v>1.92</v>
       </c>
       <c r="W12" t="n">
-        <v>12.83</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="13">
@@ -1478,31 +1478,31 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>3.7</v>
+        <v>5.25</v>
       </c>
       <c r="P13" t="n">
-        <v>3.83</v>
+        <v>5.34</v>
       </c>
       <c r="Q13" t="n">
         <v>6.29</v>
       </c>
       <c r="R13" t="n">
-        <v>10</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>5.2085</v>
+        <v>5.92</v>
       </c>
       <c r="T13" t="n">
         <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>11.89</v>
+        <v>9.57</v>
       </c>
       <c r="V13" t="n">
-        <v>2.26</v>
+        <v>1.82</v>
       </c>
       <c r="W13" t="n">
-        <v>12.12</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="14">
@@ -1559,31 +1559,31 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>3.24</v>
+        <v>4.55</v>
       </c>
       <c r="P14" t="n">
-        <v>3.38</v>
+        <v>4.66</v>
       </c>
       <c r="Q14" t="n">
         <v>10</v>
       </c>
       <c r="R14" t="n">
-        <v>9.630000000000001</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>5.599499999999999</v>
+        <v>6.214</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>12.58</v>
+        <v>10.62</v>
       </c>
       <c r="V14" t="n">
-        <v>2.39</v>
+        <v>2.02</v>
       </c>
       <c r="W14" t="n">
-        <v>12.83</v>
+        <v>10.82</v>
       </c>
     </row>
     <row r="15">
@@ -1640,31 +1640,31 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>3.54</v>
+        <v>4.81</v>
       </c>
       <c r="P15" t="n">
-        <v>3.67</v>
+        <v>4.9</v>
       </c>
       <c r="Q15" t="n">
         <v>8.6</v>
       </c>
       <c r="R15" t="n">
-        <v>9.630000000000001</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>5.510999999999999</v>
+        <v>6.096</v>
       </c>
       <c r="T15" t="n">
         <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>12.13</v>
+        <v>10.24</v>
       </c>
       <c r="V15" t="n">
-        <v>2.31</v>
+        <v>1.94</v>
       </c>
       <c r="W15" t="n">
-        <v>12.37</v>
+        <v>10.43</v>
       </c>
     </row>
     <row r="16">
@@ -1721,31 +1721,31 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>3.84</v>
+        <v>5.06</v>
       </c>
       <c r="P16" t="n">
-        <v>3.96</v>
+        <v>5.15</v>
       </c>
       <c r="Q16" t="n">
         <v>7</v>
       </c>
       <c r="R16" t="n">
-        <v>9.630000000000001</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>5.3825</v>
+        <v>5.9385</v>
       </c>
       <c r="T16" t="n">
         <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>11.68</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>2.22</v>
+        <v>1.87</v>
       </c>
       <c r="W16" t="n">
-        <v>11.91</v>
+        <v>10.05</v>
       </c>
     </row>
     <row r="17">
@@ -1802,31 +1802,31 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>5.49</v>
+        <v>7.04</v>
       </c>
       <c r="P17" t="n">
-        <v>5.57</v>
+        <v>7.06</v>
       </c>
       <c r="Q17" t="n">
         <v>6.11</v>
       </c>
       <c r="R17" t="n">
-        <v>7.6</v>
+        <v>5.68</v>
       </c>
       <c r="S17" t="n">
-        <v>5.9585</v>
+        <v>6.657000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U17" t="n">
-        <v>9.210000000000001</v>
+        <v>6.9</v>
       </c>
       <c r="V17" t="n">
-        <v>1.75</v>
+        <v>1.31</v>
       </c>
       <c r="W17" t="n">
-        <v>9.390000000000001</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="18">
@@ -1883,31 +1883,31 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>4.89</v>
+        <v>6.59</v>
       </c>
       <c r="P18" t="n">
-        <v>4.98</v>
+        <v>6.63</v>
       </c>
       <c r="Q18" t="n">
         <v>8.6</v>
       </c>
       <c r="R18" t="n">
-        <v>7.6</v>
+        <v>5.68</v>
       </c>
       <c r="S18" t="n">
-        <v>6.069999999999999</v>
+        <v>6.869499999999999</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>10.11</v>
+        <v>7.58</v>
       </c>
       <c r="V18" t="n">
-        <v>1.92</v>
+        <v>1.44</v>
       </c>
       <c r="W18" t="n">
-        <v>10.31</v>
+        <v>7.72</v>
       </c>
     </row>
     <row r="19">
@@ -1964,31 +1964,31 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>4.27</v>
+        <v>6.13</v>
       </c>
       <c r="P19" t="n">
-        <v>4.4</v>
+        <v>6.19</v>
       </c>
       <c r="Q19" t="n">
         <v>9.32</v>
       </c>
       <c r="R19" t="n">
-        <v>7.6</v>
+        <v>5.68</v>
       </c>
       <c r="S19" t="n">
-        <v>5.824999999999999</v>
+        <v>6.7215</v>
       </c>
       <c r="T19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>11.01</v>
+        <v>8.25</v>
       </c>
       <c r="V19" t="n">
-        <v>2.09</v>
+        <v>1.57</v>
       </c>
       <c r="W19" t="n">
-        <v>11.23</v>
+        <v>8.41</v>
       </c>
     </row>
     <row r="20">
@@ -2045,31 +2045,31 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>4.56</v>
+        <v>5.46</v>
       </c>
       <c r="P20" t="n">
-        <v>4.66</v>
+        <v>5.53</v>
       </c>
       <c r="Q20" t="n">
         <v>10</v>
       </c>
       <c r="R20" t="n">
-        <v>9.630000000000001</v>
+        <v>8.32</v>
       </c>
       <c r="S20" t="n">
-        <v>6.4435</v>
+        <v>6.8215</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>10.61</v>
+        <v>9.26</v>
       </c>
       <c r="V20" t="n">
-        <v>2.02</v>
+        <v>1.76</v>
       </c>
       <c r="W20" t="n">
-        <v>10.81</v>
+        <v>9.44</v>
       </c>
     </row>
     <row r="21">
@@ -2126,31 +2126,31 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>4.71</v>
+        <v>5.59</v>
       </c>
       <c r="P21" t="n">
-        <v>4.81</v>
+        <v>5.66</v>
       </c>
       <c r="Q21" t="n">
         <v>9.32</v>
       </c>
       <c r="R21" t="n">
-        <v>9.630000000000001</v>
+        <v>8.32</v>
       </c>
       <c r="S21" t="n">
-        <v>6.404999999999999</v>
+        <v>6.77</v>
       </c>
       <c r="T21" t="n">
         <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>10.38</v>
+        <v>9.06</v>
       </c>
       <c r="V21" t="n">
-        <v>1.97</v>
+        <v>1.72</v>
       </c>
       <c r="W21" t="n">
-        <v>10.58</v>
+        <v>9.24</v>
       </c>
     </row>
     <row r="22">
@@ -2207,31 +2207,31 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>4.87</v>
+        <v>5.73</v>
       </c>
       <c r="P22" t="n">
-        <v>4.96</v>
+        <v>5.79</v>
       </c>
       <c r="Q22" t="n">
         <v>8.6</v>
       </c>
       <c r="R22" t="n">
-        <v>9.630000000000001</v>
+        <v>8.32</v>
       </c>
       <c r="S22" t="n">
-        <v>6.361499999999999</v>
+        <v>6.7135</v>
       </c>
       <c r="T22" t="n">
         <v>3</v>
       </c>
       <c r="U22" t="n">
-        <v>10.15</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="V22" t="n">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="W22" t="n">
-        <v>10.35</v>
+        <v>9.029999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -2288,31 +2288,31 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>6.06</v>
+        <v>6.82</v>
       </c>
       <c r="P23" t="n">
-        <v>6.12</v>
+        <v>6.85</v>
       </c>
       <c r="Q23" t="n">
         <v>6.11</v>
       </c>
       <c r="R23" t="n">
-        <v>7.6</v>
+        <v>6.44</v>
       </c>
       <c r="S23" t="n">
-        <v>6.322</v>
+        <v>6.6315</v>
       </c>
       <c r="T23" t="n">
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>8.359999999999999</v>
+        <v>7.23</v>
       </c>
       <c r="V23" t="n">
-        <v>1.59</v>
+        <v>1.37</v>
       </c>
       <c r="W23" t="n">
-        <v>8.52</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="24">
@@ -2369,31 +2369,31 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>4.85</v>
+        <v>5.77</v>
       </c>
       <c r="P24" t="n">
-        <v>4.94</v>
+        <v>5.84</v>
       </c>
       <c r="Q24" t="n">
         <v>8.6</v>
       </c>
       <c r="R24" t="n">
-        <v>7.6</v>
+        <v>6.44</v>
       </c>
       <c r="S24" t="n">
-        <v>6.044</v>
+        <v>6.461</v>
       </c>
       <c r="T24" t="n">
         <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>10.17</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V24" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="W24" t="n">
-        <v>10.37</v>
+        <v>8.970000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -2450,31 +2450,31 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>3.64</v>
+        <v>4.72</v>
       </c>
       <c r="P25" t="n">
-        <v>3.77</v>
+        <v>4.82</v>
       </c>
       <c r="Q25" t="n">
         <v>1.53</v>
       </c>
       <c r="R25" t="n">
-        <v>6.03</v>
+        <v>5.04</v>
       </c>
       <c r="S25" t="n">
-        <v>3.622</v>
+        <v>4.165</v>
       </c>
       <c r="T25" t="n">
         <v>3</v>
       </c>
       <c r="U25" t="n">
-        <v>11.99</v>
+        <v>10.36</v>
       </c>
       <c r="V25" t="n">
-        <v>2.28</v>
+        <v>1.97</v>
       </c>
       <c r="W25" t="n">
-        <v>12.22</v>
+        <v>10.57</v>
       </c>
     </row>
     <row r="26">
@@ -2531,31 +2531,31 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>9.08</v>
+        <v>9.32</v>
       </c>
       <c r="P26" t="n">
-        <v>9.15</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="Q26" t="n">
         <v>10</v>
       </c>
       <c r="R26" t="n">
-        <v>7.6</v>
+        <v>6.74</v>
       </c>
       <c r="S26" t="n">
-        <v>9.0665</v>
+        <v>9.086499999999999</v>
       </c>
       <c r="T26" t="n">
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>3.85</v>
+        <v>3.49</v>
       </c>
       <c r="V26" t="n">
-        <v>0.73</v>
+        <v>0.66</v>
       </c>
       <c r="W26" t="n">
-        <v>3.75</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="27">
@@ -2612,31 +2612,31 @@
         </is>
       </c>
       <c r="O27" t="n">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="P27" t="n">
-        <v>9.539999999999999</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="Q27" t="n">
         <v>6.11</v>
       </c>
       <c r="R27" t="n">
-        <v>7.6</v>
+        <v>6.74</v>
       </c>
       <c r="S27" t="n">
-        <v>8.551</v>
+        <v>8.545</v>
       </c>
       <c r="T27" t="n">
         <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>3.23</v>
+        <v>2.93</v>
       </c>
       <c r="V27" t="n">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="W27" t="n">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="28">
@@ -2693,31 +2693,31 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>9.91</v>
+        <v>10</v>
       </c>
       <c r="P28" t="n">
-        <v>9.92</v>
+        <v>10</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>3.75</v>
+        <v>3.22</v>
       </c>
       <c r="S28" t="n">
-        <v>7.0075</v>
+        <v>6.983</v>
       </c>
       <c r="T28" t="n">
         <v>3</v>
       </c>
       <c r="U28" t="n">
-        <v>2.61</v>
+        <v>2.37</v>
       </c>
       <c r="V28" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="W28" t="n">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="29">
@@ -2774,31 +2774,31 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>9.109999999999999</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="P29" t="n">
-        <v>9.18</v>
+        <v>9.34</v>
       </c>
       <c r="Q29" t="n">
         <v>6.11</v>
       </c>
       <c r="R29" t="n">
-        <v>7.6</v>
+        <v>6.94</v>
       </c>
       <c r="S29" t="n">
-        <v>8.308</v>
+        <v>8.318999999999999</v>
       </c>
       <c r="T29" t="n">
         <v>3</v>
       </c>
       <c r="U29" t="n">
-        <v>3.8</v>
+        <v>3.54</v>
       </c>
       <c r="V29" t="n">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="W29" t="n">
-        <v>3.71</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="30">
@@ -2855,31 +2855,31 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>8.880000000000001</v>
+        <v>9.07</v>
       </c>
       <c r="P30" t="n">
-        <v>8.970000000000001</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="Q30" t="n">
         <v>8.6</v>
       </c>
       <c r="R30" t="n">
-        <v>7.6</v>
+        <v>6.94</v>
       </c>
       <c r="S30" t="n">
-        <v>8.663499999999999</v>
+        <v>8.680999999999999</v>
       </c>
       <c r="T30" t="n">
         <v>2</v>
       </c>
       <c r="U30" t="n">
-        <v>4.15</v>
+        <v>3.87</v>
       </c>
       <c r="V30" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="W30" t="n">
-        <v>4.05</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="31">
@@ -2936,31 +2936,31 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>8.73</v>
+        <v>8.92</v>
       </c>
       <c r="P31" t="n">
-        <v>8.82</v>
+        <v>9.01</v>
       </c>
       <c r="Q31" t="n">
         <v>10</v>
       </c>
       <c r="R31" t="n">
-        <v>7.6</v>
+        <v>6.94</v>
       </c>
       <c r="S31" t="n">
-        <v>8.846</v>
+        <v>8.8705</v>
       </c>
       <c r="T31" t="n">
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>4.38</v>
+        <v>4.08</v>
       </c>
       <c r="V31" t="n">
-        <v>0.83</v>
+        <v>0.78</v>
       </c>
       <c r="W31" t="n">
-        <v>4.27</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="32">
@@ -3017,31 +3017,31 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>8.119999999999999</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="P32" t="n">
-        <v>8.109999999999999</v>
+        <v>8.27</v>
       </c>
       <c r="Q32" t="n">
         <v>7.83</v>
       </c>
       <c r="R32" t="n">
-        <v>10</v>
+        <v>9.44</v>
       </c>
       <c r="S32" t="n">
-        <v>8.340499999999999</v>
+        <v>8.360499999999998</v>
       </c>
       <c r="T32" t="n">
         <v>3</v>
       </c>
       <c r="U32" t="n">
-        <v>5.29</v>
+        <v>5.04</v>
       </c>
       <c r="V32" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="W32" t="n">
-        <v>5.39</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="33">
@@ -3098,31 +3098,31 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>8.369999999999999</v>
+        <v>8.52</v>
       </c>
       <c r="P33" t="n">
-        <v>8.35</v>
+        <v>8.51</v>
       </c>
       <c r="Q33" t="n">
         <v>9.32</v>
       </c>
       <c r="R33" t="n">
-        <v>10</v>
+        <v>9.44</v>
       </c>
       <c r="S33" t="n">
-        <v>8.797499999999999</v>
+        <v>8.814499999999999</v>
       </c>
       <c r="T33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U33" t="n">
-        <v>4.91</v>
+        <v>4.68</v>
       </c>
       <c r="V33" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="W33" t="n">
-        <v>5.01</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="34">
@@ -3179,31 +3179,31 @@
         </is>
       </c>
       <c r="O34" t="n">
-        <v>8.56</v>
+        <v>10</v>
       </c>
       <c r="P34" t="n">
-        <v>8.539999999999999</v>
+        <v>10</v>
       </c>
       <c r="Q34" t="n">
         <v>7</v>
       </c>
       <c r="R34" t="n">
-        <v>10</v>
+        <v>6.96</v>
       </c>
       <c r="S34" t="n">
-        <v>8.457000000000001</v>
+        <v>8.944000000000001</v>
       </c>
       <c r="T34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -3269,22 +3269,22 @@
         <v>4.5</v>
       </c>
       <c r="R35" t="n">
-        <v>8.16</v>
+        <v>6.73</v>
       </c>
       <c r="S35" t="n">
-        <v>2.124</v>
+        <v>1.9095</v>
       </c>
       <c r="T35" t="n">
         <v>3</v>
       </c>
       <c r="U35" t="n">
-        <v>21.3</v>
+        <v>17.79</v>
       </c>
       <c r="V35" t="n">
-        <v>4.05</v>
+        <v>3.38</v>
       </c>
       <c r="W35" t="n">
-        <v>21.71</v>
+        <v>18.14</v>
       </c>
     </row>
     <row r="36">
@@ -3341,31 +3341,31 @@
         </is>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q36" t="n">
         <v>10</v>
       </c>
       <c r="R36" t="n">
-        <v>9.630000000000001</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="S36" t="n">
-        <v>3.4445</v>
+        <v>4.250999999999999</v>
       </c>
       <c r="T36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U36" t="n">
-        <v>18.18</v>
+        <v>15.18</v>
       </c>
       <c r="V36" t="n">
-        <v>3.45</v>
+        <v>2.88</v>
       </c>
       <c r="W36" t="n">
-        <v>18.53</v>
+        <v>15.48</v>
       </c>
     </row>
     <row r="37">
@@ -3422,31 +3422,31 @@
         </is>
       </c>
       <c r="O37" t="n">
-        <v>0.54</v>
+        <v>2.37</v>
       </c>
       <c r="P37" t="n">
-        <v>0.77</v>
+        <v>2.54</v>
       </c>
       <c r="Q37" t="n">
         <v>7.59</v>
       </c>
       <c r="R37" t="n">
-        <v>9.630000000000001</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="S37" t="n">
-        <v>3.394</v>
+        <v>4.324</v>
       </c>
       <c r="T37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>16.61</v>
+        <v>13.88</v>
       </c>
       <c r="V37" t="n">
-        <v>3.16</v>
+        <v>2.64</v>
       </c>
       <c r="W37" t="n">
-        <v>16.94</v>
+        <v>14.14</v>
       </c>
     </row>
     <row r="38">
@@ -3503,31 +3503,31 @@
         </is>
       </c>
       <c r="O38" t="n">
-        <v>6.76</v>
+        <v>7.24</v>
       </c>
       <c r="P38" t="n">
-        <v>6.69</v>
+        <v>7.17</v>
       </c>
       <c r="Q38" t="n">
         <v>7.83</v>
       </c>
       <c r="R38" t="n">
-        <v>9.630000000000001</v>
+        <v>8.51</v>
       </c>
       <c r="S38" t="n">
-        <v>7.380000000000001</v>
+        <v>7.523999999999999</v>
       </c>
       <c r="T38" t="n">
         <v>2</v>
       </c>
       <c r="U38" t="n">
-        <v>7.32</v>
+        <v>6.59</v>
       </c>
       <c r="V38" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="W38" t="n">
-        <v>7.62</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="39">
@@ -3584,31 +3584,31 @@
         </is>
       </c>
       <c r="O39" t="n">
-        <v>7.07</v>
+        <v>7.53</v>
       </c>
       <c r="P39" t="n">
-        <v>7</v>
+        <v>7.45</v>
       </c>
       <c r="Q39" t="n">
         <v>9.32</v>
       </c>
       <c r="R39" t="n">
-        <v>9.630000000000001</v>
+        <v>8.51</v>
       </c>
       <c r="S39" t="n">
-        <v>7.8795</v>
+        <v>8.007</v>
       </c>
       <c r="T39" t="n">
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>6.85</v>
+        <v>6.17</v>
       </c>
       <c r="V39" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="W39" t="n">
-        <v>7.13</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="40">
@@ -3665,31 +3665,31 @@
         </is>
       </c>
       <c r="O40" t="n">
-        <v>7.47</v>
+        <v>7.88</v>
       </c>
       <c r="P40" t="n">
-        <v>7.39</v>
+        <v>7.8</v>
       </c>
       <c r="Q40" t="n">
         <v>5.13</v>
       </c>
       <c r="R40" t="n">
-        <v>9.630000000000001</v>
+        <v>8.51</v>
       </c>
       <c r="S40" t="n">
-        <v>7.297999999999998</v>
+        <v>7.3965</v>
       </c>
       <c r="T40" t="n">
         <v>3</v>
       </c>
       <c r="U40" t="n">
-        <v>6.26</v>
+        <v>5.64</v>
       </c>
       <c r="V40" t="n">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="W40" t="n">
-        <v>6.52</v>
+        <v>5.87</v>
       </c>
     </row>
     <row r="41">
@@ -3746,31 +3746,31 @@
         </is>
       </c>
       <c r="O41" t="n">
-        <v>5.43</v>
+        <v>6.37</v>
       </c>
       <c r="P41" t="n">
-        <v>5.51</v>
+        <v>6.42</v>
       </c>
       <c r="Q41" t="n">
         <v>5.13</v>
       </c>
       <c r="R41" t="n">
-        <v>7.6</v>
+        <v>6.31</v>
       </c>
       <c r="S41" t="n">
-        <v>5.7235</v>
+        <v>6.1305</v>
       </c>
       <c r="T41" t="n">
         <v>2</v>
       </c>
       <c r="U41" t="n">
-        <v>9.31</v>
+        <v>7.89</v>
       </c>
       <c r="V41" t="n">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="W41" t="n">
-        <v>9.49</v>
+        <v>8.050000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -3827,31 +3827,31 @@
         </is>
       </c>
       <c r="O42" t="n">
-        <v>4.69</v>
+        <v>5.74</v>
       </c>
       <c r="P42" t="n">
-        <v>4.79</v>
+        <v>5.81</v>
       </c>
       <c r="Q42" t="n">
         <v>8.6</v>
       </c>
       <c r="R42" t="n">
-        <v>7.6</v>
+        <v>6.31</v>
       </c>
       <c r="S42" t="n">
-        <v>5.943499999999999</v>
+        <v>6.421999999999999</v>
       </c>
       <c r="T42" t="n">
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>10.42</v>
+        <v>8.84</v>
       </c>
       <c r="V42" t="n">
-        <v>1.98</v>
+        <v>1.68</v>
       </c>
       <c r="W42" t="n">
-        <v>10.62</v>
+        <v>9.01</v>
       </c>
     </row>
     <row r="43">
@@ -3908,31 +3908,31 @@
         </is>
       </c>
       <c r="O43" t="n">
-        <v>3.57</v>
+        <v>4.8</v>
       </c>
       <c r="P43" t="n">
-        <v>3.71</v>
+        <v>4.89</v>
       </c>
       <c r="Q43" t="n">
         <v>7</v>
       </c>
       <c r="R43" t="n">
-        <v>7.6</v>
+        <v>6.31</v>
       </c>
       <c r="S43" t="n">
-        <v>4.9095</v>
+        <v>5.497999999999999</v>
       </c>
       <c r="T43" t="n">
         <v>3</v>
       </c>
       <c r="U43" t="n">
-        <v>12.08</v>
+        <v>10.25</v>
       </c>
       <c r="V43" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="W43" t="n">
-        <v>12.31</v>
+        <v>10.45</v>
       </c>
     </row>
     <row r="44">
@@ -3989,31 +3989,31 @@
         </is>
       </c>
       <c r="O44" t="n">
-        <v>5.38</v>
+        <v>6.24</v>
       </c>
       <c r="P44" t="n">
-        <v>5.45</v>
+        <v>6.29</v>
       </c>
       <c r="Q44" t="n">
         <v>7.83</v>
       </c>
       <c r="R44" t="n">
-        <v>10</v>
+        <v>8.49</v>
       </c>
       <c r="S44" t="n">
-        <v>6.587499999999999</v>
+        <v>6.912999999999999</v>
       </c>
       <c r="T44" t="n">
         <v>3</v>
       </c>
       <c r="U44" t="n">
-        <v>9.390000000000001</v>
+        <v>8.09</v>
       </c>
       <c r="V44" t="n">
-        <v>1.78</v>
+        <v>1.54</v>
       </c>
       <c r="W44" t="n">
-        <v>9.57</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="45">
@@ -4070,31 +4070,31 @@
         </is>
       </c>
       <c r="O45" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P45" t="n">
-        <v>6.06</v>
+        <v>10</v>
       </c>
       <c r="Q45" t="n">
         <v>9.32</v>
       </c>
       <c r="R45" t="n">
-        <v>10</v>
+        <v>7.95</v>
       </c>
       <c r="S45" t="n">
-        <v>7.284999999999999</v>
+        <v>9.5565</v>
       </c>
       <c r="T45" t="n">
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>8.449999999999999</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>8.609999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -4151,31 +4151,31 @@
         </is>
       </c>
       <c r="O46" t="n">
-        <v>6.48</v>
+        <v>10</v>
       </c>
       <c r="P46" t="n">
-        <v>6.52</v>
+        <v>10</v>
       </c>
       <c r="Q46" t="n">
         <v>7</v>
       </c>
       <c r="R46" t="n">
-        <v>10</v>
+        <v>6.18</v>
       </c>
       <c r="S46" t="n">
-        <v>7.125999999999999</v>
+        <v>8.827</v>
       </c>
       <c r="T46" t="n">
         <v>2</v>
       </c>
       <c r="U46" t="n">
-        <v>7.74</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>7.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -4232,31 +4232,31 @@
         </is>
       </c>
       <c r="O47" t="n">
-        <v>9.529999999999999</v>
+        <v>9.92</v>
       </c>
       <c r="P47" t="n">
-        <v>9.44</v>
+        <v>9.82</v>
       </c>
       <c r="Q47" t="n">
         <v>6.11</v>
       </c>
       <c r="R47" t="n">
-        <v>8.859999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="S47" t="n">
-        <v>8.714</v>
+        <v>8.715</v>
       </c>
       <c r="T47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U47" t="n">
-        <v>3.18</v>
+        <v>2.6</v>
       </c>
       <c r="V47" t="n">
-        <v>0.6</v>
+        <v>0.49</v>
       </c>
       <c r="W47" t="n">
-        <v>3.31</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="48">
@@ -4313,31 +4313,31 @@
         </is>
       </c>
       <c r="O48" t="n">
-        <v>8.960000000000001</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="P48" t="n">
-        <v>8.869999999999999</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="Q48" t="n">
         <v>8.6</v>
       </c>
       <c r="R48" t="n">
-        <v>8.859999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="S48" t="n">
-        <v>8.8415</v>
+        <v>8.910999999999998</v>
       </c>
       <c r="T48" t="n">
         <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>4.03</v>
+        <v>3.29</v>
       </c>
       <c r="V48" t="n">
-        <v>0.77</v>
+        <v>0.63</v>
       </c>
       <c r="W48" t="n">
-        <v>4.19</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="49">
@@ -4394,31 +4394,31 @@
         </is>
       </c>
       <c r="O49" t="n">
-        <v>8.390000000000001</v>
+        <v>8.98</v>
       </c>
       <c r="P49" t="n">
-        <v>8.31</v>
+        <v>8.9</v>
       </c>
       <c r="Q49" t="n">
         <v>9.32</v>
       </c>
       <c r="R49" t="n">
-        <v>8.859999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="S49" t="n">
-        <v>8.618499999999999</v>
+        <v>8.753</v>
       </c>
       <c r="T49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U49" t="n">
-        <v>4.88</v>
+        <v>3.99</v>
       </c>
       <c r="V49" t="n">
-        <v>0.93</v>
+        <v>0.76</v>
       </c>
       <c r="W49" t="n">
-        <v>5.08</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="50">
@@ -4475,31 +4475,31 @@
         </is>
       </c>
       <c r="O50" t="n">
-        <v>5.88</v>
+        <v>6.95</v>
       </c>
       <c r="P50" t="n">
-        <v>5.95</v>
+        <v>6.98</v>
       </c>
       <c r="Q50" t="n">
         <v>4.06</v>
       </c>
       <c r="R50" t="n">
-        <v>7.6</v>
+        <v>6.03</v>
       </c>
       <c r="S50" t="n">
-        <v>5.7985</v>
+        <v>6.2445</v>
       </c>
       <c r="T50" t="n">
         <v>2</v>
       </c>
       <c r="U50" t="n">
-        <v>8.630000000000001</v>
+        <v>7.03</v>
       </c>
       <c r="V50" t="n">
-        <v>1.64</v>
+        <v>1.34</v>
       </c>
       <c r="W50" t="n">
-        <v>8.789999999999999</v>
+        <v>7.17</v>
       </c>
     </row>
     <row r="51">
@@ -4556,31 +4556,31 @@
         </is>
       </c>
       <c r="O51" t="n">
-        <v>5.15</v>
+        <v>6.35</v>
       </c>
       <c r="P51" t="n">
-        <v>5.23</v>
+        <v>6.4</v>
       </c>
       <c r="Q51" t="n">
         <v>8.6</v>
       </c>
       <c r="R51" t="n">
-        <v>7.6</v>
+        <v>6.03</v>
       </c>
       <c r="S51" t="n">
-        <v>6.2355</v>
+        <v>6.769499999999999</v>
       </c>
       <c r="T51" t="n">
         <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>9.73</v>
+        <v>7.93</v>
       </c>
       <c r="V51" t="n">
-        <v>1.85</v>
+        <v>1.51</v>
       </c>
       <c r="W51" t="n">
-        <v>9.91</v>
+        <v>8.08</v>
       </c>
     </row>
     <row r="52">
@@ -4637,31 +4637,31 @@
         </is>
       </c>
       <c r="O52" t="n">
-        <v>4.12</v>
+        <v>5.51</v>
       </c>
       <c r="P52" t="n">
-        <v>4.24</v>
+        <v>5.59</v>
       </c>
       <c r="Q52" t="n">
         <v>6.11</v>
       </c>
       <c r="R52" t="n">
-        <v>7.6</v>
+        <v>6.03</v>
       </c>
       <c r="S52" t="n">
-        <v>5.082</v>
+        <v>5.736</v>
       </c>
       <c r="T52" t="n">
         <v>3</v>
       </c>
       <c r="U52" t="n">
-        <v>11.26</v>
+        <v>9.18</v>
       </c>
       <c r="V52" t="n">
-        <v>2.14</v>
+        <v>1.74</v>
       </c>
       <c r="W52" t="n">
-        <v>11.48</v>
+        <v>9.359999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -4718,31 +4718,31 @@
         </is>
       </c>
       <c r="O53" t="n">
-        <v>7.59</v>
+        <v>7.73</v>
       </c>
       <c r="P53" t="n">
-        <v>7.77</v>
+        <v>7.89</v>
       </c>
       <c r="Q53" t="n">
         <v>1.38</v>
       </c>
       <c r="R53" t="n">
-        <v>7.6</v>
+        <v>7.23</v>
       </c>
       <c r="S53" t="n">
-        <v>6.412499999999999</v>
+        <v>6.441</v>
       </c>
       <c r="T53" t="n">
         <v>3</v>
       </c>
       <c r="U53" t="n">
-        <v>6.07</v>
+        <v>5.87</v>
       </c>
       <c r="V53" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="W53" t="n">
-        <v>5.93</v>
+        <v>5.73</v>
       </c>
     </row>
     <row r="54">
@@ -4799,31 +4799,31 @@
         </is>
       </c>
       <c r="O54" t="n">
-        <v>7.29</v>
+        <v>7.43</v>
       </c>
       <c r="P54" t="n">
-        <v>7.49</v>
+        <v>7.62</v>
       </c>
       <c r="Q54" t="n">
         <v>5.92</v>
       </c>
       <c r="R54" t="n">
-        <v>7.6</v>
+        <v>7.23</v>
       </c>
       <c r="S54" t="n">
-        <v>7.132499999999999</v>
+        <v>7.164499999999999</v>
       </c>
       <c r="T54" t="n">
         <v>2</v>
       </c>
       <c r="U54" t="n">
-        <v>6.53</v>
+        <v>6.31</v>
       </c>
       <c r="V54" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="W54" t="n">
-        <v>6.37</v>
+        <v>6.16</v>
       </c>
     </row>
     <row r="55">
@@ -4880,31 +4880,31 @@
         </is>
       </c>
       <c r="O55" t="n">
-        <v>6.98</v>
+        <v>7.14</v>
       </c>
       <c r="P55" t="n">
-        <v>7.21</v>
+        <v>7.35</v>
       </c>
       <c r="Q55" t="n">
         <v>9.109999999999999</v>
       </c>
       <c r="R55" t="n">
-        <v>7.6</v>
+        <v>7.23</v>
       </c>
       <c r="S55" t="n">
-        <v>7.579499999999999</v>
+        <v>7.621</v>
       </c>
       <c r="T55" t="n">
         <v>1</v>
       </c>
       <c r="U55" t="n">
-        <v>6.98</v>
+        <v>6.75</v>
       </c>
       <c r="V55" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W55" t="n">
-        <v>6.81</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="56">
@@ -4970,10 +4970,10 @@
         <v>2.86</v>
       </c>
       <c r="R56" t="n">
-        <v>8.279999999999999</v>
+        <v>7.78</v>
       </c>
       <c r="S56" t="n">
-        <v>8.314</v>
+        <v>8.239000000000001</v>
       </c>
       <c r="T56" t="n">
         <v>3</v>
@@ -5051,10 +5051,10 @@
         <v>7</v>
       </c>
       <c r="R57" t="n">
-        <v>9.630000000000001</v>
+        <v>9.08</v>
       </c>
       <c r="S57" t="n">
-        <v>9.3445</v>
+        <v>9.262</v>
       </c>
       <c r="T57" t="n">
         <v>2</v>
@@ -5132,10 +5132,10 @@
         <v>9.32</v>
       </c>
       <c r="R58" t="n">
-        <v>9.630000000000001</v>
+        <v>9.08</v>
       </c>
       <c r="S58" t="n">
-        <v>9.8085</v>
+        <v>9.726000000000001</v>
       </c>
       <c r="T58" t="n">
         <v>1</v>
@@ -5213,22 +5213,22 @@
         <v>6.11</v>
       </c>
       <c r="R59" t="n">
-        <v>9.630000000000001</v>
+        <v>8.16</v>
       </c>
       <c r="S59" t="n">
-        <v>9.166500000000001</v>
+        <v>8.946</v>
       </c>
       <c r="T59" t="n">
         <v>3</v>
       </c>
       <c r="U59" t="n">
-        <v>0.73</v>
+        <v>0.62</v>
       </c>
       <c r="V59" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W59" t="n">
-        <v>0.75</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="60">
@@ -5294,22 +5294,22 @@
         <v>8.6</v>
       </c>
       <c r="R60" t="n">
-        <v>9.630000000000001</v>
+        <v>8.16</v>
       </c>
       <c r="S60" t="n">
-        <v>9.6645</v>
+        <v>9.444000000000001</v>
       </c>
       <c r="T60" t="n">
         <v>2</v>
       </c>
       <c r="U60" t="n">
-        <v>1.97</v>
+        <v>1.67</v>
       </c>
       <c r="V60" t="n">
-        <v>0.37</v>
+        <v>0.32</v>
       </c>
       <c r="W60" t="n">
-        <v>2.01</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="61">
@@ -5366,31 +5366,31 @@
         </is>
       </c>
       <c r="O61" t="n">
-        <v>9.779999999999999</v>
+        <v>10</v>
       </c>
       <c r="P61" t="n">
-        <v>9.73</v>
+        <v>10</v>
       </c>
       <c r="Q61" t="n">
         <v>10</v>
       </c>
       <c r="R61" t="n">
-        <v>9.630000000000001</v>
+        <v>8.16</v>
       </c>
       <c r="S61" t="n">
-        <v>9.783999999999999</v>
+        <v>9.724</v>
       </c>
       <c r="T61" t="n">
         <v>1</v>
       </c>
       <c r="U61" t="n">
-        <v>2.8</v>
+        <v>2.37</v>
       </c>
       <c r="V61" t="n">
-        <v>0.53</v>
+        <v>0.45</v>
       </c>
       <c r="W61" t="n">
-        <v>2.85</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="62">
@@ -5456,10 +5456,10 @@
         <v>8.6</v>
       </c>
       <c r="R62" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="S62" t="n">
-        <v>9.720000000000001</v>
+        <v>9.583500000000001</v>
       </c>
       <c r="T62" t="n">
         <v>1</v>
@@ -5537,10 +5537,10 @@
         <v>8.6</v>
       </c>
       <c r="R63" t="n">
-        <v>9.630000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="S63" t="n">
-        <v>9.6645</v>
+        <v>9.532500000000001</v>
       </c>
       <c r="T63" t="n">
         <v>2</v>
@@ -5618,10 +5618,10 @@
         <v>5.13</v>
       </c>
       <c r="R64" t="n">
-        <v>9.630000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="S64" t="n">
-        <v>8.970499999999999</v>
+        <v>8.8385</v>
       </c>
       <c r="T64" t="n">
         <v>3</v>
@@ -5699,10 +5699,10 @@
         <v>5.13</v>
       </c>
       <c r="R65" t="n">
-        <v>10</v>
+        <v>8.74</v>
       </c>
       <c r="S65" t="n">
-        <v>9.026</v>
+        <v>8.837</v>
       </c>
       <c r="T65" t="n">
         <v>3</v>
@@ -5780,10 +5780,10 @@
         <v>8.6</v>
       </c>
       <c r="R66" t="n">
-        <v>10</v>
+        <v>8.74</v>
       </c>
       <c r="S66" t="n">
-        <v>9.720000000000001</v>
+        <v>9.531000000000001</v>
       </c>
       <c r="T66" t="n">
         <v>1</v>
@@ -5861,10 +5861,10 @@
         <v>8.6</v>
       </c>
       <c r="R67" t="n">
-        <v>9.630000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="S67" t="n">
-        <v>9.6645</v>
+        <v>9.48</v>
       </c>
       <c r="T67" t="n">
         <v>2</v>
@@ -5933,31 +5933,31 @@
         </is>
       </c>
       <c r="O68" t="n">
-        <v>10</v>
+        <v>7.18</v>
       </c>
       <c r="P68" t="n">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="Q68" t="n">
         <v>8.460000000000001</v>
       </c>
       <c r="R68" t="n">
-        <v>10</v>
+        <v>6.37</v>
       </c>
       <c r="S68" t="n">
-        <v>9.692</v>
+        <v>7.321499999999999</v>
       </c>
       <c r="T68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>6.69</v>
       </c>
       <c r="V68" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W68" t="n">
-        <v>0</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="69">
@@ -6023,13 +6023,13 @@
         <v>8.460000000000001</v>
       </c>
       <c r="R69" t="n">
-        <v>10</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="S69" t="n">
-        <v>9.692</v>
+        <v>9.471500000000001</v>
       </c>
       <c r="T69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U69" t="n">
         <v>0</v>
@@ -6104,13 +6104,13 @@
         <v>4.5</v>
       </c>
       <c r="R70" t="n">
-        <v>10</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="S70" t="n">
-        <v>8.9</v>
+        <v>8.679500000000001</v>
       </c>
       <c r="T70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U70" t="n">
         <v>0</v>
@@ -6176,31 +6176,31 @@
         </is>
       </c>
       <c r="O71" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="P71" t="n">
-        <v>7.72</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="Q71" t="n">
         <v>10</v>
       </c>
       <c r="R71" t="n">
-        <v>10</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="S71" t="n">
-        <v>8.542</v>
+        <v>8.631</v>
       </c>
       <c r="T71" t="n">
         <v>1</v>
       </c>
       <c r="U71" t="n">
-        <v>5.77</v>
+        <v>5.17</v>
       </c>
       <c r="V71" t="n">
-        <v>1.1</v>
+        <v>0.98</v>
       </c>
       <c r="W71" t="n">
-        <v>6</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="72">
@@ -6257,31 +6257,31 @@
         </is>
       </c>
       <c r="O72" t="n">
-        <v>8.16</v>
+        <v>8.52</v>
       </c>
       <c r="P72" t="n">
-        <v>8.08</v>
+        <v>8.44</v>
       </c>
       <c r="Q72" t="n">
         <v>7</v>
       </c>
       <c r="R72" t="n">
-        <v>10</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="S72" t="n">
-        <v>8.176</v>
+        <v>8.239000000000001</v>
       </c>
       <c r="T72" t="n">
         <v>2</v>
       </c>
       <c r="U72" t="n">
-        <v>5.23</v>
+        <v>4.69</v>
       </c>
       <c r="V72" t="n">
-        <v>0.99</v>
+        <v>0.89</v>
       </c>
       <c r="W72" t="n">
-        <v>5.44</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="73">
@@ -6338,31 +6338,31 @@
         </is>
       </c>
       <c r="O73" t="n">
-        <v>8.43</v>
+        <v>10</v>
       </c>
       <c r="P73" t="n">
-        <v>8.35</v>
+        <v>10</v>
       </c>
       <c r="Q73" t="n">
         <v>4.06</v>
       </c>
       <c r="R73" t="n">
-        <v>8.859999999999999</v>
+        <v>4.35</v>
       </c>
       <c r="S73" t="n">
-        <v>7.592499999999999</v>
+        <v>7.9645</v>
       </c>
       <c r="T73" t="n">
         <v>3</v>
       </c>
       <c r="U73" t="n">
-        <v>4.82</v>
+        <v>0</v>
       </c>
       <c r="V73" t="n">
-        <v>0.92</v>
+        <v>0</v>
       </c>
       <c r="W73" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -6419,31 +6419,31 @@
         </is>
       </c>
       <c r="O74" t="n">
-        <v>8.539999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="P74" t="n">
-        <v>8.52</v>
+        <v>8.93</v>
       </c>
       <c r="Q74" t="n">
         <v>8.6</v>
       </c>
       <c r="R74" t="n">
-        <v>10</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="S74" t="n">
-        <v>8.763999999999999</v>
+        <v>8.826499999999999</v>
       </c>
       <c r="T74" t="n">
         <v>2</v>
       </c>
       <c r="U74" t="n">
-        <v>4.65</v>
+        <v>4.02</v>
       </c>
       <c r="V74" t="n">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="W74" t="n">
-        <v>4.74</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="75">
@@ -6500,31 +6500,31 @@
         </is>
       </c>
       <c r="O75" t="n">
-        <v>8.789999999999999</v>
+        <v>9.18</v>
       </c>
       <c r="P75" t="n">
-        <v>8.77</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="Q75" t="n">
         <v>9.32</v>
       </c>
       <c r="R75" t="n">
-        <v>10</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="S75" t="n">
-        <v>9.070499999999999</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="T75" t="n">
         <v>1</v>
       </c>
       <c r="U75" t="n">
-        <v>4.28</v>
+        <v>3.7</v>
       </c>
       <c r="V75" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="W75" t="n">
-        <v>4.36</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="76">
@@ -6581,31 +6581,31 @@
         </is>
       </c>
       <c r="O76" t="n">
-        <v>9.119999999999999</v>
+        <v>10</v>
       </c>
       <c r="P76" t="n">
-        <v>9.09</v>
+        <v>10</v>
       </c>
       <c r="Q76" t="n">
         <v>6.11</v>
       </c>
       <c r="R76" t="n">
-        <v>10</v>
+        <v>5.63</v>
       </c>
       <c r="S76" t="n">
-        <v>8.6395</v>
+        <v>8.5665</v>
       </c>
       <c r="T76" t="n">
         <v>3</v>
       </c>
       <c r="U76" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="V76" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="W76" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -6662,31 +6662,31 @@
         </is>
       </c>
       <c r="O77" t="n">
-        <v>5.75</v>
+        <v>6.27</v>
       </c>
       <c r="P77" t="n">
-        <v>5.7</v>
+        <v>6.21</v>
       </c>
       <c r="Q77" t="n">
         <v>9.18</v>
       </c>
       <c r="R77" t="n">
-        <v>10</v>
+        <v>8.98</v>
       </c>
       <c r="S77" t="n">
-        <v>7.056</v>
+        <v>7.237499999999999</v>
       </c>
       <c r="T77" t="n">
         <v>1</v>
       </c>
       <c r="U77" t="n">
-        <v>8.82</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="V77" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="W77" t="n">
-        <v>9.19</v>
+        <v>8.380000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -6743,31 +6743,31 @@
         </is>
       </c>
       <c r="O78" t="n">
-        <v>6.34</v>
+        <v>6.81</v>
       </c>
       <c r="P78" t="n">
-        <v>6.28</v>
+        <v>6.74</v>
       </c>
       <c r="Q78" t="n">
         <v>5.13</v>
       </c>
       <c r="R78" t="n">
-        <v>10</v>
+        <v>8.98</v>
       </c>
       <c r="S78" t="n">
-        <v>6.625999999999999</v>
+        <v>6.774999999999999</v>
       </c>
       <c r="T78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U78" t="n">
-        <v>7.95</v>
+        <v>7.24</v>
       </c>
       <c r="V78" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="W78" t="n">
-        <v>8.27</v>
+        <v>7.54</v>
       </c>
     </row>
     <row r="79">
@@ -6824,31 +6824,31 @@
         </is>
       </c>
       <c r="O79" t="n">
-        <v>6.78</v>
+        <v>10</v>
       </c>
       <c r="P79" t="n">
-        <v>6.71</v>
+        <v>10</v>
       </c>
       <c r="Q79" t="n">
         <v>0.64</v>
       </c>
       <c r="R79" t="n">
-        <v>7.6</v>
+        <v>3.62</v>
       </c>
       <c r="S79" t="n">
-        <v>5.6505</v>
+        <v>7.171</v>
       </c>
       <c r="T79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U79" t="n">
-        <v>7.29</v>
+        <v>0</v>
       </c>
       <c r="V79" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W79" t="n">
-        <v>7.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -6905,31 +6905,31 @@
         </is>
       </c>
       <c r="O80" t="n">
-        <v>7.63</v>
+        <v>8.09</v>
       </c>
       <c r="P80" t="n">
-        <v>7.55</v>
+        <v>8.01</v>
       </c>
       <c r="Q80" t="n">
         <v>8.6</v>
       </c>
       <c r="R80" t="n">
-        <v>8.859999999999999</v>
+        <v>7.72</v>
       </c>
       <c r="S80" t="n">
-        <v>7.980499999999999</v>
+        <v>8.108499999999999</v>
       </c>
       <c r="T80" t="n">
         <v>1</v>
       </c>
       <c r="U80" t="n">
-        <v>6.02</v>
+        <v>5.33</v>
       </c>
       <c r="V80" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="W80" t="n">
-        <v>6.27</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="81">
@@ -6986,31 +6986,31 @@
         </is>
       </c>
       <c r="O81" t="n">
-        <v>7.82</v>
+        <v>8.27</v>
       </c>
       <c r="P81" t="n">
-        <v>7.75</v>
+        <v>8.18</v>
       </c>
       <c r="Q81" t="n">
         <v>6.11</v>
       </c>
       <c r="R81" t="n">
-        <v>9.630000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="S81" t="n">
-        <v>7.725000000000001</v>
+        <v>7.832</v>
       </c>
       <c r="T81" t="n">
         <v>2</v>
       </c>
       <c r="U81" t="n">
-        <v>5.73</v>
+        <v>5.07</v>
       </c>
       <c r="V81" t="n">
-        <v>1.09</v>
+        <v>0.96</v>
       </c>
       <c r="W81" t="n">
-        <v>5.96</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="82">
@@ -7067,31 +7067,31 @@
         </is>
       </c>
       <c r="O82" t="n">
-        <v>8.02</v>
+        <v>8.44</v>
       </c>
       <c r="P82" t="n">
-        <v>7.94</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="Q82" t="n">
         <v>2.86</v>
       </c>
       <c r="R82" t="n">
-        <v>7.29</v>
+        <v>6.29</v>
       </c>
       <c r="S82" t="n">
-        <v>6.850499999999999</v>
+        <v>6.9735</v>
       </c>
       <c r="T82" t="n">
         <v>3</v>
       </c>
       <c r="U82" t="n">
-        <v>5.43</v>
+        <v>4.8</v>
       </c>
       <c r="V82" t="n">
-        <v>1.03</v>
+        <v>0.91</v>
       </c>
       <c r="W82" t="n">
-        <v>5.65</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -7148,31 +7148,31 @@
         </is>
       </c>
       <c r="O83" t="n">
-        <v>7.82</v>
+        <v>8.43</v>
       </c>
       <c r="P83" t="n">
-        <v>7.75</v>
+        <v>8.35</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>3.75</v>
+        <v>2.91</v>
       </c>
       <c r="S83" t="n">
-        <v>5.621</v>
+        <v>5.887999999999999</v>
       </c>
       <c r="T83" t="n">
         <v>3</v>
       </c>
       <c r="U83" t="n">
-        <v>5.73</v>
+        <v>4.81</v>
       </c>
       <c r="V83" t="n">
-        <v>1.09</v>
+        <v>0.91</v>
       </c>
       <c r="W83" t="n">
-        <v>5.96</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="84">
@@ -7229,31 +7229,31 @@
         </is>
       </c>
       <c r="O84" t="n">
-        <v>7.45</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="P84" t="n">
-        <v>7.37</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="Q84" t="n">
         <v>4.06</v>
       </c>
       <c r="R84" t="n">
-        <v>7.6</v>
+        <v>6.24</v>
       </c>
       <c r="S84" t="n">
-        <v>6.7665</v>
+        <v>6.997999999999999</v>
       </c>
       <c r="T84" t="n">
         <v>2</v>
       </c>
       <c r="U84" t="n">
-        <v>6.29</v>
+        <v>5.28</v>
       </c>
       <c r="V84" t="n">
-        <v>1.19</v>
+        <v>1</v>
       </c>
       <c r="W84" t="n">
-        <v>6.55</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="85">
@@ -7310,31 +7310,31 @@
         </is>
       </c>
       <c r="O85" t="n">
-        <v>7.07</v>
+        <v>7.81</v>
       </c>
       <c r="P85" t="n">
-        <v>7</v>
+        <v>7.73</v>
       </c>
       <c r="Q85" t="n">
         <v>7</v>
       </c>
       <c r="R85" t="n">
-        <v>7.6</v>
+        <v>6.24</v>
       </c>
       <c r="S85" t="n">
-        <v>7.111</v>
+        <v>7.3845</v>
       </c>
       <c r="T85" t="n">
         <v>1</v>
       </c>
       <c r="U85" t="n">
-        <v>6.85</v>
+        <v>5.75</v>
       </c>
       <c r="V85" t="n">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="W85" t="n">
-        <v>7.13</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="86">
@@ -7391,31 +7391,31 @@
         </is>
       </c>
       <c r="O86" t="n">
-        <v>5.53</v>
+        <v>6.24</v>
       </c>
       <c r="P86" t="n">
-        <v>5.6</v>
+        <v>6.29</v>
       </c>
       <c r="Q86" t="n">
         <v>7.83</v>
       </c>
       <c r="R86" t="n">
-        <v>9.630000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="S86" t="n">
-        <v>6.6295</v>
+        <v>6.905499999999999</v>
       </c>
       <c r="T86" t="n">
         <v>3</v>
       </c>
       <c r="U86" t="n">
-        <v>9.15</v>
+        <v>8.1</v>
       </c>
       <c r="V86" t="n">
-        <v>1.74</v>
+        <v>1.54</v>
       </c>
       <c r="W86" t="n">
-        <v>9.33</v>
+        <v>8.26</v>
       </c>
     </row>
     <row r="87">
@@ -7472,31 +7472,31 @@
         </is>
       </c>
       <c r="O87" t="n">
-        <v>5.85</v>
+        <v>6.52</v>
       </c>
       <c r="P87" t="n">
-        <v>5.91</v>
+        <v>6.56</v>
       </c>
       <c r="Q87" t="n">
         <v>10</v>
       </c>
       <c r="R87" t="n">
-        <v>9.630000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="S87" t="n">
-        <v>7.267999999999999</v>
+        <v>7.518</v>
       </c>
       <c r="T87" t="n">
         <v>1</v>
       </c>
       <c r="U87" t="n">
-        <v>8.67</v>
+        <v>7.68</v>
       </c>
       <c r="V87" t="n">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="W87" t="n">
-        <v>8.84</v>
+        <v>7.82</v>
       </c>
     </row>
     <row r="88">
@@ -7553,31 +7553,31 @@
         </is>
       </c>
       <c r="O88" t="n">
-        <v>6.17</v>
+        <v>6.8</v>
       </c>
       <c r="P88" t="n">
-        <v>6.22</v>
+        <v>6.84</v>
       </c>
       <c r="Q88" t="n">
         <v>7.83</v>
       </c>
       <c r="R88" t="n">
-        <v>10</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="S88" t="n">
-        <v>7.093999999999999</v>
+        <v>7.316999999999999</v>
       </c>
       <c r="T88" t="n">
         <v>2</v>
       </c>
       <c r="U88" t="n">
-        <v>8.199999999999999</v>
+        <v>7.25</v>
       </c>
       <c r="V88" t="n">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="W88" t="n">
-        <v>8.35</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="89">
@@ -7634,31 +7634,31 @@
         </is>
       </c>
       <c r="O89" t="n">
-        <v>8.220000000000001</v>
+        <v>8.83</v>
       </c>
       <c r="P89" t="n">
-        <v>8.140000000000001</v>
+        <v>8.74</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>3.75</v>
+        <v>2.85</v>
       </c>
       <c r="S89" t="n">
-        <v>5.8775</v>
+        <v>6.1355</v>
       </c>
       <c r="T89" t="n">
         <v>3</v>
       </c>
       <c r="U89" t="n">
-        <v>5.14</v>
+        <v>4.23</v>
       </c>
       <c r="V89" t="n">
-        <v>0.98</v>
+        <v>0.8</v>
       </c>
       <c r="W89" t="n">
-        <v>5.35</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="90">
@@ -7715,31 +7715,31 @@
         </is>
       </c>
       <c r="O90" t="n">
-        <v>7.82</v>
+        <v>8.5</v>
       </c>
       <c r="P90" t="n">
-        <v>7.74</v>
+        <v>8.42</v>
       </c>
       <c r="Q90" t="n">
         <v>4.06</v>
       </c>
       <c r="R90" t="n">
-        <v>7.6</v>
+        <v>6.14</v>
       </c>
       <c r="S90" t="n">
-        <v>7.007</v>
+        <v>7.23</v>
       </c>
       <c r="T90" t="n">
         <v>2</v>
       </c>
       <c r="U90" t="n">
-        <v>5.73</v>
+        <v>4.71</v>
       </c>
       <c r="V90" t="n">
-        <v>1.09</v>
+        <v>0.9</v>
       </c>
       <c r="W90" t="n">
-        <v>5.97</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="91">
@@ -7796,31 +7796,31 @@
         </is>
       </c>
       <c r="O91" t="n">
-        <v>7.42</v>
+        <v>8.17</v>
       </c>
       <c r="P91" t="n">
-        <v>7.35</v>
+        <v>8.09</v>
       </c>
       <c r="Q91" t="n">
         <v>7</v>
       </c>
       <c r="R91" t="n">
-        <v>7.6</v>
+        <v>6.14</v>
       </c>
       <c r="S91" t="n">
-        <v>7.3385</v>
+        <v>7.6035</v>
       </c>
       <c r="T91" t="n">
         <v>1</v>
       </c>
       <c r="U91" t="n">
-        <v>6.32</v>
+        <v>5.2</v>
       </c>
       <c r="V91" t="n">
-        <v>1.2</v>
+        <v>0.99</v>
       </c>
       <c r="W91" t="n">
-        <v>6.58</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="92">
@@ -7877,31 +7877,31 @@
         </is>
       </c>
       <c r="O92" t="n">
-        <v>1.83</v>
+        <v>3.4</v>
       </c>
       <c r="P92" t="n">
-        <v>2.01</v>
+        <v>3.54</v>
       </c>
       <c r="Q92" t="n">
         <v>10</v>
       </c>
       <c r="R92" t="n">
-        <v>9.630000000000001</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="S92" t="n">
-        <v>4.697</v>
+        <v>5.465</v>
       </c>
       <c r="T92" t="n">
         <v>1</v>
       </c>
       <c r="U92" t="n">
-        <v>14.69</v>
+        <v>12.34</v>
       </c>
       <c r="V92" t="n">
-        <v>2.79</v>
+        <v>2.35</v>
       </c>
       <c r="W92" t="n">
-        <v>14.97</v>
+        <v>12.58</v>
       </c>
     </row>
     <row r="93">
@@ -7958,31 +7958,31 @@
         </is>
       </c>
       <c r="O93" t="n">
-        <v>2.47</v>
+        <v>3.94</v>
       </c>
       <c r="P93" t="n">
-        <v>2.64</v>
+        <v>4.06</v>
       </c>
       <c r="Q93" t="n">
         <v>7.59</v>
       </c>
       <c r="R93" t="n">
-        <v>9.630000000000001</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="S93" t="n">
-        <v>4.6275</v>
+        <v>5.326999999999999</v>
       </c>
       <c r="T93" t="n">
         <v>2</v>
       </c>
       <c r="U93" t="n">
-        <v>13.72</v>
+        <v>11.53</v>
       </c>
       <c r="V93" t="n">
-        <v>2.61</v>
+        <v>2.19</v>
       </c>
       <c r="W93" t="n">
-        <v>13.99</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="94">
@@ -8039,31 +8039,31 @@
         </is>
       </c>
       <c r="O94" t="n">
-        <v>3.12</v>
+        <v>4.48</v>
       </c>
       <c r="P94" t="n">
-        <v>3.27</v>
+        <v>4.59</v>
       </c>
       <c r="Q94" t="n">
         <v>4.5</v>
       </c>
       <c r="R94" t="n">
-        <v>9.630000000000001</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="S94" t="n">
-        <v>4.425</v>
+        <v>5.0565</v>
       </c>
       <c r="T94" t="n">
         <v>3</v>
       </c>
       <c r="U94" t="n">
-        <v>12.76</v>
+        <v>10.72</v>
       </c>
       <c r="V94" t="n">
-        <v>2.42</v>
+        <v>2.04</v>
       </c>
       <c r="W94" t="n">
-        <v>13.01</v>
+        <v>10.93</v>
       </c>
     </row>
     <row r="95">
@@ -8120,31 +8120,31 @@
         </is>
       </c>
       <c r="O95" t="n">
-        <v>4.37</v>
+        <v>6.57</v>
       </c>
       <c r="P95" t="n">
-        <v>4.75</v>
+        <v>6.51</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>3.75</v>
+        <v>2.54</v>
       </c>
       <c r="S95" t="n">
-        <v>3.536</v>
+        <v>4.6305</v>
       </c>
       <c r="T95" t="n">
         <v>3</v>
       </c>
       <c r="U95" t="n">
-        <v>10.26</v>
+        <v>7.59</v>
       </c>
       <c r="V95" t="n">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="W95" t="n">
-        <v>10.68</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="96">
@@ -8201,31 +8201,31 @@
         </is>
       </c>
       <c r="O96" t="n">
-        <v>2.72</v>
+        <v>6</v>
       </c>
       <c r="P96" t="n">
-        <v>3.98</v>
+        <v>5.95</v>
       </c>
       <c r="Q96" t="n">
         <v>5.13</v>
       </c>
       <c r="R96" t="n">
-        <v>7.6</v>
+        <v>5.61</v>
       </c>
       <c r="S96" t="n">
-        <v>4.375</v>
+        <v>5.75</v>
       </c>
       <c r="T96" t="n">
         <v>2</v>
       </c>
       <c r="U96" t="n">
-        <v>11.41</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="V96" t="n">
-        <v>2.17</v>
+        <v>1.6</v>
       </c>
       <c r="W96" t="n">
-        <v>11.88</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="97">
@@ -8282,31 +8282,31 @@
         </is>
       </c>
       <c r="O97" t="n">
-        <v>1.52</v>
+        <v>5.43</v>
       </c>
       <c r="P97" t="n">
-        <v>3.22</v>
+        <v>5.38</v>
       </c>
       <c r="Q97" t="n">
         <v>8.6</v>
       </c>
       <c r="R97" t="n">
-        <v>7.6</v>
+        <v>5.61</v>
       </c>
       <c r="S97" t="n">
-        <v>4.443</v>
+        <v>6.073499999999999</v>
       </c>
       <c r="T97" t="n">
         <v>1</v>
       </c>
       <c r="U97" t="n">
-        <v>12.56</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V97" t="n">
-        <v>2.39</v>
+        <v>1.77</v>
       </c>
       <c r="W97" t="n">
-        <v>13.08</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="98">
@@ -8363,31 +8363,31 @@
         </is>
       </c>
       <c r="O98" t="n">
-        <v>4.16</v>
+        <v>5.86</v>
       </c>
       <c r="P98" t="n">
-        <v>4.9</v>
+        <v>6.17</v>
       </c>
       <c r="Q98" t="n">
         <v>7</v>
       </c>
       <c r="R98" t="n">
-        <v>9.630000000000001</v>
+        <v>7.79</v>
       </c>
       <c r="S98" t="n">
-        <v>5.807500000000001</v>
+        <v>6.486</v>
       </c>
       <c r="T98" t="n">
         <v>3</v>
       </c>
       <c r="U98" t="n">
-        <v>10.69</v>
+        <v>8.66</v>
       </c>
       <c r="V98" t="n">
-        <v>2.03</v>
+        <v>1.64</v>
       </c>
       <c r="W98" t="n">
-        <v>10.43</v>
+        <v>8.449999999999999</v>
       </c>
     </row>
     <row r="99">
@@ -8444,31 +8444,31 @@
         </is>
       </c>
       <c r="O99" t="n">
-        <v>4.98</v>
+        <v>6.25</v>
       </c>
       <c r="P99" t="n">
-        <v>5.34</v>
+        <v>6.52</v>
       </c>
       <c r="Q99" t="n">
         <v>9.32</v>
       </c>
       <c r="R99" t="n">
-        <v>9.630000000000001</v>
+        <v>7.79</v>
       </c>
       <c r="S99" t="n">
-        <v>6.6715</v>
+        <v>7.1895</v>
       </c>
       <c r="T99" t="n">
         <v>2</v>
       </c>
       <c r="U99" t="n">
-        <v>9.98</v>
+        <v>8.08</v>
       </c>
       <c r="V99" t="n">
-        <v>1.9</v>
+        <v>1.54</v>
       </c>
       <c r="W99" t="n">
-        <v>9.74</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="100">
@@ -8525,31 +8525,31 @@
         </is>
       </c>
       <c r="O100" t="n">
-        <v>5.45</v>
+        <v>6.63</v>
       </c>
       <c r="P100" t="n">
-        <v>5.78</v>
+        <v>6.88</v>
       </c>
       <c r="Q100" t="n">
         <v>8.6</v>
       </c>
       <c r="R100" t="n">
-        <v>10</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="S100" t="n">
-        <v>6.878</v>
+        <v>7.335</v>
       </c>
       <c r="T100" t="n">
         <v>1</v>
       </c>
       <c r="U100" t="n">
-        <v>9.279999999999999</v>
+        <v>7.51</v>
       </c>
       <c r="V100" t="n">
-        <v>1.76</v>
+        <v>1.43</v>
       </c>
       <c r="W100" t="n">
-        <v>9.050000000000001</v>
+        <v>7.33</v>
       </c>
     </row>
     <row r="101">
@@ -8606,31 +8606,31 @@
         </is>
       </c>
       <c r="O101" t="n">
-        <v>9.83</v>
+        <v>10</v>
       </c>
       <c r="P101" t="n">
-        <v>9.84</v>
+        <v>10</v>
       </c>
       <c r="Q101" t="n">
         <v>5.13</v>
       </c>
       <c r="R101" t="n">
-        <v>8.859999999999999</v>
+        <v>7.76</v>
       </c>
       <c r="S101" t="n">
-        <v>8.747999999999999</v>
+        <v>8.69</v>
       </c>
       <c r="T101" t="n">
         <v>3</v>
       </c>
       <c r="U101" t="n">
-        <v>2.73</v>
+        <v>2.43</v>
       </c>
       <c r="V101" t="n">
-        <v>0.52</v>
+        <v>0.46</v>
       </c>
       <c r="W101" t="n">
-        <v>2.67</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="102">
@@ -8687,31 +8687,31 @@
         </is>
       </c>
       <c r="O102" t="n">
-        <v>9.52</v>
+        <v>9.76</v>
       </c>
       <c r="P102" t="n">
-        <v>9.56</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="Q102" t="n">
         <v>7.83</v>
       </c>
       <c r="R102" t="n">
-        <v>8.859999999999999</v>
+        <v>7.76</v>
       </c>
       <c r="S102" t="n">
-        <v>9.097</v>
+        <v>9.081</v>
       </c>
       <c r="T102" t="n">
         <v>2</v>
       </c>
       <c r="U102" t="n">
-        <v>3.19</v>
+        <v>2.83</v>
       </c>
       <c r="V102" t="n">
-        <v>0.61</v>
+        <v>0.54</v>
       </c>
       <c r="W102" t="n">
-        <v>3.11</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="103">
@@ -8768,31 +8768,31 @@
         </is>
       </c>
       <c r="O103" t="n">
-        <v>9.220000000000001</v>
+        <v>9.49</v>
       </c>
       <c r="P103" t="n">
-        <v>9.279999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="Q103" t="n">
         <v>10</v>
       </c>
       <c r="R103" t="n">
-        <v>7.6</v>
+        <v>6.61</v>
       </c>
       <c r="S103" t="n">
-        <v>9.154</v>
+        <v>9.173999999999999</v>
       </c>
       <c r="T103" t="n">
         <v>1</v>
       </c>
       <c r="U103" t="n">
-        <v>3.65</v>
+        <v>3.24</v>
       </c>
       <c r="V103" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="W103" t="n">
-        <v>3.56</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="104">
@@ -8849,31 +8849,31 @@
         </is>
       </c>
       <c r="O104" t="n">
-        <v>8.369999999999999</v>
+        <v>8.59</v>
       </c>
       <c r="P104" t="n">
-        <v>8.49</v>
+        <v>8.69</v>
       </c>
       <c r="Q104" t="n">
         <v>8.6</v>
       </c>
       <c r="R104" t="n">
-        <v>9.630000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="S104" t="n">
-        <v>8.647</v>
+        <v>8.667499999999999</v>
       </c>
       <c r="T104" t="n">
         <v>3</v>
       </c>
       <c r="U104" t="n">
-        <v>4.91</v>
+        <v>4.58</v>
       </c>
       <c r="V104" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="W104" t="n">
-        <v>4.8</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="105">
@@ -8930,31 +8930,31 @@
         </is>
       </c>
       <c r="O105" t="n">
-        <v>8.48</v>
+        <v>8.69</v>
       </c>
       <c r="P105" t="n">
-        <v>8.59</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="Q105" t="n">
         <v>10</v>
       </c>
       <c r="R105" t="n">
-        <v>9.630000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="S105" t="n">
-        <v>8.994999999999999</v>
+        <v>9.012499999999999</v>
       </c>
       <c r="T105" t="n">
         <v>1</v>
       </c>
       <c r="U105" t="n">
-        <v>4.75</v>
+        <v>4.43</v>
       </c>
       <c r="V105" t="n">
-        <v>0.9</v>
+        <v>0.84</v>
       </c>
       <c r="W105" t="n">
-        <v>4.63</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="106">
@@ -9011,31 +9011,31 @@
         </is>
       </c>
       <c r="O106" t="n">
-        <v>8.640000000000001</v>
+        <v>8.85</v>
       </c>
       <c r="P106" t="n">
-        <v>8.75</v>
+        <v>8.93</v>
       </c>
       <c r="Q106" t="n">
         <v>7.83</v>
       </c>
       <c r="R106" t="n">
-        <v>10</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="S106" t="n">
-        <v>8.720500000000001</v>
+        <v>8.728</v>
       </c>
       <c r="T106" t="n">
         <v>2</v>
       </c>
       <c r="U106" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="V106" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="W106" t="n">
-        <v>4.39</v>
+        <v>4.1</v>
       </c>
     </row>
   </sheetData>

--- a/workbooks/scenarios/HVACRagScenarios.xlsx
+++ b/workbooks/scenarios/HVACRagScenarios.xlsx
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>4.84</v>
+        <v>4.65</v>
       </c>
       <c r="P2" t="n">
-        <v>4.79</v>
+        <v>4.62</v>
       </c>
       <c r="Q2" t="n">
         <v>9.18</v>
@@ -599,7 +599,7 @@
         <v>8.44</v>
       </c>
       <c r="S2" t="n">
-        <v>6.2305</v>
+        <v>6.114</v>
       </c>
       <c r="T2" t="n">
         <v>2</v>
@@ -668,10 +668,10 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>5.2</v>
+        <v>5.01</v>
       </c>
       <c r="P3" t="n">
-        <v>5.15</v>
+        <v>4.98</v>
       </c>
       <c r="Q3" t="n">
         <v>8.300000000000001</v>
@@ -680,7 +680,7 @@
         <v>8.44</v>
       </c>
       <c r="S3" t="n">
-        <v>6.2885</v>
+        <v>6.172000000000001</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -749,10 +749,10 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>5.57</v>
+        <v>5.37</v>
       </c>
       <c r="P4" t="n">
-        <v>5.51</v>
+        <v>5.33</v>
       </c>
       <c r="Q4" t="n">
         <v>5.13</v>
@@ -761,7 +761,7 @@
         <v>8.44</v>
       </c>
       <c r="S4" t="n">
-        <v>5.8915</v>
+        <v>5.7685</v>
       </c>
       <c r="T4" t="n">
         <v>3</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>5.68</v>
+        <v>5.47</v>
       </c>
       <c r="P5" t="n">
-        <v>5.75</v>
+        <v>5.56</v>
       </c>
       <c r="Q5" t="n">
         <v>6.11</v>
@@ -842,7 +842,7 @@
         <v>6.14</v>
       </c>
       <c r="S5" t="n">
-        <v>5.859500000000001</v>
+        <v>5.73</v>
       </c>
       <c r="T5" t="n">
         <v>2</v>
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>5.13</v>
+        <v>4.94</v>
       </c>
       <c r="P6" t="n">
-        <v>5.22</v>
+        <v>5.04</v>
       </c>
       <c r="Q6" t="n">
         <v>8.6</v>
@@ -923,7 +923,7 @@
         <v>6.14</v>
       </c>
       <c r="S6" t="n">
-        <v>6.007</v>
+        <v>5.887</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
@@ -992,10 +992,10 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>4.59</v>
+        <v>4.41</v>
       </c>
       <c r="P7" t="n">
-        <v>4.69</v>
+        <v>4.52</v>
       </c>
       <c r="Q7" t="n">
         <v>9.32</v>
@@ -1004,7 +1004,7 @@
         <v>6.14</v>
       </c>
       <c r="S7" t="n">
-        <v>5.803500000000001</v>
+        <v>5.69</v>
       </c>
       <c r="T7" t="n">
         <v>3</v>
@@ -1073,10 +1073,10 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>4.65</v>
+        <v>4.47</v>
       </c>
       <c r="P8" t="n">
-        <v>4.75</v>
+        <v>4.58</v>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
@@ -1085,7 +1085,7 @@
         <v>6.1</v>
       </c>
       <c r="S8" t="n">
-        <v>5.3725</v>
+        <v>5.259</v>
       </c>
       <c r="T8" t="n">
         <v>2</v>
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>4.04</v>
+        <v>3.87</v>
       </c>
       <c r="P9" t="n">
-        <v>4.16</v>
+        <v>4</v>
       </c>
       <c r="Q9" t="n">
         <v>9.32</v>
@@ -1166,7 +1166,7 @@
         <v>6.1</v>
       </c>
       <c r="S9" t="n">
-        <v>5.447</v>
+        <v>5.34</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="O10" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="P10" t="n">
         <v>3.42</v>
-      </c>
-      <c r="P10" t="n">
-        <v>3.56</v>
       </c>
       <c r="Q10" t="n">
         <v>8.6</v>
@@ -1247,7 +1247,7 @@
         <v>6.1</v>
       </c>
       <c r="S10" t="n">
-        <v>4.907</v>
+        <v>4.813</v>
       </c>
       <c r="T10" t="n">
         <v>3</v>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>4.51</v>
+        <v>4.33</v>
       </c>
       <c r="P11" t="n">
-        <v>4.61</v>
+        <v>4.45</v>
       </c>
       <c r="Q11" t="n">
         <v>8.300000000000001</v>
@@ -1328,7 +1328,7 @@
         <v>7.79</v>
       </c>
       <c r="S11" t="n">
-        <v>5.795</v>
+        <v>5.685</v>
       </c>
       <c r="T11" t="n">
         <v>3</v>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>4.88</v>
+        <v>4.7</v>
       </c>
       <c r="P12" t="n">
-        <v>4.98</v>
+        <v>4.8</v>
       </c>
       <c r="Q12" t="n">
         <v>9.18</v>
@@ -1409,7 +1409,7 @@
         <v>7.79</v>
       </c>
       <c r="S12" t="n">
-        <v>6.2115</v>
+        <v>6.0945</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>5.25</v>
+        <v>5.06</v>
       </c>
       <c r="P13" t="n">
-        <v>5.34</v>
+        <v>5.15</v>
       </c>
       <c r="Q13" t="n">
         <v>6.29</v>
@@ -1490,7 +1490,7 @@
         <v>8.119999999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>5.92</v>
+        <v>5.7965</v>
       </c>
       <c r="T13" t="n">
         <v>2</v>
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>4.55</v>
+        <v>4.37</v>
       </c>
       <c r="P14" t="n">
-        <v>4.66</v>
+        <v>4.49</v>
       </c>
       <c r="Q14" t="n">
         <v>10</v>
@@ -1571,7 +1571,7 @@
         <v>8.119999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>6.214</v>
+        <v>6.1005</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>4.81</v>
+        <v>4.62</v>
       </c>
       <c r="P15" t="n">
-        <v>4.9</v>
+        <v>4.73</v>
       </c>
       <c r="Q15" t="n">
         <v>8.6</v>
@@ -1652,7 +1652,7 @@
         <v>8.119999999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>6.096</v>
+        <v>5.9795</v>
       </c>
       <c r="T15" t="n">
         <v>2</v>
@@ -1721,10 +1721,10 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>5.06</v>
+        <v>4.87</v>
       </c>
       <c r="P16" t="n">
-        <v>5.15</v>
+        <v>4.97</v>
       </c>
       <c r="Q16" t="n">
         <v>7</v>
@@ -1733,7 +1733,7 @@
         <v>8.119999999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>5.9385</v>
+        <v>5.8185</v>
       </c>
       <c r="T16" t="n">
         <v>3</v>
@@ -1802,10 +1802,10 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>7.04</v>
+        <v>6.8</v>
       </c>
       <c r="P17" t="n">
-        <v>7.06</v>
+        <v>6.84</v>
       </c>
       <c r="Q17" t="n">
         <v>6.11</v>
@@ -1814,7 +1814,7 @@
         <v>5.68</v>
       </c>
       <c r="S17" t="n">
-        <v>6.657000000000001</v>
+        <v>6.508</v>
       </c>
       <c r="T17" t="n">
         <v>3</v>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>6.59</v>
+        <v>6.36</v>
       </c>
       <c r="P18" t="n">
-        <v>6.63</v>
+        <v>6.42</v>
       </c>
       <c r="Q18" t="n">
         <v>8.6</v>
@@ -1895,7 +1895,7 @@
         <v>5.68</v>
       </c>
       <c r="S18" t="n">
-        <v>6.869499999999999</v>
+        <v>6.726999999999999</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>6.13</v>
+        <v>5.92</v>
       </c>
       <c r="P19" t="n">
-        <v>6.19</v>
+        <v>5.99</v>
       </c>
       <c r="Q19" t="n">
         <v>9.32</v>
@@ -1976,7 +1976,7 @@
         <v>5.68</v>
       </c>
       <c r="S19" t="n">
-        <v>6.7215</v>
+        <v>6.5885</v>
       </c>
       <c r="T19" t="n">
         <v>2</v>
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>5.46</v>
+        <v>5.26</v>
       </c>
       <c r="P20" t="n">
-        <v>5.53</v>
+        <v>5.35</v>
       </c>
       <c r="Q20" t="n">
         <v>10</v>
@@ -2057,7 +2057,7 @@
         <v>8.32</v>
       </c>
       <c r="S20" t="n">
-        <v>6.8215</v>
+        <v>6.6985</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>5.59</v>
+        <v>5.39</v>
       </c>
       <c r="P21" t="n">
-        <v>5.66</v>
+        <v>5.48</v>
       </c>
       <c r="Q21" t="n">
         <v>9.32</v>
@@ -2138,7 +2138,7 @@
         <v>8.32</v>
       </c>
       <c r="S21" t="n">
-        <v>6.77</v>
+        <v>6.647</v>
       </c>
       <c r="T21" t="n">
         <v>2</v>
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>5.73</v>
+        <v>5.52</v>
       </c>
       <c r="P22" t="n">
-        <v>5.79</v>
+        <v>5.6</v>
       </c>
       <c r="Q22" t="n">
         <v>8.6</v>
@@ -2219,7 +2219,7 @@
         <v>8.32</v>
       </c>
       <c r="S22" t="n">
-        <v>6.7135</v>
+        <v>6.584</v>
       </c>
       <c r="T22" t="n">
         <v>3</v>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>6.82</v>
+        <v>6.59</v>
       </c>
       <c r="P23" t="n">
-        <v>6.85</v>
+        <v>6.64</v>
       </c>
       <c r="Q23" t="n">
         <v>6.11</v>
@@ -2300,7 +2300,7 @@
         <v>6.44</v>
       </c>
       <c r="S23" t="n">
-        <v>6.6315</v>
+        <v>6.489000000000001</v>
       </c>
       <c r="T23" t="n">
         <v>1</v>
@@ -2369,10 +2369,10 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>5.77</v>
+        <v>5.56</v>
       </c>
       <c r="P24" t="n">
-        <v>5.84</v>
+        <v>5.64</v>
       </c>
       <c r="Q24" t="n">
         <v>8.6</v>
@@ -2381,7 +2381,7 @@
         <v>6.44</v>
       </c>
       <c r="S24" t="n">
-        <v>6.461</v>
+        <v>6.327999999999999</v>
       </c>
       <c r="T24" t="n">
         <v>2</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>4.72</v>
+        <v>4.54</v>
       </c>
       <c r="P25" t="n">
-        <v>4.82</v>
+        <v>4.65</v>
       </c>
       <c r="Q25" t="n">
         <v>1.53</v>
@@ -2462,7 +2462,7 @@
         <v>5.04</v>
       </c>
       <c r="S25" t="n">
-        <v>4.165</v>
+        <v>4.0515</v>
       </c>
       <c r="T25" t="n">
         <v>3</v>
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>9.32</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="P26" t="n">
-        <v>9.369999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="Q26" t="n">
         <v>10</v>
@@ -2543,7 +2543,7 @@
         <v>6.74</v>
       </c>
       <c r="S26" t="n">
-        <v>9.086499999999999</v>
+        <v>8.904999999999999</v>
       </c>
       <c r="T26" t="n">
         <v>1</v>
@@ -2612,10 +2612,10 @@
         </is>
       </c>
       <c r="O27" t="n">
-        <v>9.699999999999999</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="P27" t="n">
-        <v>9.720000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="Q27" t="n">
         <v>6.11</v>
@@ -2624,7 +2624,7 @@
         <v>6.74</v>
       </c>
       <c r="S27" t="n">
-        <v>8.545</v>
+        <v>8.354000000000001</v>
       </c>
       <c r="T27" t="n">
         <v>2</v>
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>10</v>
+        <v>9.76</v>
       </c>
       <c r="P28" t="n">
-        <v>10</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -2705,7 +2705,7 @@
         <v>3.22</v>
       </c>
       <c r="S28" t="n">
-        <v>6.983</v>
+        <v>6.833999999999999</v>
       </c>
       <c r="T28" t="n">
         <v>3</v>
@@ -2774,10 +2774,10 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>9.289999999999999</v>
+        <v>8.99</v>
       </c>
       <c r="P29" t="n">
-        <v>9.34</v>
+        <v>9.07</v>
       </c>
       <c r="Q29" t="n">
         <v>6.11</v>
@@ -2786,7 +2786,7 @@
         <v>6.94</v>
       </c>
       <c r="S29" t="n">
-        <v>8.318999999999999</v>
+        <v>8.134500000000001</v>
       </c>
       <c r="T29" t="n">
         <v>3</v>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>9.07</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="P30" t="n">
-        <v>9.140000000000001</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="Q30" t="n">
         <v>8.6</v>
@@ -2867,7 +2867,7 @@
         <v>6.94</v>
       </c>
       <c r="S30" t="n">
-        <v>8.680999999999999</v>
+        <v>8.499499999999999</v>
       </c>
       <c r="T30" t="n">
         <v>2</v>
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>8.92</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="P31" t="n">
-        <v>9.01</v>
+        <v>8.74</v>
       </c>
       <c r="Q31" t="n">
         <v>10</v>
@@ -2948,7 +2948,7 @@
         <v>6.94</v>
       </c>
       <c r="S31" t="n">
-        <v>8.8705</v>
+        <v>8.692</v>
       </c>
       <c r="T31" t="n">
         <v>1</v>
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>8.279999999999999</v>
+        <v>8.02</v>
       </c>
       <c r="P32" t="n">
-        <v>8.27</v>
+        <v>8.02</v>
       </c>
       <c r="Q32" t="n">
         <v>7.83</v>
@@ -3029,7 +3029,7 @@
         <v>9.44</v>
       </c>
       <c r="S32" t="n">
-        <v>8.360499999999998</v>
+        <v>8.194999999999999</v>
       </c>
       <c r="T32" t="n">
         <v>3</v>
@@ -3098,10 +3098,10 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>8.52</v>
+        <v>8.25</v>
       </c>
       <c r="P33" t="n">
-        <v>8.51</v>
+        <v>8.25</v>
       </c>
       <c r="Q33" t="n">
         <v>9.32</v>
@@ -3110,7 +3110,7 @@
         <v>9.44</v>
       </c>
       <c r="S33" t="n">
-        <v>8.814499999999999</v>
+        <v>8.6425</v>
       </c>
       <c r="T33" t="n">
         <v>2</v>
@@ -3341,10 +3341,10 @@
         </is>
       </c>
       <c r="O36" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="P36" t="n">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="Q36" t="n">
         <v>10</v>
@@ -3353,7 +3353,7 @@
         <v>8.039999999999999</v>
       </c>
       <c r="S36" t="n">
-        <v>4.250999999999999</v>
+        <v>4.1795</v>
       </c>
       <c r="T36" t="n">
         <v>2</v>
@@ -3422,10 +3422,10 @@
         </is>
       </c>
       <c r="O37" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="P37" t="n">
-        <v>2.54</v>
+        <v>2.42</v>
       </c>
       <c r="Q37" t="n">
         <v>7.59</v>
@@ -3434,7 +3434,7 @@
         <v>8.039999999999999</v>
       </c>
       <c r="S37" t="n">
-        <v>4.324</v>
+        <v>4.246</v>
       </c>
       <c r="T37" t="n">
         <v>1</v>
@@ -3503,10 +3503,10 @@
         </is>
       </c>
       <c r="O38" t="n">
-        <v>7.24</v>
+        <v>7</v>
       </c>
       <c r="P38" t="n">
-        <v>7.17</v>
+        <v>6.95</v>
       </c>
       <c r="Q38" t="n">
         <v>7.83</v>
@@ -3515,7 +3515,7 @@
         <v>8.51</v>
       </c>
       <c r="S38" t="n">
-        <v>7.523999999999999</v>
+        <v>7.375</v>
       </c>
       <c r="T38" t="n">
         <v>2</v>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="O39" t="n">
-        <v>7.53</v>
+        <v>7.28</v>
       </c>
       <c r="P39" t="n">
-        <v>7.45</v>
+        <v>7.22</v>
       </c>
       <c r="Q39" t="n">
         <v>9.32</v>
@@ -3596,7 +3596,7 @@
         <v>8.51</v>
       </c>
       <c r="S39" t="n">
-        <v>8.007</v>
+        <v>7.8515</v>
       </c>
       <c r="T39" t="n">
         <v>1</v>
@@ -3665,10 +3665,10 @@
         </is>
       </c>
       <c r="O40" t="n">
-        <v>7.88</v>
+        <v>7.62</v>
       </c>
       <c r="P40" t="n">
-        <v>7.8</v>
+        <v>7.57</v>
       </c>
       <c r="Q40" t="n">
         <v>5.13</v>
@@ -3677,7 +3677,7 @@
         <v>8.51</v>
       </c>
       <c r="S40" t="n">
-        <v>7.3965</v>
+        <v>7.238</v>
       </c>
       <c r="T40" t="n">
         <v>3</v>
@@ -3746,10 +3746,10 @@
         </is>
       </c>
       <c r="O41" t="n">
-        <v>6.37</v>
+        <v>6.15</v>
       </c>
       <c r="P41" t="n">
-        <v>6.42</v>
+        <v>6.21</v>
       </c>
       <c r="Q41" t="n">
         <v>5.13</v>
@@ -3758,7 +3758,7 @@
         <v>6.31</v>
       </c>
       <c r="S41" t="n">
-        <v>6.1305</v>
+        <v>5.991</v>
       </c>
       <c r="T41" t="n">
         <v>2</v>
@@ -3827,10 +3827,10 @@
         </is>
       </c>
       <c r="O42" t="n">
-        <v>5.74</v>
+        <v>5.54</v>
       </c>
       <c r="P42" t="n">
-        <v>5.81</v>
+        <v>5.62</v>
       </c>
       <c r="Q42" t="n">
         <v>8.6</v>
@@ -3839,7 +3839,7 @@
         <v>6.31</v>
       </c>
       <c r="S42" t="n">
-        <v>6.421999999999999</v>
+        <v>6.295499999999999</v>
       </c>
       <c r="T42" t="n">
         <v>1</v>
@@ -3908,10 +3908,10 @@
         </is>
       </c>
       <c r="O43" t="n">
-        <v>4.8</v>
+        <v>4.61</v>
       </c>
       <c r="P43" t="n">
-        <v>4.89</v>
+        <v>4.72</v>
       </c>
       <c r="Q43" t="n">
         <v>7</v>
@@ -3920,7 +3920,7 @@
         <v>6.31</v>
       </c>
       <c r="S43" t="n">
-        <v>5.497999999999999</v>
+        <v>5.381500000000001</v>
       </c>
       <c r="T43" t="n">
         <v>3</v>
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="O44" t="n">
-        <v>6.24</v>
+        <v>6.02</v>
       </c>
       <c r="P44" t="n">
-        <v>6.29</v>
+        <v>6.09</v>
       </c>
       <c r="Q44" t="n">
         <v>7.83</v>
@@ -4001,7 +4001,7 @@
         <v>8.49</v>
       </c>
       <c r="S44" t="n">
-        <v>6.912999999999999</v>
+        <v>6.777</v>
       </c>
       <c r="T44" t="n">
         <v>3</v>
@@ -4232,10 +4232,10 @@
         </is>
       </c>
       <c r="O47" t="n">
-        <v>9.92</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="P47" t="n">
-        <v>9.82</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="Q47" t="n">
         <v>6.11</v>
@@ -4244,7 +4244,7 @@
         <v>7.2</v>
       </c>
       <c r="S47" t="n">
-        <v>8.715</v>
+        <v>8.524000000000001</v>
       </c>
       <c r="T47" t="n">
         <v>3</v>
@@ -4313,10 +4313,10 @@
         </is>
       </c>
       <c r="O48" t="n">
-        <v>9.449999999999999</v>
+        <v>9.15</v>
       </c>
       <c r="P48" t="n">
-        <v>9.359999999999999</v>
+        <v>9.09</v>
       </c>
       <c r="Q48" t="n">
         <v>8.6</v>
@@ -4325,7 +4325,7 @@
         <v>7.2</v>
       </c>
       <c r="S48" t="n">
-        <v>8.910999999999998</v>
+        <v>8.7265</v>
       </c>
       <c r="T48" t="n">
         <v>1</v>
@@ -4394,10 +4394,10 @@
         </is>
       </c>
       <c r="O49" t="n">
-        <v>8.98</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="P49" t="n">
-        <v>8.9</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="Q49" t="n">
         <v>9.32</v>
@@ -4406,7 +4406,7 @@
         <v>7.2</v>
       </c>
       <c r="S49" t="n">
-        <v>8.753</v>
+        <v>8.577999999999999</v>
       </c>
       <c r="T49" t="n">
         <v>2</v>
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="O50" t="n">
-        <v>6.95</v>
+        <v>6.72</v>
       </c>
       <c r="P50" t="n">
-        <v>6.98</v>
+        <v>6.76</v>
       </c>
       <c r="Q50" t="n">
         <v>4.06</v>
@@ -4487,7 +4487,7 @@
         <v>6.03</v>
       </c>
       <c r="S50" t="n">
-        <v>6.2445</v>
+        <v>6.0985</v>
       </c>
       <c r="T50" t="n">
         <v>2</v>
@@ -4556,10 +4556,10 @@
         </is>
       </c>
       <c r="O51" t="n">
-        <v>6.35</v>
+        <v>6.13</v>
       </c>
       <c r="P51" t="n">
-        <v>6.4</v>
+        <v>6.19</v>
       </c>
       <c r="Q51" t="n">
         <v>8.6</v>
@@ -4568,7 +4568,7 @@
         <v>6.03</v>
       </c>
       <c r="S51" t="n">
-        <v>6.769499999999999</v>
+        <v>6.629999999999999</v>
       </c>
       <c r="T51" t="n">
         <v>1</v>
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="O52" t="n">
-        <v>5.51</v>
+        <v>5.31</v>
       </c>
       <c r="P52" t="n">
-        <v>5.59</v>
+        <v>5.4</v>
       </c>
       <c r="Q52" t="n">
         <v>6.11</v>
@@ -4649,7 +4649,7 @@
         <v>6.03</v>
       </c>
       <c r="S52" t="n">
-        <v>5.736</v>
+        <v>5.6095</v>
       </c>
       <c r="T52" t="n">
         <v>3</v>
@@ -4718,10 +4718,10 @@
         </is>
       </c>
       <c r="O53" t="n">
-        <v>7.73</v>
+        <v>7.47</v>
       </c>
       <c r="P53" t="n">
-        <v>7.89</v>
+        <v>7.66</v>
       </c>
       <c r="Q53" t="n">
         <v>1.38</v>
@@ -4730,7 +4730,7 @@
         <v>7.23</v>
       </c>
       <c r="S53" t="n">
-        <v>6.441</v>
+        <v>6.2825</v>
       </c>
       <c r="T53" t="n">
         <v>3</v>
@@ -4799,10 +4799,10 @@
         </is>
       </c>
       <c r="O54" t="n">
-        <v>7.43</v>
+        <v>7.19</v>
       </c>
       <c r="P54" t="n">
-        <v>7.62</v>
+        <v>7.39</v>
       </c>
       <c r="Q54" t="n">
         <v>5.92</v>
@@ -4811,7 +4811,7 @@
         <v>7.23</v>
       </c>
       <c r="S54" t="n">
-        <v>7.164499999999999</v>
+        <v>7.012</v>
       </c>
       <c r="T54" t="n">
         <v>2</v>
@@ -4880,10 +4880,10 @@
         </is>
       </c>
       <c r="O55" t="n">
-        <v>7.14</v>
+        <v>6.9</v>
       </c>
       <c r="P55" t="n">
-        <v>7.35</v>
+        <v>7.12</v>
       </c>
       <c r="Q55" t="n">
         <v>9.109999999999999</v>
@@ -4892,7 +4892,7 @@
         <v>7.23</v>
       </c>
       <c r="S55" t="n">
-        <v>7.621</v>
+        <v>7.4685</v>
       </c>
       <c r="T55" t="n">
         <v>1</v>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="O61" t="n">
-        <v>10</v>
+        <v>9.76</v>
       </c>
       <c r="P61" t="n">
-        <v>10</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="Q61" t="n">
         <v>10</v>
@@ -5378,7 +5378,7 @@
         <v>8.16</v>
       </c>
       <c r="S61" t="n">
-        <v>9.724</v>
+        <v>9.554</v>
       </c>
       <c r="T61" t="n">
         <v>1</v>
@@ -5933,10 +5933,10 @@
         </is>
       </c>
       <c r="O68" t="n">
-        <v>7.18</v>
+        <v>6.94</v>
       </c>
       <c r="P68" t="n">
-        <v>7.2</v>
+        <v>6.98</v>
       </c>
       <c r="Q68" t="n">
         <v>8.460000000000001</v>
@@ -5945,7 +5945,7 @@
         <v>6.37</v>
       </c>
       <c r="S68" t="n">
-        <v>7.321499999999999</v>
+        <v>7.1725</v>
       </c>
       <c r="T68" t="n">
         <v>3</v>
@@ -6176,10 +6176,10 @@
         </is>
       </c>
       <c r="O71" t="n">
-        <v>8.199999999999999</v>
+        <v>7.93</v>
       </c>
       <c r="P71" t="n">
-        <v>8.119999999999999</v>
+        <v>7.87</v>
       </c>
       <c r="Q71" t="n">
         <v>10</v>
@@ -6188,7 +6188,7 @@
         <v>8.859999999999999</v>
       </c>
       <c r="S71" t="n">
-        <v>8.631</v>
+        <v>8.4625</v>
       </c>
       <c r="T71" t="n">
         <v>1</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="O72" t="n">
-        <v>8.52</v>
+        <v>8.25</v>
       </c>
       <c r="P72" t="n">
-        <v>8.44</v>
+        <v>8.18</v>
       </c>
       <c r="Q72" t="n">
         <v>7</v>
@@ -6269,7 +6269,7 @@
         <v>8.859999999999999</v>
       </c>
       <c r="S72" t="n">
-        <v>8.239000000000001</v>
+        <v>8.067</v>
       </c>
       <c r="T72" t="n">
         <v>2</v>
@@ -6419,10 +6419,10 @@
         </is>
       </c>
       <c r="O74" t="n">
-        <v>8.960000000000001</v>
+        <v>8.68</v>
       </c>
       <c r="P74" t="n">
-        <v>8.93</v>
+        <v>8.67</v>
       </c>
       <c r="Q74" t="n">
         <v>8.6</v>
@@ -6431,7 +6431,7 @@
         <v>8.619999999999999</v>
       </c>
       <c r="S74" t="n">
-        <v>8.826499999999999</v>
+        <v>8.651499999999999</v>
       </c>
       <c r="T74" t="n">
         <v>2</v>
@@ -6500,10 +6500,10 @@
         </is>
       </c>
       <c r="O75" t="n">
-        <v>9.18</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="P75" t="n">
-        <v>9.140000000000001</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="Q75" t="n">
         <v>9.32</v>
@@ -6512,7 +6512,7 @@
         <v>8.619999999999999</v>
       </c>
       <c r="S75" t="n">
-        <v>9.109999999999999</v>
+        <v>8.9285</v>
       </c>
       <c r="T75" t="n">
         <v>1</v>
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="O77" t="n">
-        <v>6.27</v>
+        <v>6.05</v>
       </c>
       <c r="P77" t="n">
-        <v>6.21</v>
+        <v>6.01</v>
       </c>
       <c r="Q77" t="n">
         <v>9.18</v>
@@ -6674,10 +6674,10 @@
         <v>8.98</v>
       </c>
       <c r="S77" t="n">
-        <v>7.237499999999999</v>
+        <v>7.1015</v>
       </c>
       <c r="T77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U77" t="n">
         <v>8.050000000000001</v>
@@ -6743,10 +6743,10 @@
         </is>
       </c>
       <c r="O78" t="n">
-        <v>6.81</v>
+        <v>6.58</v>
       </c>
       <c r="P78" t="n">
-        <v>6.74</v>
+        <v>6.53</v>
       </c>
       <c r="Q78" t="n">
         <v>5.13</v>
@@ -6755,7 +6755,7 @@
         <v>8.98</v>
       </c>
       <c r="S78" t="n">
-        <v>6.774999999999999</v>
+        <v>6.6325</v>
       </c>
       <c r="T78" t="n">
         <v>3</v>
@@ -6839,7 +6839,7 @@
         <v>7.171</v>
       </c>
       <c r="T79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U79" t="n">
         <v>0</v>
@@ -6905,10 +6905,10 @@
         </is>
       </c>
       <c r="O80" t="n">
-        <v>8.09</v>
+        <v>7.83</v>
       </c>
       <c r="P80" t="n">
-        <v>8.01</v>
+        <v>7.77</v>
       </c>
       <c r="Q80" t="n">
         <v>8.6</v>
@@ -6917,7 +6917,7 @@
         <v>7.72</v>
       </c>
       <c r="S80" t="n">
-        <v>8.108499999999999</v>
+        <v>7.946499999999999</v>
       </c>
       <c r="T80" t="n">
         <v>1</v>
@@ -6986,10 +6986,10 @@
         </is>
       </c>
       <c r="O81" t="n">
-        <v>8.27</v>
+        <v>8</v>
       </c>
       <c r="P81" t="n">
-        <v>8.18</v>
+        <v>7.94</v>
       </c>
       <c r="Q81" t="n">
         <v>6.11</v>
@@ -6998,7 +6998,7 @@
         <v>8.44</v>
       </c>
       <c r="S81" t="n">
-        <v>7.832</v>
+        <v>7.667000000000001</v>
       </c>
       <c r="T81" t="n">
         <v>2</v>
@@ -7067,10 +7067,10 @@
         </is>
       </c>
       <c r="O82" t="n">
-        <v>8.44</v>
+        <v>8.17</v>
       </c>
       <c r="P82" t="n">
-        <v>8.359999999999999</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="Q82" t="n">
         <v>2.86</v>
@@ -7079,7 +7079,7 @@
         <v>6.29</v>
       </c>
       <c r="S82" t="n">
-        <v>6.9735</v>
+        <v>6.805000000000001</v>
       </c>
       <c r="T82" t="n">
         <v>3</v>
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="O83" t="n">
-        <v>8.43</v>
+        <v>8.16</v>
       </c>
       <c r="P83" t="n">
-        <v>8.35</v>
+        <v>8.1</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -7160,7 +7160,7 @@
         <v>2.91</v>
       </c>
       <c r="S83" t="n">
-        <v>5.887999999999999</v>
+        <v>5.719499999999999</v>
       </c>
       <c r="T83" t="n">
         <v>3</v>
@@ -7229,10 +7229,10 @@
         </is>
       </c>
       <c r="O84" t="n">
-        <v>8.119999999999999</v>
+        <v>7.86</v>
       </c>
       <c r="P84" t="n">
-        <v>8.039999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="Q84" t="n">
         <v>4.06</v>
@@ -7241,7 +7241,7 @@
         <v>6.24</v>
       </c>
       <c r="S84" t="n">
-        <v>6.997999999999999</v>
+        <v>6.836</v>
       </c>
       <c r="T84" t="n">
         <v>2</v>
@@ -7310,10 +7310,10 @@
         </is>
       </c>
       <c r="O85" t="n">
-        <v>7.81</v>
+        <v>7.55</v>
       </c>
       <c r="P85" t="n">
-        <v>7.73</v>
+        <v>7.49</v>
       </c>
       <c r="Q85" t="n">
         <v>7</v>
@@ -7322,7 +7322,7 @@
         <v>6.24</v>
       </c>
       <c r="S85" t="n">
-        <v>7.3845</v>
+        <v>7.2225</v>
       </c>
       <c r="T85" t="n">
         <v>1</v>
@@ -7391,10 +7391,10 @@
         </is>
       </c>
       <c r="O86" t="n">
-        <v>6.24</v>
+        <v>6.02</v>
       </c>
       <c r="P86" t="n">
-        <v>6.29</v>
+        <v>6.08</v>
       </c>
       <c r="Q86" t="n">
         <v>7.83</v>
@@ -7403,7 +7403,7 @@
         <v>8.44</v>
       </c>
       <c r="S86" t="n">
-        <v>6.905499999999999</v>
+        <v>6.765999999999999</v>
       </c>
       <c r="T86" t="n">
         <v>3</v>
@@ -7472,10 +7472,10 @@
         </is>
       </c>
       <c r="O87" t="n">
-        <v>6.52</v>
+        <v>6.29</v>
       </c>
       <c r="P87" t="n">
-        <v>6.56</v>
+        <v>6.35</v>
       </c>
       <c r="Q87" t="n">
         <v>10</v>
@@ -7484,7 +7484,7 @@
         <v>8.44</v>
       </c>
       <c r="S87" t="n">
-        <v>7.518</v>
+        <v>7.3755</v>
       </c>
       <c r="T87" t="n">
         <v>1</v>
@@ -7553,10 +7553,10 @@
         </is>
       </c>
       <c r="O88" t="n">
-        <v>6.8</v>
+        <v>6.57</v>
       </c>
       <c r="P88" t="n">
-        <v>6.84</v>
+        <v>6.62</v>
       </c>
       <c r="Q88" t="n">
         <v>7.83</v>
@@ -7565,7 +7565,7 @@
         <v>8.779999999999999</v>
       </c>
       <c r="S88" t="n">
-        <v>7.316999999999999</v>
+        <v>7.171</v>
       </c>
       <c r="T88" t="n">
         <v>2</v>
@@ -7634,10 +7634,10 @@
         </is>
       </c>
       <c r="O89" t="n">
-        <v>8.83</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="P89" t="n">
-        <v>8.74</v>
+        <v>8.48</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -7646,7 +7646,7 @@
         <v>2.85</v>
       </c>
       <c r="S89" t="n">
-        <v>6.1355</v>
+        <v>5.9605</v>
       </c>
       <c r="T89" t="n">
         <v>3</v>
@@ -7715,10 +7715,10 @@
         </is>
       </c>
       <c r="O90" t="n">
-        <v>8.5</v>
+        <v>8.23</v>
       </c>
       <c r="P90" t="n">
-        <v>8.42</v>
+        <v>8.17</v>
       </c>
       <c r="Q90" t="n">
         <v>4.06</v>
@@ -7727,7 +7727,7 @@
         <v>6.14</v>
       </c>
       <c r="S90" t="n">
-        <v>7.23</v>
+        <v>7.061500000000001</v>
       </c>
       <c r="T90" t="n">
         <v>2</v>
@@ -7796,10 +7796,10 @@
         </is>
       </c>
       <c r="O91" t="n">
-        <v>8.17</v>
+        <v>7.91</v>
       </c>
       <c r="P91" t="n">
-        <v>8.09</v>
+        <v>7.85</v>
       </c>
       <c r="Q91" t="n">
         <v>7</v>
@@ -7808,7 +7808,7 @@
         <v>6.14</v>
       </c>
       <c r="S91" t="n">
-        <v>7.6035</v>
+        <v>7.4415</v>
       </c>
       <c r="T91" t="n">
         <v>1</v>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="O92" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P92" t="n">
-        <v>3.54</v>
+        <v>3.39</v>
       </c>
       <c r="Q92" t="n">
         <v>10</v>
@@ -7889,7 +7889,7 @@
         <v>8.039999999999999</v>
       </c>
       <c r="S92" t="n">
-        <v>5.465</v>
+        <v>5.3675</v>
       </c>
       <c r="T92" t="n">
         <v>1</v>
@@ -7958,10 +7958,10 @@
         </is>
       </c>
       <c r="O93" t="n">
-        <v>3.94</v>
+        <v>3.78</v>
       </c>
       <c r="P93" t="n">
-        <v>4.06</v>
+        <v>3.91</v>
       </c>
       <c r="Q93" t="n">
         <v>7.59</v>
@@ -7970,7 +7970,7 @@
         <v>8.039999999999999</v>
       </c>
       <c r="S93" t="n">
-        <v>5.326999999999999</v>
+        <v>5.2265</v>
       </c>
       <c r="T93" t="n">
         <v>2</v>
@@ -8039,10 +8039,10 @@
         </is>
       </c>
       <c r="O94" t="n">
-        <v>4.48</v>
+        <v>4.31</v>
       </c>
       <c r="P94" t="n">
-        <v>4.59</v>
+        <v>4.42</v>
       </c>
       <c r="Q94" t="n">
         <v>4.5</v>
@@ -8051,7 +8051,7 @@
         <v>8.039999999999999</v>
       </c>
       <c r="S94" t="n">
-        <v>5.0565</v>
+        <v>4.946</v>
       </c>
       <c r="T94" t="n">
         <v>3</v>
@@ -8120,10 +8120,10 @@
         </is>
       </c>
       <c r="O95" t="n">
-        <v>6.57</v>
+        <v>6.35</v>
       </c>
       <c r="P95" t="n">
-        <v>6.51</v>
+        <v>6.3</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -8132,7 +8132,7 @@
         <v>2.54</v>
       </c>
       <c r="S95" t="n">
-        <v>4.6305</v>
+        <v>4.491</v>
       </c>
       <c r="T95" t="n">
         <v>3</v>
@@ -8201,10 +8201,10 @@
         </is>
       </c>
       <c r="O96" t="n">
-        <v>6</v>
+        <v>5.79</v>
       </c>
       <c r="P96" t="n">
-        <v>5.95</v>
+        <v>5.75</v>
       </c>
       <c r="Q96" t="n">
         <v>5.13</v>
@@ -8213,7 +8213,7 @@
         <v>5.61</v>
       </c>
       <c r="S96" t="n">
-        <v>5.75</v>
+        <v>5.616999999999999</v>
       </c>
       <c r="T96" t="n">
         <v>2</v>
@@ -8282,10 +8282,10 @@
         </is>
       </c>
       <c r="O97" t="n">
-        <v>5.43</v>
+        <v>5.23</v>
       </c>
       <c r="P97" t="n">
-        <v>5.38</v>
+        <v>5.2</v>
       </c>
       <c r="Q97" t="n">
         <v>8.6</v>
@@ -8294,7 +8294,7 @@
         <v>5.61</v>
       </c>
       <c r="S97" t="n">
-        <v>6.073499999999999</v>
+        <v>5.9505</v>
       </c>
       <c r="T97" t="n">
         <v>1</v>
@@ -8363,10 +8363,10 @@
         </is>
       </c>
       <c r="O98" t="n">
-        <v>5.86</v>
+        <v>5.65</v>
       </c>
       <c r="P98" t="n">
-        <v>6.17</v>
+        <v>5.96</v>
       </c>
       <c r="Q98" t="n">
         <v>7</v>
@@ -8375,7 +8375,7 @@
         <v>7.79</v>
       </c>
       <c r="S98" t="n">
-        <v>6.486</v>
+        <v>6.3495</v>
       </c>
       <c r="T98" t="n">
         <v>3</v>
@@ -8444,10 +8444,10 @@
         </is>
       </c>
       <c r="O99" t="n">
-        <v>6.25</v>
+        <v>6.03</v>
       </c>
       <c r="P99" t="n">
-        <v>6.52</v>
+        <v>6.31</v>
       </c>
       <c r="Q99" t="n">
         <v>9.32</v>
@@ -8456,7 +8456,7 @@
         <v>7.79</v>
       </c>
       <c r="S99" t="n">
-        <v>7.1895</v>
+        <v>7.05</v>
       </c>
       <c r="T99" t="n">
         <v>2</v>
@@ -8525,10 +8525,10 @@
         </is>
       </c>
       <c r="O100" t="n">
-        <v>6.63</v>
+        <v>6.4</v>
       </c>
       <c r="P100" t="n">
-        <v>6.88</v>
+        <v>6.66</v>
       </c>
       <c r="Q100" t="n">
         <v>8.6</v>
@@ -8537,7 +8537,7 @@
         <v>8.119999999999999</v>
       </c>
       <c r="S100" t="n">
-        <v>7.335</v>
+        <v>7.188999999999999</v>
       </c>
       <c r="T100" t="n">
         <v>1</v>
@@ -8606,10 +8606,10 @@
         </is>
       </c>
       <c r="O101" t="n">
-        <v>10</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="P101" t="n">
-        <v>10</v>
+        <v>9.75</v>
       </c>
       <c r="Q101" t="n">
         <v>5.13</v>
@@ -8618,7 +8618,7 @@
         <v>7.76</v>
       </c>
       <c r="S101" t="n">
-        <v>8.69</v>
+        <v>8.5185</v>
       </c>
       <c r="T101" t="n">
         <v>3</v>
@@ -8687,10 +8687,10 @@
         </is>
       </c>
       <c r="O102" t="n">
-        <v>9.76</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="P102" t="n">
-        <v>9.779999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="Q102" t="n">
         <v>7.83</v>
@@ -8699,7 +8699,7 @@
         <v>7.76</v>
       </c>
       <c r="S102" t="n">
-        <v>9.081</v>
+        <v>8.893000000000001</v>
       </c>
       <c r="T102" t="n">
         <v>2</v>
@@ -8768,10 +8768,10 @@
         </is>
       </c>
       <c r="O103" t="n">
-        <v>9.49</v>
+        <v>9.19</v>
       </c>
       <c r="P103" t="n">
-        <v>9.529999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="Q103" t="n">
         <v>10</v>
@@ -8780,7 +8780,7 @@
         <v>6.61</v>
       </c>
       <c r="S103" t="n">
-        <v>9.173999999999999</v>
+        <v>8.985999999999999</v>
       </c>
       <c r="T103" t="n">
         <v>1</v>
@@ -8849,10 +8849,10 @@
         </is>
       </c>
       <c r="O104" t="n">
-        <v>8.59</v>
+        <v>8.31</v>
       </c>
       <c r="P104" t="n">
-        <v>8.69</v>
+        <v>8.44</v>
       </c>
       <c r="Q104" t="n">
         <v>8.6</v>
@@ -8861,7 +8861,7 @@
         <v>8.859999999999999</v>
       </c>
       <c r="S104" t="n">
-        <v>8.667499999999999</v>
+        <v>8.495999999999999</v>
       </c>
       <c r="T104" t="n">
         <v>3</v>
@@ -8930,10 +8930,10 @@
         </is>
       </c>
       <c r="O105" t="n">
-        <v>8.69</v>
+        <v>8.41</v>
       </c>
       <c r="P105" t="n">
-        <v>8.789999999999999</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="Q105" t="n">
         <v>10</v>
@@ -8942,7 +8942,7 @@
         <v>8.859999999999999</v>
       </c>
       <c r="S105" t="n">
-        <v>9.012499999999999</v>
+        <v>8.8375</v>
       </c>
       <c r="T105" t="n">
         <v>1</v>
@@ -9011,10 +9011,10 @@
         </is>
       </c>
       <c r="O106" t="n">
-        <v>8.85</v>
+        <v>8.57</v>
       </c>
       <c r="P106" t="n">
-        <v>8.93</v>
+        <v>8.67</v>
       </c>
       <c r="Q106" t="n">
         <v>7.83</v>
@@ -9023,7 +9023,7 @@
         <v>9.210000000000001</v>
       </c>
       <c r="S106" t="n">
-        <v>8.728</v>
+        <v>8.553000000000001</v>
       </c>
       <c r="T106" t="n">
         <v>2</v>

--- a/workbooks/scenarios/HVACRagScenarios.xlsx
+++ b/workbooks/scenarios/HVACRagScenarios.xlsx
@@ -587,19 +587,19 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>4.65</v>
+        <v>0.47</v>
       </c>
       <c r="P2" t="n">
-        <v>4.62</v>
+        <v>0.46</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.18</v>
+        <v>0.92</v>
       </c>
       <c r="R2" t="n">
-        <v>8.44</v>
+        <v>0.84</v>
       </c>
       <c r="S2" t="n">
-        <v>6.114</v>
+        <v>0.612</v>
       </c>
       <c r="T2" t="n">
         <v>2</v>
@@ -668,19 +668,19 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>5.01</v>
+        <v>0.5</v>
       </c>
       <c r="P3" t="n">
-        <v>4.98</v>
+        <v>0.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.300000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="R3" t="n">
-        <v>8.44</v>
+        <v>0.84</v>
       </c>
       <c r="S3" t="n">
-        <v>6.172000000000001</v>
+        <v>0.617</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -749,19 +749,19 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>5.37</v>
+        <v>0.54</v>
       </c>
       <c r="P4" t="n">
-        <v>5.33</v>
+        <v>0.53</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="R4" t="n">
-        <v>8.44</v>
+        <v>0.84</v>
       </c>
       <c r="S4" t="n">
-        <v>5.7685</v>
+        <v>0.5755</v>
       </c>
       <c r="T4" t="n">
         <v>3</v>
@@ -830,19 +830,19 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>5.47</v>
+        <v>0.55</v>
       </c>
       <c r="P5" t="n">
-        <v>5.56</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.11</v>
+        <v>0.61</v>
       </c>
       <c r="R5" t="n">
-        <v>6.14</v>
+        <v>0.61</v>
       </c>
       <c r="S5" t="n">
-        <v>5.73</v>
+        <v>0.5745</v>
       </c>
       <c r="T5" t="n">
         <v>2</v>
@@ -911,19 +911,19 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>4.94</v>
+        <v>0.49</v>
       </c>
       <c r="P6" t="n">
-        <v>5.04</v>
+        <v>0.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="R6" t="n">
-        <v>6.14</v>
+        <v>0.61</v>
       </c>
       <c r="S6" t="n">
-        <v>5.887</v>
+        <v>0.5855</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>4.41</v>
+        <v>0.44</v>
       </c>
       <c r="P7" t="n">
-        <v>4.52</v>
+        <v>0.45</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="R7" t="n">
-        <v>6.14</v>
+        <v>0.61</v>
       </c>
       <c r="S7" t="n">
-        <v>5.69</v>
+        <v>0.5670000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>3</v>
@@ -1073,19 +1073,19 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>4.47</v>
+        <v>0.45</v>
       </c>
       <c r="P8" t="n">
-        <v>4.58</v>
+        <v>0.46</v>
       </c>
       <c r="Q8" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="R8" t="n">
-        <v>6.1</v>
+        <v>0.61</v>
       </c>
       <c r="S8" t="n">
-        <v>5.259</v>
+        <v>0.5275000000000001</v>
       </c>
       <c r="T8" t="n">
         <v>2</v>
@@ -1154,19 +1154,19 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>3.87</v>
+        <v>0.39</v>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="R9" t="n">
-        <v>6.1</v>
+        <v>0.61</v>
       </c>
       <c r="S9" t="n">
-        <v>5.34</v>
+        <v>0.5345000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
@@ -1235,19 +1235,19 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>3.27</v>
+        <v>0.33</v>
       </c>
       <c r="P10" t="n">
-        <v>3.42</v>
+        <v>0.34</v>
       </c>
       <c r="Q10" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="R10" t="n">
-        <v>6.1</v>
+        <v>0.61</v>
       </c>
       <c r="S10" t="n">
-        <v>4.813</v>
+        <v>0.4815</v>
       </c>
       <c r="T10" t="n">
         <v>3</v>
@@ -1316,19 +1316,19 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>4.33</v>
+        <v>0.43</v>
       </c>
       <c r="P11" t="n">
-        <v>4.45</v>
+        <v>0.44</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.300000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="R11" t="n">
-        <v>7.79</v>
+        <v>0.78</v>
       </c>
       <c r="S11" t="n">
-        <v>5.685</v>
+        <v>0.5660000000000001</v>
       </c>
       <c r="T11" t="n">
         <v>3</v>
@@ -1397,19 +1397,19 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>4.7</v>
+        <v>0.47</v>
       </c>
       <c r="P12" t="n">
-        <v>4.8</v>
+        <v>0.48</v>
       </c>
       <c r="Q12" t="n">
-        <v>9.18</v>
+        <v>0.92</v>
       </c>
       <c r="R12" t="n">
-        <v>7.79</v>
+        <v>0.78</v>
       </c>
       <c r="S12" t="n">
-        <v>6.0945</v>
+        <v>0.61</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
@@ -1478,19 +1478,19 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>5.06</v>
+        <v>0.51</v>
       </c>
       <c r="P13" t="n">
-        <v>5.15</v>
+        <v>0.52</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.29</v>
+        <v>0.63</v>
       </c>
       <c r="R13" t="n">
-        <v>8.119999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>5.7965</v>
+        <v>0.5825</v>
       </c>
       <c r="T13" t="n">
         <v>2</v>
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>4.37</v>
+        <v>0.44</v>
       </c>
       <c r="P14" t="n">
-        <v>4.49</v>
+        <v>0.45</v>
       </c>
       <c r="Q14" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>8.119999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>6.1005</v>
+        <v>0.611</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
@@ -1640,19 +1640,19 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>4.62</v>
+        <v>0.46</v>
       </c>
       <c r="P15" t="n">
-        <v>4.73</v>
+        <v>0.47</v>
       </c>
       <c r="Q15" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="R15" t="n">
-        <v>8.119999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>5.9795</v>
+        <v>0.5960000000000001</v>
       </c>
       <c r="T15" t="n">
         <v>2</v>
@@ -1721,19 +1721,19 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>4.87</v>
+        <v>0.49</v>
       </c>
       <c r="P16" t="n">
-        <v>4.97</v>
+        <v>0.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="R16" t="n">
-        <v>8.119999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="S16" t="n">
-        <v>5.8185</v>
+        <v>0.5834999999999999</v>
       </c>
       <c r="T16" t="n">
         <v>3</v>
@@ -1802,19 +1802,19 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>6.8</v>
+        <v>0.68</v>
       </c>
       <c r="P17" t="n">
-        <v>6.84</v>
+        <v>0.68</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.11</v>
+        <v>0.61</v>
       </c>
       <c r="R17" t="n">
-        <v>5.68</v>
+        <v>0.57</v>
       </c>
       <c r="S17" t="n">
-        <v>6.508</v>
+        <v>0.6495000000000001</v>
       </c>
       <c r="T17" t="n">
         <v>3</v>
@@ -1883,19 +1883,19 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>6.36</v>
+        <v>0.64</v>
       </c>
       <c r="P18" t="n">
-        <v>6.42</v>
+        <v>0.64</v>
       </c>
       <c r="Q18" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="R18" t="n">
-        <v>5.68</v>
+        <v>0.57</v>
       </c>
       <c r="S18" t="n">
-        <v>6.726999999999999</v>
+        <v>0.6735</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>5.92</v>
+        <v>0.59</v>
       </c>
       <c r="P19" t="n">
-        <v>5.99</v>
+        <v>0.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="R19" t="n">
-        <v>5.68</v>
+        <v>0.57</v>
       </c>
       <c r="S19" t="n">
-        <v>6.5885</v>
+        <v>0.6585000000000001</v>
       </c>
       <c r="T19" t="n">
         <v>2</v>
@@ -2045,19 +2045,19 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>5.26</v>
+        <v>0.53</v>
       </c>
       <c r="P20" t="n">
-        <v>5.35</v>
+        <v>0.53</v>
       </c>
       <c r="Q20" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>8.32</v>
+        <v>0.83</v>
       </c>
       <c r="S20" t="n">
-        <v>6.6985</v>
+        <v>0.6689999999999999</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
@@ -2126,19 +2126,19 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>5.39</v>
+        <v>0.54</v>
       </c>
       <c r="P21" t="n">
-        <v>5.48</v>
+        <v>0.55</v>
       </c>
       <c r="Q21" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="R21" t="n">
-        <v>8.32</v>
+        <v>0.83</v>
       </c>
       <c r="S21" t="n">
-        <v>6.647</v>
+        <v>0.665</v>
       </c>
       <c r="T21" t="n">
         <v>2</v>
@@ -2207,19 +2207,19 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>5.52</v>
+        <v>0.55</v>
       </c>
       <c r="P22" t="n">
-        <v>5.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Q22" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="R22" t="n">
-        <v>8.32</v>
+        <v>0.83</v>
       </c>
       <c r="S22" t="n">
-        <v>6.584</v>
+        <v>0.6575</v>
       </c>
       <c r="T22" t="n">
         <v>3</v>
@@ -2288,19 +2288,19 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>6.59</v>
+        <v>0.66</v>
       </c>
       <c r="P23" t="n">
-        <v>6.64</v>
+        <v>0.66</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.11</v>
+        <v>0.61</v>
       </c>
       <c r="R23" t="n">
-        <v>6.44</v>
+        <v>0.64</v>
       </c>
       <c r="S23" t="n">
-        <v>6.489000000000001</v>
+        <v>0.6469999999999999</v>
       </c>
       <c r="T23" t="n">
         <v>1</v>
@@ -2369,19 +2369,19 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>5.56</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P24" t="n">
-        <v>5.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Q24" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="R24" t="n">
-        <v>6.44</v>
+        <v>0.64</v>
       </c>
       <c r="S24" t="n">
-        <v>6.327999999999999</v>
+        <v>0.632</v>
       </c>
       <c r="T24" t="n">
         <v>2</v>
@@ -2450,19 +2450,19 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>4.54</v>
+        <v>0.45</v>
       </c>
       <c r="P25" t="n">
-        <v>4.65</v>
+        <v>0.46</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.53</v>
+        <v>0.15</v>
       </c>
       <c r="R25" t="n">
-        <v>5.04</v>
+        <v>0.5</v>
       </c>
       <c r="S25" t="n">
-        <v>4.0515</v>
+        <v>0.4010000000000001</v>
       </c>
       <c r="T25" t="n">
         <v>3</v>
@@ -2531,19 +2531,19 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>9.029999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="P26" t="n">
-        <v>9.1</v>
+        <v>0.91</v>
       </c>
       <c r="Q26" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>6.74</v>
+        <v>0.67</v>
       </c>
       <c r="S26" t="n">
-        <v>8.904999999999999</v>
+        <v>0.889</v>
       </c>
       <c r="T26" t="n">
         <v>1</v>
@@ -2612,19 +2612,19 @@
         </is>
       </c>
       <c r="O27" t="n">
-        <v>9.390000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P27" t="n">
-        <v>9.44</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Q27" t="n">
-        <v>6.11</v>
+        <v>0.61</v>
       </c>
       <c r="R27" t="n">
-        <v>6.74</v>
+        <v>0.67</v>
       </c>
       <c r="S27" t="n">
-        <v>8.354000000000001</v>
+        <v>0.8335</v>
       </c>
       <c r="T27" t="n">
         <v>2</v>
@@ -2693,19 +2693,19 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>9.76</v>
+        <v>0.98</v>
       </c>
       <c r="P28" t="n">
-        <v>9.779999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>3.22</v>
+        <v>0.32</v>
       </c>
       <c r="S28" t="n">
-        <v>6.833999999999999</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="T28" t="n">
         <v>3</v>
@@ -2774,19 +2774,19 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>8.99</v>
+        <v>0.9</v>
       </c>
       <c r="P29" t="n">
-        <v>9.07</v>
+        <v>0.91</v>
       </c>
       <c r="Q29" t="n">
-        <v>6.11</v>
+        <v>0.61</v>
       </c>
       <c r="R29" t="n">
-        <v>6.94</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="S29" t="n">
-        <v>8.134500000000001</v>
+        <v>0.8140000000000001</v>
       </c>
       <c r="T29" t="n">
         <v>3</v>
@@ -2855,19 +2855,19 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>8.779999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="P30" t="n">
-        <v>8.869999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="Q30" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="R30" t="n">
-        <v>6.94</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="S30" t="n">
-        <v>8.499499999999999</v>
+        <v>0.8510000000000001</v>
       </c>
       <c r="T30" t="n">
         <v>2</v>
@@ -2936,19 +2936,19 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>8.640000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="P31" t="n">
-        <v>8.74</v>
+        <v>0.87</v>
       </c>
       <c r="Q31" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>6.94</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="S31" t="n">
-        <v>8.692</v>
+        <v>0.866</v>
       </c>
       <c r="T31" t="n">
         <v>1</v>
@@ -3017,19 +3017,19 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>8.02</v>
+        <v>0.8</v>
       </c>
       <c r="P32" t="n">
-        <v>8.02</v>
+        <v>0.8</v>
       </c>
       <c r="Q32" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="R32" t="n">
-        <v>9.44</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="S32" t="n">
-        <v>8.194999999999999</v>
+        <v>0.8170000000000001</v>
       </c>
       <c r="T32" t="n">
         <v>3</v>
@@ -3098,19 +3098,19 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>8.25</v>
+        <v>0.83</v>
       </c>
       <c r="P33" t="n">
-        <v>8.25</v>
+        <v>0.83</v>
       </c>
       <c r="Q33" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="R33" t="n">
-        <v>9.44</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="S33" t="n">
-        <v>8.6425</v>
+        <v>0.8665</v>
       </c>
       <c r="T33" t="n">
         <v>2</v>
@@ -3179,19 +3179,19 @@
         </is>
       </c>
       <c r="O34" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P34" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="R34" t="n">
-        <v>6.96</v>
+        <v>0.7</v>
       </c>
       <c r="S34" t="n">
-        <v>8.944000000000001</v>
+        <v>0.8949999999999999</v>
       </c>
       <c r="T34" t="n">
         <v>1</v>
@@ -3266,13 +3266,13 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.5</v>
+        <v>0.45</v>
       </c>
       <c r="R35" t="n">
-        <v>6.73</v>
+        <v>0.67</v>
       </c>
       <c r="S35" t="n">
-        <v>1.9095</v>
+        <v>0.1905</v>
       </c>
       <c r="T35" t="n">
         <v>3</v>
@@ -3341,19 +3341,19 @@
         </is>
       </c>
       <c r="O36" t="n">
-        <v>1.39</v>
+        <v>0.14</v>
       </c>
       <c r="P36" t="n">
-        <v>1.59</v>
+        <v>0.16</v>
       </c>
       <c r="Q36" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>8.039999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="S36" t="n">
-        <v>4.1795</v>
+        <v>0.418</v>
       </c>
       <c r="T36" t="n">
         <v>2</v>
@@ -3422,19 +3422,19 @@
         </is>
       </c>
       <c r="O37" t="n">
-        <v>2.25</v>
+        <v>0.22</v>
       </c>
       <c r="P37" t="n">
-        <v>2.42</v>
+        <v>0.24</v>
       </c>
       <c r="Q37" t="n">
-        <v>7.59</v>
+        <v>0.76</v>
       </c>
       <c r="R37" t="n">
-        <v>8.039999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="S37" t="n">
-        <v>4.246</v>
+        <v>0.422</v>
       </c>
       <c r="T37" t="n">
         <v>1</v>
@@ -3503,19 +3503,19 @@
         </is>
       </c>
       <c r="O38" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="P38" t="n">
-        <v>6.95</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q38" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="R38" t="n">
-        <v>8.51</v>
+        <v>0.85</v>
       </c>
       <c r="S38" t="n">
-        <v>7.375</v>
+        <v>0.7349999999999999</v>
       </c>
       <c r="T38" t="n">
         <v>2</v>
@@ -3584,19 +3584,19 @@
         </is>
       </c>
       <c r="O39" t="n">
-        <v>7.28</v>
+        <v>0.73</v>
       </c>
       <c r="P39" t="n">
-        <v>7.22</v>
+        <v>0.72</v>
       </c>
       <c r="Q39" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="R39" t="n">
-        <v>8.51</v>
+        <v>0.85</v>
       </c>
       <c r="S39" t="n">
-        <v>7.8515</v>
+        <v>0.7845</v>
       </c>
       <c r="T39" t="n">
         <v>1</v>
@@ -3665,19 +3665,19 @@
         </is>
       </c>
       <c r="O40" t="n">
-        <v>7.62</v>
+        <v>0.76</v>
       </c>
       <c r="P40" t="n">
-        <v>7.57</v>
+        <v>0.76</v>
       </c>
       <c r="Q40" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="R40" t="n">
-        <v>8.51</v>
+        <v>0.85</v>
       </c>
       <c r="S40" t="n">
-        <v>7.238</v>
+        <v>0.7235</v>
       </c>
       <c r="T40" t="n">
         <v>3</v>
@@ -3746,19 +3746,19 @@
         </is>
       </c>
       <c r="O41" t="n">
-        <v>6.15</v>
+        <v>0.62</v>
       </c>
       <c r="P41" t="n">
-        <v>6.21</v>
+        <v>0.62</v>
       </c>
       <c r="Q41" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="R41" t="n">
-        <v>6.31</v>
+        <v>0.63</v>
       </c>
       <c r="S41" t="n">
-        <v>5.991</v>
+        <v>0.5995</v>
       </c>
       <c r="T41" t="n">
         <v>2</v>
@@ -3827,19 +3827,19 @@
         </is>
       </c>
       <c r="O42" t="n">
-        <v>5.54</v>
+        <v>0.55</v>
       </c>
       <c r="P42" t="n">
-        <v>5.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Q42" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="R42" t="n">
-        <v>6.31</v>
+        <v>0.63</v>
       </c>
       <c r="S42" t="n">
-        <v>6.295499999999999</v>
+        <v>0.6275000000000001</v>
       </c>
       <c r="T42" t="n">
         <v>1</v>
@@ -3908,19 +3908,19 @@
         </is>
       </c>
       <c r="O43" t="n">
-        <v>4.61</v>
+        <v>0.46</v>
       </c>
       <c r="P43" t="n">
-        <v>4.72</v>
+        <v>0.47</v>
       </c>
       <c r="Q43" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="R43" t="n">
-        <v>6.31</v>
+        <v>0.63</v>
       </c>
       <c r="S43" t="n">
-        <v>5.381500000000001</v>
+        <v>0.537</v>
       </c>
       <c r="T43" t="n">
         <v>3</v>
@@ -3989,19 +3989,19 @@
         </is>
       </c>
       <c r="O44" t="n">
-        <v>6.02</v>
+        <v>0.6</v>
       </c>
       <c r="P44" t="n">
-        <v>6.09</v>
+        <v>0.61</v>
       </c>
       <c r="Q44" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="R44" t="n">
-        <v>8.49</v>
+        <v>0.85</v>
       </c>
       <c r="S44" t="n">
-        <v>6.777</v>
+        <v>0.677</v>
       </c>
       <c r="T44" t="n">
         <v>3</v>
@@ -4070,19 +4070,19 @@
         </is>
       </c>
       <c r="O45" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P45" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="R45" t="n">
-        <v>7.95</v>
+        <v>0.8</v>
       </c>
       <c r="S45" t="n">
-        <v>9.5565</v>
+        <v>0.956</v>
       </c>
       <c r="T45" t="n">
         <v>1</v>
@@ -4151,19 +4151,19 @@
         </is>
       </c>
       <c r="O46" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P46" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="R46" t="n">
-        <v>6.18</v>
+        <v>0.62</v>
       </c>
       <c r="S46" t="n">
-        <v>8.827</v>
+        <v>0.8829999999999999</v>
       </c>
       <c r="T46" t="n">
         <v>2</v>
@@ -4232,19 +4232,19 @@
         </is>
       </c>
       <c r="O47" t="n">
-        <v>9.609999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="P47" t="n">
-        <v>9.539999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="Q47" t="n">
-        <v>6.11</v>
+        <v>0.61</v>
       </c>
       <c r="R47" t="n">
-        <v>7.2</v>
+        <v>0.72</v>
       </c>
       <c r="S47" t="n">
-        <v>8.524000000000001</v>
+        <v>0.8504999999999999</v>
       </c>
       <c r="T47" t="n">
         <v>3</v>
@@ -4313,19 +4313,19 @@
         </is>
       </c>
       <c r="O48" t="n">
-        <v>9.15</v>
+        <v>0.92</v>
       </c>
       <c r="P48" t="n">
-        <v>9.09</v>
+        <v>0.91</v>
       </c>
       <c r="Q48" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="R48" t="n">
-        <v>7.2</v>
+        <v>0.72</v>
       </c>
       <c r="S48" t="n">
-        <v>8.7265</v>
+        <v>0.8745000000000001</v>
       </c>
       <c r="T48" t="n">
         <v>1</v>
@@ -4394,19 +4394,19 @@
         </is>
       </c>
       <c r="O49" t="n">
-        <v>8.699999999999999</v>
+        <v>0.87</v>
       </c>
       <c r="P49" t="n">
-        <v>8.640000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="Q49" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="R49" t="n">
-        <v>7.2</v>
+        <v>0.72</v>
       </c>
       <c r="S49" t="n">
-        <v>8.577999999999999</v>
+        <v>0.8560000000000001</v>
       </c>
       <c r="T49" t="n">
         <v>2</v>
@@ -4475,19 +4475,19 @@
         </is>
       </c>
       <c r="O50" t="n">
-        <v>6.72</v>
+        <v>0.67</v>
       </c>
       <c r="P50" t="n">
-        <v>6.76</v>
+        <v>0.68</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.06</v>
+        <v>0.41</v>
       </c>
       <c r="R50" t="n">
-        <v>6.03</v>
+        <v>0.6</v>
       </c>
       <c r="S50" t="n">
-        <v>6.0985</v>
+        <v>0.611</v>
       </c>
       <c r="T50" t="n">
         <v>2</v>
@@ -4556,19 +4556,19 @@
         </is>
       </c>
       <c r="O51" t="n">
-        <v>6.13</v>
+        <v>0.61</v>
       </c>
       <c r="P51" t="n">
-        <v>6.19</v>
+        <v>0.62</v>
       </c>
       <c r="Q51" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="R51" t="n">
-        <v>6.03</v>
+        <v>0.6</v>
       </c>
       <c r="S51" t="n">
-        <v>6.629999999999999</v>
+        <v>0.662</v>
       </c>
       <c r="T51" t="n">
         <v>1</v>
@@ -4637,19 +4637,19 @@
         </is>
       </c>
       <c r="O52" t="n">
-        <v>5.31</v>
+        <v>0.53</v>
       </c>
       <c r="P52" t="n">
-        <v>5.4</v>
+        <v>0.54</v>
       </c>
       <c r="Q52" t="n">
-        <v>6.11</v>
+        <v>0.61</v>
       </c>
       <c r="R52" t="n">
-        <v>6.03</v>
+        <v>0.6</v>
       </c>
       <c r="S52" t="n">
-        <v>5.6095</v>
+        <v>0.5599999999999999</v>
       </c>
       <c r="T52" t="n">
         <v>3</v>
@@ -4718,19 +4718,19 @@
         </is>
       </c>
       <c r="O53" t="n">
-        <v>7.47</v>
+        <v>0.75</v>
       </c>
       <c r="P53" t="n">
-        <v>7.66</v>
+        <v>0.77</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.38</v>
+        <v>0.14</v>
       </c>
       <c r="R53" t="n">
-        <v>7.23</v>
+        <v>0.72</v>
       </c>
       <c r="S53" t="n">
-        <v>6.2825</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="T53" t="n">
         <v>3</v>
@@ -4799,19 +4799,19 @@
         </is>
       </c>
       <c r="O54" t="n">
-        <v>7.19</v>
+        <v>0.72</v>
       </c>
       <c r="P54" t="n">
-        <v>7.39</v>
+        <v>0.74</v>
       </c>
       <c r="Q54" t="n">
-        <v>5.92</v>
+        <v>0.59</v>
       </c>
       <c r="R54" t="n">
-        <v>7.23</v>
+        <v>0.72</v>
       </c>
       <c r="S54" t="n">
-        <v>7.012</v>
+        <v>0.701</v>
       </c>
       <c r="T54" t="n">
         <v>2</v>
@@ -4880,19 +4880,19 @@
         </is>
       </c>
       <c r="O55" t="n">
-        <v>6.9</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P55" t="n">
-        <v>7.12</v>
+        <v>0.71</v>
       </c>
       <c r="Q55" t="n">
-        <v>9.109999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="R55" t="n">
-        <v>7.23</v>
+        <v>0.72</v>
       </c>
       <c r="S55" t="n">
-        <v>7.4685</v>
+        <v>0.7454999999999999</v>
       </c>
       <c r="T55" t="n">
         <v>1</v>
@@ -4961,19 +4961,19 @@
         </is>
       </c>
       <c r="O56" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P56" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.86</v>
+        <v>0.29</v>
       </c>
       <c r="R56" t="n">
-        <v>7.78</v>
+        <v>0.78</v>
       </c>
       <c r="S56" t="n">
-        <v>8.239000000000001</v>
+        <v>0.825</v>
       </c>
       <c r="T56" t="n">
         <v>3</v>
@@ -5042,19 +5042,19 @@
         </is>
       </c>
       <c r="O57" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P57" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="R57" t="n">
-        <v>9.08</v>
+        <v>0.91</v>
       </c>
       <c r="S57" t="n">
-        <v>9.262</v>
+        <v>0.9264999999999999</v>
       </c>
       <c r="T57" t="n">
         <v>2</v>
@@ -5123,19 +5123,19 @@
         </is>
       </c>
       <c r="O58" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P58" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="R58" t="n">
-        <v>9.08</v>
+        <v>0.91</v>
       </c>
       <c r="S58" t="n">
-        <v>9.726000000000001</v>
+        <v>0.9724999999999999</v>
       </c>
       <c r="T58" t="n">
         <v>1</v>
@@ -5204,19 +5204,19 @@
         </is>
       </c>
       <c r="O59" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P59" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>6.11</v>
+        <v>0.61</v>
       </c>
       <c r="R59" t="n">
-        <v>8.16</v>
+        <v>0.82</v>
       </c>
       <c r="S59" t="n">
-        <v>8.946</v>
+        <v>0.8949999999999999</v>
       </c>
       <c r="T59" t="n">
         <v>3</v>
@@ -5285,19 +5285,19 @@
         </is>
       </c>
       <c r="O60" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P60" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="R60" t="n">
-        <v>8.16</v>
+        <v>0.82</v>
       </c>
       <c r="S60" t="n">
-        <v>9.444000000000001</v>
+        <v>0.945</v>
       </c>
       <c r="T60" t="n">
         <v>2</v>
@@ -5366,19 +5366,19 @@
         </is>
       </c>
       <c r="O61" t="n">
-        <v>9.76</v>
+        <v>0.98</v>
       </c>
       <c r="P61" t="n">
-        <v>9.720000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="Q61" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R61" t="n">
-        <v>8.16</v>
+        <v>0.82</v>
       </c>
       <c r="S61" t="n">
-        <v>9.554</v>
+        <v>0.9564999999999999</v>
       </c>
       <c r="T61" t="n">
         <v>1</v>
@@ -5447,19 +5447,19 @@
         </is>
       </c>
       <c r="O62" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P62" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="R62" t="n">
-        <v>9.09</v>
+        <v>0.91</v>
       </c>
       <c r="S62" t="n">
-        <v>9.583500000000001</v>
+        <v>0.9584999999999999</v>
       </c>
       <c r="T62" t="n">
         <v>1</v>
@@ -5528,19 +5528,19 @@
         </is>
       </c>
       <c r="O63" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P63" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="R63" t="n">
-        <v>8.75</v>
+        <v>0.87</v>
       </c>
       <c r="S63" t="n">
-        <v>9.532500000000001</v>
+        <v>0.9524999999999999</v>
       </c>
       <c r="T63" t="n">
         <v>2</v>
@@ -5609,19 +5609,19 @@
         </is>
       </c>
       <c r="O64" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P64" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="R64" t="n">
-        <v>8.75</v>
+        <v>0.87</v>
       </c>
       <c r="S64" t="n">
-        <v>8.8385</v>
+        <v>0.8824999999999998</v>
       </c>
       <c r="T64" t="n">
         <v>3</v>
@@ -5690,19 +5690,19 @@
         </is>
       </c>
       <c r="O65" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P65" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="R65" t="n">
-        <v>8.74</v>
+        <v>0.87</v>
       </c>
       <c r="S65" t="n">
-        <v>8.837</v>
+        <v>0.8824999999999998</v>
       </c>
       <c r="T65" t="n">
         <v>3</v>
@@ -5771,19 +5771,19 @@
         </is>
       </c>
       <c r="O66" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P66" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="R66" t="n">
-        <v>8.74</v>
+        <v>0.87</v>
       </c>
       <c r="S66" t="n">
-        <v>9.531000000000001</v>
+        <v>0.9524999999999999</v>
       </c>
       <c r="T66" t="n">
         <v>1</v>
@@ -5852,19 +5852,19 @@
         </is>
       </c>
       <c r="O67" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P67" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="R67" t="n">
-        <v>8.4</v>
+        <v>0.84</v>
       </c>
       <c r="S67" t="n">
-        <v>9.48</v>
+        <v>0.948</v>
       </c>
       <c r="T67" t="n">
         <v>2</v>
@@ -5933,19 +5933,19 @@
         </is>
       </c>
       <c r="O68" t="n">
-        <v>6.94</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P68" t="n">
-        <v>6.98</v>
+        <v>0.7</v>
       </c>
       <c r="Q68" t="n">
-        <v>8.460000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="R68" t="n">
-        <v>6.37</v>
+        <v>0.64</v>
       </c>
       <c r="S68" t="n">
-        <v>7.1725</v>
+        <v>0.718</v>
       </c>
       <c r="T68" t="n">
         <v>3</v>
@@ -6014,19 +6014,19 @@
         </is>
       </c>
       <c r="O69" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P69" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>8.460000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="R69" t="n">
-        <v>8.529999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="S69" t="n">
-        <v>9.471500000000001</v>
+        <v>0.9475</v>
       </c>
       <c r="T69" t="n">
         <v>1</v>
@@ -6095,19 +6095,19 @@
         </is>
       </c>
       <c r="O70" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P70" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>4.5</v>
+        <v>0.45</v>
       </c>
       <c r="R70" t="n">
-        <v>8.529999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="S70" t="n">
-        <v>8.679500000000001</v>
+        <v>0.8674999999999999</v>
       </c>
       <c r="T70" t="n">
         <v>2</v>
@@ -6176,19 +6176,19 @@
         </is>
       </c>
       <c r="O71" t="n">
-        <v>7.93</v>
+        <v>0.79</v>
       </c>
       <c r="P71" t="n">
-        <v>7.87</v>
+        <v>0.79</v>
       </c>
       <c r="Q71" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R71" t="n">
-        <v>8.859999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="S71" t="n">
-        <v>8.4625</v>
+        <v>0.847</v>
       </c>
       <c r="T71" t="n">
         <v>1</v>
@@ -6257,19 +6257,19 @@
         </is>
       </c>
       <c r="O72" t="n">
-        <v>8.25</v>
+        <v>0.82</v>
       </c>
       <c r="P72" t="n">
-        <v>8.18</v>
+        <v>0.82</v>
       </c>
       <c r="Q72" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="R72" t="n">
-        <v>8.859999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="S72" t="n">
-        <v>8.067</v>
+        <v>0.8065</v>
       </c>
       <c r="T72" t="n">
         <v>2</v>
@@ -6338,19 +6338,19 @@
         </is>
       </c>
       <c r="O73" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P73" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>4.06</v>
+        <v>0.41</v>
       </c>
       <c r="R73" t="n">
-        <v>4.35</v>
+        <v>0.44</v>
       </c>
       <c r="S73" t="n">
-        <v>7.9645</v>
+        <v>0.7979999999999998</v>
       </c>
       <c r="T73" t="n">
         <v>3</v>
@@ -6419,19 +6419,19 @@
         </is>
       </c>
       <c r="O74" t="n">
-        <v>8.68</v>
+        <v>0.87</v>
       </c>
       <c r="P74" t="n">
-        <v>8.67</v>
+        <v>0.87</v>
       </c>
       <c r="Q74" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="R74" t="n">
-        <v>8.619999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="S74" t="n">
-        <v>8.651499999999999</v>
+        <v>0.8665</v>
       </c>
       <c r="T74" t="n">
         <v>2</v>
@@ -6500,19 +6500,19 @@
         </is>
       </c>
       <c r="O75" t="n">
-        <v>8.890000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="P75" t="n">
-        <v>8.869999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="Q75" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="R75" t="n">
-        <v>8.619999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="S75" t="n">
-        <v>8.9285</v>
+        <v>0.8935000000000001</v>
       </c>
       <c r="T75" t="n">
         <v>1</v>
@@ -6581,19 +6581,19 @@
         </is>
       </c>
       <c r="O76" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P76" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>6.11</v>
+        <v>0.61</v>
       </c>
       <c r="R76" t="n">
-        <v>5.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="S76" t="n">
-        <v>8.5665</v>
+        <v>0.8559999999999999</v>
       </c>
       <c r="T76" t="n">
         <v>3</v>
@@ -6662,19 +6662,19 @@
         </is>
       </c>
       <c r="O77" t="n">
-        <v>6.05</v>
+        <v>0.61</v>
       </c>
       <c r="P77" t="n">
-        <v>6.01</v>
+        <v>0.6</v>
       </c>
       <c r="Q77" t="n">
-        <v>9.18</v>
+        <v>0.92</v>
       </c>
       <c r="R77" t="n">
-        <v>8.98</v>
+        <v>0.9</v>
       </c>
       <c r="S77" t="n">
-        <v>7.1015</v>
+        <v>0.7120000000000001</v>
       </c>
       <c r="T77" t="n">
         <v>2</v>
@@ -6743,19 +6743,19 @@
         </is>
       </c>
       <c r="O78" t="n">
-        <v>6.58</v>
+        <v>0.66</v>
       </c>
       <c r="P78" t="n">
-        <v>6.53</v>
+        <v>0.65</v>
       </c>
       <c r="Q78" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="R78" t="n">
-        <v>8.98</v>
+        <v>0.9</v>
       </c>
       <c r="S78" t="n">
-        <v>6.6325</v>
+        <v>0.6625</v>
       </c>
       <c r="T78" t="n">
         <v>3</v>
@@ -6824,19 +6824,19 @@
         </is>
       </c>
       <c r="O79" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P79" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.64</v>
+        <v>0.06</v>
       </c>
       <c r="R79" t="n">
-        <v>3.62</v>
+        <v>0.36</v>
       </c>
       <c r="S79" t="n">
-        <v>7.171</v>
+        <v>0.716</v>
       </c>
       <c r="T79" t="n">
         <v>1</v>
@@ -6905,19 +6905,19 @@
         </is>
       </c>
       <c r="O80" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="P80" t="n">
-        <v>7.77</v>
+        <v>0.78</v>
       </c>
       <c r="Q80" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="R80" t="n">
-        <v>7.72</v>
+        <v>0.77</v>
       </c>
       <c r="S80" t="n">
-        <v>7.946499999999999</v>
+        <v>0.7945</v>
       </c>
       <c r="T80" t="n">
         <v>1</v>
@@ -6986,19 +6986,19 @@
         </is>
       </c>
       <c r="O81" t="n">
-        <v>8</v>
+        <v>0.8</v>
       </c>
       <c r="P81" t="n">
-        <v>7.94</v>
+        <v>0.79</v>
       </c>
       <c r="Q81" t="n">
-        <v>6.11</v>
+        <v>0.61</v>
       </c>
       <c r="R81" t="n">
-        <v>8.44</v>
+        <v>0.84</v>
       </c>
       <c r="S81" t="n">
-        <v>7.667000000000001</v>
+        <v>0.7645</v>
       </c>
       <c r="T81" t="n">
         <v>2</v>
@@ -7067,19 +7067,19 @@
         </is>
       </c>
       <c r="O82" t="n">
-        <v>8.17</v>
+        <v>0.82</v>
       </c>
       <c r="P82" t="n">
-        <v>8.109999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Q82" t="n">
-        <v>2.86</v>
+        <v>0.29</v>
       </c>
       <c r="R82" t="n">
-        <v>6.29</v>
+        <v>0.63</v>
       </c>
       <c r="S82" t="n">
-        <v>6.805000000000001</v>
+        <v>0.6819999999999999</v>
       </c>
       <c r="T82" t="n">
         <v>3</v>
@@ -7148,19 +7148,19 @@
         </is>
       </c>
       <c r="O83" t="n">
-        <v>8.16</v>
+        <v>0.82</v>
       </c>
       <c r="P83" t="n">
-        <v>8.1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>2.91</v>
+        <v>0.29</v>
       </c>
       <c r="S83" t="n">
-        <v>5.719499999999999</v>
+        <v>0.573</v>
       </c>
       <c r="T83" t="n">
         <v>3</v>
@@ -7229,19 +7229,19 @@
         </is>
       </c>
       <c r="O84" t="n">
-        <v>7.86</v>
+        <v>0.79</v>
       </c>
       <c r="P84" t="n">
-        <v>7.8</v>
+        <v>0.78</v>
       </c>
       <c r="Q84" t="n">
-        <v>4.06</v>
+        <v>0.41</v>
       </c>
       <c r="R84" t="n">
-        <v>6.24</v>
+        <v>0.62</v>
       </c>
       <c r="S84" t="n">
-        <v>6.836</v>
+        <v>0.6849999999999999</v>
       </c>
       <c r="T84" t="n">
         <v>2</v>
@@ -7310,19 +7310,19 @@
         </is>
       </c>
       <c r="O85" t="n">
-        <v>7.55</v>
+        <v>0.75</v>
       </c>
       <c r="P85" t="n">
-        <v>7.49</v>
+        <v>0.75</v>
       </c>
       <c r="Q85" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="R85" t="n">
-        <v>6.24</v>
+        <v>0.62</v>
       </c>
       <c r="S85" t="n">
-        <v>7.2225</v>
+        <v>0.7204999999999999</v>
       </c>
       <c r="T85" t="n">
         <v>1</v>
@@ -7391,19 +7391,19 @@
         </is>
       </c>
       <c r="O86" t="n">
-        <v>6.02</v>
+        <v>0.6</v>
       </c>
       <c r="P86" t="n">
-        <v>6.08</v>
+        <v>0.61</v>
       </c>
       <c r="Q86" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="R86" t="n">
-        <v>8.44</v>
+        <v>0.84</v>
       </c>
       <c r="S86" t="n">
-        <v>6.765999999999999</v>
+        <v>0.6755</v>
       </c>
       <c r="T86" t="n">
         <v>3</v>
@@ -7472,19 +7472,19 @@
         </is>
       </c>
       <c r="O87" t="n">
-        <v>6.29</v>
+        <v>0.63</v>
       </c>
       <c r="P87" t="n">
-        <v>6.35</v>
+        <v>0.64</v>
       </c>
       <c r="Q87" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R87" t="n">
-        <v>8.44</v>
+        <v>0.84</v>
       </c>
       <c r="S87" t="n">
-        <v>7.3755</v>
+        <v>0.739</v>
       </c>
       <c r="T87" t="n">
         <v>1</v>
@@ -7553,19 +7553,19 @@
         </is>
       </c>
       <c r="O88" t="n">
-        <v>6.57</v>
+        <v>0.66</v>
       </c>
       <c r="P88" t="n">
-        <v>6.62</v>
+        <v>0.66</v>
       </c>
       <c r="Q88" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="R88" t="n">
-        <v>8.779999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="S88" t="n">
-        <v>7.171</v>
+        <v>0.717</v>
       </c>
       <c r="T88" t="n">
         <v>2</v>
@@ -7634,19 +7634,19 @@
         </is>
       </c>
       <c r="O89" t="n">
-        <v>8.550000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="P89" t="n">
-        <v>8.48</v>
+        <v>0.85</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>2.85</v>
+        <v>0.29</v>
       </c>
       <c r="S89" t="n">
-        <v>5.9605</v>
+        <v>0.596</v>
       </c>
       <c r="T89" t="n">
         <v>3</v>
@@ -7715,19 +7715,19 @@
         </is>
       </c>
       <c r="O90" t="n">
-        <v>8.23</v>
+        <v>0.82</v>
       </c>
       <c r="P90" t="n">
-        <v>8.17</v>
+        <v>0.82</v>
       </c>
       <c r="Q90" t="n">
-        <v>4.06</v>
+        <v>0.41</v>
       </c>
       <c r="R90" t="n">
-        <v>6.14</v>
+        <v>0.61</v>
       </c>
       <c r="S90" t="n">
-        <v>7.061500000000001</v>
+        <v>0.7064999999999999</v>
       </c>
       <c r="T90" t="n">
         <v>2</v>
@@ -7796,19 +7796,19 @@
         </is>
       </c>
       <c r="O91" t="n">
-        <v>7.91</v>
+        <v>0.79</v>
       </c>
       <c r="P91" t="n">
-        <v>7.85</v>
+        <v>0.79</v>
       </c>
       <c r="Q91" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="R91" t="n">
-        <v>6.14</v>
+        <v>0.61</v>
       </c>
       <c r="S91" t="n">
-        <v>7.4415</v>
+        <v>0.745</v>
       </c>
       <c r="T91" t="n">
         <v>1</v>
@@ -7877,19 +7877,19 @@
         </is>
       </c>
       <c r="O92" t="n">
-        <v>3.25</v>
+        <v>0.32</v>
       </c>
       <c r="P92" t="n">
-        <v>3.39</v>
+        <v>0.34</v>
       </c>
       <c r="Q92" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R92" t="n">
-        <v>8.039999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="S92" t="n">
-        <v>5.3675</v>
+        <v>0.535</v>
       </c>
       <c r="T92" t="n">
         <v>1</v>
@@ -7958,19 +7958,19 @@
         </is>
       </c>
       <c r="O93" t="n">
-        <v>3.78</v>
+        <v>0.38</v>
       </c>
       <c r="P93" t="n">
-        <v>3.91</v>
+        <v>0.39</v>
       </c>
       <c r="Q93" t="n">
-        <v>7.59</v>
+        <v>0.76</v>
       </c>
       <c r="R93" t="n">
-        <v>8.039999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="S93" t="n">
-        <v>5.2265</v>
+        <v>0.5225</v>
       </c>
       <c r="T93" t="n">
         <v>2</v>
@@ -8039,19 +8039,19 @@
         </is>
       </c>
       <c r="O94" t="n">
-        <v>4.31</v>
+        <v>0.43</v>
       </c>
       <c r="P94" t="n">
-        <v>4.42</v>
+        <v>0.44</v>
       </c>
       <c r="Q94" t="n">
-        <v>4.5</v>
+        <v>0.45</v>
       </c>
       <c r="R94" t="n">
-        <v>8.039999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="S94" t="n">
-        <v>4.946</v>
+        <v>0.493</v>
       </c>
       <c r="T94" t="n">
         <v>3</v>
@@ -8120,19 +8120,19 @@
         </is>
       </c>
       <c r="O95" t="n">
-        <v>6.35</v>
+        <v>0.63</v>
       </c>
       <c r="P95" t="n">
-        <v>6.3</v>
+        <v>0.63</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>2.54</v>
+        <v>0.25</v>
       </c>
       <c r="S95" t="n">
-        <v>4.491</v>
+        <v>0.447</v>
       </c>
       <c r="T95" t="n">
         <v>3</v>
@@ -8201,19 +8201,19 @@
         </is>
       </c>
       <c r="O96" t="n">
-        <v>5.79</v>
+        <v>0.58</v>
       </c>
       <c r="P96" t="n">
-        <v>5.75</v>
+        <v>0.58</v>
       </c>
       <c r="Q96" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="R96" t="n">
-        <v>5.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="S96" t="n">
-        <v>5.616999999999999</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="T96" t="n">
         <v>2</v>
@@ -8282,19 +8282,19 @@
         </is>
       </c>
       <c r="O97" t="n">
-        <v>5.23</v>
+        <v>0.52</v>
       </c>
       <c r="P97" t="n">
-        <v>5.2</v>
+        <v>0.52</v>
       </c>
       <c r="Q97" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="R97" t="n">
-        <v>5.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="S97" t="n">
-        <v>5.9505</v>
+        <v>0.594</v>
       </c>
       <c r="T97" t="n">
         <v>1</v>
@@ -8363,19 +8363,19 @@
         </is>
       </c>
       <c r="O98" t="n">
-        <v>5.65</v>
+        <v>0.57</v>
       </c>
       <c r="P98" t="n">
-        <v>5.96</v>
+        <v>0.6</v>
       </c>
       <c r="Q98" t="n">
-        <v>7</v>
+        <v>0.7</v>
       </c>
       <c r="R98" t="n">
-        <v>7.79</v>
+        <v>0.78</v>
       </c>
       <c r="S98" t="n">
-        <v>6.3495</v>
+        <v>0.638</v>
       </c>
       <c r="T98" t="n">
         <v>3</v>
@@ -8444,19 +8444,19 @@
         </is>
       </c>
       <c r="O99" t="n">
-        <v>6.03</v>
+        <v>0.6</v>
       </c>
       <c r="P99" t="n">
-        <v>6.31</v>
+        <v>0.63</v>
       </c>
       <c r="Q99" t="n">
-        <v>9.32</v>
+        <v>0.93</v>
       </c>
       <c r="R99" t="n">
-        <v>7.79</v>
+        <v>0.78</v>
       </c>
       <c r="S99" t="n">
-        <v>7.05</v>
+        <v>0.7035</v>
       </c>
       <c r="T99" t="n">
         <v>2</v>
@@ -8525,19 +8525,19 @@
         </is>
       </c>
       <c r="O100" t="n">
-        <v>6.4</v>
+        <v>0.64</v>
       </c>
       <c r="P100" t="n">
-        <v>6.66</v>
+        <v>0.67</v>
       </c>
       <c r="Q100" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="R100" t="n">
-        <v>8.119999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="S100" t="n">
-        <v>7.188999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="T100" t="n">
         <v>1</v>
@@ -8606,19 +8606,19 @@
         </is>
       </c>
       <c r="O101" t="n">
-        <v>9.720000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="P101" t="n">
-        <v>9.75</v>
+        <v>0.97</v>
       </c>
       <c r="Q101" t="n">
-        <v>5.13</v>
+        <v>0.51</v>
       </c>
       <c r="R101" t="n">
-        <v>7.76</v>
+        <v>0.78</v>
       </c>
       <c r="S101" t="n">
-        <v>8.5185</v>
+        <v>0.8494999999999999</v>
       </c>
       <c r="T101" t="n">
         <v>3</v>
@@ -8687,19 +8687,19 @@
         </is>
       </c>
       <c r="O102" t="n">
-        <v>9.460000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="P102" t="n">
-        <v>9.5</v>
+        <v>0.95</v>
       </c>
       <c r="Q102" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="R102" t="n">
-        <v>7.76</v>
+        <v>0.78</v>
       </c>
       <c r="S102" t="n">
-        <v>8.893000000000001</v>
+        <v>0.8905</v>
       </c>
       <c r="T102" t="n">
         <v>2</v>
@@ -8768,19 +8768,19 @@
         </is>
       </c>
       <c r="O103" t="n">
-        <v>9.19</v>
+        <v>0.92</v>
       </c>
       <c r="P103" t="n">
-        <v>9.25</v>
+        <v>0.93</v>
       </c>
       <c r="Q103" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R103" t="n">
-        <v>6.61</v>
+        <v>0.66</v>
       </c>
       <c r="S103" t="n">
-        <v>8.985999999999999</v>
+        <v>0.9005000000000001</v>
       </c>
       <c r="T103" t="n">
         <v>1</v>
@@ -8849,19 +8849,19 @@
         </is>
       </c>
       <c r="O104" t="n">
-        <v>8.31</v>
+        <v>0.83</v>
       </c>
       <c r="P104" t="n">
-        <v>8.44</v>
+        <v>0.84</v>
       </c>
       <c r="Q104" t="n">
-        <v>8.6</v>
+        <v>0.86</v>
       </c>
       <c r="R104" t="n">
-        <v>8.859999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="S104" t="n">
-        <v>8.495999999999999</v>
+        <v>0.8485</v>
       </c>
       <c r="T104" t="n">
         <v>3</v>
@@ -8930,19 +8930,19 @@
         </is>
       </c>
       <c r="O105" t="n">
-        <v>8.41</v>
+        <v>0.84</v>
       </c>
       <c r="P105" t="n">
-        <v>8.529999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="Q105" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R105" t="n">
-        <v>8.859999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="S105" t="n">
-        <v>8.8375</v>
+        <v>0.883</v>
       </c>
       <c r="T105" t="n">
         <v>1</v>
@@ -9011,19 +9011,19 @@
         </is>
       </c>
       <c r="O106" t="n">
-        <v>8.57</v>
+        <v>0.86</v>
       </c>
       <c r="P106" t="n">
-        <v>8.67</v>
+        <v>0.87</v>
       </c>
       <c r="Q106" t="n">
-        <v>7.83</v>
+        <v>0.78</v>
       </c>
       <c r="R106" t="n">
-        <v>9.210000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="S106" t="n">
-        <v>8.553000000000001</v>
+        <v>0.8565</v>
       </c>
       <c r="T106" t="n">
         <v>2</v>

--- a/workbooks/scenarios/HVACRagScenarios.xlsx
+++ b/workbooks/scenarios/HVACRagScenarios.xlsx
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>0.47</v>
+        <v>0.54</v>
       </c>
       <c r="P2" t="n">
-        <v>0.46</v>
+        <v>0.53</v>
       </c>
       <c r="Q2" t="n">
         <v>0.92</v>
@@ -599,19 +599,19 @@
         <v>0.84</v>
       </c>
       <c r="S2" t="n">
-        <v>0.612</v>
+        <v>0.6575</v>
       </c>
       <c r="T2" t="n">
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>10.19</v>
+        <v>9.65</v>
       </c>
       <c r="V2" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="W2" t="n">
-        <v>10.61</v>
+        <v>10.05</v>
       </c>
     </row>
     <row r="3">
@@ -668,10 +668,10 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="Q3" t="n">
         <v>0.83</v>
@@ -680,19 +680,19 @@
         <v>0.84</v>
       </c>
       <c r="S3" t="n">
-        <v>0.617</v>
+        <v>0.6625</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>9.640000000000001</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="W3" t="n">
-        <v>10.04</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="4">
@@ -749,10 +749,10 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>0.54</v>
+        <v>0.61</v>
       </c>
       <c r="P4" t="n">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="Q4" t="n">
         <v>0.51</v>
@@ -761,19 +761,19 @@
         <v>0.84</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5755</v>
+        <v>0.621</v>
       </c>
       <c r="T4" t="n">
         <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>9.1</v>
+        <v>8.56</v>
       </c>
       <c r="V4" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="W4" t="n">
-        <v>9.470000000000001</v>
+        <v>8.91</v>
       </c>
     </row>
     <row r="5">
@@ -830,31 +830,31 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>0.55</v>
+        <v>0.25</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.32</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.61</v>
+        <v>0.51</v>
       </c>
       <c r="R5" t="n">
         <v>0.61</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5745</v>
+        <v>0.3805</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>8.93</v>
+        <v>12.96</v>
       </c>
       <c r="V5" t="n">
-        <v>1.7</v>
+        <v>2.46</v>
       </c>
       <c r="W5" t="n">
-        <v>9.109999999999999</v>
+        <v>13.21</v>
       </c>
     </row>
     <row r="6">
@@ -911,31 +911,31 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>0.49</v>
+        <v>0.14</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5</v>
+        <v>0.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="R6" t="n">
         <v>0.61</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5855</v>
+        <v>0.3735</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>9.75</v>
+        <v>14.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.85</v>
+        <v>2.68</v>
       </c>
       <c r="W6" t="n">
-        <v>9.94</v>
+        <v>14.38</v>
       </c>
     </row>
     <row r="7">
@@ -992,31 +992,31 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>0.44</v>
+        <v>0.06</v>
       </c>
       <c r="P7" t="n">
-        <v>0.45</v>
+        <v>0.16</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0.61</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5670000000000001</v>
+        <v>0.3655</v>
       </c>
       <c r="T7" t="n">
         <v>3</v>
       </c>
       <c r="U7" t="n">
-        <v>10.56</v>
+        <v>15.26</v>
       </c>
       <c r="V7" t="n">
-        <v>2.01</v>
+        <v>2.9</v>
       </c>
       <c r="W7" t="n">
-        <v>10.77</v>
+        <v>15.55</v>
       </c>
     </row>
     <row r="8">
@@ -1073,31 +1073,31 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>0.45</v>
+        <v>0.13</v>
       </c>
       <c r="P8" t="n">
-        <v>0.46</v>
+        <v>0.15</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="R8" t="n">
         <v>0.61</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5275000000000001</v>
+        <v>0.305</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>10.47</v>
+        <v>15.32</v>
       </c>
       <c r="V8" t="n">
-        <v>1.99</v>
+        <v>2.91</v>
       </c>
       <c r="W8" t="n">
-        <v>10.67</v>
+        <v>15.61</v>
       </c>
     </row>
     <row r="9">
@@ -1154,31 +1154,31 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>0.39</v>
+        <v>0.04</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.93</v>
+        <v>0.86</v>
       </c>
       <c r="R9" t="n">
         <v>0.61</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5345000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>11.39</v>
+        <v>16.61</v>
       </c>
       <c r="V9" t="n">
-        <v>2.16</v>
+        <v>3.16</v>
       </c>
       <c r="W9" t="n">
-        <v>11.61</v>
+        <v>16.93</v>
       </c>
     </row>
     <row r="10">
@@ -1235,31 +1235,31 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.34</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="R10" t="n">
         <v>0.61</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4815</v>
+        <v>0.2775</v>
       </c>
       <c r="T10" t="n">
         <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>12.31</v>
+        <v>17.9</v>
       </c>
       <c r="V10" t="n">
-        <v>2.34</v>
+        <v>3.4</v>
       </c>
       <c r="W10" t="n">
-        <v>12.54</v>
+        <v>18.25</v>
       </c>
     </row>
     <row r="11">
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>0.43</v>
+        <v>0.51</v>
       </c>
       <c r="P11" t="n">
-        <v>0.44</v>
+        <v>0.52</v>
       </c>
       <c r="Q11" t="n">
         <v>0.83</v>
@@ -1328,19 +1328,19 @@
         <v>0.78</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5660000000000001</v>
+        <v>0.618</v>
       </c>
       <c r="T11" t="n">
         <v>3</v>
       </c>
       <c r="U11" t="n">
-        <v>10.68</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>2.03</v>
+        <v>1.89</v>
       </c>
       <c r="W11" t="n">
-        <v>10.89</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="12">
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>0.47</v>
+        <v>0.55</v>
       </c>
       <c r="P12" t="n">
-        <v>0.48</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Q12" t="n">
         <v>0.92</v>
@@ -1409,19 +1409,19 @@
         <v>0.78</v>
       </c>
       <c r="S12" t="n">
-        <v>0.61</v>
+        <v>0.662</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>10.12</v>
+        <v>9.4</v>
       </c>
       <c r="V12" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="W12" t="n">
-        <v>10.32</v>
+        <v>9.58</v>
       </c>
     </row>
     <row r="13">
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>0.51</v>
+        <v>0.59</v>
       </c>
       <c r="P13" t="n">
-        <v>0.52</v>
+        <v>0.6</v>
       </c>
       <c r="Q13" t="n">
         <v>0.63</v>
@@ -1490,19 +1490,19 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5825</v>
+        <v>0.6345</v>
       </c>
       <c r="T13" t="n">
         <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>9.57</v>
+        <v>8.84</v>
       </c>
       <c r="V13" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="W13" t="n">
-        <v>9.75</v>
+        <v>9.01</v>
       </c>
     </row>
     <row r="14">
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="P14" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="Q14" t="n">
         <v>1</v>
@@ -1571,19 +1571,19 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>0.611</v>
+        <v>0.6465</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>10.62</v>
+        <v>10.21</v>
       </c>
       <c r="V14" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="W14" t="n">
-        <v>10.82</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="15">
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>0.46</v>
+        <v>0.52</v>
       </c>
       <c r="P15" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="Q15" t="n">
         <v>0.86</v>
@@ -1652,19 +1652,19 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5960000000000001</v>
+        <v>0.635</v>
       </c>
       <c r="T15" t="n">
         <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>10.24</v>
+        <v>9.83</v>
       </c>
       <c r="V15" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="W15" t="n">
-        <v>10.43</v>
+        <v>10.02</v>
       </c>
     </row>
     <row r="16">
@@ -1721,10 +1721,10 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>0.49</v>
+        <v>0.55</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Q16" t="n">
         <v>0.7</v>
@@ -1733,19 +1733,19 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5834999999999999</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="T16" t="n">
         <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>9.859999999999999</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="W16" t="n">
-        <v>10.05</v>
+        <v>9.630000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1802,31 +1802,31 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>0.68</v>
+        <v>0.57</v>
       </c>
       <c r="P17" t="n">
-        <v>0.68</v>
+        <v>0.58</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.61</v>
+        <v>0.51</v>
       </c>
       <c r="R17" t="n">
         <v>0.57</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6495000000000001</v>
+        <v>0.5615</v>
       </c>
       <c r="T17" t="n">
         <v>3</v>
       </c>
       <c r="U17" t="n">
-        <v>6.9</v>
+        <v>9.15</v>
       </c>
       <c r="V17" t="n">
-        <v>1.31</v>
+        <v>1.74</v>
       </c>
       <c r="W17" t="n">
-        <v>7.03</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="18">
@@ -1883,31 +1883,31 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>0.64</v>
+        <v>0.51</v>
       </c>
       <c r="P18" t="n">
-        <v>0.64</v>
+        <v>0.52</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="R18" t="n">
         <v>0.57</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6735</v>
+        <v>0.5765</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>7.58</v>
+        <v>9.99</v>
       </c>
       <c r="V18" t="n">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="W18" t="n">
-        <v>7.72</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="19">
@@ -1964,31 +1964,31 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>0.59</v>
+        <v>0.45</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6</v>
+        <v>0.46</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0.57</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6585000000000001</v>
+        <v>0.5815</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>8.25</v>
+        <v>10.82</v>
       </c>
       <c r="V19" t="n">
-        <v>1.57</v>
+        <v>2.06</v>
       </c>
       <c r="W19" t="n">
-        <v>8.41</v>
+        <v>11.03</v>
       </c>
     </row>
     <row r="20">
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>0.53</v>
+        <v>0.59</v>
       </c>
       <c r="P20" t="n">
-        <v>0.53</v>
+        <v>0.59</v>
       </c>
       <c r="Q20" t="n">
         <v>1</v>
@@ -2057,19 +2057,19 @@
         <v>0.83</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6689999999999999</v>
+        <v>0.708</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>9.26</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="W20" t="n">
-        <v>9.44</v>
+        <v>9.06</v>
       </c>
     </row>
     <row r="21">
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>0.54</v>
+        <v>0.6</v>
       </c>
       <c r="P21" t="n">
-        <v>0.55</v>
+        <v>0.61</v>
       </c>
       <c r="Q21" t="n">
         <v>0.93</v>
@@ -2138,19 +2138,19 @@
         <v>0.83</v>
       </c>
       <c r="S21" t="n">
-        <v>0.665</v>
+        <v>0.704</v>
       </c>
       <c r="T21" t="n">
         <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>9.06</v>
+        <v>8.69</v>
       </c>
       <c r="V21" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="W21" t="n">
-        <v>9.24</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="Q22" t="n">
         <v>0.86</v>
@@ -2219,19 +2219,19 @@
         <v>0.83</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6575</v>
+        <v>0.6995</v>
       </c>
       <c r="T22" t="n">
         <v>3</v>
       </c>
       <c r="U22" t="n">
-        <v>8.859999999999999</v>
+        <v>8.49</v>
       </c>
       <c r="V22" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="W22" t="n">
-        <v>9.029999999999999</v>
+        <v>8.66</v>
       </c>
     </row>
     <row r="23">
@@ -2288,31 +2288,31 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>0.66</v>
+        <v>0.44</v>
       </c>
       <c r="P23" t="n">
-        <v>0.66</v>
+        <v>0.45</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.61</v>
+        <v>0.51</v>
       </c>
       <c r="R23" t="n">
         <v>0.64</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6469999999999999</v>
+        <v>0.4875</v>
       </c>
       <c r="T23" t="n">
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>7.23</v>
+        <v>11.05</v>
       </c>
       <c r="V23" t="n">
-        <v>1.37</v>
+        <v>2.1</v>
       </c>
       <c r="W23" t="n">
-        <v>7.37</v>
+        <v>11.27</v>
       </c>
     </row>
     <row r="24">
@@ -2369,31 +2369,31 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.28</v>
       </c>
       <c r="P24" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.29</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="R24" t="n">
         <v>0.64</v>
       </c>
       <c r="S24" t="n">
-        <v>0.632</v>
+        <v>0.4675</v>
       </c>
       <c r="T24" t="n">
         <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>8.800000000000001</v>
+        <v>13.33</v>
       </c>
       <c r="V24" t="n">
-        <v>1.67</v>
+        <v>2.53</v>
       </c>
       <c r="W24" t="n">
-        <v>8.970000000000001</v>
+        <v>13.59</v>
       </c>
     </row>
     <row r="25">
@@ -2450,31 +2450,31 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>0.45</v>
+        <v>0.11</v>
       </c>
       <c r="P25" t="n">
-        <v>0.46</v>
+        <v>0.13</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.15</v>
+        <v>0.29</v>
       </c>
       <c r="R25" t="n">
         <v>0.5</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4010000000000001</v>
+        <v>0.2115</v>
       </c>
       <c r="T25" t="n">
         <v>3</v>
       </c>
       <c r="U25" t="n">
-        <v>10.36</v>
+        <v>15.61</v>
       </c>
       <c r="V25" t="n">
-        <v>1.97</v>
+        <v>2.97</v>
       </c>
       <c r="W25" t="n">
-        <v>10.57</v>
+        <v>15.91</v>
       </c>
     </row>
     <row r="26">
@@ -2531,31 +2531,31 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>0.9</v>
+        <v>0.83</v>
       </c>
       <c r="P26" t="n">
-        <v>0.91</v>
+        <v>0.84</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="R26" t="n">
         <v>0.67</v>
       </c>
       <c r="S26" t="n">
-        <v>0.889</v>
+        <v>0.8295</v>
       </c>
       <c r="T26" t="n">
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>3.49</v>
+        <v>5.55</v>
       </c>
       <c r="V26" t="n">
-        <v>0.66</v>
+        <v>1.05</v>
       </c>
       <c r="W26" t="n">
-        <v>3.41</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="27">
@@ -2612,31 +2612,31 @@
         </is>
       </c>
       <c r="O27" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="P27" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.61</v>
+        <v>0.51</v>
       </c>
       <c r="R27" t="n">
         <v>0.67</v>
       </c>
       <c r="S27" t="n">
-        <v>0.8335</v>
+        <v>0.781</v>
       </c>
       <c r="T27" t="n">
         <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>2.93</v>
+        <v>4.72</v>
       </c>
       <c r="V27" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="W27" t="n">
-        <v>2.86</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="28">
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>0.98</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P28" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -2705,19 +2705,19 @@
         <v>0.32</v>
       </c>
       <c r="S28" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6625</v>
       </c>
       <c r="T28" t="n">
         <v>3</v>
       </c>
       <c r="U28" t="n">
-        <v>2.37</v>
+        <v>3.89</v>
       </c>
       <c r="V28" t="n">
-        <v>0.45</v>
+        <v>0.74</v>
       </c>
       <c r="W28" t="n">
-        <v>2.31</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="29">
@@ -2774,31 +2774,31 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>0.9</v>
+        <v>0.83</v>
       </c>
       <c r="P29" t="n">
-        <v>0.91</v>
+        <v>0.84</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.61</v>
+        <v>0.51</v>
       </c>
       <c r="R29" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="S29" t="n">
-        <v>0.8140000000000001</v>
+        <v>0.7485000000000001</v>
       </c>
       <c r="T29" t="n">
         <v>3</v>
       </c>
       <c r="U29" t="n">
-        <v>3.54</v>
+        <v>5.49</v>
       </c>
       <c r="V29" t="n">
-        <v>0.67</v>
+        <v>1.04</v>
       </c>
       <c r="W29" t="n">
-        <v>3.46</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="30">
@@ -2855,31 +2855,31 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>0.88</v>
+        <v>0.8</v>
       </c>
       <c r="P30" t="n">
-        <v>0.89</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="R30" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="S30" t="n">
-        <v>0.8510000000000001</v>
+        <v>0.783</v>
       </c>
       <c r="T30" t="n">
         <v>2</v>
       </c>
       <c r="U30" t="n">
-        <v>3.87</v>
+        <v>5.97</v>
       </c>
       <c r="V30" t="n">
-        <v>0.73</v>
+        <v>1.13</v>
       </c>
       <c r="W30" t="n">
-        <v>3.77</v>
+        <v>5.83</v>
       </c>
     </row>
     <row r="31">
@@ -2936,31 +2936,31 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>0.86</v>
+        <v>0.77</v>
       </c>
       <c r="P31" t="n">
-        <v>0.87</v>
+        <v>0.79</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="R31" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="S31" t="n">
-        <v>0.866</v>
+        <v>0.797</v>
       </c>
       <c r="T31" t="n">
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>4.08</v>
+        <v>6.29</v>
       </c>
       <c r="V31" t="n">
-        <v>0.78</v>
+        <v>1.2</v>
       </c>
       <c r="W31" t="n">
-        <v>3.98</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="32">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="P32" t="n">
-        <v>0.8</v>
+        <v>0.87</v>
       </c>
       <c r="Q32" t="n">
         <v>0.78</v>
@@ -3029,19 +3029,19 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="S32" t="n">
-        <v>0.8170000000000001</v>
+        <v>0.8655</v>
       </c>
       <c r="T32" t="n">
         <v>3</v>
       </c>
       <c r="U32" t="n">
-        <v>5.04</v>
+        <v>4.81</v>
       </c>
       <c r="V32" t="n">
-        <v>0.96</v>
+        <v>0.91</v>
       </c>
       <c r="W32" t="n">
-        <v>5.14</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="33">
@@ -3098,10 +3098,10 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="P33" t="n">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="Q33" t="n">
         <v>0.93</v>
@@ -3110,19 +3110,19 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="S33" t="n">
-        <v>0.8665</v>
+        <v>0.912</v>
       </c>
       <c r="T33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>4.68</v>
+        <v>4.45</v>
       </c>
       <c r="V33" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="W33" t="n">
-        <v>4.77</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="34">
@@ -3179,31 +3179,31 @@
         </is>
       </c>
       <c r="O34" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="P34" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="Q34" t="n">
         <v>0.7</v>
       </c>
       <c r="R34" t="n">
-        <v>0.7</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="S34" t="n">
-        <v>0.8949999999999999</v>
+        <v>0.879</v>
       </c>
       <c r="T34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="35">
@@ -3263,7 +3263,7 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="Q35" t="n">
         <v>0.45</v>
@@ -3272,19 +3272,19 @@
         <v>0.67</v>
       </c>
       <c r="S35" t="n">
-        <v>0.1905</v>
+        <v>0.1975</v>
       </c>
       <c r="T35" t="n">
         <v>3</v>
       </c>
       <c r="U35" t="n">
-        <v>17.79</v>
+        <v>17.25</v>
       </c>
       <c r="V35" t="n">
-        <v>3.38</v>
+        <v>3.28</v>
       </c>
       <c r="W35" t="n">
-        <v>18.14</v>
+        <v>17.58</v>
       </c>
     </row>
     <row r="36">
@@ -3341,10 +3341,10 @@
         </is>
       </c>
       <c r="O36" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="P36" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="Q36" t="n">
         <v>1</v>
@@ -3353,19 +3353,19 @@
         <v>0.8</v>
       </c>
       <c r="S36" t="n">
-        <v>0.418</v>
+        <v>0.444</v>
       </c>
       <c r="T36" t="n">
         <v>2</v>
       </c>
       <c r="U36" t="n">
-        <v>15.18</v>
+        <v>14.64</v>
       </c>
       <c r="V36" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="W36" t="n">
-        <v>15.48</v>
+        <v>14.92</v>
       </c>
     </row>
     <row r="37">
@@ -3422,10 +3422,10 @@
         </is>
       </c>
       <c r="O37" t="n">
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
       <c r="P37" t="n">
-        <v>0.24</v>
+        <v>0.29</v>
       </c>
       <c r="Q37" t="n">
         <v>0.76</v>
@@ -3434,19 +3434,19 @@
         <v>0.8</v>
       </c>
       <c r="S37" t="n">
-        <v>0.422</v>
+        <v>0.4575</v>
       </c>
       <c r="T37" t="n">
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>13.88</v>
+        <v>13.33</v>
       </c>
       <c r="V37" t="n">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="W37" t="n">
-        <v>14.14</v>
+        <v>13.59</v>
       </c>
     </row>
     <row r="38">
@@ -3503,10 +3503,10 @@
         </is>
       </c>
       <c r="O38" t="n">
-        <v>0.7</v>
+        <v>0.77</v>
       </c>
       <c r="P38" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="Q38" t="n">
         <v>0.78</v>
@@ -3515,19 +3515,19 @@
         <v>0.85</v>
       </c>
       <c r="S38" t="n">
-        <v>0.7349999999999999</v>
+        <v>0.7805</v>
       </c>
       <c r="T38" t="n">
         <v>2</v>
       </c>
       <c r="U38" t="n">
-        <v>6.59</v>
+        <v>6.41</v>
       </c>
       <c r="V38" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W38" t="n">
-        <v>6.86</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="39">
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="O39" t="n">
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
       <c r="P39" t="n">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="Q39" t="n">
         <v>0.93</v>
@@ -3596,19 +3596,19 @@
         <v>0.85</v>
       </c>
       <c r="S39" t="n">
-        <v>0.7845</v>
+        <v>0.8265</v>
       </c>
       <c r="T39" t="n">
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>6.17</v>
+        <v>5.98</v>
       </c>
       <c r="V39" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="W39" t="n">
-        <v>6.42</v>
+        <v>6.23</v>
       </c>
     </row>
     <row r="40">
@@ -3665,10 +3665,10 @@
         </is>
       </c>
       <c r="O40" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="P40" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="Q40" t="n">
         <v>0.51</v>
@@ -3677,19 +3677,19 @@
         <v>0.85</v>
       </c>
       <c r="S40" t="n">
-        <v>0.7235</v>
+        <v>0.7655</v>
       </c>
       <c r="T40" t="n">
         <v>3</v>
       </c>
       <c r="U40" t="n">
-        <v>5.64</v>
+        <v>5.45</v>
       </c>
       <c r="V40" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="W40" t="n">
-        <v>5.87</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="41">
@@ -3746,31 +3746,31 @@
         </is>
       </c>
       <c r="O41" t="n">
-        <v>0.62</v>
+        <v>0.37</v>
       </c>
       <c r="P41" t="n">
-        <v>0.62</v>
+        <v>0.38</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.51</v>
+        <v>0.41</v>
       </c>
       <c r="R41" t="n">
         <v>0.63</v>
       </c>
       <c r="S41" t="n">
-        <v>0.5995</v>
+        <v>0.4205</v>
       </c>
       <c r="T41" t="n">
         <v>2</v>
       </c>
       <c r="U41" t="n">
-        <v>7.89</v>
+        <v>12.02</v>
       </c>
       <c r="V41" t="n">
-        <v>1.5</v>
+        <v>2.28</v>
       </c>
       <c r="W41" t="n">
-        <v>8.050000000000001</v>
+        <v>12.26</v>
       </c>
     </row>
     <row r="42">
@@ -3827,31 +3827,31 @@
         </is>
       </c>
       <c r="O42" t="n">
-        <v>0.55</v>
+        <v>0.26</v>
       </c>
       <c r="P42" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.29</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="R42" t="n">
         <v>0.63</v>
       </c>
       <c r="S42" t="n">
-        <v>0.6275000000000001</v>
+        <v>0.43</v>
       </c>
       <c r="T42" t="n">
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>8.84</v>
+        <v>13.39</v>
       </c>
       <c r="V42" t="n">
-        <v>1.68</v>
+        <v>2.54</v>
       </c>
       <c r="W42" t="n">
-        <v>9.01</v>
+        <v>13.65</v>
       </c>
     </row>
     <row r="43">
@@ -3908,31 +3908,31 @@
         </is>
       </c>
       <c r="O43" t="n">
-        <v>0.46</v>
+        <v>0.08</v>
       </c>
       <c r="P43" t="n">
-        <v>0.47</v>
+        <v>0.15</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.7</v>
+        <v>0.78</v>
       </c>
       <c r="R43" t="n">
         <v>0.63</v>
       </c>
       <c r="S43" t="n">
-        <v>0.537</v>
+        <v>0.327</v>
       </c>
       <c r="T43" t="n">
         <v>3</v>
       </c>
       <c r="U43" t="n">
-        <v>10.25</v>
+        <v>15.44</v>
       </c>
       <c r="V43" t="n">
-        <v>1.95</v>
+        <v>2.93</v>
       </c>
       <c r="W43" t="n">
-        <v>10.45</v>
+        <v>15.74</v>
       </c>
     </row>
     <row r="44">
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="O44" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="P44" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="Q44" t="n">
         <v>0.78</v>
@@ -4001,19 +4001,19 @@
         <v>0.85</v>
       </c>
       <c r="S44" t="n">
-        <v>0.677</v>
+        <v>0.719</v>
       </c>
       <c r="T44" t="n">
         <v>3</v>
       </c>
       <c r="U44" t="n">
-        <v>8.09</v>
+        <v>7.74</v>
       </c>
       <c r="V44" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="W44" t="n">
-        <v>8.25</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="45">
@@ -4070,31 +4070,31 @@
         </is>
       </c>
       <c r="O45" t="n">
-        <v>1</v>
+        <v>0.73</v>
       </c>
       <c r="P45" t="n">
-        <v>1</v>
+        <v>0.73</v>
       </c>
       <c r="Q45" t="n">
         <v>0.93</v>
       </c>
       <c r="R45" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="S45" t="n">
-        <v>0.956</v>
+        <v>0.788</v>
       </c>
       <c r="T45" t="n">
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>6.93</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="46">
@@ -4151,31 +4151,31 @@
         </is>
       </c>
       <c r="O46" t="n">
-        <v>1</v>
+        <v>0.77</v>
       </c>
       <c r="P46" t="n">
-        <v>1</v>
+        <v>0.77</v>
       </c>
       <c r="Q46" t="n">
         <v>0.7</v>
       </c>
       <c r="R46" t="n">
-        <v>0.62</v>
+        <v>0.85</v>
       </c>
       <c r="S46" t="n">
-        <v>0.8829999999999999</v>
+        <v>0.768</v>
       </c>
       <c r="T46" t="n">
         <v>2</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>6.33</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="47">
@@ -4232,31 +4232,31 @@
         </is>
       </c>
       <c r="O47" t="n">
-        <v>0.96</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P47" t="n">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.61</v>
+        <v>0.51</v>
       </c>
       <c r="R47" t="n">
         <v>0.72</v>
       </c>
       <c r="S47" t="n">
-        <v>0.8504999999999999</v>
+        <v>0.8175</v>
       </c>
       <c r="T47" t="n">
         <v>3</v>
       </c>
       <c r="U47" t="n">
-        <v>2.6</v>
+        <v>3.98</v>
       </c>
       <c r="V47" t="n">
-        <v>0.49</v>
+        <v>0.76</v>
       </c>
       <c r="W47" t="n">
-        <v>2.71</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="48">
@@ -4313,31 +4313,31 @@
         </is>
       </c>
       <c r="O48" t="n">
-        <v>0.92</v>
+        <v>0.87</v>
       </c>
       <c r="P48" t="n">
-        <v>0.91</v>
+        <v>0.86</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="R48" t="n">
         <v>0.72</v>
       </c>
       <c r="S48" t="n">
-        <v>0.8745000000000001</v>
+        <v>0.826</v>
       </c>
       <c r="T48" t="n">
         <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>3.29</v>
+        <v>4.96</v>
       </c>
       <c r="V48" t="n">
-        <v>0.63</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="W48" t="n">
-        <v>3.43</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="49">
@@ -4394,31 +4394,31 @@
         </is>
       </c>
       <c r="O49" t="n">
-        <v>0.87</v>
+        <v>0.8</v>
       </c>
       <c r="P49" t="n">
-        <v>0.86</v>
+        <v>0.79</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="R49" t="n">
         <v>0.72</v>
       </c>
       <c r="S49" t="n">
-        <v>0.8560000000000001</v>
+        <v>0.8245</v>
       </c>
       <c r="T49" t="n">
         <v>2</v>
       </c>
       <c r="U49" t="n">
-        <v>3.99</v>
+        <v>5.94</v>
       </c>
       <c r="V49" t="n">
-        <v>0.76</v>
+        <v>1.13</v>
       </c>
       <c r="W49" t="n">
-        <v>4.15</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="50">
@@ -4475,31 +4475,31 @@
         </is>
       </c>
       <c r="O50" t="n">
-        <v>0.67</v>
+        <v>0.47</v>
       </c>
       <c r="P50" t="n">
-        <v>0.68</v>
+        <v>0.48</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.41</v>
+        <v>0.29</v>
       </c>
       <c r="R50" t="n">
         <v>0.6</v>
       </c>
       <c r="S50" t="n">
-        <v>0.611</v>
+        <v>0.457</v>
       </c>
       <c r="T50" t="n">
         <v>2</v>
       </c>
       <c r="U50" t="n">
-        <v>7.03</v>
+        <v>10.58</v>
       </c>
       <c r="V50" t="n">
-        <v>1.34</v>
+        <v>2.01</v>
       </c>
       <c r="W50" t="n">
-        <v>7.17</v>
+        <v>10.79</v>
       </c>
     </row>
     <row r="51">
@@ -4556,31 +4556,31 @@
         </is>
       </c>
       <c r="O51" t="n">
-        <v>0.61</v>
+        <v>0.38</v>
       </c>
       <c r="P51" t="n">
-        <v>0.62</v>
+        <v>0.39</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="R51" t="n">
         <v>0.6</v>
       </c>
       <c r="S51" t="n">
-        <v>0.662</v>
+        <v>0.4965</v>
       </c>
       <c r="T51" t="n">
         <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>7.93</v>
+        <v>11.88</v>
       </c>
       <c r="V51" t="n">
-        <v>1.51</v>
+        <v>2.26</v>
       </c>
       <c r="W51" t="n">
-        <v>8.08</v>
+        <v>12.11</v>
       </c>
     </row>
     <row r="52">
@@ -4637,31 +4637,31 @@
         </is>
       </c>
       <c r="O52" t="n">
-        <v>0.53</v>
+        <v>0.22</v>
       </c>
       <c r="P52" t="n">
-        <v>0.54</v>
+        <v>0.26</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="R52" t="n">
         <v>0.6</v>
       </c>
       <c r="S52" t="n">
-        <v>0.5599999999999999</v>
+        <v>0.387</v>
       </c>
       <c r="T52" t="n">
         <v>3</v>
       </c>
       <c r="U52" t="n">
-        <v>9.18</v>
+        <v>13.71</v>
       </c>
       <c r="V52" t="n">
-        <v>1.74</v>
+        <v>2.6</v>
       </c>
       <c r="W52" t="n">
-        <v>9.359999999999999</v>
+        <v>13.97</v>
       </c>
     </row>
     <row r="53">
@@ -4718,31 +4718,31 @@
         </is>
       </c>
       <c r="O53" t="n">
-        <v>0.75</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P53" t="n">
-        <v>0.77</v>
+        <v>0.59</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
         <v>0.72</v>
       </c>
       <c r="S53" t="n">
-        <v>0.6304999999999999</v>
+        <v>0.4825</v>
       </c>
       <c r="T53" t="n">
         <v>3</v>
       </c>
       <c r="U53" t="n">
-        <v>5.87</v>
+        <v>9.33</v>
       </c>
       <c r="V53" t="n">
-        <v>1.12</v>
+        <v>1.77</v>
       </c>
       <c r="W53" t="n">
-        <v>5.73</v>
+        <v>9.109999999999999</v>
       </c>
     </row>
     <row r="54">
@@ -4799,31 +4799,31 @@
         </is>
       </c>
       <c r="O54" t="n">
-        <v>0.72</v>
+        <v>0.51</v>
       </c>
       <c r="P54" t="n">
-        <v>0.74</v>
+        <v>0.55</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.59</v>
+        <v>0.46</v>
       </c>
       <c r="R54" t="n">
         <v>0.72</v>
       </c>
       <c r="S54" t="n">
-        <v>0.701</v>
+        <v>0.5455</v>
       </c>
       <c r="T54" t="n">
         <v>2</v>
       </c>
       <c r="U54" t="n">
-        <v>6.31</v>
+        <v>9.98</v>
       </c>
       <c r="V54" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="W54" t="n">
-        <v>6.16</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="55">
@@ -4880,31 +4880,31 @@
         </is>
       </c>
       <c r="O55" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.47</v>
       </c>
       <c r="P55" t="n">
-        <v>0.71</v>
+        <v>0.51</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.91</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="R55" t="n">
         <v>0.72</v>
       </c>
       <c r="S55" t="n">
-        <v>0.7454999999999999</v>
+        <v>0.5895</v>
       </c>
       <c r="T55" t="n">
         <v>1</v>
       </c>
       <c r="U55" t="n">
-        <v>6.75</v>
+        <v>10.62</v>
       </c>
       <c r="V55" t="n">
-        <v>1.28</v>
+        <v>2.02</v>
       </c>
       <c r="W55" t="n">
-        <v>6.59</v>
+        <v>10.37</v>
       </c>
     </row>
     <row r="56">
@@ -4967,13 +4967,13 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.29</v>
+        <v>0.15</v>
       </c>
       <c r="R56" t="n">
         <v>0.78</v>
       </c>
       <c r="S56" t="n">
-        <v>0.825</v>
+        <v>0.797</v>
       </c>
       <c r="T56" t="n">
         <v>3</v>
@@ -5048,13 +5048,13 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="R57" t="n">
         <v>0.91</v>
       </c>
       <c r="S57" t="n">
-        <v>0.9264999999999999</v>
+        <v>0.9085</v>
       </c>
       <c r="T57" t="n">
         <v>2</v>
@@ -5129,25 +5129,25 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.93</v>
+        <v>0.86</v>
       </c>
       <c r="R58" t="n">
         <v>0.91</v>
       </c>
       <c r="S58" t="n">
-        <v>0.9724999999999999</v>
+        <v>0.9585</v>
       </c>
       <c r="T58" t="n">
         <v>1</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="59">
@@ -5210,25 +5210,25 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.61</v>
+        <v>0.51</v>
       </c>
       <c r="R59" t="n">
         <v>0.82</v>
       </c>
       <c r="S59" t="n">
-        <v>0.8949999999999999</v>
+        <v>0.875</v>
       </c>
       <c r="T59" t="n">
         <v>3</v>
       </c>
       <c r="U59" t="n">
-        <v>0.62</v>
+        <v>1.45</v>
       </c>
       <c r="V59" t="n">
-        <v>0.12</v>
+        <v>0.28</v>
       </c>
       <c r="W59" t="n">
-        <v>0.64</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="60">
@@ -5291,25 +5291,25 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="R60" t="n">
         <v>0.82</v>
       </c>
       <c r="S60" t="n">
-        <v>0.945</v>
+        <v>0.929</v>
       </c>
       <c r="T60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U60" t="n">
-        <v>1.67</v>
+        <v>2.93</v>
       </c>
       <c r="V60" t="n">
-        <v>0.32</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="W60" t="n">
-        <v>1.7</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="61">
@@ -5366,31 +5366,31 @@
         </is>
       </c>
       <c r="O61" t="n">
-        <v>0.98</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P61" t="n">
-        <v>0.97</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Q61" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="R61" t="n">
         <v>0.82</v>
       </c>
       <c r="S61" t="n">
-        <v>0.9564999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="T61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U61" t="n">
-        <v>2.37</v>
+        <v>3.91</v>
       </c>
       <c r="V61" t="n">
-        <v>0.45</v>
+        <v>0.74</v>
       </c>
       <c r="W61" t="n">
-        <v>2.42</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="62">
@@ -5453,16 +5453,16 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="R62" t="n">
         <v>0.91</v>
       </c>
       <c r="S62" t="n">
-        <v>0.9584999999999999</v>
+        <v>0.9425</v>
       </c>
       <c r="T62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
@@ -5534,16 +5534,16 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="R63" t="n">
         <v>0.87</v>
       </c>
       <c r="S63" t="n">
-        <v>0.9524999999999999</v>
+        <v>0.9665</v>
       </c>
       <c r="T63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
@@ -5615,13 +5615,13 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.51</v>
+        <v>0.61</v>
       </c>
       <c r="R64" t="n">
         <v>0.87</v>
       </c>
       <c r="S64" t="n">
-        <v>0.8824999999999998</v>
+        <v>0.9025</v>
       </c>
       <c r="T64" t="n">
         <v>3</v>
@@ -5696,13 +5696,13 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.51</v>
+        <v>0.41</v>
       </c>
       <c r="R65" t="n">
         <v>0.87</v>
       </c>
       <c r="S65" t="n">
-        <v>0.8824999999999998</v>
+        <v>0.8625</v>
       </c>
       <c r="T65" t="n">
         <v>3</v>
@@ -5777,16 +5777,16 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="R66" t="n">
         <v>0.87</v>
       </c>
       <c r="S66" t="n">
-        <v>0.9524999999999999</v>
+        <v>0.9365</v>
       </c>
       <c r="T66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U66" t="n">
         <v>0</v>
@@ -5858,25 +5858,25 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="R67" t="n">
         <v>0.84</v>
       </c>
       <c r="S67" t="n">
-        <v>0.948</v>
+        <v>0.962</v>
       </c>
       <c r="T67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="W67" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -5933,31 +5933,31 @@
         </is>
       </c>
       <c r="O68" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="P68" t="n">
-        <v>0.7</v>
+        <v>0.78</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.85</v>
+        <v>0.18</v>
       </c>
       <c r="R68" t="n">
         <v>0.64</v>
       </c>
       <c r="S68" t="n">
-        <v>0.718</v>
+        <v>0.639</v>
       </c>
       <c r="T68" t="n">
         <v>3</v>
       </c>
       <c r="U68" t="n">
-        <v>6.69</v>
+        <v>6.14</v>
       </c>
       <c r="V68" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="W68" t="n">
-        <v>6.82</v>
+        <v>6.26</v>
       </c>
     </row>
     <row r="69">
@@ -6014,31 +6014,31 @@
         </is>
       </c>
       <c r="O69" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="P69" t="n">
-        <v>1</v>
+        <v>0.84</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.85</v>
+        <v>0.67</v>
       </c>
       <c r="R69" t="n">
         <v>0.85</v>
       </c>
       <c r="S69" t="n">
-        <v>0.9475</v>
+        <v>0.8105</v>
       </c>
       <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="V69" t="n">
         <v>1</v>
       </c>
-      <c r="U69" t="n">
-        <v>0</v>
-      </c>
-      <c r="V69" t="n">
-        <v>0</v>
-      </c>
       <c r="W69" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="70">
@@ -6095,31 +6095,31 @@
         </is>
       </c>
       <c r="O70" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q70" t="n">
         <v>1</v>
-      </c>
-      <c r="P70" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>0.45</v>
       </c>
       <c r="R70" t="n">
         <v>0.85</v>
       </c>
       <c r="S70" t="n">
-        <v>0.8674999999999999</v>
+        <v>0.9155</v>
       </c>
       <c r="T70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U70" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V70" t="n">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="W70" t="n">
-        <v>0</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="71">
@@ -6176,10 +6176,10 @@
         </is>
       </c>
       <c r="O71" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="P71" t="n">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="Q71" t="n">
         <v>1</v>
@@ -6188,19 +6188,19 @@
         <v>0.89</v>
       </c>
       <c r="S71" t="n">
-        <v>0.847</v>
+        <v>0.8955</v>
       </c>
       <c r="T71" t="n">
         <v>1</v>
       </c>
       <c r="U71" t="n">
-        <v>5.17</v>
+        <v>4.88</v>
       </c>
       <c r="V71" t="n">
-        <v>0.98</v>
+        <v>0.93</v>
       </c>
       <c r="W71" t="n">
-        <v>5.38</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="72">
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="O72" t="n">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="P72" t="n">
-        <v>0.82</v>
+        <v>0.9</v>
       </c>
       <c r="Q72" t="n">
         <v>0.7</v>
@@ -6269,19 +6269,19 @@
         <v>0.89</v>
       </c>
       <c r="S72" t="n">
-        <v>0.8065</v>
+        <v>0.8615</v>
       </c>
       <c r="T72" t="n">
         <v>2</v>
       </c>
       <c r="U72" t="n">
-        <v>4.69</v>
+        <v>4.39</v>
       </c>
       <c r="V72" t="n">
-        <v>0.89</v>
+        <v>0.83</v>
       </c>
       <c r="W72" t="n">
-        <v>4.88</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="73">
@@ -6338,31 +6338,31 @@
         </is>
       </c>
       <c r="O73" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="P73" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="Q73" t="n">
         <v>0.41</v>
       </c>
       <c r="R73" t="n">
-        <v>0.44</v>
+        <v>0.78</v>
       </c>
       <c r="S73" t="n">
-        <v>0.7979999999999998</v>
+        <v>0.8</v>
       </c>
       <c r="T73" t="n">
         <v>3</v>
       </c>
       <c r="U73" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="V73" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="W73" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="74">
@@ -6419,10 +6419,10 @@
         </is>
       </c>
       <c r="O74" t="n">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P74" t="n">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Q74" t="n">
         <v>0.86</v>
@@ -6431,19 +6431,19 @@
         <v>0.86</v>
       </c>
       <c r="S74" t="n">
-        <v>0.8665</v>
+        <v>0.912</v>
       </c>
       <c r="T74" t="n">
         <v>2</v>
       </c>
       <c r="U74" t="n">
-        <v>4.02</v>
+        <v>3.89</v>
       </c>
       <c r="V74" t="n">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="W74" t="n">
-        <v>4.1</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="75">
@@ -6500,10 +6500,10 @@
         </is>
       </c>
       <c r="O75" t="n">
-        <v>0.89</v>
+        <v>0.97</v>
       </c>
       <c r="P75" t="n">
-        <v>0.89</v>
+        <v>0.96</v>
       </c>
       <c r="Q75" t="n">
         <v>0.93</v>
@@ -6512,19 +6512,19 @@
         <v>0.86</v>
       </c>
       <c r="S75" t="n">
-        <v>0.8935000000000001</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="T75" t="n">
         <v>1</v>
       </c>
       <c r="U75" t="n">
-        <v>3.7</v>
+        <v>3.57</v>
       </c>
       <c r="V75" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="W75" t="n">
-        <v>3.77</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="76">
@@ -6584,28 +6584,28 @@
         <v>1</v>
       </c>
       <c r="P76" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="Q76" t="n">
         <v>0.61</v>
       </c>
       <c r="R76" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="S76" t="n">
-        <v>0.8559999999999999</v>
+        <v>0.8975</v>
       </c>
       <c r="T76" t="n">
         <v>3</v>
       </c>
       <c r="U76" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V76" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W76" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="77">
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="O77" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="P77" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="Q77" t="n">
         <v>0.92</v>
@@ -6674,19 +6674,19 @@
         <v>0.9</v>
       </c>
       <c r="S77" t="n">
-        <v>0.7120000000000001</v>
+        <v>0.7575</v>
       </c>
       <c r="T77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U77" t="n">
-        <v>8.050000000000001</v>
+        <v>7.62</v>
       </c>
       <c r="V77" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="W77" t="n">
-        <v>8.380000000000001</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="78">
@@ -6743,10 +6743,10 @@
         </is>
       </c>
       <c r="O78" t="n">
-        <v>0.66</v>
+        <v>0.74</v>
       </c>
       <c r="P78" t="n">
-        <v>0.65</v>
+        <v>0.73</v>
       </c>
       <c r="Q78" t="n">
         <v>0.51</v>
@@ -6755,19 +6755,19 @@
         <v>0.9</v>
       </c>
       <c r="S78" t="n">
-        <v>0.6625</v>
+        <v>0.7145</v>
       </c>
       <c r="T78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U78" t="n">
-        <v>7.24</v>
+        <v>6.82</v>
       </c>
       <c r="V78" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="W78" t="n">
-        <v>7.54</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="79">
@@ -6824,31 +6824,31 @@
         </is>
       </c>
       <c r="O79" t="n">
-        <v>1</v>
+        <v>0.78</v>
       </c>
       <c r="P79" t="n">
-        <v>1</v>
+        <v>0.77</v>
       </c>
       <c r="Q79" t="n">
         <v>0.06</v>
       </c>
       <c r="R79" t="n">
-        <v>0.36</v>
+        <v>0.67</v>
       </c>
       <c r="S79" t="n">
-        <v>0.716</v>
+        <v>0.616</v>
       </c>
       <c r="T79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U79" t="n">
-        <v>0</v>
+        <v>6.22</v>
       </c>
       <c r="V79" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W79" t="n">
-        <v>0</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="80">
@@ -6905,10 +6905,10 @@
         </is>
       </c>
       <c r="O80" t="n">
-        <v>0.78</v>
+        <v>0.86</v>
       </c>
       <c r="P80" t="n">
-        <v>0.78</v>
+        <v>0.85</v>
       </c>
       <c r="Q80" t="n">
         <v>0.86</v>
@@ -6917,19 +6917,19 @@
         <v>0.77</v>
       </c>
       <c r="S80" t="n">
-        <v>0.7945</v>
+        <v>0.843</v>
       </c>
       <c r="T80" t="n">
         <v>1</v>
       </c>
       <c r="U80" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="V80" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="W80" t="n">
         <v>5.33</v>
-      </c>
-      <c r="V80" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W80" t="n">
-        <v>5.55</v>
       </c>
     </row>
     <row r="81">
@@ -6986,10 +6986,10 @@
         </is>
       </c>
       <c r="O81" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="P81" t="n">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="Q81" t="n">
         <v>0.61</v>
@@ -6998,19 +6998,19 @@
         <v>0.84</v>
       </c>
       <c r="S81" t="n">
-        <v>0.7645</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="T81" t="n">
         <v>2</v>
       </c>
       <c r="U81" t="n">
-        <v>5.07</v>
+        <v>4.86</v>
       </c>
       <c r="V81" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="W81" t="n">
-        <v>5.27</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="82">
@@ -7067,10 +7067,10 @@
         </is>
       </c>
       <c r="O82" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="P82" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="Q82" t="n">
         <v>0.29</v>
@@ -7079,19 +7079,19 @@
         <v>0.63</v>
       </c>
       <c r="S82" t="n">
-        <v>0.6819999999999999</v>
+        <v>0.7275</v>
       </c>
       <c r="T82" t="n">
         <v>3</v>
       </c>
       <c r="U82" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="V82" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="W82" t="n">
-        <v>5</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="83">
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="O83" t="n">
-        <v>0.82</v>
+        <v>0.7</v>
       </c>
       <c r="P83" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -7160,19 +7160,19 @@
         <v>0.29</v>
       </c>
       <c r="S83" t="n">
-        <v>0.573</v>
+        <v>0.495</v>
       </c>
       <c r="T83" t="n">
         <v>3</v>
       </c>
       <c r="U83" t="n">
-        <v>4.81</v>
+        <v>7.27</v>
       </c>
       <c r="V83" t="n">
-        <v>0.91</v>
+        <v>1.38</v>
       </c>
       <c r="W83" t="n">
-        <v>5.01</v>
+        <v>7.57</v>
       </c>
     </row>
     <row r="84">
@@ -7229,31 +7229,31 @@
         </is>
       </c>
       <c r="O84" t="n">
-        <v>0.79</v>
+        <v>0.66</v>
       </c>
       <c r="P84" t="n">
-        <v>0.78</v>
+        <v>0.65</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.41</v>
+        <v>0.29</v>
       </c>
       <c r="R84" t="n">
         <v>0.62</v>
       </c>
       <c r="S84" t="n">
-        <v>0.6849999999999999</v>
+        <v>0.5765</v>
       </c>
       <c r="T84" t="n">
         <v>2</v>
       </c>
       <c r="U84" t="n">
-        <v>5.28</v>
+        <v>7.95</v>
       </c>
       <c r="V84" t="n">
-        <v>1</v>
+        <v>1.51</v>
       </c>
       <c r="W84" t="n">
-        <v>5.5</v>
+        <v>8.279999999999999</v>
       </c>
     </row>
     <row r="85">
@@ -7310,31 +7310,31 @@
         </is>
       </c>
       <c r="O85" t="n">
-        <v>0.75</v>
+        <v>0.61</v>
       </c>
       <c r="P85" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="R85" t="n">
         <v>0.62</v>
       </c>
       <c r="S85" t="n">
-        <v>0.7204999999999999</v>
+        <v>0.608</v>
       </c>
       <c r="T85" t="n">
         <v>1</v>
       </c>
       <c r="U85" t="n">
-        <v>5.75</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="V85" t="n">
-        <v>1.09</v>
+        <v>1.64</v>
       </c>
       <c r="W85" t="n">
-        <v>5.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="86">
@@ -7391,10 +7391,10 @@
         </is>
       </c>
       <c r="O86" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="P86" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="Q86" t="n">
         <v>0.78</v>
@@ -7403,19 +7403,19 @@
         <v>0.84</v>
       </c>
       <c r="S86" t="n">
-        <v>0.6755</v>
+        <v>0.7175</v>
       </c>
       <c r="T86" t="n">
         <v>3</v>
       </c>
       <c r="U86" t="n">
-        <v>8.1</v>
+        <v>7.73</v>
       </c>
       <c r="V86" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="W86" t="n">
-        <v>8.26</v>
+        <v>7.88</v>
       </c>
     </row>
     <row r="87">
@@ -7472,10 +7472,10 @@
         </is>
       </c>
       <c r="O87" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="P87" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="Q87" t="n">
         <v>1</v>
@@ -7484,19 +7484,19 @@
         <v>0.84</v>
       </c>
       <c r="S87" t="n">
-        <v>0.739</v>
+        <v>0.781</v>
       </c>
       <c r="T87" t="n">
         <v>1</v>
       </c>
       <c r="U87" t="n">
-        <v>7.68</v>
+        <v>7.31</v>
       </c>
       <c r="V87" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="W87" t="n">
-        <v>7.82</v>
+        <v>7.45</v>
       </c>
     </row>
     <row r="88">
@@ -7553,10 +7553,10 @@
         </is>
       </c>
       <c r="O88" t="n">
-        <v>0.66</v>
+        <v>0.73</v>
       </c>
       <c r="P88" t="n">
-        <v>0.66</v>
+        <v>0.73</v>
       </c>
       <c r="Q88" t="n">
         <v>0.78</v>
@@ -7565,19 +7565,19 @@
         <v>0.88</v>
       </c>
       <c r="S88" t="n">
-        <v>0.717</v>
+        <v>0.7625</v>
       </c>
       <c r="T88" t="n">
         <v>2</v>
       </c>
       <c r="U88" t="n">
-        <v>7.25</v>
+        <v>6.88</v>
       </c>
       <c r="V88" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="W88" t="n">
-        <v>7.39</v>
+        <v>7.02</v>
       </c>
     </row>
     <row r="89">
@@ -7634,10 +7634,10 @@
         </is>
       </c>
       <c r="O89" t="n">
-        <v>0.85</v>
+        <v>0.78</v>
       </c>
       <c r="P89" t="n">
-        <v>0.85</v>
+        <v>0.76</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -7646,19 +7646,19 @@
         <v>0.29</v>
       </c>
       <c r="S89" t="n">
-        <v>0.596</v>
+        <v>0.5435</v>
       </c>
       <c r="T89" t="n">
         <v>3</v>
       </c>
       <c r="U89" t="n">
-        <v>4.23</v>
+        <v>6.27</v>
       </c>
       <c r="V89" t="n">
-        <v>0.8</v>
+        <v>1.19</v>
       </c>
       <c r="W89" t="n">
-        <v>4.4</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="90">
@@ -7715,31 +7715,31 @@
         </is>
       </c>
       <c r="O90" t="n">
-        <v>0.82</v>
+        <v>0.73</v>
       </c>
       <c r="P90" t="n">
-        <v>0.82</v>
+        <v>0.72</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.41</v>
+        <v>0.29</v>
       </c>
       <c r="R90" t="n">
         <v>0.61</v>
       </c>
       <c r="S90" t="n">
-        <v>0.7064999999999999</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="T90" t="n">
         <v>2</v>
       </c>
       <c r="U90" t="n">
-        <v>4.71</v>
+        <v>6.96</v>
       </c>
       <c r="V90" t="n">
-        <v>0.9</v>
+        <v>1.32</v>
       </c>
       <c r="W90" t="n">
-        <v>4.91</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="91">
@@ -7796,31 +7796,31 @@
         </is>
       </c>
       <c r="O91" t="n">
-        <v>0.79</v>
+        <v>0.68</v>
       </c>
       <c r="P91" t="n">
-        <v>0.79</v>
+        <v>0.67</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="R91" t="n">
         <v>0.61</v>
       </c>
       <c r="S91" t="n">
-        <v>0.745</v>
+        <v>0.652</v>
       </c>
       <c r="T91" t="n">
         <v>1</v>
       </c>
       <c r="U91" t="n">
-        <v>5.2</v>
+        <v>7.65</v>
       </c>
       <c r="V91" t="n">
-        <v>0.99</v>
+        <v>1.45</v>
       </c>
       <c r="W91" t="n">
-        <v>5.42</v>
+        <v>7.96</v>
       </c>
     </row>
     <row r="92">
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="O92" t="n">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="P92" t="n">
-        <v>0.34</v>
+        <v>0.39</v>
       </c>
       <c r="Q92" t="n">
         <v>1</v>
@@ -7889,19 +7889,19 @@
         <v>0.8</v>
       </c>
       <c r="S92" t="n">
-        <v>0.535</v>
+        <v>0.5705</v>
       </c>
       <c r="T92" t="n">
         <v>1</v>
       </c>
       <c r="U92" t="n">
-        <v>12.34</v>
+        <v>11.83</v>
       </c>
       <c r="V92" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="W92" t="n">
-        <v>12.58</v>
+        <v>12.06</v>
       </c>
     </row>
     <row r="93">
@@ -7958,10 +7958,10 @@
         </is>
       </c>
       <c r="O93" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="P93" t="n">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="Q93" t="n">
         <v>0.76</v>
@@ -7970,19 +7970,19 @@
         <v>0.8</v>
       </c>
       <c r="S93" t="n">
-        <v>0.5225</v>
+        <v>0.5615</v>
       </c>
       <c r="T93" t="n">
         <v>2</v>
       </c>
       <c r="U93" t="n">
-        <v>11.53</v>
+        <v>11.02</v>
       </c>
       <c r="V93" t="n">
-        <v>2.19</v>
+        <v>2.09</v>
       </c>
       <c r="W93" t="n">
-        <v>11.75</v>
+        <v>11.23</v>
       </c>
     </row>
     <row r="94">
@@ -8039,10 +8039,10 @@
         </is>
       </c>
       <c r="O94" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="P94" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="Q94" t="n">
         <v>0.45</v>
@@ -8051,19 +8051,19 @@
         <v>0.8</v>
       </c>
       <c r="S94" t="n">
-        <v>0.493</v>
+        <v>0.535</v>
       </c>
       <c r="T94" t="n">
         <v>3</v>
       </c>
       <c r="U94" t="n">
-        <v>10.72</v>
+        <v>10.2</v>
       </c>
       <c r="V94" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="W94" t="n">
-        <v>10.93</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="95">
@@ -8120,10 +8120,10 @@
         </is>
       </c>
       <c r="O95" t="n">
-        <v>0.63</v>
+        <v>0.51</v>
       </c>
       <c r="P95" t="n">
-        <v>0.63</v>
+        <v>0.51</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -8132,19 +8132,19 @@
         <v>0.25</v>
       </c>
       <c r="S95" t="n">
-        <v>0.447</v>
+        <v>0.369</v>
       </c>
       <c r="T95" t="n">
         <v>3</v>
       </c>
       <c r="U95" t="n">
-        <v>7.59</v>
+        <v>9.9</v>
       </c>
       <c r="V95" t="n">
-        <v>1.44</v>
+        <v>1.88</v>
       </c>
       <c r="W95" t="n">
-        <v>7.9</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="96">
@@ -8201,31 +8201,31 @@
         </is>
       </c>
       <c r="O96" t="n">
-        <v>0.58</v>
+        <v>0.34</v>
       </c>
       <c r="P96" t="n">
-        <v>0.58</v>
+        <v>0.44</v>
       </c>
       <c r="Q96" t="n">
-        <v>0.51</v>
+        <v>0.41</v>
       </c>
       <c r="R96" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="S96" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.422</v>
       </c>
       <c r="T96" t="n">
         <v>2</v>
       </c>
       <c r="U96" t="n">
-        <v>8.449999999999999</v>
+        <v>10.96</v>
       </c>
       <c r="V96" t="n">
-        <v>1.6</v>
+        <v>2.08</v>
       </c>
       <c r="W96" t="n">
-        <v>8.789999999999999</v>
+        <v>11.41</v>
       </c>
     </row>
     <row r="97">
@@ -8282,31 +8282,31 @@
         </is>
       </c>
       <c r="O97" t="n">
-        <v>0.52</v>
+        <v>0.2</v>
       </c>
       <c r="P97" t="n">
-        <v>0.52</v>
+        <v>0.36</v>
       </c>
       <c r="Q97" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="R97" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="S97" t="n">
-        <v>0.594</v>
+        <v>0.426</v>
       </c>
       <c r="T97" t="n">
         <v>1</v>
       </c>
       <c r="U97" t="n">
-        <v>9.300000000000001</v>
+        <v>12.01</v>
       </c>
       <c r="V97" t="n">
-        <v>1.77</v>
+        <v>2.28</v>
       </c>
       <c r="W97" t="n">
-        <v>9.68</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="98">
@@ -8363,10 +8363,10 @@
         </is>
       </c>
       <c r="O98" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="P98" t="n">
-        <v>0.6</v>
+        <v>0.66</v>
       </c>
       <c r="Q98" t="n">
         <v>0.7</v>
@@ -8375,19 +8375,19 @@
         <v>0.78</v>
       </c>
       <c r="S98" t="n">
-        <v>0.638</v>
+        <v>0.677</v>
       </c>
       <c r="T98" t="n">
         <v>3</v>
       </c>
       <c r="U98" t="n">
-        <v>8.66</v>
+        <v>8.35</v>
       </c>
       <c r="V98" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="W98" t="n">
-        <v>8.449999999999999</v>
+        <v>8.15</v>
       </c>
     </row>
     <row r="99">
@@ -8444,10 +8444,10 @@
         </is>
       </c>
       <c r="O99" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="P99" t="n">
-        <v>0.63</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q99" t="n">
         <v>0.93</v>
@@ -8456,19 +8456,19 @@
         <v>0.78</v>
       </c>
       <c r="S99" t="n">
-        <v>0.7035</v>
+        <v>0.7455000000000001</v>
       </c>
       <c r="T99" t="n">
         <v>2</v>
       </c>
       <c r="U99" t="n">
-        <v>8.08</v>
+        <v>7.78</v>
       </c>
       <c r="V99" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="W99" t="n">
-        <v>7.89</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="100">
@@ -8525,10 +8525,10 @@
         </is>
       </c>
       <c r="O100" t="n">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="P100" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="Q100" t="n">
         <v>0.86</v>
@@ -8537,19 +8537,19 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="S100" t="n">
-        <v>0.72</v>
+        <v>0.762</v>
       </c>
       <c r="T100" t="n">
         <v>1</v>
       </c>
       <c r="U100" t="n">
-        <v>7.51</v>
+        <v>7.21</v>
       </c>
       <c r="V100" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="W100" t="n">
-        <v>7.33</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="101">
@@ -8606,31 +8606,31 @@
         </is>
       </c>
       <c r="O101" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="P101" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.51</v>
+        <v>0.41</v>
       </c>
       <c r="R101" t="n">
         <v>0.78</v>
       </c>
       <c r="S101" t="n">
-        <v>0.8494999999999999</v>
+        <v>0.8165</v>
       </c>
       <c r="T101" t="n">
         <v>3</v>
       </c>
       <c r="U101" t="n">
-        <v>2.43</v>
+        <v>3.84</v>
       </c>
       <c r="V101" t="n">
-        <v>0.46</v>
+        <v>0.73</v>
       </c>
       <c r="W101" t="n">
-        <v>2.37</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="102">
@@ -8687,31 +8687,31 @@
         </is>
       </c>
       <c r="O102" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="P102" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="Q102" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="R102" t="n">
         <v>0.78</v>
       </c>
       <c r="S102" t="n">
-        <v>0.8905</v>
+        <v>0.8485</v>
       </c>
       <c r="T102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U102" t="n">
-        <v>2.83</v>
+        <v>4.44</v>
       </c>
       <c r="V102" t="n">
-        <v>0.54</v>
+        <v>0.84</v>
       </c>
       <c r="W102" t="n">
-        <v>2.77</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="103">
@@ -8768,31 +8768,31 @@
         </is>
       </c>
       <c r="O103" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="P103" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="Q103" t="n">
         <v>0.93</v>
-      </c>
-      <c r="Q103" t="n">
-        <v>1</v>
       </c>
       <c r="R103" t="n">
         <v>0.66</v>
       </c>
       <c r="S103" t="n">
-        <v>0.9005000000000001</v>
+        <v>0.8475</v>
       </c>
       <c r="T103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U103" t="n">
-        <v>3.24</v>
+        <v>5.03</v>
       </c>
       <c r="V103" t="n">
-        <v>0.62</v>
+        <v>0.96</v>
       </c>
       <c r="W103" t="n">
-        <v>3.16</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="104">
@@ -8849,10 +8849,10 @@
         </is>
       </c>
       <c r="O104" t="n">
-        <v>0.83</v>
+        <v>0.91</v>
       </c>
       <c r="P104" t="n">
-        <v>0.84</v>
+        <v>0.92</v>
       </c>
       <c r="Q104" t="n">
         <v>0.86</v>
@@ -8861,19 +8861,19 @@
         <v>0.89</v>
       </c>
       <c r="S104" t="n">
-        <v>0.8485</v>
+        <v>0.9005</v>
       </c>
       <c r="T104" t="n">
         <v>3</v>
       </c>
       <c r="U104" t="n">
-        <v>4.58</v>
+        <v>4.33</v>
       </c>
       <c r="V104" t="n">
-        <v>0.87</v>
+        <v>0.82</v>
       </c>
       <c r="W104" t="n">
-        <v>4.47</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="105">
@@ -8930,10 +8930,10 @@
         </is>
       </c>
       <c r="O105" t="n">
-        <v>0.84</v>
+        <v>0.92</v>
       </c>
       <c r="P105" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="Q105" t="n">
         <v>1</v>
@@ -8942,19 +8942,19 @@
         <v>0.89</v>
       </c>
       <c r="S105" t="n">
-        <v>0.883</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="T105" t="n">
         <v>1</v>
       </c>
       <c r="U105" t="n">
-        <v>4.43</v>
+        <v>4.17</v>
       </c>
       <c r="V105" t="n">
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
       <c r="W105" t="n">
-        <v>4.32</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="106">
@@ -9011,10 +9011,10 @@
         </is>
       </c>
       <c r="O106" t="n">
-        <v>0.86</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P106" t="n">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Q106" t="n">
         <v>0.78</v>
@@ -9023,19 +9023,19 @@
         <v>0.92</v>
       </c>
       <c r="S106" t="n">
-        <v>0.8565</v>
+        <v>0.905</v>
       </c>
       <c r="T106" t="n">
         <v>2</v>
       </c>
       <c r="U106" t="n">
-        <v>4.2</v>
+        <v>3.94</v>
       </c>
       <c r="V106" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="W106" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
     </row>
   </sheetData>

--- a/workbooks/scenarios/HVACRagScenarios.xlsx
+++ b/workbooks/scenarios/HVACRagScenarios.xlsx
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>0.54</v>
+        <v>0.46</v>
       </c>
       <c r="P2" t="n">
-        <v>0.53</v>
+        <v>0.45</v>
       </c>
       <c r="Q2" t="n">
         <v>0.92</v>
@@ -599,7 +599,7 @@
         <v>0.84</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6575</v>
+        <v>0.6055</v>
       </c>
       <c r="T2" t="n">
         <v>2</v>
@@ -668,10 +668,10 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>0.57</v>
+        <v>0.49</v>
       </c>
       <c r="P3" t="n">
-        <v>0.57</v>
+        <v>0.49</v>
       </c>
       <c r="Q3" t="n">
         <v>0.83</v>
@@ -680,7 +680,7 @@
         <v>0.84</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6625</v>
+        <v>0.6105</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -749,10 +749,10 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>0.61</v>
+        <v>0.52</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6</v>
+        <v>0.52</v>
       </c>
       <c r="Q4" t="n">
         <v>0.51</v>
@@ -761,7 +761,7 @@
         <v>0.84</v>
       </c>
       <c r="S4" t="n">
-        <v>0.621</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="T4" t="n">
         <v>3</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>0.25</v>
+        <v>0.58</v>
       </c>
       <c r="P5" t="n">
-        <v>0.32</v>
+        <v>0.59</v>
       </c>
       <c r="Q5" t="n">
         <v>0.51</v>
@@ -842,19 +842,19 @@
         <v>0.61</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3805</v>
+        <v>0.574</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>12.96</v>
+        <v>7.68</v>
       </c>
       <c r="V5" t="n">
-        <v>2.46</v>
+        <v>1.46</v>
       </c>
       <c r="W5" t="n">
-        <v>13.21</v>
+        <v>7.83</v>
       </c>
     </row>
     <row r="6">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>0.14</v>
+        <v>0.51</v>
       </c>
       <c r="P6" t="n">
-        <v>0.24</v>
+        <v>0.52</v>
       </c>
       <c r="Q6" t="n">
         <v>0.78</v>
@@ -923,19 +923,19 @@
         <v>0.61</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3735</v>
+        <v>0.5825</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>14.11</v>
+        <v>8.83</v>
       </c>
       <c r="V6" t="n">
-        <v>2.68</v>
+        <v>1.68</v>
       </c>
       <c r="W6" t="n">
-        <v>14.38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -992,10 +992,10 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>0.06</v>
+        <v>0.44</v>
       </c>
       <c r="P7" t="n">
-        <v>0.16</v>
+        <v>0.45</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -1004,19 +1004,19 @@
         <v>0.61</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3655</v>
+        <v>0.581</v>
       </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>15.26</v>
+        <v>9.98</v>
       </c>
       <c r="V7" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="W7" t="n">
-        <v>15.55</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="8">
@@ -1073,10 +1073,10 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>0.13</v>
+        <v>0.57</v>
       </c>
       <c r="P8" t="n">
-        <v>0.15</v>
+        <v>0.58</v>
       </c>
       <c r="Q8" t="n">
         <v>0.61</v>
@@ -1085,19 +1085,19 @@
         <v>0.61</v>
       </c>
       <c r="S8" t="n">
-        <v>0.305</v>
+        <v>0.5875</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>15.32</v>
+        <v>7.8</v>
       </c>
       <c r="V8" t="n">
-        <v>2.91</v>
+        <v>1.48</v>
       </c>
       <c r="W8" t="n">
-        <v>15.61</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="9">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>0.04</v>
+        <v>0.49</v>
       </c>
       <c r="P9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="Q9" t="n">
         <v>0.86</v>
@@ -1166,19 +1166,19 @@
         <v>0.61</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3</v>
+        <v>0.5855</v>
       </c>
       <c r="T9" t="n">
         <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>16.61</v>
+        <v>9.09</v>
       </c>
       <c r="V9" t="n">
-        <v>3.16</v>
+        <v>1.73</v>
       </c>
       <c r="W9" t="n">
-        <v>16.93</v>
+        <v>9.27</v>
       </c>
     </row>
     <row r="10">
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="Q10" t="n">
         <v>0.93</v>
@@ -1247,19 +1247,19 @@
         <v>0.61</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2775</v>
+        <v>0.5475</v>
       </c>
       <c r="T10" t="n">
         <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>17.9</v>
+        <v>10.38</v>
       </c>
       <c r="V10" t="n">
-        <v>3.4</v>
+        <v>1.97</v>
       </c>
       <c r="W10" t="n">
-        <v>18.25</v>
+        <v>10.58</v>
       </c>
     </row>
     <row r="11">
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>0.51</v>
+        <v>0.44</v>
       </c>
       <c r="P11" t="n">
-        <v>0.52</v>
+        <v>0.45</v>
       </c>
       <c r="Q11" t="n">
         <v>0.83</v>
@@ -1328,7 +1328,7 @@
         <v>0.78</v>
       </c>
       <c r="S11" t="n">
-        <v>0.618</v>
+        <v>0.5725</v>
       </c>
       <c r="T11" t="n">
         <v>3</v>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>0.55</v>
+        <v>0.47</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="Q12" t="n">
         <v>0.92</v>
@@ -1409,7 +1409,7 @@
         <v>0.78</v>
       </c>
       <c r="S12" t="n">
-        <v>0.662</v>
+        <v>0.61</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>0.59</v>
+        <v>0.51</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6</v>
+        <v>0.52</v>
       </c>
       <c r="Q13" t="n">
         <v>0.63</v>
@@ -1490,7 +1490,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6345</v>
+        <v>0.5825</v>
       </c>
       <c r="T13" t="n">
         <v>2</v>
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>0.5</v>
+        <v>0.42</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="Q14" t="n">
         <v>1</v>
@@ -1571,7 +1571,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6465</v>
+        <v>0.598</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>0.52</v>
+        <v>0.44</v>
       </c>
       <c r="P15" t="n">
-        <v>0.53</v>
+        <v>0.46</v>
       </c>
       <c r="Q15" t="n">
         <v>0.86</v>
@@ -1652,7 +1652,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>0.635</v>
+        <v>0.5865</v>
       </c>
       <c r="T15" t="n">
         <v>2</v>
@@ -1721,10 +1721,10 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>0.55</v>
+        <v>0.47</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="Q16" t="n">
         <v>0.7</v>
@@ -1733,7 +1733,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.5705</v>
       </c>
       <c r="T16" t="n">
         <v>3</v>
@@ -1802,10 +1802,10 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>0.57</v>
+        <v>0.91</v>
       </c>
       <c r="P17" t="n">
-        <v>0.58</v>
+        <v>0.91</v>
       </c>
       <c r="Q17" t="n">
         <v>0.51</v>
@@ -1814,19 +1814,19 @@
         <v>0.57</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5615</v>
+        <v>0.779</v>
       </c>
       <c r="T17" t="n">
         <v>3</v>
       </c>
       <c r="U17" t="n">
-        <v>9.15</v>
+        <v>2.5</v>
       </c>
       <c r="V17" t="n">
-        <v>1.74</v>
+        <v>0.47</v>
       </c>
       <c r="W17" t="n">
-        <v>9.33</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="18">
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>0.51</v>
+        <v>0.85</v>
       </c>
       <c r="P18" t="n">
-        <v>0.52</v>
+        <v>0.85</v>
       </c>
       <c r="Q18" t="n">
         <v>0.78</v>
@@ -1895,19 +1895,19 @@
         <v>0.57</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5765</v>
+        <v>0.794</v>
       </c>
       <c r="T18" t="n">
         <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>9.99</v>
+        <v>3.33</v>
       </c>
       <c r="V18" t="n">
-        <v>1.9</v>
+        <v>0.63</v>
       </c>
       <c r="W18" t="n">
-        <v>10.18</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="19">
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>0.45</v>
+        <v>0.8</v>
       </c>
       <c r="P19" t="n">
-        <v>0.46</v>
+        <v>0.8</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
@@ -1976,19 +1976,19 @@
         <v>0.57</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5815</v>
+        <v>0.8055</v>
       </c>
       <c r="T19" t="n">
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>10.82</v>
+        <v>4.17</v>
       </c>
       <c r="V19" t="n">
-        <v>2.06</v>
+        <v>0.79</v>
       </c>
       <c r="W19" t="n">
-        <v>11.03</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="20">
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>0.59</v>
+        <v>0.5</v>
       </c>
       <c r="P20" t="n">
-        <v>0.59</v>
+        <v>0.51</v>
       </c>
       <c r="Q20" t="n">
         <v>1</v>
@@ -2057,7 +2057,7 @@
         <v>0.83</v>
       </c>
       <c r="S20" t="n">
-        <v>0.708</v>
+        <v>0.653</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>0.6</v>
+        <v>0.52</v>
       </c>
       <c r="P21" t="n">
-        <v>0.61</v>
+        <v>0.53</v>
       </c>
       <c r="Q21" t="n">
         <v>0.93</v>
@@ -2138,7 +2138,7 @@
         <v>0.83</v>
       </c>
       <c r="S21" t="n">
-        <v>0.704</v>
+        <v>0.652</v>
       </c>
       <c r="T21" t="n">
         <v>2</v>
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>0.62</v>
+        <v>0.53</v>
       </c>
       <c r="P22" t="n">
-        <v>0.62</v>
+        <v>0.54</v>
       </c>
       <c r="Q22" t="n">
         <v>0.86</v>
@@ -2219,7 +2219,7 @@
         <v>0.83</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6995</v>
+        <v>0.6445</v>
       </c>
       <c r="T22" t="n">
         <v>3</v>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>0.44</v>
+        <v>0.76</v>
       </c>
       <c r="P23" t="n">
-        <v>0.45</v>
+        <v>0.76</v>
       </c>
       <c r="Q23" t="n">
         <v>0.51</v>
@@ -2300,19 +2300,19 @@
         <v>0.64</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4875</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="T23" t="n">
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>11.05</v>
+        <v>4.82</v>
       </c>
       <c r="V23" t="n">
-        <v>2.1</v>
+        <v>0.92</v>
       </c>
       <c r="W23" t="n">
-        <v>11.27</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="24">
@@ -2369,10 +2369,10 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>0.28</v>
+        <v>0.62</v>
       </c>
       <c r="P24" t="n">
-        <v>0.29</v>
+        <v>0.62</v>
       </c>
       <c r="Q24" t="n">
         <v>0.93</v>
@@ -2381,19 +2381,19 @@
         <v>0.64</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4675</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="T24" t="n">
         <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>13.33</v>
+        <v>7.1</v>
       </c>
       <c r="V24" t="n">
-        <v>2.53</v>
+        <v>1.35</v>
       </c>
       <c r="W24" t="n">
-        <v>13.59</v>
+        <v>7.23</v>
       </c>
     </row>
     <row r="25">
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>0.11</v>
+        <v>0.47</v>
       </c>
       <c r="P25" t="n">
-        <v>0.13</v>
+        <v>0.48</v>
       </c>
       <c r="Q25" t="n">
         <v>0.29</v>
@@ -2462,19 +2462,19 @@
         <v>0.5</v>
       </c>
       <c r="S25" t="n">
-        <v>0.2115</v>
+        <v>0.442</v>
       </c>
       <c r="T25" t="n">
         <v>3</v>
       </c>
       <c r="U25" t="n">
-        <v>15.61</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="V25" t="n">
-        <v>2.97</v>
+        <v>1.78</v>
       </c>
       <c r="W25" t="n">
-        <v>15.91</v>
+        <v>9.56</v>
       </c>
     </row>
     <row r="26">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>0.83</v>
+        <v>0.97</v>
       </c>
       <c r="P26" t="n">
-        <v>0.84</v>
+        <v>0.97</v>
       </c>
       <c r="Q26" t="n">
         <v>0.93</v>
@@ -2543,19 +2543,19 @@
         <v>0.67</v>
       </c>
       <c r="S26" t="n">
-        <v>0.8295</v>
+        <v>0.917</v>
       </c>
       <c r="T26" t="n">
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>5.55</v>
+        <v>1.44</v>
       </c>
       <c r="V26" t="n">
-        <v>1.05</v>
+        <v>0.27</v>
       </c>
       <c r="W26" t="n">
-        <v>5.41</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="27">
@@ -2612,10 +2612,10 @@
         </is>
       </c>
       <c r="O27" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="P27" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="Q27" t="n">
         <v>0.51</v>
@@ -2624,19 +2624,19 @@
         <v>0.67</v>
       </c>
       <c r="S27" t="n">
-        <v>0.781</v>
+        <v>0.8525</v>
       </c>
       <c r="T27" t="n">
         <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>4.72</v>
+        <v>0.61</v>
       </c>
       <c r="V27" t="n">
-        <v>0.9</v>
+        <v>0.12</v>
       </c>
       <c r="W27" t="n">
-        <v>4.6</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="28">
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="P28" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -2705,19 +2705,19 @@
         <v>0.32</v>
       </c>
       <c r="S28" t="n">
-        <v>0.6625</v>
+        <v>0.698</v>
       </c>
       <c r="T28" t="n">
         <v>3</v>
       </c>
       <c r="U28" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2774,10 +2774,10 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>0.83</v>
+        <v>0.97</v>
       </c>
       <c r="P29" t="n">
-        <v>0.84</v>
+        <v>0.97</v>
       </c>
       <c r="Q29" t="n">
         <v>0.51</v>
@@ -2786,19 +2786,19 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="S29" t="n">
-        <v>0.7485000000000001</v>
+        <v>0.836</v>
       </c>
       <c r="T29" t="n">
         <v>3</v>
       </c>
       <c r="U29" t="n">
-        <v>5.49</v>
+        <v>1.54</v>
       </c>
       <c r="V29" t="n">
-        <v>1.04</v>
+        <v>0.29</v>
       </c>
       <c r="W29" t="n">
-        <v>5.36</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="30">
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P30" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Q30" t="n">
         <v>0.78</v>
@@ -2867,19 +2867,19 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="S30" t="n">
-        <v>0.783</v>
+        <v>0.8705000000000001</v>
       </c>
       <c r="T30" t="n">
         <v>2</v>
       </c>
       <c r="U30" t="n">
-        <v>5.97</v>
+        <v>2.02</v>
       </c>
       <c r="V30" t="n">
-        <v>1.13</v>
+        <v>0.38</v>
       </c>
       <c r="W30" t="n">
-        <v>5.83</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="31">
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>0.77</v>
+        <v>0.92</v>
       </c>
       <c r="P31" t="n">
-        <v>0.79</v>
+        <v>0.92</v>
       </c>
       <c r="Q31" t="n">
         <v>0.93</v>
@@ -2948,19 +2948,19 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="S31" t="n">
-        <v>0.797</v>
+        <v>0.8875</v>
       </c>
       <c r="T31" t="n">
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>6.29</v>
+        <v>2.34</v>
       </c>
       <c r="V31" t="n">
-        <v>1.2</v>
+        <v>0.44</v>
       </c>
       <c r="W31" t="n">
-        <v>6.14</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="32">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="P32" t="n">
-        <v>0.87</v>
+        <v>0.76</v>
       </c>
       <c r="Q32" t="n">
         <v>0.78</v>
@@ -3029,7 +3029,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="S32" t="n">
-        <v>0.8655</v>
+        <v>0.791</v>
       </c>
       <c r="T32" t="n">
         <v>3</v>
@@ -3098,10 +3098,10 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>0.9</v>
+        <v>0.78</v>
       </c>
       <c r="P33" t="n">
-        <v>0.9</v>
+        <v>0.79</v>
       </c>
       <c r="Q33" t="n">
         <v>0.93</v>
@@ -3110,7 +3110,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="S33" t="n">
-        <v>0.912</v>
+        <v>0.8375</v>
       </c>
       <c r="T33" t="n">
         <v>1</v>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="O34" t="n">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="P34" t="n">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="Q34" t="n">
         <v>0.7</v>
@@ -3191,7 +3191,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="S34" t="n">
-        <v>0.879</v>
+        <v>0.801</v>
       </c>
       <c r="T34" t="n">
         <v>2</v>
@@ -3263,7 +3263,7 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0.45</v>
@@ -3272,7 +3272,7 @@
         <v>0.67</v>
       </c>
       <c r="S35" t="n">
-        <v>0.1975</v>
+        <v>0.1905</v>
       </c>
       <c r="T35" t="n">
         <v>3</v>
@@ -3341,10 +3341,10 @@
         </is>
       </c>
       <c r="O36" t="n">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="P36" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="Q36" t="n">
         <v>1</v>
@@ -3353,7 +3353,7 @@
         <v>0.8</v>
       </c>
       <c r="S36" t="n">
-        <v>0.444</v>
+        <v>0.418</v>
       </c>
       <c r="T36" t="n">
         <v>2</v>
@@ -3422,10 +3422,10 @@
         </is>
       </c>
       <c r="O37" t="n">
-        <v>0.28</v>
+        <v>0.22</v>
       </c>
       <c r="P37" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="Q37" t="n">
         <v>0.76</v>
@@ -3434,7 +3434,7 @@
         <v>0.8</v>
       </c>
       <c r="S37" t="n">
-        <v>0.4575</v>
+        <v>0.422</v>
       </c>
       <c r="T37" t="n">
         <v>1</v>
@@ -3503,10 +3503,10 @@
         </is>
       </c>
       <c r="O38" t="n">
-        <v>0.77</v>
+        <v>0.66</v>
       </c>
       <c r="P38" t="n">
-        <v>0.76</v>
+        <v>0.66</v>
       </c>
       <c r="Q38" t="n">
         <v>0.78</v>
@@ -3515,7 +3515,7 @@
         <v>0.85</v>
       </c>
       <c r="S38" t="n">
-        <v>0.7805</v>
+        <v>0.7125</v>
       </c>
       <c r="T38" t="n">
         <v>2</v>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="O39" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P39" t="n">
-        <v>0.78</v>
+        <v>0.68</v>
       </c>
       <c r="Q39" t="n">
         <v>0.93</v>
@@ -3596,7 +3596,7 @@
         <v>0.85</v>
       </c>
       <c r="S39" t="n">
-        <v>0.8265</v>
+        <v>0.7585</v>
       </c>
       <c r="T39" t="n">
         <v>1</v>
@@ -3665,10 +3665,10 @@
         </is>
       </c>
       <c r="O40" t="n">
-        <v>0.83</v>
+        <v>0.72</v>
       </c>
       <c r="P40" t="n">
-        <v>0.82</v>
+        <v>0.72</v>
       </c>
       <c r="Q40" t="n">
         <v>0.51</v>
@@ -3677,7 +3677,7 @@
         <v>0.85</v>
       </c>
       <c r="S40" t="n">
-        <v>0.7655</v>
+        <v>0.6975</v>
       </c>
       <c r="T40" t="n">
         <v>3</v>
@@ -3746,10 +3746,10 @@
         </is>
       </c>
       <c r="O41" t="n">
-        <v>0.37</v>
+        <v>0.72</v>
       </c>
       <c r="P41" t="n">
-        <v>0.38</v>
+        <v>0.72</v>
       </c>
       <c r="Q41" t="n">
         <v>0.41</v>
@@ -3758,19 +3758,19 @@
         <v>0.63</v>
       </c>
       <c r="S41" t="n">
-        <v>0.4205</v>
+        <v>0.6445</v>
       </c>
       <c r="T41" t="n">
         <v>2</v>
       </c>
       <c r="U41" t="n">
-        <v>12.02</v>
+        <v>5.48</v>
       </c>
       <c r="V41" t="n">
-        <v>2.28</v>
+        <v>1.04</v>
       </c>
       <c r="W41" t="n">
-        <v>12.26</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="42">
@@ -3827,10 +3827,10 @@
         </is>
       </c>
       <c r="O42" t="n">
-        <v>0.26</v>
+        <v>0.63</v>
       </c>
       <c r="P42" t="n">
-        <v>0.29</v>
+        <v>0.64</v>
       </c>
       <c r="Q42" t="n">
         <v>0.78</v>
@@ -3839,19 +3839,19 @@
         <v>0.63</v>
       </c>
       <c r="S42" t="n">
-        <v>0.43</v>
+        <v>0.6635</v>
       </c>
       <c r="T42" t="n">
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>13.39</v>
+        <v>6.84</v>
       </c>
       <c r="V42" t="n">
-        <v>2.54</v>
+        <v>1.3</v>
       </c>
       <c r="W42" t="n">
-        <v>13.65</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="43">
@@ -3908,10 +3908,10 @@
         </is>
       </c>
       <c r="O43" t="n">
-        <v>0.08</v>
+        <v>0.5</v>
       </c>
       <c r="P43" t="n">
-        <v>0.15</v>
+        <v>0.51</v>
       </c>
       <c r="Q43" t="n">
         <v>0.78</v>
@@ -3920,19 +3920,19 @@
         <v>0.63</v>
       </c>
       <c r="S43" t="n">
-        <v>0.327</v>
+        <v>0.579</v>
       </c>
       <c r="T43" t="n">
         <v>3</v>
       </c>
       <c r="U43" t="n">
-        <v>15.44</v>
+        <v>8.9</v>
       </c>
       <c r="V43" t="n">
-        <v>2.93</v>
+        <v>1.69</v>
       </c>
       <c r="W43" t="n">
-        <v>15.74</v>
+        <v>9.07</v>
       </c>
     </row>
     <row r="44">
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="O44" t="n">
-        <v>0.67</v>
+        <v>0.58</v>
       </c>
       <c r="P44" t="n">
-        <v>0.67</v>
+        <v>0.58</v>
       </c>
       <c r="Q44" t="n">
         <v>0.78</v>
@@ -4001,7 +4001,7 @@
         <v>0.85</v>
       </c>
       <c r="S44" t="n">
-        <v>0.719</v>
+        <v>0.6605</v>
       </c>
       <c r="T44" t="n">
         <v>3</v>
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="O45" t="n">
-        <v>0.73</v>
+        <v>0.63</v>
       </c>
       <c r="P45" t="n">
-        <v>0.73</v>
+        <v>0.63</v>
       </c>
       <c r="Q45" t="n">
         <v>0.93</v>
@@ -4082,7 +4082,7 @@
         <v>0.85</v>
       </c>
       <c r="S45" t="n">
-        <v>0.788</v>
+        <v>0.723</v>
       </c>
       <c r="T45" t="n">
         <v>1</v>
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="O46" t="n">
-        <v>0.77</v>
+        <v>0.66</v>
       </c>
       <c r="P46" t="n">
-        <v>0.77</v>
+        <v>0.67</v>
       </c>
       <c r="Q46" t="n">
         <v>0.7</v>
@@ -4163,7 +4163,7 @@
         <v>0.85</v>
       </c>
       <c r="S46" t="n">
-        <v>0.768</v>
+        <v>0.7</v>
       </c>
       <c r="T46" t="n">
         <v>2</v>
@@ -4232,10 +4232,10 @@
         </is>
       </c>
       <c r="O47" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="P47" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="Q47" t="n">
         <v>0.51</v>
@@ -4244,19 +4244,19 @@
         <v>0.72</v>
       </c>
       <c r="S47" t="n">
-        <v>0.8175</v>
+        <v>0.86</v>
       </c>
       <c r="T47" t="n">
         <v>3</v>
       </c>
       <c r="U47" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -4313,10 +4313,10 @@
         </is>
       </c>
       <c r="O48" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="P48" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="Q48" t="n">
         <v>0.78</v>
@@ -4325,19 +4325,19 @@
         <v>0.72</v>
       </c>
       <c r="S48" t="n">
-        <v>0.826</v>
+        <v>0.914</v>
       </c>
       <c r="T48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U48" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>5.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -4394,10 +4394,10 @@
         </is>
       </c>
       <c r="O49" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="P49" t="n">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="Q49" t="n">
         <v>1</v>
@@ -4406,19 +4406,19 @@
         <v>0.72</v>
       </c>
       <c r="S49" t="n">
-        <v>0.8245</v>
+        <v>0.958</v>
       </c>
       <c r="T49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>5.94</v>
+        <v>0.61</v>
       </c>
       <c r="V49" t="n">
-        <v>1.13</v>
+        <v>0.12</v>
       </c>
       <c r="W49" t="n">
-        <v>6.18</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="50">
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="O50" t="n">
-        <v>0.47</v>
+        <v>0.76</v>
       </c>
       <c r="P50" t="n">
-        <v>0.48</v>
+        <v>0.76</v>
       </c>
       <c r="Q50" t="n">
         <v>0.29</v>
@@ -4487,19 +4487,19 @@
         <v>0.6</v>
       </c>
       <c r="S50" t="n">
-        <v>0.457</v>
+        <v>0.642</v>
       </c>
       <c r="T50" t="n">
         <v>2</v>
       </c>
       <c r="U50" t="n">
-        <v>10.58</v>
+        <v>4.82</v>
       </c>
       <c r="V50" t="n">
-        <v>2.01</v>
+        <v>0.92</v>
       </c>
       <c r="W50" t="n">
-        <v>10.79</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="51">
@@ -4556,10 +4556,10 @@
         </is>
       </c>
       <c r="O51" t="n">
-        <v>0.38</v>
+        <v>0.68</v>
       </c>
       <c r="P51" t="n">
-        <v>0.39</v>
+        <v>0.68</v>
       </c>
       <c r="Q51" t="n">
         <v>0.78</v>
@@ -4568,19 +4568,19 @@
         <v>0.6</v>
       </c>
       <c r="S51" t="n">
-        <v>0.4965</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="T51" t="n">
         <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>11.88</v>
+        <v>6.12</v>
       </c>
       <c r="V51" t="n">
-        <v>2.26</v>
+        <v>1.16</v>
       </c>
       <c r="W51" t="n">
-        <v>12.11</v>
+        <v>6.24</v>
       </c>
     </row>
     <row r="52">
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="O52" t="n">
-        <v>0.22</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P52" t="n">
-        <v>0.26</v>
+        <v>0.57</v>
       </c>
       <c r="Q52" t="n">
         <v>0.7</v>
@@ -4649,19 +4649,19 @@
         <v>0.6</v>
       </c>
       <c r="S52" t="n">
-        <v>0.387</v>
+        <v>0.5975</v>
       </c>
       <c r="T52" t="n">
         <v>3</v>
       </c>
       <c r="U52" t="n">
-        <v>13.71</v>
+        <v>7.94</v>
       </c>
       <c r="V52" t="n">
-        <v>2.6</v>
+        <v>1.51</v>
       </c>
       <c r="W52" t="n">
-        <v>13.97</v>
+        <v>8.09</v>
       </c>
     </row>
     <row r="53">
@@ -4718,10 +4718,10 @@
         </is>
       </c>
       <c r="O53" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P53" t="n">
-        <v>0.59</v>
+        <v>0.82</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -4730,19 +4730,19 @@
         <v>0.72</v>
       </c>
       <c r="S53" t="n">
-        <v>0.4825</v>
+        <v>0.638</v>
       </c>
       <c r="T53" t="n">
         <v>3</v>
       </c>
       <c r="U53" t="n">
-        <v>9.33</v>
+        <v>4.01</v>
       </c>
       <c r="V53" t="n">
-        <v>1.77</v>
+        <v>0.76</v>
       </c>
       <c r="W53" t="n">
-        <v>9.109999999999999</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="54">
@@ -4799,10 +4799,10 @@
         </is>
       </c>
       <c r="O54" t="n">
-        <v>0.51</v>
+        <v>0.77</v>
       </c>
       <c r="P54" t="n">
-        <v>0.55</v>
+        <v>0.78</v>
       </c>
       <c r="Q54" t="n">
         <v>0.46</v>
@@ -4811,19 +4811,19 @@
         <v>0.72</v>
       </c>
       <c r="S54" t="n">
-        <v>0.5455</v>
+        <v>0.704</v>
       </c>
       <c r="T54" t="n">
         <v>2</v>
       </c>
       <c r="U54" t="n">
-        <v>9.98</v>
+        <v>4.66</v>
       </c>
       <c r="V54" t="n">
-        <v>1.9</v>
+        <v>0.88</v>
       </c>
       <c r="W54" t="n">
-        <v>9.74</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="55">
@@ -4880,10 +4880,10 @@
         </is>
       </c>
       <c r="O55" t="n">
-        <v>0.47</v>
+        <v>0.73</v>
       </c>
       <c r="P55" t="n">
-        <v>0.51</v>
+        <v>0.75</v>
       </c>
       <c r="Q55" t="n">
         <v>0.8100000000000001</v>
@@ -4892,19 +4892,19 @@
         <v>0.72</v>
       </c>
       <c r="S55" t="n">
-        <v>0.5895</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="T55" t="n">
         <v>1</v>
       </c>
       <c r="U55" t="n">
-        <v>10.62</v>
+        <v>5.3</v>
       </c>
       <c r="V55" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="W55" t="n">
-        <v>10.37</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="56">
@@ -5141,13 +5141,13 @@
         <v>1</v>
       </c>
       <c r="U58" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="V58" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -5222,13 +5222,13 @@
         <v>3</v>
       </c>
       <c r="U59" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V59" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -5300,16 +5300,16 @@
         <v>0.929</v>
       </c>
       <c r="T60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U60" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="V60" t="n">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="O61" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="P61" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="Q61" t="n">
         <v>0.93</v>
@@ -5378,19 +5378,19 @@
         <v>0.82</v>
       </c>
       <c r="S61" t="n">
-        <v>0.92</v>
+        <v>0.959</v>
       </c>
       <c r="T61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U61" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="V61" t="n">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -5870,13 +5870,13 @@
         <v>1</v>
       </c>
       <c r="U67" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="V67" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="W67" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -5933,10 +5933,10 @@
         </is>
       </c>
       <c r="O68" t="n">
-        <v>0.78</v>
+        <v>0.68</v>
       </c>
       <c r="P68" t="n">
-        <v>0.78</v>
+        <v>0.68</v>
       </c>
       <c r="Q68" t="n">
         <v>0.18</v>
@@ -5945,7 +5945,7 @@
         <v>0.64</v>
       </c>
       <c r="S68" t="n">
-        <v>0.639</v>
+        <v>0.574</v>
       </c>
       <c r="T68" t="n">
         <v>3</v>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="O69" t="n">
-        <v>0.85</v>
+        <v>0.73</v>
       </c>
       <c r="P69" t="n">
-        <v>0.84</v>
+        <v>0.73</v>
       </c>
       <c r="Q69" t="n">
         <v>0.67</v>
@@ -6026,7 +6026,7 @@
         <v>0.85</v>
       </c>
       <c r="S69" t="n">
-        <v>0.8105</v>
+        <v>0.736</v>
       </c>
       <c r="T69" t="n">
         <v>2</v>
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="O70" t="n">
-        <v>0.91</v>
+        <v>0.79</v>
       </c>
       <c r="P70" t="n">
-        <v>0.9</v>
+        <v>0.79</v>
       </c>
       <c r="Q70" t="n">
         <v>1</v>
@@ -6107,7 +6107,7 @@
         <v>0.85</v>
       </c>
       <c r="S70" t="n">
-        <v>0.9155</v>
+        <v>0.841</v>
       </c>
       <c r="T70" t="n">
         <v>1</v>
@@ -6176,10 +6176,10 @@
         </is>
       </c>
       <c r="O71" t="n">
-        <v>0.87</v>
+        <v>0.76</v>
       </c>
       <c r="P71" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="Q71" t="n">
         <v>1</v>
@@ -6188,7 +6188,7 @@
         <v>0.89</v>
       </c>
       <c r="S71" t="n">
-        <v>0.8955</v>
+        <v>0.824</v>
       </c>
       <c r="T71" t="n">
         <v>1</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="O72" t="n">
-        <v>0.91</v>
+        <v>0.79</v>
       </c>
       <c r="P72" t="n">
-        <v>0.9</v>
+        <v>0.78</v>
       </c>
       <c r="Q72" t="n">
         <v>0.7</v>
@@ -6269,7 +6269,7 @@
         <v>0.89</v>
       </c>
       <c r="S72" t="n">
-        <v>0.8615</v>
+        <v>0.7835</v>
       </c>
       <c r="T72" t="n">
         <v>2</v>
@@ -6338,10 +6338,10 @@
         </is>
       </c>
       <c r="O73" t="n">
-        <v>0.93</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P73" t="n">
-        <v>0.92</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Q73" t="n">
         <v>0.41</v>
@@ -6350,7 +6350,7 @@
         <v>0.78</v>
       </c>
       <c r="S73" t="n">
-        <v>0.8</v>
+        <v>0.7255</v>
       </c>
       <c r="T73" t="n">
         <v>3</v>
@@ -6419,10 +6419,10 @@
         </is>
       </c>
       <c r="O74" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="P74" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="Q74" t="n">
         <v>0.86</v>
@@ -6431,7 +6431,7 @@
         <v>0.86</v>
       </c>
       <c r="S74" t="n">
-        <v>0.912</v>
+        <v>0.834</v>
       </c>
       <c r="T74" t="n">
         <v>2</v>
@@ -6500,10 +6500,10 @@
         </is>
       </c>
       <c r="O75" t="n">
-        <v>0.97</v>
+        <v>0.84</v>
       </c>
       <c r="P75" t="n">
-        <v>0.96</v>
+        <v>0.84</v>
       </c>
       <c r="Q75" t="n">
         <v>0.93</v>
@@ -6512,7 +6512,7 @@
         <v>0.86</v>
       </c>
       <c r="S75" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.861</v>
       </c>
       <c r="T75" t="n">
         <v>1</v>
@@ -6581,10 +6581,10 @@
         </is>
       </c>
       <c r="O76" t="n">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="P76" t="n">
-        <v>0.99</v>
+        <v>0.87</v>
       </c>
       <c r="Q76" t="n">
         <v>0.61</v>
@@ -6593,7 +6593,7 @@
         <v>0.86</v>
       </c>
       <c r="S76" t="n">
-        <v>0.8975</v>
+        <v>0.8165</v>
       </c>
       <c r="T76" t="n">
         <v>3</v>
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="O77" t="n">
-        <v>0.68</v>
+        <v>0.58</v>
       </c>
       <c r="P77" t="n">
-        <v>0.67</v>
+        <v>0.58</v>
       </c>
       <c r="Q77" t="n">
         <v>0.92</v>
@@ -6674,7 +6674,7 @@
         <v>0.9</v>
       </c>
       <c r="S77" t="n">
-        <v>0.7575</v>
+        <v>0.696</v>
       </c>
       <c r="T77" t="n">
         <v>1</v>
@@ -6743,10 +6743,10 @@
         </is>
       </c>
       <c r="O78" t="n">
-        <v>0.74</v>
+        <v>0.63</v>
       </c>
       <c r="P78" t="n">
-        <v>0.73</v>
+        <v>0.63</v>
       </c>
       <c r="Q78" t="n">
         <v>0.51</v>
@@ -6755,7 +6755,7 @@
         <v>0.9</v>
       </c>
       <c r="S78" t="n">
-        <v>0.7145</v>
+        <v>0.6465</v>
       </c>
       <c r="T78" t="n">
         <v>2</v>
@@ -6824,10 +6824,10 @@
         </is>
       </c>
       <c r="O79" t="n">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="P79" t="n">
-        <v>0.77</v>
+        <v>0.67</v>
       </c>
       <c r="Q79" t="n">
         <v>0.06</v>
@@ -6836,7 +6836,7 @@
         <v>0.67</v>
       </c>
       <c r="S79" t="n">
-        <v>0.616</v>
+        <v>0.548</v>
       </c>
       <c r="T79" t="n">
         <v>3</v>
@@ -6905,10 +6905,10 @@
         </is>
       </c>
       <c r="O80" t="n">
-        <v>0.86</v>
+        <v>0.74</v>
       </c>
       <c r="P80" t="n">
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
       <c r="Q80" t="n">
         <v>0.86</v>
@@ -6917,7 +6917,7 @@
         <v>0.77</v>
       </c>
       <c r="S80" t="n">
-        <v>0.843</v>
+        <v>0.7685</v>
       </c>
       <c r="T80" t="n">
         <v>1</v>
@@ -6986,10 +6986,10 @@
         </is>
       </c>
       <c r="O81" t="n">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="P81" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="Q81" t="n">
         <v>0.61</v>
@@ -6998,7 +6998,7 @@
         <v>0.84</v>
       </c>
       <c r="S81" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.7385</v>
       </c>
       <c r="T81" t="n">
         <v>2</v>
@@ -7067,10 +7067,10 @@
         </is>
       </c>
       <c r="O82" t="n">
-        <v>0.89</v>
+        <v>0.77</v>
       </c>
       <c r="P82" t="n">
-        <v>0.88</v>
+        <v>0.77</v>
       </c>
       <c r="Q82" t="n">
         <v>0.29</v>
@@ -7079,7 +7079,7 @@
         <v>0.63</v>
       </c>
       <c r="S82" t="n">
-        <v>0.7275</v>
+        <v>0.653</v>
       </c>
       <c r="T82" t="n">
         <v>3</v>
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="O83" t="n">
-        <v>0.7</v>
+        <v>0.86</v>
       </c>
       <c r="P83" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
@@ -7160,19 +7160,19 @@
         <v>0.29</v>
       </c>
       <c r="S83" t="n">
-        <v>0.495</v>
+        <v>0.599</v>
       </c>
       <c r="T83" t="n">
         <v>3</v>
       </c>
       <c r="U83" t="n">
-        <v>7.27</v>
+        <v>3.29</v>
       </c>
       <c r="V83" t="n">
-        <v>1.38</v>
+        <v>0.63</v>
       </c>
       <c r="W83" t="n">
-        <v>7.57</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="84">
@@ -7229,10 +7229,10 @@
         </is>
       </c>
       <c r="O84" t="n">
-        <v>0.66</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P84" t="n">
-        <v>0.65</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Q84" t="n">
         <v>0.29</v>
@@ -7241,19 +7241,19 @@
         <v>0.62</v>
       </c>
       <c r="S84" t="n">
-        <v>0.5765</v>
+        <v>0.6775</v>
       </c>
       <c r="T84" t="n">
         <v>2</v>
       </c>
       <c r="U84" t="n">
-        <v>7.95</v>
+        <v>3.98</v>
       </c>
       <c r="V84" t="n">
-        <v>1.51</v>
+        <v>0.76</v>
       </c>
       <c r="W84" t="n">
-        <v>8.279999999999999</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="85">
@@ -7310,10 +7310,10 @@
         </is>
       </c>
       <c r="O85" t="n">
-        <v>0.61</v>
+        <v>0.77</v>
       </c>
       <c r="P85" t="n">
-        <v>0.6</v>
+        <v>0.77</v>
       </c>
       <c r="Q85" t="n">
         <v>0.61</v>
@@ -7322,19 +7322,19 @@
         <v>0.62</v>
       </c>
       <c r="S85" t="n">
-        <v>0.608</v>
+        <v>0.7155</v>
       </c>
       <c r="T85" t="n">
         <v>1</v>
       </c>
       <c r="U85" t="n">
-        <v>8.630000000000001</v>
+        <v>4.66</v>
       </c>
       <c r="V85" t="n">
-        <v>1.64</v>
+        <v>0.89</v>
       </c>
       <c r="W85" t="n">
-        <v>8.99</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="86">
@@ -7391,10 +7391,10 @@
         </is>
       </c>
       <c r="O86" t="n">
-        <v>0.67</v>
+        <v>0.58</v>
       </c>
       <c r="P86" t="n">
-        <v>0.67</v>
+        <v>0.58</v>
       </c>
       <c r="Q86" t="n">
         <v>0.78</v>
@@ -7403,7 +7403,7 @@
         <v>0.84</v>
       </c>
       <c r="S86" t="n">
-        <v>0.7175</v>
+        <v>0.659</v>
       </c>
       <c r="T86" t="n">
         <v>3</v>
@@ -7472,10 +7472,10 @@
         </is>
       </c>
       <c r="O87" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="P87" t="n">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="Q87" t="n">
         <v>1</v>
@@ -7484,7 +7484,7 @@
         <v>0.84</v>
       </c>
       <c r="S87" t="n">
-        <v>0.781</v>
+        <v>0.7195</v>
       </c>
       <c r="T87" t="n">
         <v>1</v>
@@ -7553,10 +7553,10 @@
         </is>
       </c>
       <c r="O88" t="n">
-        <v>0.73</v>
+        <v>0.63</v>
       </c>
       <c r="P88" t="n">
-        <v>0.73</v>
+        <v>0.64</v>
       </c>
       <c r="Q88" t="n">
         <v>0.78</v>
@@ -7565,7 +7565,7 @@
         <v>0.88</v>
       </c>
       <c r="S88" t="n">
-        <v>0.7625</v>
+        <v>0.701</v>
       </c>
       <c r="T88" t="n">
         <v>2</v>
@@ -7634,10 +7634,10 @@
         </is>
       </c>
       <c r="O89" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="P89" t="n">
-        <v>0.76</v>
+        <v>0.92</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -7646,19 +7646,19 @@
         <v>0.29</v>
       </c>
       <c r="S89" t="n">
-        <v>0.5435</v>
+        <v>0.6415</v>
       </c>
       <c r="T89" t="n">
         <v>3</v>
       </c>
       <c r="U89" t="n">
-        <v>6.27</v>
+        <v>2.27</v>
       </c>
       <c r="V89" t="n">
-        <v>1.19</v>
+        <v>0.43</v>
       </c>
       <c r="W89" t="n">
-        <v>6.53</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="90">
@@ -7715,10 +7715,10 @@
         </is>
       </c>
       <c r="O90" t="n">
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
       <c r="P90" t="n">
-        <v>0.72</v>
+        <v>0.87</v>
       </c>
       <c r="Q90" t="n">
         <v>0.29</v>
@@ -7727,19 +7727,19 @@
         <v>0.61</v>
       </c>
       <c r="S90" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.718</v>
       </c>
       <c r="T90" t="n">
         <v>2</v>
       </c>
       <c r="U90" t="n">
-        <v>6.96</v>
+        <v>2.96</v>
       </c>
       <c r="V90" t="n">
-        <v>1.32</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="W90" t="n">
-        <v>7.24</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="91">
@@ -7796,10 +7796,10 @@
         </is>
       </c>
       <c r="O91" t="n">
-        <v>0.68</v>
+        <v>0.83</v>
       </c>
       <c r="P91" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="Q91" t="n">
         <v>0.61</v>
@@ -7808,19 +7808,19 @@
         <v>0.61</v>
       </c>
       <c r="S91" t="n">
-        <v>0.652</v>
+        <v>0.753</v>
       </c>
       <c r="T91" t="n">
         <v>1</v>
       </c>
       <c r="U91" t="n">
-        <v>7.65</v>
+        <v>3.65</v>
       </c>
       <c r="V91" t="n">
-        <v>1.45</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="W91" t="n">
-        <v>7.96</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="92">
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="O92" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="P92" t="n">
-        <v>0.39</v>
+        <v>0.33</v>
       </c>
       <c r="Q92" t="n">
         <v>1</v>
@@ -7889,7 +7889,7 @@
         <v>0.8</v>
       </c>
       <c r="S92" t="n">
-        <v>0.5705</v>
+        <v>0.5315</v>
       </c>
       <c r="T92" t="n">
         <v>1</v>
@@ -7958,10 +7958,10 @@
         </is>
       </c>
       <c r="O93" t="n">
-        <v>0.44</v>
+        <v>0.37</v>
       </c>
       <c r="P93" t="n">
-        <v>0.45</v>
+        <v>0.38</v>
       </c>
       <c r="Q93" t="n">
         <v>0.76</v>
@@ -7970,7 +7970,7 @@
         <v>0.8</v>
       </c>
       <c r="S93" t="n">
-        <v>0.5615</v>
+        <v>0.516</v>
       </c>
       <c r="T93" t="n">
         <v>2</v>
@@ -8039,10 +8039,10 @@
         </is>
       </c>
       <c r="O94" t="n">
-        <v>0.5</v>
+        <v>0.42</v>
       </c>
       <c r="P94" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="Q94" t="n">
         <v>0.45</v>
@@ -8051,7 +8051,7 @@
         <v>0.8</v>
       </c>
       <c r="S94" t="n">
-        <v>0.535</v>
+        <v>0.4865</v>
       </c>
       <c r="T94" t="n">
         <v>3</v>
@@ -8120,10 +8120,10 @@
         </is>
       </c>
       <c r="O95" t="n">
-        <v>0.51</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P95" t="n">
-        <v>0.51</v>
+        <v>0.68</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
@@ -8132,19 +8132,19 @@
         <v>0.25</v>
       </c>
       <c r="S95" t="n">
-        <v>0.369</v>
+        <v>0.4825</v>
       </c>
       <c r="T95" t="n">
         <v>3</v>
       </c>
       <c r="U95" t="n">
-        <v>9.9</v>
+        <v>5.96</v>
       </c>
       <c r="V95" t="n">
-        <v>1.88</v>
+        <v>1.13</v>
       </c>
       <c r="W95" t="n">
-        <v>10.31</v>
+        <v>6.21</v>
       </c>
     </row>
     <row r="96">
@@ -8201,10 +8201,10 @@
         </is>
       </c>
       <c r="O96" t="n">
-        <v>0.34</v>
+        <v>0.62</v>
       </c>
       <c r="P96" t="n">
-        <v>0.44</v>
+        <v>0.62</v>
       </c>
       <c r="Q96" t="n">
         <v>0.41</v>
@@ -8213,19 +8213,19 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="S96" t="n">
-        <v>0.422</v>
+        <v>0.569</v>
       </c>
       <c r="T96" t="n">
         <v>2</v>
       </c>
       <c r="U96" t="n">
-        <v>10.96</v>
+        <v>7.02</v>
       </c>
       <c r="V96" t="n">
-        <v>2.08</v>
+        <v>1.33</v>
       </c>
       <c r="W96" t="n">
-        <v>11.41</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="97">
@@ -8282,10 +8282,10 @@
         </is>
       </c>
       <c r="O97" t="n">
-        <v>0.2</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P97" t="n">
-        <v>0.36</v>
+        <v>0.55</v>
       </c>
       <c r="Q97" t="n">
         <v>0.78</v>
@@ -8294,19 +8294,19 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="S97" t="n">
-        <v>0.426</v>
+        <v>0.6005</v>
       </c>
       <c r="T97" t="n">
         <v>1</v>
       </c>
       <c r="U97" t="n">
-        <v>12.01</v>
+        <v>8.07</v>
       </c>
       <c r="V97" t="n">
-        <v>2.28</v>
+        <v>1.53</v>
       </c>
       <c r="W97" t="n">
-        <v>12.5</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="98">
@@ -8363,10 +8363,10 @@
         </is>
       </c>
       <c r="O98" t="n">
-        <v>0.63</v>
+        <v>0.54</v>
       </c>
       <c r="P98" t="n">
-        <v>0.66</v>
+        <v>0.57</v>
       </c>
       <c r="Q98" t="n">
         <v>0.7</v>
@@ -8375,7 +8375,7 @@
         <v>0.78</v>
       </c>
       <c r="S98" t="n">
-        <v>0.677</v>
+        <v>0.6185</v>
       </c>
       <c r="T98" t="n">
         <v>3</v>
@@ -8444,10 +8444,10 @@
         </is>
       </c>
       <c r="O99" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="P99" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="Q99" t="n">
         <v>0.93</v>
@@ -8456,7 +8456,7 @@
         <v>0.78</v>
       </c>
       <c r="S99" t="n">
-        <v>0.7455000000000001</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="T99" t="n">
         <v>2</v>
@@ -8525,10 +8525,10 @@
         </is>
       </c>
       <c r="O100" t="n">
-        <v>0.71</v>
+        <v>0.61</v>
       </c>
       <c r="P100" t="n">
-        <v>0.73</v>
+        <v>0.64</v>
       </c>
       <c r="Q100" t="n">
         <v>0.86</v>
@@ -8537,7 +8537,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="S100" t="n">
-        <v>0.762</v>
+        <v>0.7005</v>
       </c>
       <c r="T100" t="n">
         <v>1</v>
@@ -8606,10 +8606,10 @@
         </is>
       </c>
       <c r="O101" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="P101" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="Q101" t="n">
         <v>0.41</v>
@@ -8618,19 +8618,19 @@
         <v>0.78</v>
       </c>
       <c r="S101" t="n">
-        <v>0.8165</v>
+        <v>0.849</v>
       </c>
       <c r="T101" t="n">
         <v>3</v>
       </c>
       <c r="U101" t="n">
-        <v>3.84</v>
+        <v>0.24</v>
       </c>
       <c r="V101" t="n">
-        <v>0.73</v>
+        <v>0.05</v>
       </c>
       <c r="W101" t="n">
-        <v>3.75</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="102">
@@ -8687,10 +8687,10 @@
         </is>
       </c>
       <c r="O102" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="P102" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="Q102" t="n">
         <v>0.7</v>
@@ -8699,19 +8699,19 @@
         <v>0.78</v>
       </c>
       <c r="S102" t="n">
-        <v>0.8485</v>
+        <v>0.907</v>
       </c>
       <c r="T102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U102" t="n">
-        <v>4.44</v>
+        <v>0.84</v>
       </c>
       <c r="V102" t="n">
-        <v>0.84</v>
+        <v>0.16</v>
       </c>
       <c r="W102" t="n">
-        <v>4.33</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="103">
@@ -8768,10 +8768,10 @@
         </is>
       </c>
       <c r="O103" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="P103" t="n">
-        <v>0.87</v>
+        <v>0.97</v>
       </c>
       <c r="Q103" t="n">
         <v>0.93</v>
@@ -8780,19 +8780,19 @@
         <v>0.66</v>
       </c>
       <c r="S103" t="n">
-        <v>0.8475</v>
+        <v>0.9155</v>
       </c>
       <c r="T103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U103" t="n">
-        <v>5.03</v>
+        <v>1.43</v>
       </c>
       <c r="V103" t="n">
-        <v>0.96</v>
+        <v>0.27</v>
       </c>
       <c r="W103" t="n">
-        <v>4.91</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="104">
@@ -8849,10 +8849,10 @@
         </is>
       </c>
       <c r="O104" t="n">
-        <v>0.91</v>
+        <v>0.79</v>
       </c>
       <c r="P104" t="n">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="Q104" t="n">
         <v>0.86</v>
@@ -8861,7 +8861,7 @@
         <v>0.89</v>
       </c>
       <c r="S104" t="n">
-        <v>0.9005</v>
+        <v>0.8225</v>
       </c>
       <c r="T104" t="n">
         <v>3</v>
@@ -8930,10 +8930,10 @@
         </is>
       </c>
       <c r="O105" t="n">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="P105" t="n">
-        <v>0.93</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Q105" t="n">
         <v>1</v>
@@ -8942,7 +8942,7 @@
         <v>0.89</v>
       </c>
       <c r="S105" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.857</v>
       </c>
       <c r="T105" t="n">
         <v>1</v>
@@ -9011,10 +9011,10 @@
         </is>
       </c>
       <c r="O106" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P106" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="Q106" t="n">
         <v>0.78</v>
@@ -9023,7 +9023,7 @@
         <v>0.92</v>
       </c>
       <c r="S106" t="n">
-        <v>0.905</v>
+        <v>0.8275</v>
       </c>
       <c r="T106" t="n">
         <v>2</v>

--- a/workbooks/scenarios/HVACRagScenarios.xlsx
+++ b/workbooks/scenarios/HVACRagScenarios.xlsx
@@ -587,31 +587,31 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>0.46</v>
+        <v>0.59</v>
       </c>
       <c r="P2" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="Q2" t="n">
         <v>0.92</v>
       </c>
       <c r="R2" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6055</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>9.65</v>
+        <v>7.33</v>
       </c>
       <c r="V2" t="n">
-        <v>1.83</v>
+        <v>1.39</v>
       </c>
       <c r="W2" t="n">
-        <v>10.05</v>
+        <v>7.63</v>
       </c>
     </row>
     <row r="3">
@@ -668,31 +668,31 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>0.49</v>
+        <v>0.63</v>
       </c>
       <c r="P3" t="n">
-        <v>0.49</v>
+        <v>0.62</v>
       </c>
       <c r="Q3" t="n">
         <v>0.83</v>
       </c>
       <c r="R3" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6105</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>9.109999999999999</v>
+        <v>6.78</v>
       </c>
       <c r="V3" t="n">
-        <v>1.73</v>
+        <v>1.29</v>
       </c>
       <c r="W3" t="n">
-        <v>9.48</v>
+        <v>7.06</v>
       </c>
     </row>
     <row r="4">
@@ -749,31 +749,31 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>0.52</v>
+        <v>0.67</v>
       </c>
       <c r="P4" t="n">
-        <v>0.52</v>
+        <v>0.67</v>
       </c>
       <c r="Q4" t="n">
         <v>0.51</v>
       </c>
       <c r="R4" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.6575</v>
       </c>
       <c r="T4" t="n">
         <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>8.56</v>
+        <v>6.23</v>
       </c>
       <c r="V4" t="n">
-        <v>1.63</v>
+        <v>1.18</v>
       </c>
       <c r="W4" t="n">
-        <v>8.91</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="5">
@@ -830,31 +830,31 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>0.58</v>
+        <v>0.26</v>
       </c>
       <c r="P5" t="n">
-        <v>0.59</v>
+        <v>0.28</v>
       </c>
       <c r="Q5" t="n">
         <v>0.51</v>
       </c>
       <c r="R5" t="n">
-        <v>0.61</v>
+        <v>0.54</v>
       </c>
       <c r="S5" t="n">
-        <v>0.574</v>
+        <v>0.359</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>7.68</v>
+        <v>11.48</v>
       </c>
       <c r="V5" t="n">
-        <v>1.46</v>
+        <v>2.18</v>
       </c>
       <c r="W5" t="n">
-        <v>7.83</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="6">
@@ -911,31 +911,31 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>0.51</v>
+        <v>0.15</v>
       </c>
       <c r="P6" t="n">
-        <v>0.52</v>
+        <v>0.19</v>
       </c>
       <c r="Q6" t="n">
         <v>0.78</v>
       </c>
       <c r="R6" t="n">
-        <v>0.61</v>
+        <v>0.54</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5825</v>
+        <v>0.3485</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>8.83</v>
+        <v>12.63</v>
       </c>
       <c r="V6" t="n">
-        <v>1.68</v>
+        <v>2.4</v>
       </c>
       <c r="W6" t="n">
-        <v>9</v>
+        <v>12.87</v>
       </c>
     </row>
     <row r="7">
@@ -992,31 +992,31 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>0.44</v>
+        <v>0.06</v>
       </c>
       <c r="P7" t="n">
-        <v>0.45</v>
+        <v>0.1</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0.61</v>
+        <v>0.54</v>
       </c>
       <c r="S7" t="n">
-        <v>0.581</v>
+        <v>0.334</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U7" t="n">
-        <v>9.98</v>
+        <v>13.77</v>
       </c>
       <c r="V7" t="n">
-        <v>1.9</v>
+        <v>2.62</v>
       </c>
       <c r="W7" t="n">
-        <v>10.17</v>
+        <v>14.04</v>
       </c>
     </row>
     <row r="8">
@@ -1073,31 +1073,31 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>0.57</v>
+        <v>0.18</v>
       </c>
       <c r="P8" t="n">
-        <v>0.58</v>
+        <v>0.2</v>
       </c>
       <c r="Q8" t="n">
         <v>0.61</v>
       </c>
       <c r="R8" t="n">
-        <v>0.61</v>
+        <v>0.54</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5875</v>
+        <v>0.327</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>7.8</v>
+        <v>12.45</v>
       </c>
       <c r="V8" t="n">
-        <v>1.48</v>
+        <v>2.36</v>
       </c>
       <c r="W8" t="n">
-        <v>7.95</v>
+        <v>12.69</v>
       </c>
     </row>
     <row r="9">
@@ -1154,31 +1154,31 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>0.49</v>
+        <v>0.08</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="Q9" t="n">
         <v>0.86</v>
       </c>
       <c r="R9" t="n">
-        <v>0.61</v>
+        <v>0.54</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5855</v>
+        <v>0.312</v>
       </c>
       <c r="T9" t="n">
         <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>9.09</v>
+        <v>13.74</v>
       </c>
       <c r="V9" t="n">
-        <v>1.73</v>
+        <v>2.61</v>
       </c>
       <c r="W9" t="n">
-        <v>9.27</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
@@ -1235,31 +1235,31 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.42</v>
+        <v>0.01</v>
       </c>
       <c r="Q10" t="n">
         <v>0.93</v>
       </c>
       <c r="R10" t="n">
-        <v>0.61</v>
+        <v>0.54</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5475</v>
+        <v>0.2705</v>
       </c>
       <c r="T10" t="n">
         <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>10.38</v>
+        <v>15.03</v>
       </c>
       <c r="V10" t="n">
-        <v>1.97</v>
+        <v>2.86</v>
       </c>
       <c r="W10" t="n">
-        <v>10.58</v>
+        <v>15.32</v>
       </c>
     </row>
     <row r="11">
@@ -1316,31 +1316,31 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>0.44</v>
+        <v>0.54</v>
       </c>
       <c r="P11" t="n">
-        <v>0.45</v>
+        <v>0.54</v>
       </c>
       <c r="Q11" t="n">
         <v>0.83</v>
       </c>
       <c r="R11" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5725</v>
+        <v>0.622</v>
       </c>
       <c r="T11" t="n">
         <v>3</v>
       </c>
       <c r="U11" t="n">
-        <v>9.949999999999999</v>
+        <v>7.97</v>
       </c>
       <c r="V11" t="n">
-        <v>1.89</v>
+        <v>1.52</v>
       </c>
       <c r="W11" t="n">
-        <v>10.15</v>
+        <v>8.130000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1397,31 +1397,31 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>0.47</v>
+        <v>0.58</v>
       </c>
       <c r="P12" t="n">
-        <v>0.48</v>
+        <v>0.59</v>
       </c>
       <c r="Q12" t="n">
         <v>0.92</v>
       </c>
       <c r="R12" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="S12" t="n">
-        <v>0.61</v>
+        <v>0.6695</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>9.4</v>
+        <v>7.42</v>
       </c>
       <c r="V12" t="n">
-        <v>1.79</v>
+        <v>1.41</v>
       </c>
       <c r="W12" t="n">
-        <v>9.58</v>
+        <v>7.56</v>
       </c>
     </row>
     <row r="13">
@@ -1478,31 +1478,31 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>0.51</v>
+        <v>0.63</v>
       </c>
       <c r="P13" t="n">
-        <v>0.52</v>
+        <v>0.63</v>
       </c>
       <c r="Q13" t="n">
         <v>0.63</v>
       </c>
       <c r="R13" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.73</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5825</v>
+        <v>0.645</v>
       </c>
       <c r="T13" t="n">
         <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>8.84</v>
+        <v>6.86</v>
       </c>
       <c r="V13" t="n">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="W13" t="n">
-        <v>9.01</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="14">
@@ -1559,31 +1559,31 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>0.42</v>
+        <v>0.61</v>
       </c>
       <c r="P14" t="n">
-        <v>0.43</v>
+        <v>0.62</v>
       </c>
       <c r="Q14" t="n">
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="S14" t="n">
-        <v>0.598</v>
+        <v>0.705</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>10.21</v>
+        <v>7.03</v>
       </c>
       <c r="V14" t="n">
-        <v>1.94</v>
+        <v>1.34</v>
       </c>
       <c r="W14" t="n">
-        <v>10.4</v>
+        <v>7.17</v>
       </c>
     </row>
     <row r="15">
@@ -1640,31 +1640,31 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>0.44</v>
+        <v>0.64</v>
       </c>
       <c r="P15" t="n">
-        <v>0.46</v>
+        <v>0.65</v>
       </c>
       <c r="Q15" t="n">
         <v>0.86</v>
       </c>
       <c r="R15" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5865</v>
+        <v>0.6965</v>
       </c>
       <c r="T15" t="n">
         <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>9.83</v>
+        <v>6.65</v>
       </c>
       <c r="V15" t="n">
-        <v>1.87</v>
+        <v>1.26</v>
       </c>
       <c r="W15" t="n">
-        <v>10.02</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="16">
@@ -1721,31 +1721,31 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>0.47</v>
+        <v>0.67</v>
       </c>
       <c r="P16" t="n">
-        <v>0.48</v>
+        <v>0.67</v>
       </c>
       <c r="Q16" t="n">
         <v>0.7</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5705</v>
+        <v>0.6805</v>
       </c>
       <c r="T16" t="n">
         <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>9.449999999999999</v>
+        <v>6.27</v>
       </c>
       <c r="V16" t="n">
-        <v>1.79</v>
+        <v>1.19</v>
       </c>
       <c r="W16" t="n">
-        <v>9.630000000000001</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="17">
@@ -1802,31 +1802,31 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>0.91</v>
+        <v>0.55</v>
       </c>
       <c r="P17" t="n">
-        <v>0.91</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Q17" t="n">
         <v>0.51</v>
       </c>
       <c r="R17" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="S17" t="n">
-        <v>0.779</v>
+        <v>0.544</v>
       </c>
       <c r="T17" t="n">
         <v>3</v>
       </c>
       <c r="U17" t="n">
-        <v>2.5</v>
+        <v>7.77</v>
       </c>
       <c r="V17" t="n">
-        <v>0.47</v>
+        <v>1.48</v>
       </c>
       <c r="W17" t="n">
-        <v>2.55</v>
+        <v>7.92</v>
       </c>
     </row>
     <row r="18">
@@ -1883,31 +1883,31 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>0.85</v>
+        <v>0.49</v>
       </c>
       <c r="P18" t="n">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="Q18" t="n">
         <v>0.78</v>
       </c>
       <c r="R18" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="S18" t="n">
-        <v>0.794</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>3.33</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>0.63</v>
+        <v>1.64</v>
       </c>
       <c r="W18" t="n">
-        <v>3.4</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="19">
@@ -1964,31 +1964,31 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>0.8</v>
+        <v>0.42</v>
       </c>
       <c r="P19" t="n">
-        <v>0.8</v>
+        <v>0.43</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8055</v>
+        <v>0.5575</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>4.17</v>
+        <v>9.44</v>
       </c>
       <c r="V19" t="n">
-        <v>0.79</v>
+        <v>1.79</v>
       </c>
       <c r="W19" t="n">
-        <v>4.25</v>
+        <v>9.630000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -2045,31 +2045,31 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>0.5</v>
+        <v>0.61</v>
       </c>
       <c r="P20" t="n">
-        <v>0.51</v>
+        <v>0.61</v>
       </c>
       <c r="Q20" t="n">
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0.83</v>
+        <v>0.76</v>
       </c>
       <c r="S20" t="n">
-        <v>0.653</v>
+        <v>0.7105</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>8.890000000000001</v>
+        <v>7.09</v>
       </c>
       <c r="V20" t="n">
-        <v>1.69</v>
+        <v>1.35</v>
       </c>
       <c r="W20" t="n">
-        <v>9.06</v>
+        <v>7.23</v>
       </c>
     </row>
     <row r="21">
@@ -2126,31 +2126,31 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>0.52</v>
+        <v>0.62</v>
       </c>
       <c r="P21" t="n">
-        <v>0.53</v>
+        <v>0.63</v>
       </c>
       <c r="Q21" t="n">
         <v>0.93</v>
       </c>
       <c r="R21" t="n">
-        <v>0.83</v>
+        <v>0.76</v>
       </c>
       <c r="S21" t="n">
-        <v>0.652</v>
+        <v>0.7065</v>
       </c>
       <c r="T21" t="n">
         <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>8.69</v>
+        <v>6.89</v>
       </c>
       <c r="V21" t="n">
-        <v>1.65</v>
+        <v>1.31</v>
       </c>
       <c r="W21" t="n">
-        <v>8.859999999999999</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="22">
@@ -2207,31 +2207,31 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>0.53</v>
+        <v>0.64</v>
       </c>
       <c r="P22" t="n">
-        <v>0.54</v>
+        <v>0.64</v>
       </c>
       <c r="Q22" t="n">
         <v>0.86</v>
       </c>
       <c r="R22" t="n">
-        <v>0.83</v>
+        <v>0.76</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6445</v>
+        <v>0.702</v>
       </c>
       <c r="T22" t="n">
         <v>3</v>
       </c>
       <c r="U22" t="n">
-        <v>8.49</v>
+        <v>6.69</v>
       </c>
       <c r="V22" t="n">
-        <v>1.61</v>
+        <v>1.27</v>
       </c>
       <c r="W22" t="n">
-        <v>8.66</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="23">
@@ -2288,31 +2288,31 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>0.76</v>
+        <v>0.48</v>
       </c>
       <c r="P23" t="n">
-        <v>0.76</v>
+        <v>0.49</v>
       </c>
       <c r="Q23" t="n">
         <v>0.51</v>
       </c>
       <c r="R23" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="T23" t="n">
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>4.82</v>
+        <v>8.68</v>
       </c>
       <c r="V23" t="n">
-        <v>0.92</v>
+        <v>1.65</v>
       </c>
       <c r="W23" t="n">
-        <v>4.91</v>
+        <v>8.85</v>
       </c>
     </row>
     <row r="24">
@@ -2369,31 +2369,31 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>0.62</v>
+        <v>0.3</v>
       </c>
       <c r="P24" t="n">
-        <v>0.62</v>
+        <v>0.32</v>
       </c>
       <c r="Q24" t="n">
         <v>0.93</v>
       </c>
       <c r="R24" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.475</v>
       </c>
       <c r="T24" t="n">
         <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>7.1</v>
+        <v>10.96</v>
       </c>
       <c r="V24" t="n">
-        <v>1.35</v>
+        <v>2.08</v>
       </c>
       <c r="W24" t="n">
-        <v>7.23</v>
+        <v>11.17</v>
       </c>
     </row>
     <row r="25">
@@ -2450,31 +2450,31 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>0.47</v>
+        <v>0.12</v>
       </c>
       <c r="P25" t="n">
-        <v>0.48</v>
+        <v>0.14</v>
       </c>
       <c r="Q25" t="n">
         <v>0.29</v>
       </c>
       <c r="R25" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="S25" t="n">
-        <v>0.442</v>
+        <v>0.2105</v>
       </c>
       <c r="T25" t="n">
         <v>3</v>
       </c>
       <c r="U25" t="n">
-        <v>9.380000000000001</v>
+        <v>13.24</v>
       </c>
       <c r="V25" t="n">
-        <v>1.78</v>
+        <v>2.52</v>
       </c>
       <c r="W25" t="n">
-        <v>9.56</v>
+        <v>13.49</v>
       </c>
     </row>
     <row r="26">
@@ -2531,31 +2531,31 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>0.97</v>
+        <v>0.85</v>
       </c>
       <c r="P26" t="n">
-        <v>0.97</v>
+        <v>0.86</v>
       </c>
       <c r="Q26" t="n">
         <v>0.93</v>
       </c>
       <c r="R26" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="S26" t="n">
-        <v>0.917</v>
+        <v>0.8395</v>
       </c>
       <c r="T26" t="n">
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>1.44</v>
+        <v>3.99</v>
       </c>
       <c r="V26" t="n">
-        <v>0.27</v>
+        <v>0.76</v>
       </c>
       <c r="W26" t="n">
-        <v>1.4</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="27">
@@ -2612,31 +2612,31 @@
         </is>
       </c>
       <c r="O27" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="P27" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="Q27" t="n">
         <v>0.51</v>
       </c>
       <c r="R27" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="S27" t="n">
-        <v>0.8525</v>
+        <v>0.7975</v>
       </c>
       <c r="T27" t="n">
         <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>0.61</v>
+        <v>3.16</v>
       </c>
       <c r="V27" t="n">
-        <v>0.12</v>
+        <v>0.6</v>
       </c>
       <c r="W27" t="n">
-        <v>0.59</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="28">
@@ -2693,31 +2693,31 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="P28" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="S28" t="n">
-        <v>0.698</v>
+        <v>0.6835</v>
       </c>
       <c r="T28" t="n">
         <v>3</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="29">
@@ -2774,31 +2774,31 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>0.97</v>
+        <v>0.85</v>
       </c>
       <c r="P29" t="n">
-        <v>0.97</v>
+        <v>0.86</v>
       </c>
       <c r="Q29" t="n">
         <v>0.51</v>
       </c>
       <c r="R29" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="S29" t="n">
-        <v>0.836</v>
+        <v>0.76</v>
       </c>
       <c r="T29" t="n">
         <v>3</v>
       </c>
       <c r="U29" t="n">
-        <v>1.54</v>
+        <v>3.99</v>
       </c>
       <c r="V29" t="n">
-        <v>0.29</v>
+        <v>0.76</v>
       </c>
       <c r="W29" t="n">
-        <v>1.5</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="30">
@@ -2855,31 +2855,31 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P30" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="Q30" t="n">
         <v>0.78</v>
       </c>
       <c r="R30" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="S30" t="n">
-        <v>0.8705000000000001</v>
+        <v>0.7915</v>
       </c>
       <c r="T30" t="n">
         <v>2</v>
       </c>
       <c r="U30" t="n">
-        <v>2.02</v>
+        <v>4.47</v>
       </c>
       <c r="V30" t="n">
-        <v>0.38</v>
+        <v>0.85</v>
       </c>
       <c r="W30" t="n">
-        <v>1.97</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="31">
@@ -2936,31 +2936,31 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>0.92</v>
+        <v>0.79</v>
       </c>
       <c r="P31" t="n">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="Q31" t="n">
         <v>0.93</v>
       </c>
       <c r="R31" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="S31" t="n">
-        <v>0.8875</v>
+        <v>0.805</v>
       </c>
       <c r="T31" t="n">
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>2.34</v>
+        <v>4.79</v>
       </c>
       <c r="V31" t="n">
-        <v>0.44</v>
+        <v>0.91</v>
       </c>
       <c r="W31" t="n">
-        <v>2.28</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="32">
@@ -3017,31 +3017,31 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>0.76</v>
+        <v>0.93</v>
       </c>
       <c r="P32" t="n">
-        <v>0.76</v>
+        <v>0.93</v>
       </c>
       <c r="Q32" t="n">
         <v>0.78</v>
       </c>
       <c r="R32" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="S32" t="n">
-        <v>0.791</v>
+        <v>0.9</v>
       </c>
       <c r="T32" t="n">
         <v>3</v>
       </c>
       <c r="U32" t="n">
-        <v>4.81</v>
+        <v>2.97</v>
       </c>
       <c r="V32" t="n">
-        <v>0.91</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="W32" t="n">
-        <v>4.91</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="33">
@@ -3098,31 +3098,31 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>0.78</v>
+        <v>0.96</v>
       </c>
       <c r="P33" t="n">
-        <v>0.79</v>
+        <v>0.95</v>
       </c>
       <c r="Q33" t="n">
         <v>0.93</v>
       </c>
       <c r="R33" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="S33" t="n">
-        <v>0.8375</v>
+        <v>0.946</v>
       </c>
       <c r="T33" t="n">
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>4.45</v>
+        <v>2.61</v>
       </c>
       <c r="V33" t="n">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="W33" t="n">
-        <v>4.54</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="34">
@@ -3179,31 +3179,31 @@
         </is>
       </c>
       <c r="O34" t="n">
-        <v>0.8</v>
+        <v>0.98</v>
       </c>
       <c r="P34" t="n">
-        <v>0.8</v>
+        <v>0.97</v>
       </c>
       <c r="Q34" t="n">
         <v>0.7</v>
       </c>
       <c r="R34" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="S34" t="n">
-        <v>0.801</v>
+        <v>0.913</v>
       </c>
       <c r="T34" t="n">
         <v>2</v>
       </c>
       <c r="U34" t="n">
-        <v>4.19</v>
+        <v>2.34</v>
       </c>
       <c r="V34" t="n">
-        <v>0.8</v>
+        <v>0.44</v>
       </c>
       <c r="W34" t="n">
-        <v>4.27</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="35">
@@ -3263,28 +3263,28 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="Q35" t="n">
         <v>0.45</v>
       </c>
       <c r="R35" t="n">
-        <v>0.67</v>
+        <v>0.58</v>
       </c>
       <c r="S35" t="n">
-        <v>0.1905</v>
+        <v>0.184</v>
       </c>
       <c r="T35" t="n">
         <v>3</v>
       </c>
       <c r="U35" t="n">
-        <v>17.25</v>
+        <v>14.79</v>
       </c>
       <c r="V35" t="n">
-        <v>3.28</v>
+        <v>2.81</v>
       </c>
       <c r="W35" t="n">
-        <v>17.58</v>
+        <v>15.07</v>
       </c>
     </row>
     <row r="36">
@@ -3341,31 +3341,31 @@
         </is>
       </c>
       <c r="O36" t="n">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
       <c r="P36" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="Q36" t="n">
         <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="S36" t="n">
-        <v>0.418</v>
+        <v>0.445</v>
       </c>
       <c r="T36" t="n">
         <v>2</v>
       </c>
       <c r="U36" t="n">
-        <v>14.64</v>
+        <v>12.18</v>
       </c>
       <c r="V36" t="n">
-        <v>2.78</v>
+        <v>2.31</v>
       </c>
       <c r="W36" t="n">
-        <v>14.92</v>
+        <v>12.41</v>
       </c>
     </row>
     <row r="37">
@@ -3422,31 +3422,31 @@
         </is>
       </c>
       <c r="O37" t="n">
-        <v>0.22</v>
+        <v>0.31</v>
       </c>
       <c r="P37" t="n">
-        <v>0.24</v>
+        <v>0.32</v>
       </c>
       <c r="Q37" t="n">
         <v>0.76</v>
       </c>
       <c r="R37" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="S37" t="n">
-        <v>0.422</v>
+        <v>0.462</v>
       </c>
       <c r="T37" t="n">
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>13.33</v>
+        <v>10.87</v>
       </c>
       <c r="V37" t="n">
-        <v>2.53</v>
+        <v>2.07</v>
       </c>
       <c r="W37" t="n">
-        <v>13.59</v>
+        <v>11.08</v>
       </c>
     </row>
     <row r="38">
@@ -3503,31 +3503,31 @@
         </is>
       </c>
       <c r="O38" t="n">
-        <v>0.66</v>
+        <v>0.79</v>
       </c>
       <c r="P38" t="n">
-        <v>0.66</v>
+        <v>0.78</v>
       </c>
       <c r="Q38" t="n">
         <v>0.78</v>
       </c>
       <c r="R38" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="S38" t="n">
-        <v>0.7125</v>
+        <v>0.7905</v>
       </c>
       <c r="T38" t="n">
         <v>2</v>
       </c>
       <c r="U38" t="n">
-        <v>6.41</v>
+        <v>4.74</v>
       </c>
       <c r="V38" t="n">
-        <v>1.22</v>
+        <v>0.9</v>
       </c>
       <c r="W38" t="n">
-        <v>6.67</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="39">
@@ -3584,31 +3584,31 @@
         </is>
       </c>
       <c r="O39" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="P39" t="n">
-        <v>0.68</v>
+        <v>0.82</v>
       </c>
       <c r="Q39" t="n">
         <v>0.93</v>
       </c>
       <c r="R39" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="S39" t="n">
-        <v>0.7585</v>
+        <v>0.8465</v>
       </c>
       <c r="T39" t="n">
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>5.98</v>
+        <v>4.31</v>
       </c>
       <c r="V39" t="n">
-        <v>1.14</v>
+        <v>0.82</v>
       </c>
       <c r="W39" t="n">
-        <v>6.23</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="40">
@@ -3665,31 +3665,31 @@
         </is>
       </c>
       <c r="O40" t="n">
-        <v>0.72</v>
+        <v>0.87</v>
       </c>
       <c r="P40" t="n">
-        <v>0.72</v>
+        <v>0.86</v>
       </c>
       <c r="Q40" t="n">
         <v>0.51</v>
       </c>
       <c r="R40" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="S40" t="n">
-        <v>0.6975</v>
+        <v>0.7885</v>
       </c>
       <c r="T40" t="n">
         <v>3</v>
       </c>
       <c r="U40" t="n">
-        <v>5.45</v>
+        <v>3.79</v>
       </c>
       <c r="V40" t="n">
-        <v>1.04</v>
+        <v>0.72</v>
       </c>
       <c r="W40" t="n">
-        <v>5.68</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="41">
@@ -3746,31 +3746,31 @@
         </is>
       </c>
       <c r="O41" t="n">
-        <v>0.72</v>
+        <v>0.41</v>
       </c>
       <c r="P41" t="n">
-        <v>0.72</v>
+        <v>0.43</v>
       </c>
       <c r="Q41" t="n">
         <v>0.41</v>
       </c>
       <c r="R41" t="n">
-        <v>0.63</v>
+        <v>0.54</v>
       </c>
       <c r="S41" t="n">
-        <v>0.6445</v>
+        <v>0.4365</v>
       </c>
       <c r="T41" t="n">
         <v>2</v>
       </c>
       <c r="U41" t="n">
-        <v>5.48</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="V41" t="n">
-        <v>1.04</v>
+        <v>1.81</v>
       </c>
       <c r="W41" t="n">
-        <v>5.58</v>
+        <v>9.710000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -3827,31 +3827,31 @@
         </is>
       </c>
       <c r="O42" t="n">
-        <v>0.63</v>
+        <v>0.31</v>
       </c>
       <c r="P42" t="n">
-        <v>0.64</v>
+        <v>0.32</v>
       </c>
       <c r="Q42" t="n">
         <v>0.78</v>
       </c>
       <c r="R42" t="n">
-        <v>0.63</v>
+        <v>0.54</v>
       </c>
       <c r="S42" t="n">
-        <v>0.6635</v>
+        <v>0.442</v>
       </c>
       <c r="T42" t="n">
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>6.84</v>
+        <v>10.9</v>
       </c>
       <c r="V42" t="n">
-        <v>1.3</v>
+        <v>2.07</v>
       </c>
       <c r="W42" t="n">
-        <v>6.98</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="43">
@@ -3908,31 +3908,31 @@
         </is>
       </c>
       <c r="O43" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="P43" t="n">
-        <v>0.51</v>
+        <v>0.16</v>
       </c>
       <c r="Q43" t="n">
         <v>0.78</v>
       </c>
       <c r="R43" t="n">
-        <v>0.63</v>
+        <v>0.54</v>
       </c>
       <c r="S43" t="n">
-        <v>0.579</v>
+        <v>0.338</v>
       </c>
       <c r="T43" t="n">
         <v>3</v>
       </c>
       <c r="U43" t="n">
-        <v>8.9</v>
+        <v>12.95</v>
       </c>
       <c r="V43" t="n">
-        <v>1.69</v>
+        <v>2.46</v>
       </c>
       <c r="W43" t="n">
-        <v>9.07</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="44">
@@ -3989,31 +3989,31 @@
         </is>
       </c>
       <c r="O44" t="n">
-        <v>0.58</v>
+        <v>0.72</v>
       </c>
       <c r="P44" t="n">
-        <v>0.58</v>
+        <v>0.72</v>
       </c>
       <c r="Q44" t="n">
         <v>0.78</v>
       </c>
       <c r="R44" t="n">
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
       <c r="S44" t="n">
-        <v>0.6605</v>
+        <v>0.735</v>
       </c>
       <c r="T44" t="n">
         <v>3</v>
       </c>
       <c r="U44" t="n">
-        <v>7.74</v>
+        <v>5.72</v>
       </c>
       <c r="V44" t="n">
-        <v>1.47</v>
+        <v>1.09</v>
       </c>
       <c r="W44" t="n">
-        <v>7.89</v>
+        <v>5.83</v>
       </c>
     </row>
     <row r="45">
@@ -4070,31 +4070,31 @@
         </is>
       </c>
       <c r="O45" t="n">
-        <v>0.63</v>
+        <v>0.78</v>
       </c>
       <c r="P45" t="n">
-        <v>0.63</v>
+        <v>0.78</v>
       </c>
       <c r="Q45" t="n">
         <v>0.93</v>
       </c>
       <c r="R45" t="n">
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
       <c r="S45" t="n">
-        <v>0.723</v>
+        <v>0.804</v>
       </c>
       <c r="T45" t="n">
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>6.93</v>
+        <v>4.91</v>
       </c>
       <c r="V45" t="n">
-        <v>1.32</v>
+        <v>0.93</v>
       </c>
       <c r="W45" t="n">
-        <v>7.07</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
@@ -4151,31 +4151,31 @@
         </is>
       </c>
       <c r="O46" t="n">
-        <v>0.66</v>
+        <v>0.83</v>
       </c>
       <c r="P46" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="Q46" t="n">
         <v>0.7</v>
       </c>
       <c r="R46" t="n">
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
       <c r="S46" t="n">
-        <v>0.7</v>
+        <v>0.7905</v>
       </c>
       <c r="T46" t="n">
         <v>2</v>
       </c>
       <c r="U46" t="n">
-        <v>6.33</v>
+        <v>4.3</v>
       </c>
       <c r="V46" t="n">
-        <v>1.2</v>
+        <v>0.82</v>
       </c>
       <c r="W46" t="n">
-        <v>6.45</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="47">
@@ -4232,31 +4232,31 @@
         </is>
       </c>
       <c r="O47" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P47" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="Q47" t="n">
         <v>0.51</v>
       </c>
       <c r="R47" t="n">
-        <v>0.72</v>
+        <v>0.64</v>
       </c>
       <c r="S47" t="n">
-        <v>0.86</v>
+        <v>0.8055</v>
       </c>
       <c r="T47" t="n">
         <v>3</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="48">
@@ -4313,31 +4313,31 @@
         </is>
       </c>
       <c r="O48" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="P48" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="Q48" t="n">
         <v>0.78</v>
       </c>
       <c r="R48" t="n">
-        <v>0.72</v>
+        <v>0.64</v>
       </c>
       <c r="S48" t="n">
-        <v>0.914</v>
+        <v>0.8075</v>
       </c>
       <c r="T48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="49">
@@ -4394,31 +4394,31 @@
         </is>
       </c>
       <c r="O49" t="n">
-        <v>1</v>
+        <v>0.79</v>
       </c>
       <c r="P49" t="n">
-        <v>1</v>
+        <v>0.78</v>
       </c>
       <c r="Q49" t="n">
         <v>1</v>
       </c>
       <c r="R49" t="n">
-        <v>0.72</v>
+        <v>0.64</v>
       </c>
       <c r="S49" t="n">
-        <v>0.958</v>
+        <v>0.806</v>
       </c>
       <c r="T49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U49" t="n">
-        <v>0.61</v>
+        <v>4.83</v>
       </c>
       <c r="V49" t="n">
-        <v>0.12</v>
+        <v>0.92</v>
       </c>
       <c r="W49" t="n">
-        <v>0.63</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="50">
@@ -4475,31 +4475,31 @@
         </is>
       </c>
       <c r="O50" t="n">
-        <v>0.76</v>
+        <v>0.5</v>
       </c>
       <c r="P50" t="n">
-        <v>0.76</v>
+        <v>0.51</v>
       </c>
       <c r="Q50" t="n">
         <v>0.29</v>
       </c>
       <c r="R50" t="n">
-        <v>0.6</v>
+        <v>0.54</v>
       </c>
       <c r="S50" t="n">
-        <v>0.642</v>
+        <v>0.4675</v>
       </c>
       <c r="T50" t="n">
         <v>2</v>
       </c>
       <c r="U50" t="n">
-        <v>4.82</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="V50" t="n">
-        <v>0.92</v>
+        <v>1.59</v>
       </c>
       <c r="W50" t="n">
-        <v>4.91</v>
+        <v>8.550000000000001</v>
       </c>
     </row>
     <row r="51">
@@ -4556,31 +4556,31 @@
         </is>
       </c>
       <c r="O51" t="n">
-        <v>0.68</v>
+        <v>0.4</v>
       </c>
       <c r="P51" t="n">
-        <v>0.68</v>
+        <v>0.41</v>
       </c>
       <c r="Q51" t="n">
         <v>0.78</v>
       </c>
       <c r="R51" t="n">
-        <v>0.6</v>
+        <v>0.54</v>
       </c>
       <c r="S51" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="T51" t="n">
         <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>6.12</v>
+        <v>9.69</v>
       </c>
       <c r="V51" t="n">
-        <v>1.16</v>
+        <v>1.84</v>
       </c>
       <c r="W51" t="n">
-        <v>6.24</v>
+        <v>9.880000000000001</v>
       </c>
     </row>
     <row r="52">
@@ -4637,31 +4637,31 @@
         </is>
       </c>
       <c r="O52" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="P52" t="n">
-        <v>0.57</v>
+        <v>0.27</v>
       </c>
       <c r="Q52" t="n">
         <v>0.7</v>
       </c>
       <c r="R52" t="n">
-        <v>0.6</v>
+        <v>0.54</v>
       </c>
       <c r="S52" t="n">
-        <v>0.5975</v>
+        <v>0.3935</v>
       </c>
       <c r="T52" t="n">
         <v>3</v>
       </c>
       <c r="U52" t="n">
-        <v>7.94</v>
+        <v>11.52</v>
       </c>
       <c r="V52" t="n">
-        <v>1.51</v>
+        <v>2.19</v>
       </c>
       <c r="W52" t="n">
-        <v>8.09</v>
+        <v>11.74</v>
       </c>
     </row>
     <row r="53">
@@ -4718,31 +4718,31 @@
         </is>
       </c>
       <c r="O53" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="P53" t="n">
-        <v>0.82</v>
+        <v>0.62</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="S53" t="n">
-        <v>0.638</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="T53" t="n">
         <v>3</v>
       </c>
       <c r="U53" t="n">
-        <v>4.01</v>
+        <v>7.29</v>
       </c>
       <c r="V53" t="n">
-        <v>0.76</v>
+        <v>1.39</v>
       </c>
       <c r="W53" t="n">
-        <v>3.91</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="54">
@@ -4799,31 +4799,31 @@
         </is>
       </c>
       <c r="O54" t="n">
-        <v>0.77</v>
+        <v>0.54</v>
       </c>
       <c r="P54" t="n">
-        <v>0.78</v>
+        <v>0.57</v>
       </c>
       <c r="Q54" t="n">
         <v>0.46</v>
       </c>
       <c r="R54" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="S54" t="n">
-        <v>0.704</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="T54" t="n">
         <v>2</v>
       </c>
       <c r="U54" t="n">
-        <v>4.66</v>
+        <v>7.94</v>
       </c>
       <c r="V54" t="n">
-        <v>0.88</v>
+        <v>1.51</v>
       </c>
       <c r="W54" t="n">
-        <v>4.54</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="55">
@@ -4880,31 +4880,31 @@
         </is>
       </c>
       <c r="O55" t="n">
-        <v>0.73</v>
+        <v>0.49</v>
       </c>
       <c r="P55" t="n">
-        <v>0.75</v>
+        <v>0.53</v>
       </c>
       <c r="Q55" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="R55" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="S55" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.601</v>
       </c>
       <c r="T55" t="n">
         <v>1</v>
       </c>
       <c r="U55" t="n">
-        <v>5.3</v>
+        <v>8.59</v>
       </c>
       <c r="V55" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="W55" t="n">
-        <v>5.17</v>
+        <v>8.380000000000001</v>
       </c>
     </row>
     <row r="56">
@@ -4970,10 +4970,10 @@
         <v>0.15</v>
       </c>
       <c r="R56" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="S56" t="n">
-        <v>0.797</v>
+        <v>0.794</v>
       </c>
       <c r="T56" t="n">
         <v>3</v>
@@ -5051,10 +5051,10 @@
         <v>0.61</v>
       </c>
       <c r="R57" t="n">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="S57" t="n">
-        <v>0.9085</v>
+        <v>0.9055</v>
       </c>
       <c r="T57" t="n">
         <v>2</v>
@@ -5132,10 +5132,10 @@
         <v>0.86</v>
       </c>
       <c r="R58" t="n">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="S58" t="n">
-        <v>0.9585</v>
+        <v>0.9555</v>
       </c>
       <c r="T58" t="n">
         <v>1</v>
@@ -5213,10 +5213,10 @@
         <v>0.51</v>
       </c>
       <c r="R59" t="n">
-        <v>0.82</v>
+        <v>0.71</v>
       </c>
       <c r="S59" t="n">
-        <v>0.875</v>
+        <v>0.8585</v>
       </c>
       <c r="T59" t="n">
         <v>3</v>
@@ -5294,22 +5294,22 @@
         <v>0.78</v>
       </c>
       <c r="R60" t="n">
-        <v>0.82</v>
+        <v>0.71</v>
       </c>
       <c r="S60" t="n">
-        <v>0.929</v>
+        <v>0.9125</v>
       </c>
       <c r="T60" t="n">
         <v>2</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="61">
@@ -5375,22 +5375,22 @@
         <v>0.93</v>
       </c>
       <c r="R61" t="n">
-        <v>0.82</v>
+        <v>0.71</v>
       </c>
       <c r="S61" t="n">
-        <v>0.959</v>
+        <v>0.9425</v>
       </c>
       <c r="T61" t="n">
         <v>1</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V61" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="W61" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="62">
@@ -5456,10 +5456,10 @@
         <v>0.78</v>
       </c>
       <c r="R62" t="n">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="S62" t="n">
-        <v>0.9425</v>
+        <v>0.9395</v>
       </c>
       <c r="T62" t="n">
         <v>2</v>
@@ -5537,10 +5537,10 @@
         <v>0.93</v>
       </c>
       <c r="R63" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="S63" t="n">
-        <v>0.9665</v>
+        <v>0.9635</v>
       </c>
       <c r="T63" t="n">
         <v>1</v>
@@ -5618,10 +5618,10 @@
         <v>0.61</v>
       </c>
       <c r="R64" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="S64" t="n">
-        <v>0.9025</v>
+        <v>0.8995</v>
       </c>
       <c r="T64" t="n">
         <v>3</v>
@@ -5699,10 +5699,10 @@
         <v>0.41</v>
       </c>
       <c r="R65" t="n">
-        <v>0.87</v>
+        <v>0.82</v>
       </c>
       <c r="S65" t="n">
-        <v>0.8625</v>
+        <v>0.855</v>
       </c>
       <c r="T65" t="n">
         <v>3</v>
@@ -5780,10 +5780,10 @@
         <v>0.78</v>
       </c>
       <c r="R66" t="n">
-        <v>0.87</v>
+        <v>0.82</v>
       </c>
       <c r="S66" t="n">
-        <v>0.9365</v>
+        <v>0.929</v>
       </c>
       <c r="T66" t="n">
         <v>2</v>
@@ -5861,10 +5861,10 @@
         <v>0.93</v>
       </c>
       <c r="R67" t="n">
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
       <c r="S67" t="n">
-        <v>0.962</v>
+        <v>0.9545</v>
       </c>
       <c r="T67" t="n">
         <v>1</v>
@@ -5933,31 +5933,31 @@
         </is>
       </c>
       <c r="O68" t="n">
-        <v>0.68</v>
+        <v>0.82</v>
       </c>
       <c r="P68" t="n">
-        <v>0.68</v>
+        <v>0.82</v>
       </c>
       <c r="Q68" t="n">
         <v>0.18</v>
       </c>
       <c r="R68" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="S68" t="n">
-        <v>0.574</v>
+        <v>0.653</v>
       </c>
       <c r="T68" t="n">
         <v>3</v>
       </c>
       <c r="U68" t="n">
-        <v>6.14</v>
+        <v>4.35</v>
       </c>
       <c r="V68" t="n">
-        <v>1.17</v>
+        <v>0.83</v>
       </c>
       <c r="W68" t="n">
-        <v>6.26</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="69">
@@ -6014,31 +6014,31 @@
         </is>
       </c>
       <c r="O69" t="n">
-        <v>0.73</v>
+        <v>0.89</v>
       </c>
       <c r="P69" t="n">
-        <v>0.73</v>
+        <v>0.89</v>
       </c>
       <c r="Q69" t="n">
         <v>0.67</v>
       </c>
       <c r="R69" t="n">
-        <v>0.85</v>
+        <v>0.76</v>
       </c>
       <c r="S69" t="n">
-        <v>0.736</v>
+        <v>0.8265</v>
       </c>
       <c r="T69" t="n">
         <v>2</v>
       </c>
       <c r="U69" t="n">
-        <v>5.27</v>
+        <v>3.48</v>
       </c>
       <c r="V69" t="n">
-        <v>1</v>
+        <v>0.66</v>
       </c>
       <c r="W69" t="n">
-        <v>5.37</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="70">
@@ -6095,31 +6095,31 @@
         </is>
       </c>
       <c r="O70" t="n">
-        <v>0.79</v>
+        <v>0.96</v>
       </c>
       <c r="P70" t="n">
-        <v>0.79</v>
+        <v>0.95</v>
       </c>
       <c r="Q70" t="n">
         <v>1</v>
       </c>
       <c r="R70" t="n">
-        <v>0.85</v>
+        <v>0.76</v>
       </c>
       <c r="S70" t="n">
-        <v>0.841</v>
+        <v>0.9345</v>
       </c>
       <c r="T70" t="n">
         <v>1</v>
       </c>
       <c r="U70" t="n">
-        <v>4.4</v>
+        <v>2.61</v>
       </c>
       <c r="V70" t="n">
-        <v>0.84</v>
+        <v>0.5</v>
       </c>
       <c r="W70" t="n">
-        <v>4.49</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="71">
@@ -6176,31 +6176,31 @@
         </is>
       </c>
       <c r="O71" t="n">
-        <v>0.76</v>
+        <v>0.9</v>
       </c>
       <c r="P71" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="Q71" t="n">
         <v>1</v>
       </c>
       <c r="R71" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="S71" t="n">
-        <v>0.824</v>
+        <v>0.9105</v>
       </c>
       <c r="T71" t="n">
         <v>1</v>
       </c>
       <c r="U71" t="n">
-        <v>4.88</v>
+        <v>3.38</v>
       </c>
       <c r="V71" t="n">
-        <v>0.93</v>
+        <v>0.64</v>
       </c>
       <c r="W71" t="n">
-        <v>5.08</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="72">
@@ -6257,31 +6257,31 @@
         </is>
       </c>
       <c r="O72" t="n">
-        <v>0.79</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P72" t="n">
-        <v>0.78</v>
+        <v>0.93</v>
       </c>
       <c r="Q72" t="n">
         <v>0.7</v>
       </c>
       <c r="R72" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="S72" t="n">
-        <v>0.7835</v>
+        <v>0.8764999999999999</v>
       </c>
       <c r="T72" t="n">
         <v>2</v>
       </c>
       <c r="U72" t="n">
-        <v>4.39</v>
+        <v>2.89</v>
       </c>
       <c r="V72" t="n">
-        <v>0.83</v>
+        <v>0.55</v>
       </c>
       <c r="W72" t="n">
-        <v>4.57</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="73">
@@ -6338,31 +6338,31 @@
         </is>
       </c>
       <c r="O73" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="P73" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="Q73" t="n">
         <v>0.41</v>
       </c>
       <c r="R73" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="S73" t="n">
-        <v>0.7255</v>
+        <v>0.823</v>
       </c>
       <c r="T73" t="n">
         <v>3</v>
       </c>
       <c r="U73" t="n">
-        <v>4.03</v>
+        <v>2.53</v>
       </c>
       <c r="V73" t="n">
-        <v>0.77</v>
+        <v>0.48</v>
       </c>
       <c r="W73" t="n">
-        <v>4.2</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="74">
@@ -6419,31 +6419,31 @@
         </is>
       </c>
       <c r="O74" t="n">
-        <v>0.82</v>
+        <v>0.96</v>
       </c>
       <c r="P74" t="n">
-        <v>0.82</v>
+        <v>0.96</v>
       </c>
       <c r="Q74" t="n">
         <v>0.86</v>
       </c>
       <c r="R74" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="S74" t="n">
-        <v>0.834</v>
+        <v>0.913</v>
       </c>
       <c r="T74" t="n">
         <v>2</v>
       </c>
       <c r="U74" t="n">
-        <v>3.89</v>
+        <v>2.55</v>
       </c>
       <c r="V74" t="n">
-        <v>0.74</v>
+        <v>0.48</v>
       </c>
       <c r="W74" t="n">
-        <v>3.97</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="75">
@@ -6500,31 +6500,31 @@
         </is>
       </c>
       <c r="O75" t="n">
-        <v>0.84</v>
+        <v>0.99</v>
       </c>
       <c r="P75" t="n">
-        <v>0.84</v>
+        <v>0.98</v>
       </c>
       <c r="Q75" t="n">
         <v>0.93</v>
       </c>
       <c r="R75" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="S75" t="n">
-        <v>0.861</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="T75" t="n">
         <v>1</v>
       </c>
       <c r="U75" t="n">
-        <v>3.57</v>
+        <v>2.23</v>
       </c>
       <c r="V75" t="n">
-        <v>0.68</v>
+        <v>0.42</v>
       </c>
       <c r="W75" t="n">
-        <v>3.64</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="76">
@@ -6581,31 +6581,31 @@
         </is>
       </c>
       <c r="O76" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="P76" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="Q76" t="n">
         <v>0.61</v>
       </c>
       <c r="R76" t="n">
-        <v>0.86</v>
+        <v>0.78</v>
       </c>
       <c r="S76" t="n">
-        <v>0.8165</v>
+        <v>0.889</v>
       </c>
       <c r="T76" t="n">
         <v>3</v>
       </c>
       <c r="U76" t="n">
-        <v>3.14</v>
+        <v>1.8</v>
       </c>
       <c r="V76" t="n">
-        <v>0.6</v>
+        <v>0.34</v>
       </c>
       <c r="W76" t="n">
-        <v>3.2</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="77">
@@ -6662,31 +6662,31 @@
         </is>
       </c>
       <c r="O77" t="n">
-        <v>0.58</v>
+        <v>0.71</v>
       </c>
       <c r="P77" t="n">
-        <v>0.58</v>
+        <v>0.7</v>
       </c>
       <c r="Q77" t="n">
         <v>0.92</v>
       </c>
       <c r="R77" t="n">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="S77" t="n">
-        <v>0.696</v>
+        <v>0.7725</v>
       </c>
       <c r="T77" t="n">
         <v>1</v>
       </c>
       <c r="U77" t="n">
-        <v>7.62</v>
+        <v>5.76</v>
       </c>
       <c r="V77" t="n">
-        <v>1.45</v>
+        <v>1.09</v>
       </c>
       <c r="W77" t="n">
-        <v>7.94</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="78">
@@ -6743,31 +6743,31 @@
         </is>
       </c>
       <c r="O78" t="n">
-        <v>0.63</v>
+        <v>0.78</v>
       </c>
       <c r="P78" t="n">
-        <v>0.63</v>
+        <v>0.77</v>
       </c>
       <c r="Q78" t="n">
         <v>0.51</v>
       </c>
       <c r="R78" t="n">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="S78" t="n">
-        <v>0.6465</v>
+        <v>0.736</v>
       </c>
       <c r="T78" t="n">
         <v>2</v>
       </c>
       <c r="U78" t="n">
-        <v>6.82</v>
+        <v>4.96</v>
       </c>
       <c r="V78" t="n">
-        <v>1.3</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="W78" t="n">
-        <v>7.1</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="79">
@@ -6824,31 +6824,31 @@
         </is>
       </c>
       <c r="O79" t="n">
-        <v>0.67</v>
+        <v>0.82</v>
       </c>
       <c r="P79" t="n">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Q79" t="n">
         <v>0.06</v>
       </c>
       <c r="R79" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="S79" t="n">
-        <v>0.548</v>
+        <v>0.639</v>
       </c>
       <c r="T79" t="n">
         <v>3</v>
       </c>
       <c r="U79" t="n">
-        <v>6.22</v>
+        <v>4.36</v>
       </c>
       <c r="V79" t="n">
-        <v>1.18</v>
+        <v>0.83</v>
       </c>
       <c r="W79" t="n">
-        <v>6.48</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="80">
@@ -6905,31 +6905,31 @@
         </is>
       </c>
       <c r="O80" t="n">
-        <v>0.74</v>
+        <v>0.87</v>
       </c>
       <c r="P80" t="n">
-        <v>0.74</v>
+        <v>0.86</v>
       </c>
       <c r="Q80" t="n">
         <v>0.86</v>
       </c>
       <c r="R80" t="n">
-        <v>0.77</v>
+        <v>0.73</v>
       </c>
       <c r="S80" t="n">
-        <v>0.7685</v>
+        <v>0.8435</v>
       </c>
       <c r="T80" t="n">
         <v>1</v>
       </c>
       <c r="U80" t="n">
-        <v>5.12</v>
+        <v>3.71</v>
       </c>
       <c r="V80" t="n">
-        <v>0.97</v>
+        <v>0.7</v>
       </c>
       <c r="W80" t="n">
-        <v>5.33</v>
+        <v>3.86</v>
       </c>
     </row>
     <row r="81">
@@ -6986,31 +6986,31 @@
         </is>
       </c>
       <c r="O81" t="n">
-        <v>0.76</v>
+        <v>0.89</v>
       </c>
       <c r="P81" t="n">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="Q81" t="n">
         <v>0.61</v>
       </c>
       <c r="R81" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="S81" t="n">
-        <v>0.7385</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="T81" t="n">
         <v>2</v>
       </c>
       <c r="U81" t="n">
-        <v>4.86</v>
+        <v>3.45</v>
       </c>
       <c r="V81" t="n">
-        <v>0.92</v>
+        <v>0.65</v>
       </c>
       <c r="W81" t="n">
-        <v>5.06</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="82">
@@ -7067,31 +7067,31 @@
         </is>
       </c>
       <c r="O82" t="n">
-        <v>0.77</v>
+        <v>0.91</v>
       </c>
       <c r="P82" t="n">
-        <v>0.77</v>
+        <v>0.91</v>
       </c>
       <c r="Q82" t="n">
         <v>0.29</v>
       </c>
       <c r="R82" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="S82" t="n">
-        <v>0.653</v>
+        <v>0.738</v>
       </c>
       <c r="T82" t="n">
         <v>3</v>
       </c>
       <c r="U82" t="n">
-        <v>4.6</v>
+        <v>3.19</v>
       </c>
       <c r="V82" t="n">
-        <v>0.87</v>
+        <v>0.61</v>
       </c>
       <c r="W82" t="n">
-        <v>4.79</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="83">
@@ -7148,31 +7148,31 @@
         </is>
       </c>
       <c r="O83" t="n">
-        <v>0.86</v>
+        <v>0.71</v>
       </c>
       <c r="P83" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="S83" t="n">
-        <v>0.599</v>
+        <v>0.494</v>
       </c>
       <c r="T83" t="n">
         <v>3</v>
       </c>
       <c r="U83" t="n">
-        <v>3.29</v>
+        <v>5.76</v>
       </c>
       <c r="V83" t="n">
-        <v>0.63</v>
+        <v>1.09</v>
       </c>
       <c r="W83" t="n">
-        <v>3.43</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84">
@@ -7229,31 +7229,31 @@
         </is>
       </c>
       <c r="O84" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="P84" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="Q84" t="n">
         <v>0.29</v>
       </c>
       <c r="R84" t="n">
-        <v>0.62</v>
+        <v>0.54</v>
       </c>
       <c r="S84" t="n">
-        <v>0.6775</v>
+        <v>0.5645</v>
       </c>
       <c r="T84" t="n">
         <v>2</v>
       </c>
       <c r="U84" t="n">
-        <v>3.98</v>
+        <v>6.45</v>
       </c>
       <c r="V84" t="n">
-        <v>0.76</v>
+        <v>1.22</v>
       </c>
       <c r="W84" t="n">
-        <v>4.14</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="85">
@@ -7310,31 +7310,31 @@
         </is>
       </c>
       <c r="O85" t="n">
-        <v>0.77</v>
+        <v>0.6</v>
       </c>
       <c r="P85" t="n">
-        <v>0.77</v>
+        <v>0.6</v>
       </c>
       <c r="Q85" t="n">
         <v>0.61</v>
       </c>
       <c r="R85" t="n">
-        <v>0.62</v>
+        <v>0.54</v>
       </c>
       <c r="S85" t="n">
-        <v>0.7155</v>
+        <v>0.593</v>
       </c>
       <c r="T85" t="n">
         <v>1</v>
       </c>
       <c r="U85" t="n">
-        <v>4.66</v>
+        <v>7.13</v>
       </c>
       <c r="V85" t="n">
-        <v>0.89</v>
+        <v>1.35</v>
       </c>
       <c r="W85" t="n">
-        <v>4.85</v>
+        <v>7.42</v>
       </c>
     </row>
     <row r="86">
@@ -7391,31 +7391,31 @@
         </is>
       </c>
       <c r="O86" t="n">
-        <v>0.58</v>
+        <v>0.72</v>
       </c>
       <c r="P86" t="n">
-        <v>0.58</v>
+        <v>0.73</v>
       </c>
       <c r="Q86" t="n">
         <v>0.78</v>
       </c>
       <c r="R86" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="S86" t="n">
-        <v>0.659</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="T86" t="n">
         <v>3</v>
       </c>
       <c r="U86" t="n">
-        <v>7.73</v>
+        <v>5.61</v>
       </c>
       <c r="V86" t="n">
-        <v>1.47</v>
+        <v>1.07</v>
       </c>
       <c r="W86" t="n">
-        <v>7.88</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="87">
@@ -7472,31 +7472,31 @@
         </is>
       </c>
       <c r="O87" t="n">
-        <v>0.6</v>
+        <v>0.76</v>
       </c>
       <c r="P87" t="n">
-        <v>0.61</v>
+        <v>0.76</v>
       </c>
       <c r="Q87" t="n">
         <v>1</v>
       </c>
       <c r="R87" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="S87" t="n">
-        <v>0.7195</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="T87" t="n">
         <v>1</v>
       </c>
       <c r="U87" t="n">
-        <v>7.31</v>
+        <v>5.19</v>
       </c>
       <c r="V87" t="n">
-        <v>1.39</v>
+        <v>0.99</v>
       </c>
       <c r="W87" t="n">
-        <v>7.45</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="88">
@@ -7553,31 +7553,31 @@
         </is>
       </c>
       <c r="O88" t="n">
-        <v>0.63</v>
+        <v>0.79</v>
       </c>
       <c r="P88" t="n">
-        <v>0.64</v>
+        <v>0.79</v>
       </c>
       <c r="Q88" t="n">
         <v>0.78</v>
       </c>
       <c r="R88" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="S88" t="n">
-        <v>0.701</v>
+        <v>0.794</v>
       </c>
       <c r="T88" t="n">
         <v>2</v>
       </c>
       <c r="U88" t="n">
-        <v>6.88</v>
+        <v>4.76</v>
       </c>
       <c r="V88" t="n">
-        <v>1.31</v>
+        <v>0.91</v>
       </c>
       <c r="W88" t="n">
-        <v>7.02</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="89">
@@ -7634,31 +7634,31 @@
         </is>
       </c>
       <c r="O89" t="n">
-        <v>0.92</v>
+        <v>0.79</v>
       </c>
       <c r="P89" t="n">
-        <v>0.92</v>
+        <v>0.78</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="S89" t="n">
-        <v>0.6415</v>
+        <v>0.546</v>
       </c>
       <c r="T89" t="n">
         <v>3</v>
       </c>
       <c r="U89" t="n">
-        <v>2.27</v>
+        <v>4.76</v>
       </c>
       <c r="V89" t="n">
-        <v>0.43</v>
+        <v>0.9</v>
       </c>
       <c r="W89" t="n">
-        <v>2.36</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="90">
@@ -7715,31 +7715,31 @@
         </is>
       </c>
       <c r="O90" t="n">
-        <v>0.88</v>
+        <v>0.74</v>
       </c>
       <c r="P90" t="n">
-        <v>0.87</v>
+        <v>0.73</v>
       </c>
       <c r="Q90" t="n">
         <v>0.29</v>
       </c>
       <c r="R90" t="n">
-        <v>0.61</v>
+        <v>0.54</v>
       </c>
       <c r="S90" t="n">
-        <v>0.718</v>
+        <v>0.6165</v>
       </c>
       <c r="T90" t="n">
         <v>2</v>
       </c>
       <c r="U90" t="n">
-        <v>2.96</v>
+        <v>5.45</v>
       </c>
       <c r="V90" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="W90" t="n">
-        <v>3.08</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="91">
@@ -7796,31 +7796,31 @@
         </is>
       </c>
       <c r="O91" t="n">
-        <v>0.83</v>
+        <v>0.68</v>
       </c>
       <c r="P91" t="n">
-        <v>0.83</v>
+        <v>0.68</v>
       </c>
       <c r="Q91" t="n">
         <v>0.61</v>
       </c>
       <c r="R91" t="n">
-        <v>0.61</v>
+        <v>0.54</v>
       </c>
       <c r="S91" t="n">
-        <v>0.753</v>
+        <v>0.645</v>
       </c>
       <c r="T91" t="n">
         <v>1</v>
       </c>
       <c r="U91" t="n">
-        <v>3.65</v>
+        <v>6.13</v>
       </c>
       <c r="V91" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.17</v>
       </c>
       <c r="W91" t="n">
-        <v>3.79</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="92">
@@ -7877,31 +7877,31 @@
         </is>
       </c>
       <c r="O92" t="n">
-        <v>0.32</v>
+        <v>0.4</v>
       </c>
       <c r="P92" t="n">
-        <v>0.33</v>
+        <v>0.41</v>
       </c>
       <c r="Q92" t="n">
         <v>1</v>
       </c>
       <c r="R92" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="S92" t="n">
-        <v>0.5315</v>
+        <v>0.5685</v>
       </c>
       <c r="T92" t="n">
         <v>1</v>
       </c>
       <c r="U92" t="n">
-        <v>11.83</v>
+        <v>9.69</v>
       </c>
       <c r="V92" t="n">
-        <v>2.25</v>
+        <v>1.84</v>
       </c>
       <c r="W92" t="n">
-        <v>12.06</v>
+        <v>9.880000000000001</v>
       </c>
     </row>
     <row r="93">
@@ -7958,31 +7958,31 @@
         </is>
       </c>
       <c r="O93" t="n">
-        <v>0.37</v>
+        <v>0.47</v>
       </c>
       <c r="P93" t="n">
-        <v>0.38</v>
+        <v>0.48</v>
       </c>
       <c r="Q93" t="n">
         <v>0.76</v>
       </c>
       <c r="R93" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="S93" t="n">
-        <v>0.516</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="T93" t="n">
         <v>2</v>
       </c>
       <c r="U93" t="n">
-        <v>11.02</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="V93" t="n">
-        <v>2.09</v>
+        <v>1.69</v>
       </c>
       <c r="W93" t="n">
-        <v>11.23</v>
+        <v>9.050000000000001</v>
       </c>
     </row>
     <row r="94">
@@ -8039,31 +8039,31 @@
         </is>
       </c>
       <c r="O94" t="n">
-        <v>0.42</v>
+        <v>0.53</v>
       </c>
       <c r="P94" t="n">
-        <v>0.43</v>
+        <v>0.54</v>
       </c>
       <c r="Q94" t="n">
         <v>0.45</v>
       </c>
       <c r="R94" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="S94" t="n">
-        <v>0.4865</v>
+        <v>0.543</v>
       </c>
       <c r="T94" t="n">
         <v>3</v>
       </c>
       <c r="U94" t="n">
-        <v>10.2</v>
+        <v>8.07</v>
       </c>
       <c r="V94" t="n">
-        <v>1.94</v>
+        <v>1.53</v>
       </c>
       <c r="W94" t="n">
-        <v>10.4</v>
+        <v>8.23</v>
       </c>
     </row>
     <row r="95">
@@ -8120,31 +8120,31 @@
         </is>
       </c>
       <c r="O95" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.47</v>
       </c>
       <c r="P95" t="n">
-        <v>0.68</v>
+        <v>0.47</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="S95" t="n">
-        <v>0.4825</v>
+        <v>0.3415</v>
       </c>
       <c r="T95" t="n">
         <v>3</v>
       </c>
       <c r="U95" t="n">
-        <v>5.96</v>
+        <v>8.81</v>
       </c>
       <c r="V95" t="n">
-        <v>1.13</v>
+        <v>1.67</v>
       </c>
       <c r="W95" t="n">
-        <v>6.21</v>
+        <v>9.17</v>
       </c>
     </row>
     <row r="96">
@@ -8201,31 +8201,31 @@
         </is>
       </c>
       <c r="O96" t="n">
-        <v>0.62</v>
+        <v>0.39</v>
       </c>
       <c r="P96" t="n">
-        <v>0.62</v>
+        <v>0.38</v>
       </c>
       <c r="Q96" t="n">
         <v>0.41</v>
       </c>
       <c r="R96" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="S96" t="n">
-        <v>0.569</v>
+        <v>0.413</v>
       </c>
       <c r="T96" t="n">
         <v>2</v>
       </c>
       <c r="U96" t="n">
-        <v>7.02</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="V96" t="n">
-        <v>1.33</v>
+        <v>1.87</v>
       </c>
       <c r="W96" t="n">
-        <v>7.3</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="97">
@@ -8282,31 +8282,31 @@
         </is>
       </c>
       <c r="O97" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="P97" t="n">
-        <v>0.55</v>
+        <v>0.3</v>
       </c>
       <c r="Q97" t="n">
         <v>0.78</v>
       </c>
       <c r="R97" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="S97" t="n">
-        <v>0.6005</v>
+        <v>0.414</v>
       </c>
       <c r="T97" t="n">
         <v>1</v>
       </c>
       <c r="U97" t="n">
-        <v>8.07</v>
+        <v>10.91</v>
       </c>
       <c r="V97" t="n">
-        <v>1.53</v>
+        <v>2.07</v>
       </c>
       <c r="W97" t="n">
-        <v>8.4</v>
+        <v>11.36</v>
       </c>
     </row>
     <row r="98">
@@ -8363,31 +8363,31 @@
         </is>
       </c>
       <c r="O98" t="n">
-        <v>0.54</v>
+        <v>0.63</v>
       </c>
       <c r="P98" t="n">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="Q98" t="n">
         <v>0.7</v>
       </c>
       <c r="R98" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="S98" t="n">
-        <v>0.6185</v>
+        <v>0.665</v>
       </c>
       <c r="T98" t="n">
         <v>3</v>
       </c>
       <c r="U98" t="n">
-        <v>8.35</v>
+        <v>6.77</v>
       </c>
       <c r="V98" t="n">
-        <v>1.59</v>
+        <v>1.29</v>
       </c>
       <c r="W98" t="n">
-        <v>8.15</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="99">
@@ -8444,31 +8444,31 @@
         </is>
       </c>
       <c r="O99" t="n">
-        <v>0.57</v>
+        <v>0.68</v>
       </c>
       <c r="P99" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="Q99" t="n">
         <v>0.93</v>
       </c>
       <c r="R99" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="S99" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="T99" t="n">
         <v>2</v>
       </c>
       <c r="U99" t="n">
-        <v>7.78</v>
+        <v>6.2</v>
       </c>
       <c r="V99" t="n">
-        <v>1.48</v>
+        <v>1.18</v>
       </c>
       <c r="W99" t="n">
-        <v>7.59</v>
+        <v>6.05</v>
       </c>
     </row>
     <row r="100">
@@ -8525,31 +8525,31 @@
         </is>
       </c>
       <c r="O100" t="n">
-        <v>0.61</v>
+        <v>0.72</v>
       </c>
       <c r="P100" t="n">
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="Q100" t="n">
         <v>0.86</v>
       </c>
       <c r="R100" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.73</v>
       </c>
       <c r="S100" t="n">
-        <v>0.7005</v>
+        <v>0.7565</v>
       </c>
       <c r="T100" t="n">
         <v>1</v>
       </c>
       <c r="U100" t="n">
-        <v>7.21</v>
+        <v>5.62</v>
       </c>
       <c r="V100" t="n">
-        <v>1.37</v>
+        <v>1.07</v>
       </c>
       <c r="W100" t="n">
-        <v>7.03</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="101">
@@ -8606,31 +8606,31 @@
         </is>
       </c>
       <c r="O101" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P101" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="Q101" t="n">
         <v>0.41</v>
       </c>
       <c r="R101" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="S101" t="n">
-        <v>0.849</v>
+        <v>0.8075</v>
       </c>
       <c r="T101" t="n">
         <v>3</v>
       </c>
       <c r="U101" t="n">
-        <v>0.24</v>
+        <v>2.83</v>
       </c>
       <c r="V101" t="n">
-        <v>0.05</v>
+        <v>0.54</v>
       </c>
       <c r="W101" t="n">
-        <v>0.23</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="102">
@@ -8687,31 +8687,31 @@
         </is>
       </c>
       <c r="O102" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="P102" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="Q102" t="n">
         <v>0.7</v>
       </c>
       <c r="R102" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="S102" t="n">
-        <v>0.907</v>
+        <v>0.836</v>
       </c>
       <c r="T102" t="n">
         <v>2</v>
       </c>
       <c r="U102" t="n">
-        <v>0.84</v>
+        <v>3.43</v>
       </c>
       <c r="V102" t="n">
-        <v>0.16</v>
+        <v>0.65</v>
       </c>
       <c r="W102" t="n">
-        <v>0.82</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="103">
@@ -8768,31 +8768,31 @@
         </is>
       </c>
       <c r="O103" t="n">
-        <v>0.97</v>
+        <v>0.85</v>
       </c>
       <c r="P103" t="n">
-        <v>0.97</v>
+        <v>0.86</v>
       </c>
       <c r="Q103" t="n">
         <v>0.93</v>
       </c>
       <c r="R103" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="S103" t="n">
-        <v>0.9155</v>
+        <v>0.8365</v>
       </c>
       <c r="T103" t="n">
         <v>1</v>
       </c>
       <c r="U103" t="n">
-        <v>1.43</v>
+        <v>4.02</v>
       </c>
       <c r="V103" t="n">
-        <v>0.27</v>
+        <v>0.76</v>
       </c>
       <c r="W103" t="n">
-        <v>1.4</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="104">
@@ -8849,31 +8849,31 @@
         </is>
       </c>
       <c r="O104" t="n">
-        <v>0.79</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P104" t="n">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Q104" t="n">
         <v>0.86</v>
       </c>
       <c r="R104" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="S104" t="n">
-        <v>0.8225</v>
+        <v>0.9135</v>
       </c>
       <c r="T104" t="n">
         <v>3</v>
       </c>
       <c r="U104" t="n">
-        <v>4.33</v>
+        <v>2.9</v>
       </c>
       <c r="V104" t="n">
-        <v>0.82</v>
+        <v>0.55</v>
       </c>
       <c r="W104" t="n">
-        <v>4.23</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="105">
@@ -8930,31 +8930,31 @@
         </is>
       </c>
       <c r="O105" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="P105" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="Q105" t="n">
         <v>1</v>
       </c>
       <c r="R105" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="S105" t="n">
-        <v>0.857</v>
+        <v>0.948</v>
       </c>
       <c r="T105" t="n">
         <v>1</v>
       </c>
       <c r="U105" t="n">
-        <v>4.17</v>
+        <v>2.74</v>
       </c>
       <c r="V105" t="n">
-        <v>0.79</v>
+        <v>0.52</v>
       </c>
       <c r="W105" t="n">
-        <v>4.07</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="106">
@@ -9011,31 +9011,31 @@
         </is>
       </c>
       <c r="O106" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="P106" t="n">
-        <v>0.83</v>
+        <v>0.97</v>
       </c>
       <c r="Q106" t="n">
         <v>0.78</v>
       </c>
       <c r="R106" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="S106" t="n">
-        <v>0.8275</v>
+        <v>0.9215</v>
       </c>
       <c r="T106" t="n">
         <v>2</v>
       </c>
       <c r="U106" t="n">
-        <v>3.94</v>
+        <v>2.51</v>
       </c>
       <c r="V106" t="n">
-        <v>0.75</v>
+        <v>0.48</v>
       </c>
       <c r="W106" t="n">
-        <v>3.85</v>
+        <v>2.45</v>
       </c>
     </row>
   </sheetData>
